--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_oil_gas_distribution.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0233</v>
+        <v>0.0206</v>
       </c>
       <c r="E2">
-        <v>0.0173</v>
+        <v>-0.118</v>
       </c>
       <c r="G2">
-        <v>0.4693323683734394</v>
+        <v>0.476049089469517</v>
       </c>
       <c r="H2">
-        <v>0.4693323683734394</v>
+        <v>0.476049089469517</v>
       </c>
       <c r="I2">
-        <v>0.2131355165550932</v>
+        <v>0.06730007917656373</v>
       </c>
       <c r="J2">
-        <v>0.1718259283496308</v>
+        <v>0.05550006529419446</v>
       </c>
       <c r="K2">
-        <v>125.2</v>
+        <v>55.5</v>
       </c>
       <c r="L2">
-        <v>0.2265243350823231</v>
+        <v>0.1098574821852732</v>
       </c>
       <c r="M2">
-        <v>107.3</v>
+        <v>18.9</v>
       </c>
       <c r="N2">
-        <v>0.1108585597685711</v>
+        <v>0.03096330275229358</v>
       </c>
       <c r="O2">
-        <v>0.8570287539936102</v>
+        <v>0.3405405405405405</v>
       </c>
       <c r="P2">
-        <v>107.3</v>
+        <v>18.9</v>
       </c>
       <c r="Q2">
-        <v>0.1108585597685711</v>
+        <v>0.03096330275229358</v>
       </c>
       <c r="R2">
-        <v>0.8570287539936102</v>
+        <v>0.3405405405405405</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +636,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>131.3</v>
+        <v>130.1</v>
       </c>
       <c r="V2">
-        <v>0.1356545097634053</v>
+        <v>0.2131389252948886</v>
       </c>
       <c r="W2">
-        <v>0.08259664863438448</v>
+        <v>0.03262403009640254</v>
       </c>
       <c r="X2">
-        <v>0.05911680033225791</v>
+        <v>0.09828524363866575</v>
       </c>
       <c r="Y2">
-        <v>0.02347984830212657</v>
+        <v>-0.06566121354226322</v>
       </c>
       <c r="Z2">
-        <v>0.3942197273913882</v>
+        <v>0.3209086058388596</v>
       </c>
       <c r="AA2">
-        <v>0.06773717063276365</v>
+        <v>0.01781044857752562</v>
       </c>
       <c r="AB2">
-        <v>0.05904085469931167</v>
+        <v>0.09820591911384731</v>
       </c>
       <c r="AC2">
-        <v>0.008696315933451979</v>
+        <v>-0.08039547053632168</v>
       </c>
       <c r="AD2">
-        <v>4.38</v>
+        <v>1.66</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.38</v>
+        <v>1.66</v>
       </c>
       <c r="AG2">
-        <v>-126.92</v>
+        <v>-128.44</v>
       </c>
       <c r="AH2">
-        <v>0.004504875138848891</v>
+        <v>0.002712152403359148</v>
       </c>
       <c r="AI2">
-        <v>0.002568041370091112</v>
+        <v>0.001004198274714771</v>
       </c>
       <c r="AJ2">
-        <v>-0.1509191657352137</v>
+        <v>-0.2664951448252967</v>
       </c>
       <c r="AK2">
-        <v>-0.08062098229031686</v>
+        <v>-0.08433576719020854</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-7.34</v>
+        <v>-5.28</v>
       </c>
       <c r="AN2">
-        <v>0.0178702570379437</v>
+        <v>0.01109625668449198</v>
       </c>
       <c r="AP2">
-        <v>-0.5178294573643412</v>
+        <v>-0.8585561497326203</v>
       </c>
       <c r="AQ2">
-        <v>-16.04904632152589</v>
+        <v>-6.439393939393939</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0233</v>
+        <v>0.0206</v>
       </c>
       <c r="E3">
-        <v>0.0173</v>
+        <v>-0.118</v>
       </c>
       <c r="G3">
-        <v>0.4693323683734394</v>
+        <v>0.476049089469517</v>
       </c>
       <c r="H3">
-        <v>0.4693323683734394</v>
+        <v>0.476049089469517</v>
       </c>
       <c r="I3">
-        <v>0.2131355165550932</v>
+        <v>0.06730007917656373</v>
       </c>
       <c r="J3">
-        <v>0.1718259283496308</v>
+        <v>0.05550006529419446</v>
       </c>
       <c r="K3">
-        <v>125.2</v>
+        <v>55.5</v>
       </c>
       <c r="L3">
-        <v>0.2265243350823231</v>
+        <v>0.1098574821852732</v>
       </c>
       <c r="M3">
-        <v>107.3</v>
+        <v>18.9</v>
       </c>
       <c r="N3">
-        <v>0.1108585597685711</v>
+        <v>0.03096330275229358</v>
       </c>
       <c r="O3">
-        <v>0.8570287539936102</v>
+        <v>0.3405405405405405</v>
       </c>
       <c r="P3">
-        <v>107.3</v>
+        <v>18.9</v>
       </c>
       <c r="Q3">
-        <v>0.1108585597685711</v>
+        <v>0.03096330275229358</v>
       </c>
       <c r="R3">
-        <v>0.8570287539936102</v>
+        <v>0.3405405405405405</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +767,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>131.3</v>
+        <v>130.1</v>
       </c>
       <c r="V3">
-        <v>0.1356545097634053</v>
+        <v>0.2131389252948886</v>
       </c>
       <c r="W3">
-        <v>0.08259664863438448</v>
+        <v>0.03262403009640254</v>
       </c>
       <c r="X3">
-        <v>0.05911680033225791</v>
+        <v>0.09828524363866575</v>
       </c>
       <c r="Y3">
-        <v>0.02347984830212657</v>
+        <v>-0.06566121354226322</v>
       </c>
       <c r="Z3">
-        <v>0.3942197273913882</v>
+        <v>0.3209086058388596</v>
       </c>
       <c r="AA3">
-        <v>0.06773717063276365</v>
+        <v>0.01781044857752562</v>
       </c>
       <c r="AB3">
-        <v>0.05904085469931167</v>
+        <v>0.09820591911384731</v>
       </c>
       <c r="AC3">
-        <v>0.008696315933451979</v>
+        <v>-0.08039547053632168</v>
       </c>
       <c r="AD3">
-        <v>4.38</v>
+        <v>1.66</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.38</v>
+        <v>1.66</v>
       </c>
       <c r="AG3">
-        <v>-126.92</v>
+        <v>-128.44</v>
       </c>
       <c r="AH3">
-        <v>0.004504875138848891</v>
+        <v>0.002712152403359148</v>
       </c>
       <c r="AI3">
-        <v>0.002568041370091112</v>
+        <v>0.001004198274714771</v>
       </c>
       <c r="AJ3">
-        <v>-0.1509191657352137</v>
+        <v>-0.2664951448252967</v>
       </c>
       <c r="AK3">
-        <v>-0.08062098229031686</v>
+        <v>-0.08433576719020854</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-7.34</v>
+        <v>-5.28</v>
       </c>
       <c r="AN3">
-        <v>0.0178702570379437</v>
+        <v>0.01109625668449198</v>
       </c>
       <c r="AP3">
-        <v>-0.5178294573643412</v>
+        <v>-0.8585561497326203</v>
       </c>
       <c r="AQ3">
-        <v>-16.04904632152589</v>
+        <v>-6.439393939393939</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_oil_gas_distribution.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="kas_kzto" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0206</v>
+        <v>0.0488</v>
       </c>
       <c r="E2">
-        <v>-0.118</v>
+        <v>-0.0563</v>
       </c>
       <c r="G2">
-        <v>0.476049089469517</v>
+        <v>0.2744606121424987</v>
       </c>
       <c r="H2">
-        <v>0.476049089469517</v>
+        <v>0.2744606121424987</v>
       </c>
       <c r="I2">
-        <v>0.06730007917656373</v>
+        <v>0.09048335842114066</v>
       </c>
       <c r="J2">
-        <v>0.05550006529419446</v>
+        <v>0.07372251347683466</v>
       </c>
       <c r="K2">
-        <v>55.5</v>
+        <v>58.5</v>
       </c>
       <c r="L2">
-        <v>0.1098574821852732</v>
+        <v>0.09784244856999498</v>
       </c>
       <c r="M2">
-        <v>18.9</v>
+        <v>28.3</v>
       </c>
       <c r="N2">
-        <v>0.03096330275229358</v>
+        <v>0.03856111186810193</v>
       </c>
       <c r="O2">
-        <v>0.3405405405405405</v>
+        <v>0.4837606837606838</v>
       </c>
       <c r="P2">
-        <v>18.9</v>
+        <v>28.3</v>
       </c>
       <c r="Q2">
-        <v>0.03096330275229358</v>
+        <v>0.03856111186810193</v>
       </c>
       <c r="R2">
-        <v>0.3405405405405405</v>
+        <v>0.4837606837606838</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>130.1</v>
+        <v>165.5</v>
       </c>
       <c r="V2">
-        <v>0.2131389252948886</v>
+        <v>0.2255075623381932</v>
       </c>
       <c r="W2">
-        <v>0.03262403009640254</v>
+        <v>0.03542448831294659</v>
       </c>
       <c r="X2">
-        <v>0.09828524363866575</v>
+        <v>0.0885301593002287</v>
       </c>
       <c r="Y2">
-        <v>-0.06566121354226322</v>
+        <v>-0.05310567098728211</v>
       </c>
       <c r="Z2">
-        <v>0.3209086058388596</v>
+        <v>0.3925907443399694</v>
       </c>
       <c r="AA2">
-        <v>0.01781044857752562</v>
+        <v>0.02894277644048395</v>
       </c>
       <c r="AB2">
-        <v>0.09820591911384731</v>
+        <v>0.08336588297868752</v>
       </c>
       <c r="AC2">
-        <v>-0.08039547053632168</v>
+        <v>-0.05442310653820357</v>
       </c>
       <c r="AD2">
-        <v>1.66</v>
+        <v>173.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.66</v>
+        <v>173.9</v>
       </c>
       <c r="AG2">
-        <v>-128.44</v>
+        <v>8.400000000000006</v>
       </c>
       <c r="AH2">
-        <v>0.002712152403359148</v>
+        <v>0.1915620180656532</v>
       </c>
       <c r="AI2">
-        <v>0.001004198274714771</v>
+        <v>0.07912817946034492</v>
       </c>
       <c r="AJ2">
-        <v>-0.2664951448252967</v>
+        <v>0.01131617944227402</v>
       </c>
       <c r="AK2">
-        <v>-0.08433576719020854</v>
+        <v>0.004133451431945677</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AM2">
-        <v>-5.28</v>
+        <v>-17.58</v>
       </c>
       <c r="AN2">
-        <v>0.01109625668449198</v>
+        <v>0.8686313686313687</v>
+      </c>
+      <c r="AO2">
+        <v>48.30357142857142</v>
       </c>
       <c r="AP2">
-        <v>-0.8585561497326203</v>
+        <v>0.04195804195804199</v>
       </c>
       <c r="AQ2">
-        <v>-6.439393939393939</v>
+        <v>-3.0773606370876</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0206</v>
+        <v>0.0488</v>
       </c>
       <c r="E3">
-        <v>-0.118</v>
+        <v>-0.0563</v>
       </c>
       <c r="G3">
-        <v>0.476049089469517</v>
+        <v>0.2744606121424987</v>
       </c>
       <c r="H3">
-        <v>0.476049089469517</v>
+        <v>0.2744606121424987</v>
       </c>
       <c r="I3">
-        <v>0.06730007917656373</v>
+        <v>0.09048335842114066</v>
       </c>
       <c r="J3">
-        <v>0.05550006529419446</v>
+        <v>0.07372251347683466</v>
       </c>
       <c r="K3">
-        <v>55.5</v>
+        <v>58.5</v>
       </c>
       <c r="L3">
-        <v>0.1098574821852732</v>
+        <v>0.09784244856999498</v>
       </c>
       <c r="M3">
-        <v>18.9</v>
+        <v>28.3</v>
       </c>
       <c r="N3">
-        <v>0.03096330275229358</v>
+        <v>0.03856111186810193</v>
       </c>
       <c r="O3">
-        <v>0.3405405405405405</v>
+        <v>0.4837606837606838</v>
       </c>
       <c r="P3">
-        <v>18.9</v>
+        <v>28.3</v>
       </c>
       <c r="Q3">
-        <v>0.03096330275229358</v>
+        <v>0.03856111186810193</v>
       </c>
       <c r="R3">
-        <v>0.3405405405405405</v>
+        <v>0.4837606837606838</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +772,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>130.1</v>
+        <v>165.5</v>
       </c>
       <c r="V3">
-        <v>0.2131389252948886</v>
+        <v>0.2255075623381932</v>
       </c>
       <c r="W3">
-        <v>0.03262403009640254</v>
+        <v>0.03542448831294659</v>
       </c>
       <c r="X3">
-        <v>0.09828524363866575</v>
+        <v>0.0885301593002287</v>
       </c>
       <c r="Y3">
-        <v>-0.06566121354226322</v>
+        <v>-0.05310567098728211</v>
       </c>
       <c r="Z3">
-        <v>0.3209086058388596</v>
+        <v>0.3925907443399694</v>
       </c>
       <c r="AA3">
-        <v>0.01781044857752562</v>
+        <v>0.02894277644048395</v>
       </c>
       <c r="AB3">
-        <v>0.09820591911384731</v>
+        <v>0.08336588297868752</v>
       </c>
       <c r="AC3">
-        <v>-0.08039547053632168</v>
+        <v>-0.05442310653820357</v>
       </c>
       <c r="AD3">
-        <v>1.66</v>
+        <v>173.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.66</v>
+        <v>173.9</v>
       </c>
       <c r="AG3">
-        <v>-128.44</v>
+        <v>8.400000000000006</v>
       </c>
       <c r="AH3">
-        <v>0.002712152403359148</v>
+        <v>0.1915620180656532</v>
       </c>
       <c r="AI3">
-        <v>0.001004198274714771</v>
+        <v>0.07912817946034492</v>
       </c>
       <c r="AJ3">
-        <v>-0.2664951448252967</v>
+        <v>0.01131617944227402</v>
       </c>
       <c r="AK3">
-        <v>-0.08433576719020854</v>
+        <v>0.004133451431945677</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AM3">
-        <v>-5.28</v>
+        <v>-17.58</v>
       </c>
       <c r="AN3">
-        <v>0.01109625668449198</v>
+        <v>0.8686313686313687</v>
+      </c>
+      <c r="AO3">
+        <v>48.30357142857142</v>
       </c>
       <c r="AP3">
-        <v>-0.8585561497326203</v>
+        <v>0.04195804195804199</v>
       </c>
       <c r="AQ3">
-        <v>-6.439393939393939</v>
+        <v>-3.0773606370876</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KazTransOil JSC (KAS:KZTO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KAS:KZTO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oil/Gas Distribution</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>48.3035714285714</v>
+      </c>
+      <c r="F2">
+        <v>10000000</v>
+      </c>
+      <c r="G2">
+        <v>0.868631368631369</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0.191562018065653</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>733.9</v>
+      </c>
+      <c r="L2">
+        <v>956.815059912797</v>
+      </c>
+      <c r="M2">
+        <v>742.3</v>
+      </c>
+      <c r="N2">
+        <v>791.315059912797</v>
+      </c>
+      <c r="O2">
+        <v>173.9</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0.08336588297868749</v>
+      </c>
+      <c r="R2">
+        <v>0.08060541558090061</v>
+      </c>
+      <c r="S2">
+        <v>0.0615713896355071</v>
+      </c>
+      <c r="T2">
+        <v>0.0523545896355071</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.0885301593002287</v>
+      </c>
+      <c r="X2">
+        <v>0.08060541558090061</v>
+      </c>
+      <c r="Y2">
+        <v>0.6734256956424139</v>
+      </c>
+      <c r="Z2">
+        <v>0.566112022670692</v>
+      </c>
+      <c r="AA2">
+        <v>173.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.07696423704438383</v>
+      </c>
+      <c r="AC2">
+        <v>48.30357142857142</v>
+      </c>
+      <c r="AD2">
+        <v>173.9</v>
+      </c>
+      <c r="AE2">
+        <v>1.12</v>
+      </c>
+      <c r="AF2">
+        <v>146.1</v>
+      </c>
+      <c r="AG2">
+        <v>200.2</v>
+      </c>
+      <c r="AH2">
+        <v>0.02074323704438383</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>733.9</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>424.9000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>1.12</v>
+      </c>
+      <c r="AS2">
+        <v>173.9</v>
+      </c>
+      <c r="AT2">
+        <v>165.5</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08060541558090059</v>
+      </c>
+      <c r="C2">
+        <v>956.8150599127974</v>
+      </c>
+      <c r="D2">
+        <v>791.3150599127974</v>
+      </c>
+      <c r="E2">
+        <v>-173.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>165.5</v>
+      </c>
+      <c r="H2">
+        <v>733.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>200.2</v>
+      </c>
+      <c r="K2">
+        <v>146.1</v>
+      </c>
+      <c r="L2">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="O2">
+        <v>10.82</v>
+      </c>
+      <c r="P2">
+        <v>43.27999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>189.38</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08060541558090059</v>
+      </c>
+      <c r="T2">
+        <v>0.5661120226706918</v>
+      </c>
+      <c r="U2">
+        <v>0.06544323704438383</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.05235458963550707</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08065735064609388</v>
+      </c>
+      <c r="C3">
+        <v>946.7552252149333</v>
+      </c>
+      <c r="D3">
+        <v>790.3332252149332</v>
+      </c>
+      <c r="E3">
+        <v>-164.822</v>
+      </c>
+      <c r="F3">
+        <v>9.077999999999999</v>
+      </c>
+      <c r="G3">
+        <v>165.5</v>
+      </c>
+      <c r="H3">
+        <v>733.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>200.2</v>
+      </c>
+      <c r="K3">
+        <v>146.1</v>
+      </c>
+      <c r="L3">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.5940937058889164</v>
+      </c>
+      <c r="N3">
+        <v>53.50590629411108</v>
+      </c>
+      <c r="O3">
+        <v>10.70118125882222</v>
+      </c>
+      <c r="P3">
+        <v>42.80472503528886</v>
+      </c>
+      <c r="Q3">
+        <v>188.9047250352889</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08094323712094828</v>
+      </c>
+      <c r="T3">
+        <v>0.5706866652781318</v>
+      </c>
+      <c r="U3">
+        <v>0.06544323704438383</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.05235458963550707</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>91.06307551104675</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08070928571128713</v>
+      </c>
+      <c r="C4">
+        <v>936.697823946711</v>
+      </c>
+      <c r="D4">
+        <v>789.3538239467109</v>
+      </c>
+      <c r="E4">
+        <v>-155.744</v>
+      </c>
+      <c r="F4">
+        <v>18.156</v>
+      </c>
+      <c r="G4">
+        <v>165.5</v>
+      </c>
+      <c r="H4">
+        <v>733.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>200.2</v>
+      </c>
+      <c r="K4">
+        <v>146.1</v>
+      </c>
+      <c r="L4">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M4">
+        <v>1.188187411777833</v>
+      </c>
+      <c r="N4">
+        <v>52.91181258822216</v>
+      </c>
+      <c r="O4">
+        <v>10.58236251764443</v>
+      </c>
+      <c r="P4">
+        <v>42.32945007057773</v>
+      </c>
+      <c r="Q4">
+        <v>188.4294500705777</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08128795297813979</v>
+      </c>
+      <c r="T4">
+        <v>0.5753546679387848</v>
+      </c>
+      <c r="U4">
+        <v>0.06544323704438383</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.05235458963550707</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>45.53153775552337</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.0807612207764804</v>
+      </c>
+      <c r="C5">
+        <v>926.6428470726203</v>
+      </c>
+      <c r="D5">
+        <v>788.3768470726203</v>
+      </c>
+      <c r="E5">
+        <v>-146.666</v>
+      </c>
+      <c r="F5">
+        <v>27.234</v>
+      </c>
+      <c r="G5">
+        <v>165.5</v>
+      </c>
+      <c r="H5">
+        <v>733.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>200.2</v>
+      </c>
+      <c r="K5">
+        <v>146.1</v>
+      </c>
+      <c r="L5">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M5">
+        <v>1.782281117666749</v>
+      </c>
+      <c r="N5">
+        <v>52.31771888233325</v>
+      </c>
+      <c r="O5">
+        <v>10.46354377646665</v>
+      </c>
+      <c r="P5">
+        <v>41.8541751058666</v>
+      </c>
+      <c r="Q5">
+        <v>187.9541751058666</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08163977637877855</v>
+      </c>
+      <c r="T5">
+        <v>0.5801189180769769</v>
+      </c>
+      <c r="U5">
+        <v>0.06544323704438383</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.05235458963550707</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>30.35435850368225</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08081315584167369</v>
+      </c>
+      <c r="C6">
+        <v>916.5902856018301</v>
+      </c>
+      <c r="D6">
+        <v>787.4022856018302</v>
+      </c>
+      <c r="E6">
+        <v>-137.588</v>
+      </c>
+      <c r="F6">
+        <v>36.312</v>
+      </c>
+      <c r="G6">
+        <v>165.5</v>
+      </c>
+      <c r="H6">
+        <v>733.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>200.2</v>
+      </c>
+      <c r="K6">
+        <v>146.1</v>
+      </c>
+      <c r="L6">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M6">
+        <v>2.376374823555666</v>
+      </c>
+      <c r="N6">
+        <v>51.72362517644433</v>
+      </c>
+      <c r="O6">
+        <v>10.34472503528887</v>
+      </c>
+      <c r="P6">
+        <v>41.37890014115546</v>
+      </c>
+      <c r="Q6">
+        <v>187.4789001411555</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0819989294335973</v>
+      </c>
+      <c r="T6">
+        <v>0.5849824234263816</v>
+      </c>
+      <c r="U6">
+        <v>0.06544323704438383</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.05235458963550707</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>22.76576887776169</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08086509090686693</v>
+      </c>
+      <c r="C7">
+        <v>906.5401305879119</v>
+      </c>
+      <c r="D7">
+        <v>786.4301305879119</v>
+      </c>
+      <c r="E7">
+        <v>-128.51</v>
+      </c>
+      <c r="F7">
+        <v>45.39</v>
+      </c>
+      <c r="G7">
+        <v>165.5</v>
+      </c>
+      <c r="H7">
+        <v>733.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>200.2</v>
+      </c>
+      <c r="K7">
+        <v>146.1</v>
+      </c>
+      <c r="L7">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M7">
+        <v>2.970468529444582</v>
+      </c>
+      <c r="N7">
+        <v>51.12953147055541</v>
+      </c>
+      <c r="O7">
+        <v>10.22590629411108</v>
+      </c>
+      <c r="P7">
+        <v>40.90362517644433</v>
+      </c>
+      <c r="Q7">
+        <v>187.0036251764443</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08236564360535956</v>
+      </c>
+      <c r="T7">
+        <v>0.5899483183620893</v>
+      </c>
+      <c r="U7">
+        <v>0.06544323704438383</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.05235458963550707</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>18.21261510220935</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08091702597206023</v>
+      </c>
+      <c r="C8">
+        <v>896.4923731285617</v>
+      </c>
+      <c r="D8">
+        <v>785.4603731285616</v>
+      </c>
+      <c r="E8">
+        <v>-119.432</v>
+      </c>
+      <c r="F8">
+        <v>54.468</v>
+      </c>
+      <c r="G8">
+        <v>165.5</v>
+      </c>
+      <c r="H8">
+        <v>733.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>200.2</v>
+      </c>
+      <c r="K8">
+        <v>146.1</v>
+      </c>
+      <c r="L8">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M8">
+        <v>3.564562235333498</v>
+      </c>
+      <c r="N8">
+        <v>50.5354377646665</v>
+      </c>
+      <c r="O8">
+        <v>10.1070875529333</v>
+      </c>
+      <c r="P8">
+        <v>40.4283502117332</v>
+      </c>
+      <c r="Q8">
+        <v>186.5283502117332</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0827401602063083</v>
+      </c>
+      <c r="T8">
+        <v>0.5950198706368549</v>
+      </c>
+      <c r="U8">
+        <v>0.06544323704438383</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.05235458963550707</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>15.17717925184112</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08096896103725348</v>
+      </c>
+      <c r="C9">
+        <v>886.4470043653351</v>
+      </c>
+      <c r="D9">
+        <v>784.4930043653352</v>
+      </c>
+      <c r="E9">
+        <v>-110.354</v>
+      </c>
+      <c r="F9">
+        <v>63.546</v>
+      </c>
+      <c r="G9">
+        <v>165.5</v>
+      </c>
+      <c r="H9">
+        <v>733.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>200.2</v>
+      </c>
+      <c r="K9">
+        <v>146.1</v>
+      </c>
+      <c r="L9">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M9">
+        <v>4.158655941222415</v>
+      </c>
+      <c r="N9">
+        <v>49.94134405877758</v>
+      </c>
+      <c r="O9">
+        <v>9.988268811755518</v>
+      </c>
+      <c r="P9">
+        <v>39.95307524702206</v>
+      </c>
+      <c r="Q9">
+        <v>186.0530752470221</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08312273092770753</v>
+      </c>
+      <c r="T9">
+        <v>0.6002004885519379</v>
+      </c>
+      <c r="U9">
+        <v>0.06544323704438383</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.05235458963550707</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>13.00901078729239</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08109129610244675</v>
+      </c>
+      <c r="C10">
+        <v>875.0997193900008</v>
+      </c>
+      <c r="D10">
+        <v>782.2237193900008</v>
+      </c>
+      <c r="E10">
+        <v>-101.276</v>
+      </c>
+      <c r="F10">
+        <v>72.624</v>
+      </c>
+      <c r="G10">
+        <v>165.5</v>
+      </c>
+      <c r="H10">
+        <v>733.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>200.2</v>
+      </c>
+      <c r="K10">
+        <v>146.1</v>
+      </c>
+      <c r="L10">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M10">
+        <v>4.832636047111332</v>
+      </c>
+      <c r="N10">
+        <v>49.26736395288867</v>
+      </c>
+      <c r="O10">
+        <v>9.853472790577733</v>
+      </c>
+      <c r="P10">
+        <v>39.41389116231093</v>
+      </c>
+      <c r="Q10">
+        <v>185.5138911623109</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08351361840391977</v>
+      </c>
+      <c r="T10">
+        <v>0.6054937285956096</v>
+      </c>
+      <c r="U10">
+        <v>0.06654323704438384</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.05323458963550707</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>11.19471846681643</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08115203116764003</v>
+      </c>
+      <c r="C11">
+        <v>864.8999689737144</v>
+      </c>
+      <c r="D11">
+        <v>781.1019689737144</v>
+      </c>
+      <c r="E11">
+        <v>-92.19800000000001</v>
+      </c>
+      <c r="F11">
+        <v>81.702</v>
+      </c>
+      <c r="G11">
+        <v>165.5</v>
+      </c>
+      <c r="H11">
+        <v>733.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>200.2</v>
+      </c>
+      <c r="K11">
+        <v>146.1</v>
+      </c>
+      <c r="L11">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M11">
+        <v>5.436715553000248</v>
+      </c>
+      <c r="N11">
+        <v>48.66328444699975</v>
+      </c>
+      <c r="O11">
+        <v>9.73265688939995</v>
+      </c>
+      <c r="P11">
+        <v>38.9306275575998</v>
+      </c>
+      <c r="Q11">
+        <v>185.0306275575998</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08391309681367515</v>
+      </c>
+      <c r="T11">
+        <v>0.610903303585296</v>
+      </c>
+      <c r="U11">
+        <v>0.06654323704438384</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.05323458963550707</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>9.950860859392385</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08138876623283331</v>
+      </c>
+      <c r="C12">
+        <v>851.4801144917916</v>
+      </c>
+      <c r="D12">
+        <v>776.7601144917916</v>
+      </c>
+      <c r="E12">
+        <v>-83.12</v>
+      </c>
+      <c r="F12">
+        <v>90.78</v>
+      </c>
+      <c r="G12">
+        <v>165.5</v>
+      </c>
+      <c r="H12">
+        <v>733.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>200.2</v>
+      </c>
+      <c r="K12">
+        <v>146.1</v>
+      </c>
+      <c r="L12">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M12">
+        <v>6.240511058889164</v>
+      </c>
+      <c r="N12">
+        <v>47.85948894111083</v>
+      </c>
+      <c r="O12">
+        <v>9.571897788222167</v>
+      </c>
+      <c r="P12">
+        <v>38.28759115288867</v>
+      </c>
+      <c r="Q12">
+        <v>184.3875911528887</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.0843214525214251</v>
+      </c>
+      <c r="T12">
+        <v>0.6164330913525312</v>
+      </c>
+      <c r="U12">
+        <v>0.06874323704438383</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.05499458963550707</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>8.669161786507596</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08146710129802658</v>
+      </c>
+      <c r="C13">
+        <v>840.9760144672498</v>
+      </c>
+      <c r="D13">
+        <v>775.3340144672497</v>
+      </c>
+      <c r="E13">
+        <v>-74.04200000000002</v>
+      </c>
+      <c r="F13">
+        <v>99.85799999999999</v>
+      </c>
+      <c r="G13">
+        <v>165.5</v>
+      </c>
+      <c r="H13">
+        <v>733.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>200.2</v>
+      </c>
+      <c r="K13">
+        <v>146.1</v>
+      </c>
+      <c r="L13">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M13">
+        <v>6.864562164778079</v>
+      </c>
+      <c r="N13">
+        <v>47.23543783522192</v>
+      </c>
+      <c r="O13">
+        <v>9.447087567044383</v>
+      </c>
+      <c r="P13">
+        <v>37.78835026817753</v>
+      </c>
+      <c r="Q13">
+        <v>183.8883502681775</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08473898476193348</v>
+      </c>
+      <c r="T13">
+        <v>0.6220871440134119</v>
+      </c>
+      <c r="U13">
+        <v>0.06874323704438383</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.05499458963550707</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>7.881056169552362</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08168943636321985</v>
+      </c>
+      <c r="C14">
+        <v>827.8787511411182</v>
+      </c>
+      <c r="D14">
+        <v>771.3147511411182</v>
+      </c>
+      <c r="E14">
+        <v>-64.96400000000001</v>
+      </c>
+      <c r="F14">
+        <v>108.936</v>
+      </c>
+      <c r="G14">
+        <v>165.5</v>
+      </c>
+      <c r="H14">
+        <v>733.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>200.2</v>
+      </c>
+      <c r="K14">
+        <v>146.1</v>
+      </c>
+      <c r="L14">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M14">
+        <v>7.652017270666996</v>
+      </c>
+      <c r="N14">
+        <v>46.447982729333</v>
+      </c>
+      <c r="O14">
+        <v>9.289596545866599</v>
+      </c>
+      <c r="P14">
+        <v>37.1583861834664</v>
+      </c>
+      <c r="Q14">
+        <v>183.2583861834664</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08516600637154431</v>
+      </c>
+      <c r="T14">
+        <v>0.627869697871131</v>
+      </c>
+      <c r="U14">
+        <v>0.07024323704438383</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.05619458963550707</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>7.070031089368452</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08177977142841311</v>
+      </c>
+      <c r="C15">
+        <v>817.1795985380869</v>
+      </c>
+      <c r="D15">
+        <v>769.6935985380869</v>
+      </c>
+      <c r="E15">
+        <v>-55.88600000000001</v>
+      </c>
+      <c r="F15">
+        <v>118.014</v>
+      </c>
+      <c r="G15">
+        <v>165.5</v>
+      </c>
+      <c r="H15">
+        <v>733.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>200.2</v>
+      </c>
+      <c r="K15">
+        <v>146.1</v>
+      </c>
+      <c r="L15">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M15">
+        <v>8.289685376555912</v>
+      </c>
+      <c r="N15">
+        <v>45.81031462344409</v>
+      </c>
+      <c r="O15">
+        <v>9.162062924688817</v>
+      </c>
+      <c r="P15">
+        <v>36.64825169875527</v>
+      </c>
+      <c r="Q15">
+        <v>182.7482516987553</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08560284456988182</v>
+      </c>
+      <c r="T15">
+        <v>0.6337851840014411</v>
+      </c>
+      <c r="U15">
+        <v>0.07024323704438383</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.05619458963550707</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.526182544032419</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08202690649360637</v>
+      </c>
+      <c r="C16">
+        <v>803.70113842925</v>
+      </c>
+      <c r="D16">
+        <v>765.29313842925</v>
+      </c>
+      <c r="E16">
+        <v>-46.80800000000001</v>
+      </c>
+      <c r="F16">
+        <v>127.092</v>
+      </c>
+      <c r="G16">
+        <v>165.5</v>
+      </c>
+      <c r="H16">
+        <v>733.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>200.2</v>
+      </c>
+      <c r="K16">
+        <v>146.1</v>
+      </c>
+      <c r="L16">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M16">
+        <v>9.105282282444829</v>
+      </c>
+      <c r="N16">
+        <v>44.99471771755516</v>
+      </c>
+      <c r="O16">
+        <v>8.998943543511032</v>
+      </c>
+      <c r="P16">
+        <v>35.99577417404413</v>
+      </c>
+      <c r="Q16">
+        <v>182.0957741740441</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08604984179608766</v>
+      </c>
+      <c r="T16">
+        <v>0.6398382395766424</v>
+      </c>
+      <c r="U16">
+        <v>0.07164323704438383</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.05731458963550706</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.941606017454934</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08212844155879964</v>
+      </c>
+      <c r="C17">
+        <v>792.8297647027355</v>
+      </c>
+      <c r="D17">
+        <v>763.4997647027354</v>
+      </c>
+      <c r="E17">
+        <v>-37.73000000000002</v>
+      </c>
+      <c r="F17">
+        <v>136.17</v>
+      </c>
+      <c r="G17">
+        <v>165.5</v>
+      </c>
+      <c r="H17">
+        <v>733.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>200.2</v>
+      </c>
+      <c r="K17">
+        <v>146.1</v>
+      </c>
+      <c r="L17">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M17">
+        <v>9.755659588333746</v>
+      </c>
+      <c r="N17">
+        <v>44.34434041166625</v>
+      </c>
+      <c r="O17">
+        <v>8.86886808233325</v>
+      </c>
+      <c r="P17">
+        <v>35.475472329333</v>
+      </c>
+      <c r="Q17">
+        <v>181.575472329333</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08650735660408657</v>
+      </c>
+      <c r="T17">
+        <v>0.6460337199889071</v>
+      </c>
+      <c r="U17">
+        <v>0.07164323704438383</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.05731458963550706</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.545498949624605</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08222997662399291</v>
+      </c>
+      <c r="C18">
+        <v>781.9667764432365</v>
+      </c>
+      <c r="D18">
+        <v>761.7147764432365</v>
+      </c>
+      <c r="E18">
+        <v>-28.65200000000002</v>
+      </c>
+      <c r="F18">
+        <v>145.248</v>
+      </c>
+      <c r="G18">
+        <v>165.5</v>
+      </c>
+      <c r="H18">
+        <v>733.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>200.2</v>
+      </c>
+      <c r="K18">
+        <v>146.1</v>
+      </c>
+      <c r="L18">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M18">
+        <v>10.40603689422266</v>
+      </c>
+      <c r="N18">
+        <v>43.69396310577733</v>
+      </c>
+      <c r="O18">
+        <v>8.738792621155467</v>
+      </c>
+      <c r="P18">
+        <v>34.95517048462186</v>
+      </c>
+      <c r="Q18">
+        <v>181.0551704846218</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08697576462179973</v>
+      </c>
+      <c r="T18">
+        <v>0.6523767118395591</v>
+      </c>
+      <c r="U18">
+        <v>0.07164323704438383</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.05731458963550706</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.198905265273067</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08233151168918618</v>
+      </c>
+      <c r="C19">
+        <v>771.1121149747111</v>
+      </c>
+      <c r="D19">
+        <v>759.9381149747111</v>
+      </c>
+      <c r="E19">
+        <v>-19.57400000000001</v>
+      </c>
+      <c r="F19">
+        <v>154.326</v>
+      </c>
+      <c r="G19">
+        <v>165.5</v>
+      </c>
+      <c r="H19">
+        <v>733.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>200.2</v>
+      </c>
+      <c r="K19">
+        <v>146.1</v>
+      </c>
+      <c r="L19">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M19">
+        <v>11.05641420011158</v>
+      </c>
+      <c r="N19">
+        <v>43.04358579988842</v>
+      </c>
+      <c r="O19">
+        <v>8.608717159977685</v>
+      </c>
+      <c r="P19">
+        <v>34.43486863991073</v>
+      </c>
+      <c r="Q19">
+        <v>180.5348686399107</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08745545957969877</v>
+      </c>
+      <c r="T19">
+        <v>0.6588725468673353</v>
+      </c>
+      <c r="U19">
+        <v>0.07164323704438383</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.05731458963550706</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.893087308492299</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08243304675437944</v>
+      </c>
+      <c r="C20">
+        <v>760.2657221672787</v>
+      </c>
+      <c r="D20">
+        <v>758.1697221672787</v>
+      </c>
+      <c r="E20">
+        <v>-10.49600000000001</v>
+      </c>
+      <c r="F20">
+        <v>163.404</v>
+      </c>
+      <c r="G20">
+        <v>165.5</v>
+      </c>
+      <c r="H20">
+        <v>733.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>200.2</v>
+      </c>
+      <c r="K20">
+        <v>146.1</v>
+      </c>
+      <c r="L20">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M20">
+        <v>11.7067915060005</v>
+      </c>
+      <c r="N20">
+        <v>42.3932084939995</v>
+      </c>
+      <c r="O20">
+        <v>8.478641698799899</v>
+      </c>
+      <c r="P20">
+        <v>33.9145667951996</v>
+      </c>
+      <c r="Q20">
+        <v>180.0145667951996</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08794685441461972</v>
+      </c>
+      <c r="T20">
+        <v>0.6655268168957889</v>
+      </c>
+      <c r="U20">
+        <v>0.07164323704438383</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.05731458963550706</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.62124912468717</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08292978181957272</v>
+      </c>
+      <c r="C21">
+        <v>742.6535878289735</v>
+      </c>
+      <c r="D21">
+        <v>749.6355878289735</v>
+      </c>
+      <c r="E21">
+        <v>-1.418000000000006</v>
+      </c>
+      <c r="F21">
+        <v>172.482</v>
+      </c>
+      <c r="G21">
+        <v>165.5</v>
+      </c>
+      <c r="H21">
+        <v>733.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>200.2</v>
+      </c>
+      <c r="K21">
+        <v>146.1</v>
+      </c>
+      <c r="L21">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M21">
+        <v>12.80562201188941</v>
+      </c>
+      <c r="N21">
+        <v>41.29437798811058</v>
+      </c>
+      <c r="O21">
+        <v>8.258875597622117</v>
+      </c>
+      <c r="P21">
+        <v>33.03550239048847</v>
+      </c>
+      <c r="Q21">
+        <v>179.1355023904885</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.0884503824553412</v>
+      </c>
+      <c r="T21">
+        <v>0.6723453898879082</v>
+      </c>
+      <c r="U21">
+        <v>0.07424323704438382</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.05939458963550706</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.224706925580867</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08305211688476599</v>
+      </c>
+      <c r="C22">
+        <v>731.5032187545842</v>
+      </c>
+      <c r="D22">
+        <v>747.5632187545842</v>
+      </c>
+      <c r="E22">
+        <v>7.659999999999997</v>
+      </c>
+      <c r="F22">
+        <v>181.56</v>
+      </c>
+      <c r="G22">
+        <v>165.5</v>
+      </c>
+      <c r="H22">
+        <v>733.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>200.2</v>
+      </c>
+      <c r="K22">
+        <v>146.1</v>
+      </c>
+      <c r="L22">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M22">
+        <v>13.47960211777833</v>
+      </c>
+      <c r="N22">
+        <v>40.62039788222167</v>
+      </c>
+      <c r="O22">
+        <v>8.124079576444334</v>
+      </c>
+      <c r="P22">
+        <v>32.49631830577734</v>
+      </c>
+      <c r="Q22">
+        <v>178.5963183057773</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08896649869708072</v>
+      </c>
+      <c r="T22">
+        <v>0.6793344272048302</v>
+      </c>
+      <c r="U22">
+        <v>0.07424323704438382</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.05939458963550706</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.013471579301824</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08362805194995926</v>
+      </c>
+      <c r="C23">
+        <v>712.8207891083857</v>
+      </c>
+      <c r="D23">
+        <v>737.9587891083858</v>
+      </c>
+      <c r="E23">
+        <v>16.73799999999997</v>
+      </c>
+      <c r="F23">
+        <v>190.638</v>
+      </c>
+      <c r="G23">
+        <v>165.5</v>
+      </c>
+      <c r="H23">
+        <v>733.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>200.2</v>
+      </c>
+      <c r="K23">
+        <v>146.1</v>
+      </c>
+      <c r="L23">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M23">
+        <v>14.66830482366724</v>
+      </c>
+      <c r="N23">
+        <v>39.43169517633275</v>
+      </c>
+      <c r="O23">
+        <v>7.886339035266551</v>
+      </c>
+      <c r="P23">
+        <v>31.5453561410662</v>
+      </c>
+      <c r="Q23">
+        <v>177.6453561410662</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08949568117278832</v>
+      </c>
+      <c r="T23">
+        <v>0.6865004021753452</v>
+      </c>
+      <c r="U23">
+        <v>0.07694323704438383</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.06155458963550706</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.68822441654675</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08377198701515252</v>
+      </c>
+      <c r="C24">
+        <v>701.3809155628724</v>
+      </c>
+      <c r="D24">
+        <v>735.5969155628724</v>
+      </c>
+      <c r="E24">
+        <v>25.81599999999997</v>
+      </c>
+      <c r="F24">
+        <v>199.716</v>
+      </c>
+      <c r="G24">
+        <v>165.5</v>
+      </c>
+      <c r="H24">
+        <v>733.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>200.2</v>
+      </c>
+      <c r="K24">
+        <v>146.1</v>
+      </c>
+      <c r="L24">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M24">
+        <v>15.36679552955616</v>
+      </c>
+      <c r="N24">
+        <v>38.73320447044384</v>
+      </c>
+      <c r="O24">
+        <v>7.746640894088768</v>
+      </c>
+      <c r="P24">
+        <v>30.98656357635507</v>
+      </c>
+      <c r="Q24">
+        <v>177.0865635763551</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09003843242992432</v>
+      </c>
+      <c r="T24">
+        <v>0.6938501200938223</v>
+      </c>
+      <c r="U24">
+        <v>0.07694323704438383</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.06155458963550706</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>3.520577852158262</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08478072208034582</v>
+      </c>
+      <c r="C25">
+        <v>676.165230702689</v>
+      </c>
+      <c r="D25">
+        <v>719.459230702689</v>
+      </c>
+      <c r="E25">
+        <v>34.89400000000001</v>
+      </c>
+      <c r="F25">
+        <v>208.794</v>
+      </c>
+      <c r="G25">
+        <v>165.5</v>
+      </c>
+      <c r="H25">
+        <v>733.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>200.2</v>
+      </c>
+      <c r="K25">
+        <v>146.1</v>
+      </c>
+      <c r="L25">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M25">
+        <v>17.04661803544508</v>
+      </c>
+      <c r="N25">
+        <v>37.05338196455492</v>
+      </c>
+      <c r="O25">
+        <v>7.410676392910983</v>
+      </c>
+      <c r="P25">
+        <v>29.64270557164393</v>
+      </c>
+      <c r="Q25">
+        <v>175.7427055716439</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09059528112231062</v>
+      </c>
+      <c r="T25">
+        <v>0.7013907397764156</v>
+      </c>
+      <c r="U25">
+        <v>0.08164323704438384</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.06531458963550707</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.173650039410147</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08496225714553908</v>
+      </c>
+      <c r="C26">
+        <v>664.2579262789965</v>
+      </c>
+      <c r="D26">
+        <v>716.6299262789964</v>
+      </c>
+      <c r="E26">
+        <v>43.97199999999998</v>
+      </c>
+      <c r="F26">
+        <v>217.872</v>
+      </c>
+      <c r="G26">
+        <v>165.5</v>
+      </c>
+      <c r="H26">
+        <v>733.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>200.2</v>
+      </c>
+      <c r="K26">
+        <v>146.1</v>
+      </c>
+      <c r="L26">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M26">
+        <v>17.78777534133399</v>
+      </c>
+      <c r="N26">
+        <v>36.312224658666</v>
+      </c>
+      <c r="O26">
+        <v>7.262444931733199</v>
+      </c>
+      <c r="P26">
+        <v>29.0497797269328</v>
+      </c>
+      <c r="Q26">
+        <v>175.1497797269328</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09116678372765444</v>
+      </c>
+      <c r="T26">
+        <v>0.7091297968190771</v>
+      </c>
+      <c r="U26">
+        <v>0.08164323704438384</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.06531458963550707</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>3.041414621101391</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08700379221073233</v>
+      </c>
+      <c r="C27">
+        <v>624.8290958532589</v>
+      </c>
+      <c r="D27">
+        <v>686.2790958532588</v>
+      </c>
+      <c r="E27">
+        <v>53.04999999999998</v>
+      </c>
+      <c r="F27">
+        <v>226.95</v>
+      </c>
+      <c r="G27">
+        <v>165.5</v>
+      </c>
+      <c r="H27">
+        <v>733.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>200.2</v>
+      </c>
+      <c r="K27">
+        <v>146.1</v>
+      </c>
+      <c r="L27">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M27">
+        <v>20.63956764722291</v>
+      </c>
+      <c r="N27">
+        <v>33.46043235277709</v>
+      </c>
+      <c r="O27">
+        <v>6.692086470555418</v>
+      </c>
+      <c r="P27">
+        <v>26.76834588222167</v>
+      </c>
+      <c r="Q27">
+        <v>172.8683458822217</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09175352640247408</v>
+      </c>
+      <c r="T27">
+        <v>0.7170752287162097</v>
+      </c>
+      <c r="U27">
+        <v>0.09094323704438383</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.07275458963550706</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.621178937693458</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08725972727592561</v>
+      </c>
+      <c r="C28">
+        <v>612.1265833970104</v>
+      </c>
+      <c r="D28">
+        <v>682.6545833970105</v>
+      </c>
+      <c r="E28">
+        <v>62.12799999999999</v>
+      </c>
+      <c r="F28">
+        <v>236.028</v>
+      </c>
+      <c r="G28">
+        <v>165.5</v>
+      </c>
+      <c r="H28">
+        <v>733.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>200.2</v>
+      </c>
+      <c r="K28">
+        <v>146.1</v>
+      </c>
+      <c r="L28">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M28">
+        <v>21.46515035311182</v>
+      </c>
+      <c r="N28">
+        <v>32.63484964688817</v>
+      </c>
+      <c r="O28">
+        <v>6.526969929377635</v>
+      </c>
+      <c r="P28">
+        <v>26.10787971751054</v>
+      </c>
+      <c r="Q28">
+        <v>172.2078797175105</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09235612698742401</v>
+      </c>
+      <c r="T28">
+        <v>0.7252354020159674</v>
+      </c>
+      <c r="U28">
+        <v>0.09094323704438383</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.07275458963550706</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.520364363166786</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08853086234111887</v>
+      </c>
+      <c r="C29">
+        <v>585.5997369961839</v>
+      </c>
+      <c r="D29">
+        <v>665.2057369961839</v>
+      </c>
+      <c r="E29">
+        <v>71.20599999999999</v>
+      </c>
+      <c r="F29">
+        <v>245.106</v>
+      </c>
+      <c r="G29">
+        <v>165.5</v>
+      </c>
+      <c r="H29">
+        <v>733.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>200.2</v>
+      </c>
+      <c r="K29">
+        <v>146.1</v>
+      </c>
+      <c r="L29">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M29">
+        <v>23.44273125900074</v>
+      </c>
+      <c r="N29">
+        <v>30.65726874099925</v>
+      </c>
+      <c r="O29">
+        <v>6.131453748199851</v>
+      </c>
+      <c r="P29">
+        <v>24.5258149927994</v>
+      </c>
+      <c r="Q29">
+        <v>170.6258149927994</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09297523717744105</v>
+      </c>
+      <c r="T29">
+        <v>0.7336191417074993</v>
+      </c>
+      <c r="U29">
+        <v>0.09564323704438382</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.07651458963550706</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.307751575628736</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08882439740631215</v>
+      </c>
+      <c r="C30">
+        <v>572.6184174261319</v>
+      </c>
+      <c r="D30">
+        <v>661.3024174261319</v>
+      </c>
+      <c r="E30">
+        <v>80.28399999999999</v>
+      </c>
+      <c r="F30">
+        <v>254.184</v>
+      </c>
+      <c r="G30">
+        <v>165.5</v>
+      </c>
+      <c r="H30">
+        <v>733.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>200.2</v>
+      </c>
+      <c r="K30">
+        <v>146.1</v>
+      </c>
+      <c r="L30">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M30">
+        <v>24.31098056488966</v>
+      </c>
+      <c r="N30">
+        <v>29.78901943511034</v>
+      </c>
+      <c r="O30">
+        <v>5.957803887022068</v>
+      </c>
+      <c r="P30">
+        <v>23.83121554808827</v>
+      </c>
+      <c r="Q30">
+        <v>169.9312155480883</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09361154487273635</v>
+      </c>
+      <c r="T30">
+        <v>0.7422357630571292</v>
+      </c>
+      <c r="U30">
+        <v>0.09564323704438382</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.07651458963550706</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.225331876499139</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.0891179324715054</v>
+      </c>
+      <c r="C31">
+        <v>559.6826387242435</v>
+      </c>
+      <c r="D31">
+        <v>657.4446387242434</v>
+      </c>
+      <c r="E31">
+        <v>89.36199999999994</v>
+      </c>
+      <c r="F31">
+        <v>263.2619999999999</v>
+      </c>
+      <c r="G31">
+        <v>165.5</v>
+      </c>
+      <c r="H31">
+        <v>733.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>200.2</v>
+      </c>
+      <c r="K31">
+        <v>146.1</v>
+      </c>
+      <c r="L31">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M31">
+        <v>25.17922987077857</v>
+      </c>
+      <c r="N31">
+        <v>28.92077012922143</v>
+      </c>
+      <c r="O31">
+        <v>5.784154025844286</v>
+      </c>
+      <c r="P31">
+        <v>23.13661610337714</v>
+      </c>
+      <c r="Q31">
+        <v>169.2366161033771</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09426577672846248</v>
+      </c>
+      <c r="T31">
+        <v>0.7510951061349179</v>
+      </c>
+      <c r="U31">
+        <v>0.09564323704438382</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.07651458963550706</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>2.148596294550893</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08941146753669868</v>
+      </c>
+      <c r="C32">
+        <v>546.7916085103111</v>
+      </c>
+      <c r="D32">
+        <v>653.631608510311</v>
+      </c>
+      <c r="E32">
+        <v>98.43999999999997</v>
+      </c>
+      <c r="F32">
+        <v>272.34</v>
+      </c>
+      <c r="G32">
+        <v>165.5</v>
+      </c>
+      <c r="H32">
+        <v>733.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>200.2</v>
+      </c>
+      <c r="K32">
+        <v>146.1</v>
+      </c>
+      <c r="L32">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M32">
+        <v>26.04747917666749</v>
+      </c>
+      <c r="N32">
+        <v>28.05252082333251</v>
+      </c>
+      <c r="O32">
+        <v>5.610504164666501</v>
+      </c>
+      <c r="P32">
+        <v>22.44201665866601</v>
+      </c>
+      <c r="Q32">
+        <v>168.542016658666</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09493870092292367</v>
+      </c>
+      <c r="T32">
+        <v>0.7602075733006434</v>
+      </c>
+      <c r="U32">
+        <v>0.09564323704438382</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.07651458963550706</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>2.076976418065863</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08970500260189194</v>
+      </c>
+      <c r="C33">
+        <v>533.9445526806327</v>
+      </c>
+      <c r="D33">
+        <v>649.8625526806327</v>
+      </c>
+      <c r="E33">
+        <v>107.518</v>
+      </c>
+      <c r="F33">
+        <v>281.418</v>
+      </c>
+      <c r="G33">
+        <v>165.5</v>
+      </c>
+      <c r="H33">
+        <v>733.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>200.2</v>
+      </c>
+      <c r="K33">
+        <v>146.1</v>
+      </c>
+      <c r="L33">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M33">
+        <v>26.91572848255641</v>
+      </c>
+      <c r="N33">
+        <v>27.18427151744359</v>
+      </c>
+      <c r="O33">
+        <v>5.436854303488718</v>
+      </c>
+      <c r="P33">
+        <v>21.74741721395487</v>
+      </c>
+      <c r="Q33">
+        <v>167.8474172139549</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09563113016649966</v>
+      </c>
+      <c r="T33">
+        <v>0.7695841699494332</v>
+      </c>
+      <c r="U33">
+        <v>0.09564323704438382</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.07651458963550706</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.009977178773416</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09417133766708521</v>
+      </c>
+      <c r="C34">
+        <v>472.447665420864</v>
+      </c>
+      <c r="D34">
+        <v>597.443665420864</v>
+      </c>
+      <c r="E34">
+        <v>116.596</v>
+      </c>
+      <c r="F34">
+        <v>290.496</v>
+      </c>
+      <c r="G34">
+        <v>165.5</v>
+      </c>
+      <c r="H34">
+        <v>733.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>200.2</v>
+      </c>
+      <c r="K34">
+        <v>146.1</v>
+      </c>
+      <c r="L34">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M34">
+        <v>32.51906258844532</v>
+      </c>
+      <c r="N34">
+        <v>21.58093741155467</v>
+      </c>
+      <c r="O34">
+        <v>4.316187482310935</v>
+      </c>
+      <c r="P34">
+        <v>17.26474992924374</v>
+      </c>
+      <c r="Q34">
+        <v>163.3647499292437</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09634392497606317</v>
+      </c>
+      <c r="T34">
+        <v>0.7792365488525993</v>
+      </c>
+      <c r="U34">
+        <v>0.1119432370443838</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.08955458963550707</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>1.663639591481423</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.0945952727322785</v>
+      </c>
+      <c r="C35">
+        <v>458.8302607930777</v>
+      </c>
+      <c r="D35">
+        <v>592.9042607930777</v>
+      </c>
+      <c r="E35">
+        <v>125.674</v>
+      </c>
+      <c r="F35">
+        <v>299.574</v>
+      </c>
+      <c r="G35">
+        <v>165.5</v>
+      </c>
+      <c r="H35">
+        <v>733.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>200.2</v>
+      </c>
+      <c r="K35">
+        <v>146.1</v>
+      </c>
+      <c r="L35">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M35">
+        <v>33.53528329433424</v>
+      </c>
+      <c r="N35">
+        <v>20.56471670566575</v>
+      </c>
+      <c r="O35">
+        <v>4.112943341133151</v>
+      </c>
+      <c r="P35">
+        <v>16.4517733645326</v>
+      </c>
+      <c r="Q35">
+        <v>162.5517733645326</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09707799724262861</v>
+      </c>
+      <c r="T35">
+        <v>0.7891770584692929</v>
+      </c>
+      <c r="U35">
+        <v>0.1119432370443838</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.08955458963550707</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>1.61322627052744</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09501920779747175</v>
+      </c>
+      <c r="C36">
+        <v>445.2813172081349</v>
+      </c>
+      <c r="D36">
+        <v>588.4333172081349</v>
+      </c>
+      <c r="E36">
+        <v>134.752</v>
+      </c>
+      <c r="F36">
+        <v>308.652</v>
+      </c>
+      <c r="G36">
+        <v>165.5</v>
+      </c>
+      <c r="H36">
+        <v>733.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>200.2</v>
+      </c>
+      <c r="K36">
+        <v>146.1</v>
+      </c>
+      <c r="L36">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M36">
+        <v>34.55150400022315</v>
+      </c>
+      <c r="N36">
+        <v>19.54849599977684</v>
+      </c>
+      <c r="O36">
+        <v>3.909699199955368</v>
+      </c>
+      <c r="P36">
+        <v>15.63879679982147</v>
+      </c>
+      <c r="Q36">
+        <v>161.7387967998215</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09783431412333235</v>
+      </c>
+      <c r="T36">
+        <v>0.7994187956501284</v>
+      </c>
+      <c r="U36">
+        <v>0.1119432370443838</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.08955458963550707</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>1.565778439041339</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09544314286266502</v>
+      </c>
+      <c r="C37">
+        <v>431.799297514218</v>
+      </c>
+      <c r="D37">
+        <v>584.029297514218</v>
+      </c>
+      <c r="E37">
+        <v>143.83</v>
+      </c>
+      <c r="F37">
+        <v>317.73</v>
+      </c>
+      <c r="G37">
+        <v>165.5</v>
+      </c>
+      <c r="H37">
+        <v>733.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>200.2</v>
+      </c>
+      <c r="K37">
+        <v>146.1</v>
+      </c>
+      <c r="L37">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M37">
+        <v>35.56772470611207</v>
+      </c>
+      <c r="N37">
+        <v>18.53227529388792</v>
+      </c>
+      <c r="O37">
+        <v>3.706455058777584</v>
+      </c>
+      <c r="P37">
+        <v>14.82582023511034</v>
+      </c>
+      <c r="Q37">
+        <v>160.9258202351103</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.09861390229267317</v>
+      </c>
+      <c r="T37">
+        <v>0.8099756632057591</v>
+      </c>
+      <c r="U37">
+        <v>0.1119432370443838</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.08955458963550707</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>1.521041912211587</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1157523881029539</v>
+      </c>
+      <c r="C38">
+        <v>268.5845056207567</v>
+      </c>
+      <c r="D38">
+        <v>429.8925056207567</v>
+      </c>
+      <c r="E38">
+        <v>152.908</v>
+      </c>
+      <c r="F38">
+        <v>326.808</v>
+      </c>
+      <c r="G38">
+        <v>165.5</v>
+      </c>
+      <c r="H38">
+        <v>733.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>200.2</v>
+      </c>
+      <c r="K38">
+        <v>146.1</v>
+      </c>
+      <c r="L38">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M38">
+        <v>57.95718861200098</v>
+      </c>
+      <c r="N38">
+        <v>-3.857188612000989</v>
+      </c>
+      <c r="O38">
+        <v>-0.7714377224001979</v>
+      </c>
+      <c r="P38">
+        <v>-3.085750889600791</v>
+      </c>
+      <c r="Q38">
+        <v>143.0142491103992</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.09973085568796221</v>
+      </c>
+      <c r="T38">
+        <v>0.8251009941479268</v>
+      </c>
+      <c r="U38">
+        <v>0.1773432370443838</v>
+      </c>
+      <c r="V38">
+        <v>0.186689524787604</v>
+      </c>
+      <c r="W38">
+        <v>0.1442351123962724</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.9334476239380201</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1171378204733977</v>
+      </c>
+      <c r="C39">
+        <v>251.9037029195957</v>
+      </c>
+      <c r="D39">
+        <v>422.2897029195957</v>
+      </c>
+      <c r="E39">
+        <v>161.986</v>
+      </c>
+      <c r="F39">
+        <v>335.886</v>
+      </c>
+      <c r="G39">
+        <v>165.5</v>
+      </c>
+      <c r="H39">
+        <v>733.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>200.2</v>
+      </c>
+      <c r="K39">
+        <v>146.1</v>
+      </c>
+      <c r="L39">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M39">
+        <v>59.56711051788989</v>
+      </c>
+      <c r="N39">
+        <v>-5.4671105178899</v>
+      </c>
+      <c r="O39">
+        <v>-1.09342210357798</v>
+      </c>
+      <c r="P39">
+        <v>-4.373688414311919</v>
+      </c>
+      <c r="Q39">
+        <v>141.7263115856881</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1006980121274537</v>
+      </c>
+      <c r="T39">
+        <v>0.838197835324878</v>
+      </c>
+      <c r="U39">
+        <v>0.1773432370443838</v>
+      </c>
+      <c r="V39">
+        <v>0.1816438619555066</v>
+      </c>
+      <c r="W39">
+        <v>0.1451299265759511</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.9082193097775332</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1185232528438415</v>
+      </c>
+      <c r="C40">
+        <v>235.487143550024</v>
+      </c>
+      <c r="D40">
+        <v>414.9511435500239</v>
+      </c>
+      <c r="E40">
+        <v>171.064</v>
+      </c>
+      <c r="F40">
+        <v>344.964</v>
+      </c>
+      <c r="G40">
+        <v>165.5</v>
+      </c>
+      <c r="H40">
+        <v>733.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>200.2</v>
+      </c>
+      <c r="K40">
+        <v>146.1</v>
+      </c>
+      <c r="L40">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M40">
+        <v>61.17703242377882</v>
+      </c>
+      <c r="N40">
+        <v>-7.077032423778824</v>
+      </c>
+      <c r="O40">
+        <v>-1.415406484755765</v>
+      </c>
+      <c r="P40">
+        <v>-5.661625939023059</v>
+      </c>
+      <c r="Q40">
+        <v>140.4383740609769</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1016963671617674</v>
+      </c>
+      <c r="T40">
+        <v>0.8517171552494729</v>
+      </c>
+      <c r="U40">
+        <v>0.1773432370443838</v>
+      </c>
+      <c r="V40">
+        <v>0.1768637603250985</v>
+      </c>
+      <c r="W40">
+        <v>0.1459776452724888</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.8843188016254927</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1199086852142854</v>
+      </c>
+      <c r="C41">
+        <v>219.3212867451938</v>
+      </c>
+      <c r="D41">
+        <v>407.8632867451939</v>
+      </c>
+      <c r="E41">
+        <v>180.142</v>
+      </c>
+      <c r="F41">
+        <v>354.042</v>
+      </c>
+      <c r="G41">
+        <v>165.5</v>
+      </c>
+      <c r="H41">
+        <v>733.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>200.2</v>
+      </c>
+      <c r="K41">
+        <v>146.1</v>
+      </c>
+      <c r="L41">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M41">
+        <v>62.78695432966773</v>
+      </c>
+      <c r="N41">
+        <v>-8.686954329667735</v>
+      </c>
+      <c r="O41">
+        <v>-1.737390865933547</v>
+      </c>
+      <c r="P41">
+        <v>-6.949563463734188</v>
+      </c>
+      <c r="Q41">
+        <v>139.1504365362658</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1027274551480259</v>
+      </c>
+      <c r="T41">
+        <v>0.865679731565038</v>
+      </c>
+      <c r="U41">
+        <v>0.1773432370443838</v>
+      </c>
+      <c r="V41">
+        <v>0.1723287921116345</v>
+      </c>
+      <c r="W41">
+        <v>0.1467818912153579</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.8616439605581725</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1212941175847292</v>
+      </c>
+      <c r="C42">
+        <v>203.3935013699878</v>
+      </c>
+      <c r="D42">
+        <v>401.0135013699878</v>
+      </c>
+      <c r="E42">
+        <v>189.22</v>
+      </c>
+      <c r="F42">
+        <v>363.12</v>
+      </c>
+      <c r="G42">
+        <v>165.5</v>
+      </c>
+      <c r="H42">
+        <v>733.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>200.2</v>
+      </c>
+      <c r="K42">
+        <v>146.1</v>
+      </c>
+      <c r="L42">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M42">
+        <v>64.39687623555665</v>
+      </c>
+      <c r="N42">
+        <v>-10.29687623555665</v>
+      </c>
+      <c r="O42">
+        <v>-2.059375247111331</v>
+      </c>
+      <c r="P42">
+        <v>-8.237500988445323</v>
+      </c>
+      <c r="Q42">
+        <v>137.8624990115547</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1037929127338264</v>
+      </c>
+      <c r="T42">
+        <v>0.8801077270911219</v>
+      </c>
+      <c r="U42">
+        <v>0.1773432370443838</v>
+      </c>
+      <c r="V42">
+        <v>0.1680205723088436</v>
+      </c>
+      <c r="W42">
+        <v>0.1475459248610835</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.8401028615442181</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1226795499551731</v>
+      </c>
+      <c r="C43">
+        <v>187.6919907994146</v>
+      </c>
+      <c r="D43">
+        <v>394.3899907994145</v>
+      </c>
+      <c r="E43">
+        <v>198.298</v>
+      </c>
+      <c r="F43">
+        <v>372.198</v>
+      </c>
+      <c r="G43">
+        <v>165.5</v>
+      </c>
+      <c r="H43">
+        <v>733.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>200.2</v>
+      </c>
+      <c r="K43">
+        <v>146.1</v>
+      </c>
+      <c r="L43">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M43">
+        <v>66.00679814144557</v>
+      </c>
+      <c r="N43">
+        <v>-11.90679814144558</v>
+      </c>
+      <c r="O43">
+        <v>-2.381359628289116</v>
+      </c>
+      <c r="P43">
+        <v>-9.525438513156463</v>
+      </c>
+      <c r="Q43">
+        <v>136.5745614868435</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1048944875259251</v>
+      </c>
+      <c r="T43">
+        <v>0.8950248072113105</v>
+      </c>
+      <c r="U43">
+        <v>0.1773432370443838</v>
+      </c>
+      <c r="V43">
+        <v>0.1639225095696035</v>
+      </c>
+      <c r="W43">
+        <v>0.1482726885728713</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.8196125478480175</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1240649823256169</v>
+      </c>
+      <c r="C44">
+        <v>172.2057251207107</v>
+      </c>
+      <c r="D44">
+        <v>387.9817251207106</v>
+      </c>
+      <c r="E44">
+        <v>207.3759999999999</v>
+      </c>
+      <c r="F44">
+        <v>381.276</v>
+      </c>
+      <c r="G44">
+        <v>165.5</v>
+      </c>
+      <c r="H44">
+        <v>733.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>200.2</v>
+      </c>
+      <c r="K44">
+        <v>146.1</v>
+      </c>
+      <c r="L44">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M44">
+        <v>67.61672004733448</v>
+      </c>
+      <c r="N44">
+        <v>-13.51672004733449</v>
+      </c>
+      <c r="O44">
+        <v>-2.703344009466898</v>
+      </c>
+      <c r="P44">
+        <v>-10.81337603786759</v>
+      </c>
+      <c r="Q44">
+        <v>135.2866239621324</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1060340476556824</v>
+      </c>
+      <c r="T44">
+        <v>0.9104562694046088</v>
+      </c>
+      <c r="U44">
+        <v>0.1773432370443838</v>
+      </c>
+      <c r="V44">
+        <v>0.1600195926750892</v>
+      </c>
+      <c r="W44">
+        <v>0.1489648444888597</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.8000979633754458</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1485353560492804</v>
+      </c>
+      <c r="C45">
+        <v>76.60995953026725</v>
+      </c>
+      <c r="D45">
+        <v>301.4639595302672</v>
+      </c>
+      <c r="E45">
+        <v>216.454</v>
+      </c>
+      <c r="F45">
+        <v>390.354</v>
+      </c>
+      <c r="G45">
+        <v>165.5</v>
+      </c>
+      <c r="H45">
+        <v>733.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>200.2</v>
+      </c>
+      <c r="K45">
+        <v>146.1</v>
+      </c>
+      <c r="L45">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M45">
+        <v>89.60312075322341</v>
+      </c>
+      <c r="N45">
+        <v>-35.50312075322341</v>
+      </c>
+      <c r="O45">
+        <v>-7.100624150644683</v>
+      </c>
+      <c r="P45">
+        <v>-28.40249660257873</v>
+      </c>
+      <c r="Q45">
+        <v>117.6975033974213</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1083345420938869</v>
+      </c>
+      <c r="T45">
+        <v>0.9416086342706952</v>
+      </c>
+      <c r="U45">
+        <v>0.2295432370443838</v>
+      </c>
+      <c r="V45">
+        <v>0.1207547227043513</v>
+      </c>
+      <c r="W45">
+        <v>0.2018248071064301</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.6037736135217566</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1504427884197243</v>
+      </c>
+      <c r="C46">
+        <v>62.38140638599793</v>
+      </c>
+      <c r="D46">
+        <v>296.3134063859979</v>
+      </c>
+      <c r="E46">
+        <v>225.532</v>
+      </c>
+      <c r="F46">
+        <v>399.432</v>
+      </c>
+      <c r="G46">
+        <v>165.5</v>
+      </c>
+      <c r="H46">
+        <v>733.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>200.2</v>
+      </c>
+      <c r="K46">
+        <v>146.1</v>
+      </c>
+      <c r="L46">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M46">
+        <v>91.68691425911231</v>
+      </c>
+      <c r="N46">
+        <v>-37.58691425911232</v>
+      </c>
+      <c r="O46">
+        <v>-7.517382851822465</v>
+      </c>
+      <c r="P46">
+        <v>-30.06953140728985</v>
+      </c>
+      <c r="Q46">
+        <v>116.0304685927101</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1095762303455634</v>
+      </c>
+      <c r="T46">
+        <v>0.9584230741683863</v>
+      </c>
+      <c r="U46">
+        <v>0.2295432370443838</v>
+      </c>
+      <c r="V46">
+        <v>0.1180102971883434</v>
+      </c>
+      <c r="W46">
+        <v>0.2024547714232018</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.5900514859417167</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1523502207901681</v>
+      </c>
+      <c r="C47">
+        <v>48.32589265503321</v>
+      </c>
+      <c r="D47">
+        <v>291.3358926550332</v>
+      </c>
+      <c r="E47">
+        <v>234.61</v>
+      </c>
+      <c r="F47">
+        <v>408.51</v>
+      </c>
+      <c r="G47">
+        <v>165.5</v>
+      </c>
+      <c r="H47">
+        <v>733.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>200.2</v>
+      </c>
+      <c r="K47">
+        <v>146.1</v>
+      </c>
+      <c r="L47">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M47">
+        <v>93.77070776500123</v>
+      </c>
+      <c r="N47">
+        <v>-39.67070776500124</v>
+      </c>
+      <c r="O47">
+        <v>-7.934141553000249</v>
+      </c>
+      <c r="P47">
+        <v>-31.73656621200099</v>
+      </c>
+      <c r="Q47">
+        <v>114.363433787999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1108630708973009</v>
+      </c>
+      <c r="T47">
+        <v>0.975848948244175</v>
+      </c>
+      <c r="U47">
+        <v>0.2295432370443838</v>
+      </c>
+      <c r="V47">
+        <v>0.1153878461397135</v>
+      </c>
+      <c r="W47">
+        <v>0.2030567373258947</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.5769392306985675</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.154257653160612</v>
+      </c>
+      <c r="C48">
+        <v>34.43484218059359</v>
+      </c>
+      <c r="D48">
+        <v>286.5228421805936</v>
+      </c>
+      <c r="E48">
+        <v>243.688</v>
+      </c>
+      <c r="F48">
+        <v>417.588</v>
+      </c>
+      <c r="G48">
+        <v>165.5</v>
+      </c>
+      <c r="H48">
+        <v>733.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>200.2</v>
+      </c>
+      <c r="K48">
+        <v>146.1</v>
+      </c>
+      <c r="L48">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M48">
+        <v>95.85450127089017</v>
+      </c>
+      <c r="N48">
+        <v>-41.75450127089017</v>
+      </c>
+      <c r="O48">
+        <v>-8.350900254178034</v>
+      </c>
+      <c r="P48">
+        <v>-33.40360101671214</v>
+      </c>
+      <c r="Q48">
+        <v>112.6963989832878</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1121975722102139</v>
+      </c>
+      <c r="T48">
+        <v>0.9939202250635117</v>
+      </c>
+      <c r="U48">
+        <v>0.2295432370443838</v>
+      </c>
+      <c r="V48">
+        <v>0.1128794147018936</v>
+      </c>
+      <c r="W48">
+        <v>0.2036325307980358</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5643970735094681</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1561650855310558</v>
+      </c>
+      <c r="C49">
+        <v>20.70023632908413</v>
+      </c>
+      <c r="D49">
+        <v>281.8662363290841</v>
+      </c>
+      <c r="E49">
+        <v>252.766</v>
+      </c>
+      <c r="F49">
+        <v>426.666</v>
+      </c>
+      <c r="G49">
+        <v>165.5</v>
+      </c>
+      <c r="H49">
+        <v>733.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>200.2</v>
+      </c>
+      <c r="K49">
+        <v>146.1</v>
+      </c>
+      <c r="L49">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M49">
+        <v>97.93829477677907</v>
+      </c>
+      <c r="N49">
+        <v>-43.83829477677908</v>
+      </c>
+      <c r="O49">
+        <v>-8.767658955355817</v>
+      </c>
+      <c r="P49">
+        <v>-35.07063582142327</v>
+      </c>
+      <c r="Q49">
+        <v>111.0293641785767</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1135824320632368</v>
+      </c>
+      <c r="T49">
+        <v>1.012673436857163</v>
+      </c>
+      <c r="U49">
+        <v>0.2295432370443838</v>
+      </c>
+      <c r="V49">
+        <v>0.1104777250273852</v>
+      </c>
+      <c r="W49">
+        <v>0.2041838224202985</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.5523886251369262</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1580725179014996</v>
+      </c>
+      <c r="C50">
+        <v>7.114569409926105</v>
+      </c>
+      <c r="D50">
+        <v>277.3585694099261</v>
+      </c>
+      <c r="E50">
+        <v>261.8439999999999</v>
+      </c>
+      <c r="F50">
+        <v>435.744</v>
+      </c>
+      <c r="G50">
+        <v>165.5</v>
+      </c>
+      <c r="H50">
+        <v>733.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>200.2</v>
+      </c>
+      <c r="K50">
+        <v>146.1</v>
+      </c>
+      <c r="L50">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M50">
+        <v>100.022088282668</v>
+      </c>
+      <c r="N50">
+        <v>-45.92208828266799</v>
+      </c>
+      <c r="O50">
+        <v>-9.184417656533597</v>
+      </c>
+      <c r="P50">
+        <v>-36.73767062613439</v>
+      </c>
+      <c r="Q50">
+        <v>109.3623293738656</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1150205557567606</v>
+      </c>
+      <c r="T50">
+        <v>1.032147926027493</v>
+      </c>
+      <c r="U50">
+        <v>0.2295432370443838</v>
+      </c>
+      <c r="V50">
+        <v>0.1081761057559814</v>
+      </c>
+      <c r="W50">
+        <v>0.2047121435583003</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.540880528779907</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1599799502719435</v>
+      </c>
+      <c r="C51">
+        <v>-6.329191694326198</v>
+      </c>
+      <c r="D51">
+        <v>272.9928083056737</v>
+      </c>
+      <c r="E51">
+        <v>270.9219999999999</v>
+      </c>
+      <c r="F51">
+        <v>444.8219999999999</v>
+      </c>
+      <c r="G51">
+        <v>165.5</v>
+      </c>
+      <c r="H51">
+        <v>733.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>200.2</v>
+      </c>
+      <c r="K51">
+        <v>146.1</v>
+      </c>
+      <c r="L51">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M51">
+        <v>102.1058817885569</v>
+      </c>
+      <c r="N51">
+        <v>-48.00588178855691</v>
+      </c>
+      <c r="O51">
+        <v>-9.601176357711381</v>
+      </c>
+      <c r="P51">
+        <v>-38.40470543084552</v>
+      </c>
+      <c r="Q51">
+        <v>107.6952945691545</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1165150764578736</v>
+      </c>
+      <c r="T51">
+        <v>1.052386120655483</v>
+      </c>
+      <c r="U51">
+        <v>0.2295432370443838</v>
+      </c>
+      <c r="V51">
+        <v>0.1059684301283083</v>
+      </c>
+      <c r="W51">
+        <v>0.2052189005682203</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5298421506415415</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1618873826423873</v>
+      </c>
+      <c r="C52">
+        <v>-19.63764414430216</v>
+      </c>
+      <c r="D52">
+        <v>268.7623558556978</v>
+      </c>
+      <c r="E52">
+        <v>280</v>
+      </c>
+      <c r="F52">
+        <v>453.9</v>
+      </c>
+      <c r="G52">
+        <v>165.5</v>
+      </c>
+      <c r="H52">
+        <v>733.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>200.2</v>
+      </c>
+      <c r="K52">
+        <v>146.1</v>
+      </c>
+      <c r="L52">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M52">
+        <v>104.1896752944458</v>
+      </c>
+      <c r="N52">
+        <v>-50.08967529444583</v>
+      </c>
+      <c r="O52">
+        <v>-10.01793505888917</v>
+      </c>
+      <c r="P52">
+        <v>-40.07174023555666</v>
+      </c>
+      <c r="Q52">
+        <v>106.0282597644433</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.118069377987031</v>
+      </c>
+      <c r="T52">
+        <v>1.073433843068593</v>
+      </c>
+      <c r="U52">
+        <v>0.2295432370443838</v>
+      </c>
+      <c r="V52">
+        <v>0.1038490615257421</v>
+      </c>
+      <c r="W52">
+        <v>0.2057053872977436</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5192453076287107</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1637948150128312</v>
+      </c>
+      <c r="C53">
+        <v>-32.81698240751956</v>
+      </c>
+      <c r="D53">
+        <v>264.6610175924804</v>
+      </c>
+      <c r="E53">
+        <v>289.078</v>
+      </c>
+      <c r="F53">
+        <v>462.978</v>
+      </c>
+      <c r="G53">
+        <v>165.5</v>
+      </c>
+      <c r="H53">
+        <v>733.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>200.2</v>
+      </c>
+      <c r="K53">
+        <v>146.1</v>
+      </c>
+      <c r="L53">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M53">
+        <v>106.2734688003347</v>
+      </c>
+      <c r="N53">
+        <v>-52.17346880033475</v>
+      </c>
+      <c r="O53">
+        <v>-10.43469376006695</v>
+      </c>
+      <c r="P53">
+        <v>-41.7387750402678</v>
+      </c>
+      <c r="Q53">
+        <v>104.3612249597322</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1196871203949296</v>
+      </c>
+      <c r="T53">
+        <v>1.095340656192441</v>
+      </c>
+      <c r="U53">
+        <v>0.2295432370443838</v>
+      </c>
+      <c r="V53">
+        <v>0.1018128054173942</v>
+      </c>
+      <c r="W53">
+        <v>0.2061727961163052</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5090640270869713</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.181553156628159</v>
+      </c>
+      <c r="C54">
+        <v>-74.81853291722825</v>
+      </c>
+      <c r="D54">
+        <v>231.7374670827717</v>
+      </c>
+      <c r="E54">
+        <v>298.1559999999999</v>
+      </c>
+      <c r="F54">
+        <v>472.056</v>
+      </c>
+      <c r="G54">
+        <v>165.5</v>
+      </c>
+      <c r="H54">
+        <v>733.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>200.2</v>
+      </c>
+      <c r="K54">
+        <v>146.1</v>
+      </c>
+      <c r="L54">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M54">
+        <v>122.5189423062237</v>
+      </c>
+      <c r="N54">
+        <v>-68.41894230622367</v>
+      </c>
+      <c r="O54">
+        <v>-13.68378846124473</v>
+      </c>
+      <c r="P54">
+        <v>-54.73515384497894</v>
+      </c>
+      <c r="Q54">
+        <v>91.36484615502106</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.121894996329999</v>
+      </c>
+      <c r="T54">
+        <v>1.125238818763969</v>
+      </c>
+      <c r="U54">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V54">
+        <v>0.08831287469782842</v>
+      </c>
+      <c r="W54">
+        <v>0.2366222276726144</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.441564373489142</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1837605889986029</v>
+      </c>
+      <c r="C55">
+        <v>-87.42538713765452</v>
+      </c>
+      <c r="D55">
+        <v>228.2086128623455</v>
+      </c>
+      <c r="E55">
+        <v>307.234</v>
+      </c>
+      <c r="F55">
+        <v>481.134</v>
+      </c>
+      <c r="G55">
+        <v>165.5</v>
+      </c>
+      <c r="H55">
+        <v>733.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>200.2</v>
+      </c>
+      <c r="K55">
+        <v>146.1</v>
+      </c>
+      <c r="L55">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M55">
+        <v>124.8750758121126</v>
+      </c>
+      <c r="N55">
+        <v>-70.7750758121126</v>
+      </c>
+      <c r="O55">
+        <v>-14.15501516242252</v>
+      </c>
+      <c r="P55">
+        <v>-56.62006064969008</v>
+      </c>
+      <c r="Q55">
+        <v>89.47993935030991</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1236629749753181</v>
+      </c>
+      <c r="T55">
+        <v>1.149180070227033</v>
+      </c>
+      <c r="U55">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V55">
+        <v>0.08664659404315239</v>
+      </c>
+      <c r="W55">
+        <v>0.2370546995475535</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.433232970215762</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1859680213690467</v>
+      </c>
+      <c r="C56">
+        <v>-99.92637994927327</v>
+      </c>
+      <c r="D56">
+        <v>224.7856200507267</v>
+      </c>
+      <c r="E56">
+        <v>316.312</v>
+      </c>
+      <c r="F56">
+        <v>490.212</v>
+      </c>
+      <c r="G56">
+        <v>165.5</v>
+      </c>
+      <c r="H56">
+        <v>733.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>200.2</v>
+      </c>
+      <c r="K56">
+        <v>146.1</v>
+      </c>
+      <c r="L56">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M56">
+        <v>127.2312093180015</v>
+      </c>
+      <c r="N56">
+        <v>-73.13120931800151</v>
+      </c>
+      <c r="O56">
+        <v>-14.6262418636003</v>
+      </c>
+      <c r="P56">
+        <v>-58.50496745440121</v>
+      </c>
+      <c r="Q56">
+        <v>87.59503254559878</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1255078222573902</v>
+      </c>
+      <c r="T56">
+        <v>1.174162245666751</v>
+      </c>
+      <c r="U56">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V56">
+        <v>0.08504202748679773</v>
+      </c>
+      <c r="W56">
+        <v>0.2374711539456429</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.4252101374339886</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1881754537394905</v>
+      </c>
+      <c r="C57">
+        <v>-112.3262045308116</v>
+      </c>
+      <c r="D57">
+        <v>221.4637954691885</v>
+      </c>
+      <c r="E57">
+        <v>325.39</v>
+      </c>
+      <c r="F57">
+        <v>499.29</v>
+      </c>
+      <c r="G57">
+        <v>165.5</v>
+      </c>
+      <c r="H57">
+        <v>733.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>200.2</v>
+      </c>
+      <c r="K57">
+        <v>146.1</v>
+      </c>
+      <c r="L57">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M57">
+        <v>129.5873428238904</v>
+      </c>
+      <c r="N57">
+        <v>-75.48734282389043</v>
+      </c>
+      <c r="O57">
+        <v>-15.09746856477809</v>
+      </c>
+      <c r="P57">
+        <v>-60.38987425911235</v>
+      </c>
+      <c r="Q57">
+        <v>85.71012574088765</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1274346627519989</v>
+      </c>
+      <c r="T57">
+        <v>1.200254740014901</v>
+      </c>
+      <c r="U57">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V57">
+        <v>0.08349580880521959</v>
+      </c>
+      <c r="W57">
+        <v>0.2378724645474382</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.4174790440260979</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1903828861099343</v>
+      </c>
+      <c r="C58">
+        <v>-124.6292806825184</v>
+      </c>
+      <c r="D58">
+        <v>218.2387193174816</v>
+      </c>
+      <c r="E58">
+        <v>334.468</v>
+      </c>
+      <c r="F58">
+        <v>508.368</v>
+      </c>
+      <c r="G58">
+        <v>165.5</v>
+      </c>
+      <c r="H58">
+        <v>733.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>200.2</v>
+      </c>
+      <c r="K58">
+        <v>146.1</v>
+      </c>
+      <c r="L58">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M58">
+        <v>131.9434763297793</v>
+      </c>
+      <c r="N58">
+        <v>-77.84347632977935</v>
+      </c>
+      <c r="O58">
+        <v>-15.56869526595587</v>
+      </c>
+      <c r="P58">
+        <v>-62.27478106382348</v>
+      </c>
+      <c r="Q58">
+        <v>83.82521893617651</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1294490869054534</v>
+      </c>
+      <c r="T58">
+        <v>1.227533256833421</v>
+      </c>
+      <c r="U58">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V58">
+        <v>0.0820048122194121</v>
+      </c>
+      <c r="W58">
+        <v>0.2382594426277408</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.4100240610970605</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1925903184803782</v>
+      </c>
+      <c r="C59">
+        <v>-136.8397744458829</v>
+      </c>
+      <c r="D59">
+        <v>215.1062255541171</v>
+      </c>
+      <c r="E59">
+        <v>343.546</v>
+      </c>
+      <c r="F59">
+        <v>517.446</v>
+      </c>
+      <c r="G59">
+        <v>165.5</v>
+      </c>
+      <c r="H59">
+        <v>733.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>200.2</v>
+      </c>
+      <c r="K59">
+        <v>146.1</v>
+      </c>
+      <c r="L59">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M59">
+        <v>134.2996098356683</v>
+      </c>
+      <c r="N59">
+        <v>-80.19960983566827</v>
+      </c>
+      <c r="O59">
+        <v>-16.03992196713365</v>
+      </c>
+      <c r="P59">
+        <v>-64.15968786853462</v>
+      </c>
+      <c r="Q59">
+        <v>81.94031213146538</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1315572052055803</v>
+      </c>
+      <c r="T59">
+        <v>1.256080541876059</v>
+      </c>
+      <c r="U59">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V59">
+        <v>0.08056613130328205</v>
+      </c>
+      <c r="W59">
+        <v>0.2386328425297872</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.4028306565164103</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.194797750850822</v>
+      </c>
+      <c r="C60">
+        <v>-148.9616160575879</v>
+      </c>
+      <c r="D60">
+        <v>212.0623839424119</v>
+      </c>
+      <c r="E60">
+        <v>352.6239999999999</v>
+      </c>
+      <c r="F60">
+        <v>526.5239999999999</v>
+      </c>
+      <c r="G60">
+        <v>165.5</v>
+      </c>
+      <c r="H60">
+        <v>733.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>200.2</v>
+      </c>
+      <c r="K60">
+        <v>146.1</v>
+      </c>
+      <c r="L60">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M60">
+        <v>136.6557433415572</v>
+      </c>
+      <c r="N60">
+        <v>-82.55574334155716</v>
+      </c>
+      <c r="O60">
+        <v>-16.51114866831143</v>
+      </c>
+      <c r="P60">
+        <v>-66.04459467324573</v>
+      </c>
+      <c r="Q60">
+        <v>80.05540532675427</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1337657100914274</v>
+      </c>
+      <c r="T60">
+        <v>1.285987221444536</v>
+      </c>
+      <c r="U60">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V60">
+        <v>0.07917706007391513</v>
+      </c>
+      <c r="W60">
+        <v>0.2389933665731423</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3958853003695757</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1970051832212658</v>
+      </c>
+      <c r="C61">
+        <v>-160.9985164003995</v>
+      </c>
+      <c r="D61">
+        <v>209.1034835996005</v>
+      </c>
+      <c r="E61">
+        <v>361.702</v>
+      </c>
+      <c r="F61">
+        <v>535.602</v>
+      </c>
+      <c r="G61">
+        <v>165.5</v>
+      </c>
+      <c r="H61">
+        <v>733.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>200.2</v>
+      </c>
+      <c r="K61">
+        <v>146.1</v>
+      </c>
+      <c r="L61">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M61">
+        <v>139.0118768474461</v>
+      </c>
+      <c r="N61">
+        <v>-84.91187684744608</v>
+      </c>
+      <c r="O61">
+        <v>-16.98237536948922</v>
+      </c>
+      <c r="P61">
+        <v>-67.92950147795686</v>
+      </c>
+      <c r="Q61">
+        <v>78.17049852204313</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1360819469229256</v>
+      </c>
+      <c r="T61">
+        <v>1.317352763430988</v>
+      </c>
+      <c r="U61">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V61">
+        <v>0.07783507600486572</v>
+      </c>
+      <c r="W61">
+        <v>0.2393416694624854</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3891753800243286</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1992126155917097</v>
+      </c>
+      <c r="C62">
+        <v>-172.9539820957733</v>
+      </c>
+      <c r="D62">
+        <v>206.2260179042267</v>
+      </c>
+      <c r="E62">
+        <v>370.78</v>
+      </c>
+      <c r="F62">
+        <v>544.6799999999999</v>
+      </c>
+      <c r="G62">
+        <v>165.5</v>
+      </c>
+      <c r="H62">
+        <v>733.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>200.2</v>
+      </c>
+      <c r="K62">
+        <v>146.1</v>
+      </c>
+      <c r="L62">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M62">
+        <v>141.368010353335</v>
+      </c>
+      <c r="N62">
+        <v>-87.268010353335</v>
+      </c>
+      <c r="O62">
+        <v>-17.453602070667</v>
+      </c>
+      <c r="P62">
+        <v>-69.814408282668</v>
+      </c>
+      <c r="Q62">
+        <v>76.285591717332</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1385139955959988</v>
+      </c>
+      <c r="T62">
+        <v>1.350286582516763</v>
+      </c>
+      <c r="U62">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V62">
+        <v>0.07653782473811796</v>
+      </c>
+      <c r="W62">
+        <v>0.239678362255517</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3826891236905898</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2014200479621536</v>
+      </c>
+      <c r="C63">
+        <v>-184.8313293672455</v>
+      </c>
+      <c r="D63">
+        <v>203.4266706327545</v>
+      </c>
+      <c r="E63">
+        <v>379.8579999999999</v>
+      </c>
+      <c r="F63">
+        <v>553.7579999999999</v>
+      </c>
+      <c r="G63">
+        <v>165.5</v>
+      </c>
+      <c r="H63">
+        <v>733.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>200.2</v>
+      </c>
+      <c r="K63">
+        <v>146.1</v>
+      </c>
+      <c r="L63">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M63">
+        <v>143.7241438592239</v>
+      </c>
+      <c r="N63">
+        <v>-89.62414385922392</v>
+      </c>
+      <c r="O63">
+        <v>-17.92482877184478</v>
+      </c>
+      <c r="P63">
+        <v>-71.69931508737913</v>
+      </c>
+      <c r="Q63">
+        <v>74.40068491262086</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1410707647138449</v>
+      </c>
+      <c r="T63">
+        <v>1.384909315401809</v>
+      </c>
+      <c r="U63">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V63">
+        <v>0.07528310629978816</v>
+      </c>
+      <c r="W63">
+        <v>0.2400040159405804</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3764155314989408</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2036274803325974</v>
+      </c>
+      <c r="C64">
+        <v>-196.6336967898394</v>
+      </c>
+      <c r="D64">
+        <v>200.7023032101606</v>
+      </c>
+      <c r="E64">
+        <v>388.936</v>
+      </c>
+      <c r="F64">
+        <v>562.836</v>
+      </c>
+      <c r="G64">
+        <v>165.5</v>
+      </c>
+      <c r="H64">
+        <v>733.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>200.2</v>
+      </c>
+      <c r="K64">
+        <v>146.1</v>
+      </c>
+      <c r="L64">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M64">
+        <v>146.0802773651128</v>
+      </c>
+      <c r="N64">
+        <v>-91.98027736511284</v>
+      </c>
+      <c r="O64">
+        <v>-18.39605547302257</v>
+      </c>
+      <c r="P64">
+        <v>-73.58422189209027</v>
+      </c>
+      <c r="Q64">
+        <v>72.51577810790972</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1437621006273671</v>
+      </c>
+      <c r="T64">
+        <v>1.421354297386067</v>
+      </c>
+      <c r="U64">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V64">
+        <v>0.07406886264979157</v>
+      </c>
+      <c r="W64">
+        <v>0.2403191646680611</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3703443132489579</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2058349127030412</v>
+      </c>
+      <c r="C65">
+        <v>-208.3640570285422</v>
+      </c>
+      <c r="D65">
+        <v>198.0499429714578</v>
+      </c>
+      <c r="E65">
+        <v>398.014</v>
+      </c>
+      <c r="F65">
+        <v>571.914</v>
+      </c>
+      <c r="G65">
+        <v>165.5</v>
+      </c>
+      <c r="H65">
+        <v>733.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>200.2</v>
+      </c>
+      <c r="K65">
+        <v>146.1</v>
+      </c>
+      <c r="L65">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M65">
+        <v>148.4364108710018</v>
+      </c>
+      <c r="N65">
+        <v>-94.33641087100176</v>
+      </c>
+      <c r="O65">
+        <v>-18.86728217420035</v>
+      </c>
+      <c r="P65">
+        <v>-75.46912869680141</v>
+      </c>
+      <c r="Q65">
+        <v>70.63087130319859</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1465989141578365</v>
+      </c>
+      <c r="T65">
+        <v>1.459769278396501</v>
+      </c>
+      <c r="U65">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V65">
+        <v>0.0728931664172552</v>
+      </c>
+      <c r="W65">
+        <v>0.2406243086740345</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3644658320862759</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.208042345073485</v>
+      </c>
+      <c r="C66">
+        <v>-220.0252276581498</v>
+      </c>
+      <c r="D66">
+        <v>195.4667723418502</v>
+      </c>
+      <c r="E66">
+        <v>407.092</v>
+      </c>
+      <c r="F66">
+        <v>580.992</v>
+      </c>
+      <c r="G66">
+        <v>165.5</v>
+      </c>
+      <c r="H66">
+        <v>733.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>200.2</v>
+      </c>
+      <c r="K66">
+        <v>146.1</v>
+      </c>
+      <c r="L66">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M66">
+        <v>150.7925443768907</v>
+      </c>
+      <c r="N66">
+        <v>-96.69254437689068</v>
+      </c>
+      <c r="O66">
+        <v>-19.33850887537814</v>
+      </c>
+      <c r="P66">
+        <v>-77.35403550151254</v>
+      </c>
+      <c r="Q66">
+        <v>68.74596449848745</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1495933284399986</v>
+      </c>
+      <c r="T66">
+        <v>1.500318425018626</v>
+      </c>
+      <c r="U66">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V66">
+        <v>0.07175421069198558</v>
+      </c>
+      <c r="W66">
+        <v>0.2409199169298212</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3587710534599279</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2102497774439289</v>
+      </c>
+      <c r="C67">
+        <v>-231.6198811472725</v>
+      </c>
+      <c r="D67">
+        <v>192.9501188527274</v>
+      </c>
+      <c r="E67">
+        <v>416.17</v>
+      </c>
+      <c r="F67">
+        <v>590.0699999999999</v>
+      </c>
+      <c r="G67">
+        <v>165.5</v>
+      </c>
+      <c r="H67">
+        <v>733.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>200.2</v>
+      </c>
+      <c r="K67">
+        <v>146.1</v>
+      </c>
+      <c r="L67">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M67">
+        <v>153.1486778827796</v>
+      </c>
+      <c r="N67">
+        <v>-99.04867788277957</v>
+      </c>
+      <c r="O67">
+        <v>-19.80973557655592</v>
+      </c>
+      <c r="P67">
+        <v>-79.23894230622366</v>
+      </c>
+      <c r="Q67">
+        <v>66.86105769377633</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1527588521097129</v>
+      </c>
+      <c r="T67">
+        <v>1.543184665733444</v>
+      </c>
+      <c r="U67">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V67">
+        <v>0.07065029975826274</v>
+      </c>
+      <c r="W67">
+        <v>0.2412064295469683</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3532514987913137</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2124572098143728</v>
+      </c>
+      <c r="C68">
+        <v>-243.1505540808743</v>
+      </c>
+      <c r="D68">
+        <v>190.4974459191257</v>
+      </c>
+      <c r="E68">
+        <v>425.248</v>
+      </c>
+      <c r="F68">
+        <v>599.148</v>
+      </c>
+      <c r="G68">
+        <v>165.5</v>
+      </c>
+      <c r="H68">
+        <v>733.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>200.2</v>
+      </c>
+      <c r="K68">
+        <v>146.1</v>
+      </c>
+      <c r="L68">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M68">
+        <v>155.5048113886685</v>
+      </c>
+      <c r="N68">
+        <v>-101.4048113886685</v>
+      </c>
+      <c r="O68">
+        <v>-20.28096227773371</v>
+      </c>
+      <c r="P68">
+        <v>-81.12384911093481</v>
+      </c>
+      <c r="Q68">
+        <v>64.97615088906518</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1561105830541162</v>
+      </c>
+      <c r="T68">
+        <v>1.588572450019722</v>
+      </c>
+      <c r="U68">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V68">
+        <v>0.06957984067101632</v>
+      </c>
+      <c r="W68">
+        <v>0.2414842599635958</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3478992033550816</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2146646421848166</v>
+      </c>
+      <c r="C69">
+        <v>-254.6196556882504</v>
+      </c>
+      <c r="D69">
+        <v>188.1063443117496</v>
+      </c>
+      <c r="E69">
+        <v>434.326</v>
+      </c>
+      <c r="F69">
+        <v>608.226</v>
+      </c>
+      <c r="G69">
+        <v>165.5</v>
+      </c>
+      <c r="H69">
+        <v>733.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>200.2</v>
+      </c>
+      <c r="K69">
+        <v>146.1</v>
+      </c>
+      <c r="L69">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M69">
+        <v>157.8609448945574</v>
+      </c>
+      <c r="N69">
+        <v>-103.7609448945574</v>
+      </c>
+      <c r="O69">
+        <v>-20.75218897891149</v>
+      </c>
+      <c r="P69">
+        <v>-83.00875591564595</v>
+      </c>
+      <c r="Q69">
+        <v>63.09124408435405</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1596654492072712</v>
+      </c>
+      <c r="T69">
+        <v>1.636711009111228</v>
+      </c>
+      <c r="U69">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V69">
+        <v>0.06854133558637429</v>
+      </c>
+      <c r="W69">
+        <v>0.2417537969349509</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3427066779318714</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2168720745552604</v>
+      </c>
+      <c r="C70">
+        <v>-266.0294757367149</v>
+      </c>
+      <c r="D70">
+        <v>185.7745242632851</v>
+      </c>
+      <c r="E70">
+        <v>443.404</v>
+      </c>
+      <c r="F70">
+        <v>617.304</v>
+      </c>
+      <c r="G70">
+        <v>165.5</v>
+      </c>
+      <c r="H70">
+        <v>733.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>200.2</v>
+      </c>
+      <c r="K70">
+        <v>146.1</v>
+      </c>
+      <c r="L70">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M70">
+        <v>160.2170784004463</v>
+      </c>
+      <c r="N70">
+        <v>-106.1170784004463</v>
+      </c>
+      <c r="O70">
+        <v>-21.22341568008927</v>
+      </c>
+      <c r="P70">
+        <v>-84.89366272035707</v>
+      </c>
+      <c r="Q70">
+        <v>61.20633727964292</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1634424944949985</v>
+      </c>
+      <c r="T70">
+        <v>1.687858228145954</v>
+      </c>
+      <c r="U70">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V70">
+        <v>0.06753337476892761</v>
+      </c>
+      <c r="W70">
+        <v>0.2420154063483249</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.337666873844638</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2190795069257043</v>
+      </c>
+      <c r="C71">
+        <v>-277.3821918453605</v>
+      </c>
+      <c r="D71">
+        <v>183.4998081546396</v>
+      </c>
+      <c r="E71">
+        <v>452.4820000000001</v>
+      </c>
+      <c r="F71">
+        <v>626.3820000000001</v>
+      </c>
+      <c r="G71">
+        <v>165.5</v>
+      </c>
+      <c r="H71">
+        <v>733.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>200.2</v>
+      </c>
+      <c r="K71">
+        <v>146.1</v>
+      </c>
+      <c r="L71">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M71">
+        <v>162.5732119063353</v>
+      </c>
+      <c r="N71">
+        <v>-108.4732119063353</v>
+      </c>
+      <c r="O71">
+        <v>-21.69464238126706</v>
+      </c>
+      <c r="P71">
+        <v>-86.77856952506822</v>
+      </c>
+      <c r="Q71">
+        <v>59.32143047493177</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1674632201238694</v>
+      </c>
+      <c r="T71">
+        <v>1.742305267763566</v>
+      </c>
+      <c r="U71">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V71">
+        <v>0.06655463020705908</v>
+      </c>
+      <c r="W71">
+        <v>0.2422694328801518</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3327731510352954</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2212869392961481</v>
+      </c>
+      <c r="C72">
+        <v>-288.6798762679998</v>
+      </c>
+      <c r="D72">
+        <v>181.2801237320002</v>
+      </c>
+      <c r="E72">
+        <v>461.5600000000001</v>
+      </c>
+      <c r="F72">
+        <v>635.46</v>
+      </c>
+      <c r="G72">
+        <v>165.5</v>
+      </c>
+      <c r="H72">
+        <v>733.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>200.2</v>
+      </c>
+      <c r="K72">
+        <v>146.1</v>
+      </c>
+      <c r="L72">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M72">
+        <v>164.9293454122242</v>
+      </c>
+      <c r="N72">
+        <v>-110.8293454122242</v>
+      </c>
+      <c r="O72">
+        <v>-22.16586908244484</v>
+      </c>
+      <c r="P72">
+        <v>-88.66347632977936</v>
+      </c>
+      <c r="Q72">
+        <v>57.43652367022064</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1717519941279984</v>
+      </c>
+      <c r="T72">
+        <v>1.800382110022351</v>
+      </c>
+      <c r="U72">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V72">
+        <v>0.06560384977552967</v>
+      </c>
+      <c r="W72">
+        <v>0.2425162015110694</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3280192488776483</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2234943716665919</v>
+      </c>
+      <c r="C73">
+        <v>-299.924502189695</v>
+      </c>
+      <c r="D73">
+        <v>179.1134978103049</v>
+      </c>
+      <c r="E73">
+        <v>470.6379999999999</v>
+      </c>
+      <c r="F73">
+        <v>644.5379999999999</v>
+      </c>
+      <c r="G73">
+        <v>165.5</v>
+      </c>
+      <c r="H73">
+        <v>733.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>200.2</v>
+      </c>
+      <c r="K73">
+        <v>146.1</v>
+      </c>
+      <c r="L73">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M73">
+        <v>167.2854789181131</v>
+      </c>
+      <c r="N73">
+        <v>-113.1854789181131</v>
+      </c>
+      <c r="O73">
+        <v>-22.63709578362261</v>
+      </c>
+      <c r="P73">
+        <v>-90.54838313449045</v>
+      </c>
+      <c r="Q73">
+        <v>55.55161686550954</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1763365456496535</v>
+      </c>
+      <c r="T73">
+        <v>1.86246425174726</v>
+      </c>
+      <c r="U73">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V73">
+        <v>0.06467985189136731</v>
+      </c>
+      <c r="W73">
+        <v>0.2427560189129471</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3233992594568365</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2257018040370357</v>
+      </c>
+      <c r="C74">
+        <v>-311.1179495770918</v>
+      </c>
+      <c r="D74">
+        <v>176.9980504229081</v>
+      </c>
+      <c r="E74">
+        <v>479.716</v>
+      </c>
+      <c r="F74">
+        <v>653.616</v>
+      </c>
+      <c r="G74">
+        <v>165.5</v>
+      </c>
+      <c r="H74">
+        <v>733.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>200.2</v>
+      </c>
+      <c r="K74">
+        <v>146.1</v>
+      </c>
+      <c r="L74">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M74">
+        <v>169.641612424002</v>
+      </c>
+      <c r="N74">
+        <v>-115.541612424002</v>
+      </c>
+      <c r="O74">
+        <v>-23.1083224848004</v>
+      </c>
+      <c r="P74">
+        <v>-92.43328993920161</v>
+      </c>
+      <c r="Q74">
+        <v>53.66671006079838</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1812485651371411</v>
+      </c>
+      <c r="T74">
+        <v>1.928980832166804</v>
+      </c>
+      <c r="U74">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V74">
+        <v>0.0637815206150983</v>
+      </c>
+      <c r="W74">
+        <v>0.2429891747203281</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3189076030754915</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2279092364074796</v>
+      </c>
+      <c r="C75">
+        <v>-322.2620106190132</v>
+      </c>
+      <c r="D75">
+        <v>174.9319893809868</v>
+      </c>
+      <c r="E75">
+        <v>488.794</v>
+      </c>
+      <c r="F75">
+        <v>662.694</v>
+      </c>
+      <c r="G75">
+        <v>165.5</v>
+      </c>
+      <c r="H75">
+        <v>733.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>200.2</v>
+      </c>
+      <c r="K75">
+        <v>146.1</v>
+      </c>
+      <c r="L75">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M75">
+        <v>171.9977459298909</v>
+      </c>
+      <c r="N75">
+        <v>-117.8977459298909</v>
+      </c>
+      <c r="O75">
+        <v>-23.57954918597819</v>
+      </c>
+      <c r="P75">
+        <v>-94.31819674391275</v>
+      </c>
+      <c r="Q75">
+        <v>51.78180325608724</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1865244379199981</v>
+      </c>
+      <c r="T75">
+        <v>2.000424566691501</v>
+      </c>
+      <c r="U75">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V75">
+        <v>0.0629078011546175</v>
+      </c>
+      <c r="W75">
+        <v>0.24321594269737</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3145390057730875</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2301166687779234</v>
+      </c>
+      <c r="C76">
+        <v>-333.35839479041</v>
+      </c>
+      <c r="D76">
+        <v>172.9136052095899</v>
+      </c>
+      <c r="E76">
+        <v>497.872</v>
+      </c>
+      <c r="F76">
+        <v>671.7719999999999</v>
+      </c>
+      <c r="G76">
+        <v>165.5</v>
+      </c>
+      <c r="H76">
+        <v>733.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>200.2</v>
+      </c>
+      <c r="K76">
+        <v>146.1</v>
+      </c>
+      <c r="L76">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M76">
+        <v>174.3538794357798</v>
+      </c>
+      <c r="N76">
+        <v>-120.2538794357798</v>
+      </c>
+      <c r="O76">
+        <v>-24.05077588715596</v>
+      </c>
+      <c r="P76">
+        <v>-96.20310354862386</v>
+      </c>
+      <c r="Q76">
+        <v>49.89689645137614</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1922061470707673</v>
+      </c>
+      <c r="T76">
+        <v>2.077363973102712</v>
+      </c>
+      <c r="U76">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V76">
+        <v>0.06205769573360917</v>
+      </c>
+      <c r="W76">
+        <v>0.2434365818101675</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3102884786680458</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2323241011483673</v>
+      </c>
+      <c r="C77">
+        <v>-344.4087335697394</v>
+      </c>
+      <c r="D77">
+        <v>170.9412664302605</v>
+      </c>
+      <c r="E77">
+        <v>506.9499999999999</v>
+      </c>
+      <c r="F77">
+        <v>680.8499999999999</v>
+      </c>
+      <c r="G77">
+        <v>165.5</v>
+      </c>
+      <c r="H77">
+        <v>733.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>200.2</v>
+      </c>
+      <c r="K77">
+        <v>146.1</v>
+      </c>
+      <c r="L77">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M77">
+        <v>176.7100129416687</v>
+      </c>
+      <c r="N77">
+        <v>-122.6100129416687</v>
+      </c>
+      <c r="O77">
+        <v>-24.52200258833375</v>
+      </c>
+      <c r="P77">
+        <v>-98.08801035333499</v>
+      </c>
+      <c r="Q77">
+        <v>48.011989646665</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.198342392953598</v>
+      </c>
+      <c r="T77">
+        <v>2.160458532026821</v>
+      </c>
+      <c r="U77">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V77">
+        <v>0.06123025979049437</v>
+      </c>
+      <c r="W77">
+        <v>0.2436513372132904</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3061512989524718</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2345315335188111</v>
+      </c>
+      <c r="C78">
+        <v>-355.4145848371315</v>
+      </c>
+      <c r="D78">
+        <v>169.0134151628685</v>
+      </c>
+      <c r="E78">
+        <v>516.028</v>
+      </c>
+      <c r="F78">
+        <v>689.928</v>
+      </c>
+      <c r="G78">
+        <v>165.5</v>
+      </c>
+      <c r="H78">
+        <v>733.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>200.2</v>
+      </c>
+      <c r="K78">
+        <v>146.1</v>
+      </c>
+      <c r="L78">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M78">
+        <v>179.0661464475577</v>
+      </c>
+      <c r="N78">
+        <v>-124.9661464475577</v>
+      </c>
+      <c r="O78">
+        <v>-24.99322928951154</v>
+      </c>
+      <c r="P78">
+        <v>-99.97291715804616</v>
+      </c>
+      <c r="Q78">
+        <v>46.12708284195384</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.204989992659998</v>
+      </c>
+      <c r="T78">
+        <v>2.250477637527939</v>
+      </c>
+      <c r="U78">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V78">
+        <v>0.06042459847746154</v>
+      </c>
+      <c r="W78">
+        <v>0.2438604411584364</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3021229923873077</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.236738965889255</v>
+      </c>
+      <c r="C79">
+        <v>-366.3774369782632</v>
+      </c>
+      <c r="D79">
+        <v>167.1285630217367</v>
+      </c>
+      <c r="E79">
+        <v>525.106</v>
+      </c>
+      <c r="F79">
+        <v>699.006</v>
+      </c>
+      <c r="G79">
+        <v>165.5</v>
+      </c>
+      <c r="H79">
+        <v>733.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>200.2</v>
+      </c>
+      <c r="K79">
+        <v>146.1</v>
+      </c>
+      <c r="L79">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M79">
+        <v>181.4222799534466</v>
+      </c>
+      <c r="N79">
+        <v>-127.3222799534466</v>
+      </c>
+      <c r="O79">
+        <v>-25.46445599068932</v>
+      </c>
+      <c r="P79">
+        <v>-101.8578239627573</v>
+      </c>
+      <c r="Q79">
+        <v>44.24217603724273</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2122156445147805</v>
+      </c>
+      <c r="T79">
+        <v>2.348324491333502</v>
+      </c>
+      <c r="U79">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V79">
+        <v>0.05963986343229971</v>
+      </c>
+      <c r="W79">
+        <v>0.2440641138322798</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2981993171614985</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2389463982596988</v>
+      </c>
+      <c r="C80">
+        <v>-377.2987127166617</v>
+      </c>
+      <c r="D80">
+        <v>165.2852872833382</v>
+      </c>
+      <c r="E80">
+        <v>534.184</v>
+      </c>
+      <c r="F80">
+        <v>708.0839999999999</v>
+      </c>
+      <c r="G80">
+        <v>165.5</v>
+      </c>
+      <c r="H80">
+        <v>733.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>200.2</v>
+      </c>
+      <c r="K80">
+        <v>146.1</v>
+      </c>
+      <c r="L80">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M80">
+        <v>183.7784134593355</v>
+      </c>
+      <c r="N80">
+        <v>-129.6784134593355</v>
+      </c>
+      <c r="O80">
+        <v>-25.9356826918671</v>
+      </c>
+      <c r="P80">
+        <v>-103.7427307674684</v>
+      </c>
+      <c r="Q80">
+        <v>42.35726923253159</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2200981738109068</v>
+      </c>
+      <c r="T80">
+        <v>2.455066513666842</v>
+      </c>
+      <c r="U80">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V80">
+        <v>0.05887524979855228</v>
+      </c>
+      <c r="W80">
+        <v>0.2442625641298709</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2943762489927614</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2411538306301426</v>
+      </c>
+      <c r="C81">
+        <v>-388.1797726951716</v>
+      </c>
+      <c r="D81">
+        <v>163.4822273048285</v>
+      </c>
+      <c r="E81">
+        <v>543.2620000000001</v>
+      </c>
+      <c r="F81">
+        <v>717.162</v>
+      </c>
+      <c r="G81">
+        <v>165.5</v>
+      </c>
+      <c r="H81">
+        <v>733.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>200.2</v>
+      </c>
+      <c r="K81">
+        <v>146.1</v>
+      </c>
+      <c r="L81">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M81">
+        <v>186.1345469652244</v>
+      </c>
+      <c r="N81">
+        <v>-132.0345469652245</v>
+      </c>
+      <c r="O81">
+        <v>-26.40690939304489</v>
+      </c>
+      <c r="P81">
+        <v>-105.6276375721796</v>
+      </c>
+      <c r="Q81">
+        <v>40.47236242782043</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2287314201828549</v>
+      </c>
+      <c r="T81">
+        <v>2.571974442889074</v>
+      </c>
+      <c r="U81">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V81">
+        <v>0.05812999347198832</v>
+      </c>
+      <c r="W81">
+        <v>0.2444559903692951</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2906499673599415</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2433612630005865</v>
+      </c>
+      <c r="C82">
+        <v>-399.021918825536</v>
+      </c>
+      <c r="D82">
+        <v>161.718081174464</v>
+      </c>
+      <c r="E82">
+        <v>552.34</v>
+      </c>
+      <c r="F82">
+        <v>726.24</v>
+      </c>
+      <c r="G82">
+        <v>165.5</v>
+      </c>
+      <c r="H82">
+        <v>733.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>200.2</v>
+      </c>
+      <c r="K82">
+        <v>146.1</v>
+      </c>
+      <c r="L82">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M82">
+        <v>188.4906804711133</v>
+      </c>
+      <c r="N82">
+        <v>-134.3906804711133</v>
+      </c>
+      <c r="O82">
+        <v>-26.87813609422267</v>
+      </c>
+      <c r="P82">
+        <v>-107.5125443768907</v>
+      </c>
+      <c r="Q82">
+        <v>38.58745562310932</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2382279911919976</v>
+      </c>
+      <c r="T82">
+        <v>2.700573165033527</v>
+      </c>
+      <c r="U82">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V82">
+        <v>0.05740336855358846</v>
+      </c>
+      <c r="W82">
+        <v>0.2446445809527338</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2870168427679424</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2455686953710303</v>
+      </c>
+      <c r="C83">
+        <v>-409.8263974234204</v>
+      </c>
+      <c r="D83">
+        <v>159.9916025765796</v>
+      </c>
+      <c r="E83">
+        <v>561.418</v>
+      </c>
+      <c r="F83">
+        <v>735.318</v>
+      </c>
+      <c r="G83">
+        <v>165.5</v>
+      </c>
+      <c r="H83">
+        <v>733.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>200.2</v>
+      </c>
+      <c r="K83">
+        <v>146.1</v>
+      </c>
+      <c r="L83">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M83">
+        <v>190.8468139770023</v>
+      </c>
+      <c r="N83">
+        <v>-136.7468139770023</v>
+      </c>
+      <c r="O83">
+        <v>-27.34936279540045</v>
+      </c>
+      <c r="P83">
+        <v>-109.3974511816018</v>
+      </c>
+      <c r="Q83">
+        <v>36.70254881839818</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2487242012547343</v>
+      </c>
+      <c r="T83">
+        <v>2.842708594772134</v>
+      </c>
+      <c r="U83">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V83">
+        <v>0.05669468499119849</v>
+      </c>
+      <c r="W83">
+        <v>0.2448285149785566</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2834734249559924</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2477761277414742</v>
+      </c>
+      <c r="C84">
+        <v>-420.5944021447427</v>
+      </c>
+      <c r="D84">
+        <v>158.3015978552574</v>
+      </c>
+      <c r="E84">
+        <v>570.4960000000001</v>
+      </c>
+      <c r="F84">
+        <v>744.3960000000001</v>
+      </c>
+      <c r="G84">
+        <v>165.5</v>
+      </c>
+      <c r="H84">
+        <v>733.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>200.2</v>
+      </c>
+      <c r="K84">
+        <v>146.1</v>
+      </c>
+      <c r="L84">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M84">
+        <v>193.2029474828912</v>
+      </c>
+      <c r="N84">
+        <v>-139.1029474828912</v>
+      </c>
+      <c r="O84">
+        <v>-27.82058949657824</v>
+      </c>
+      <c r="P84">
+        <v>-111.282357986313</v>
+      </c>
+      <c r="Q84">
+        <v>34.81764201368702</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2603866568799973</v>
+      </c>
+      <c r="T84">
+        <v>3.000636850037253</v>
+      </c>
+      <c r="U84">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V84">
+        <v>0.05600328639374483</v>
+      </c>
+      <c r="W84">
+        <v>0.2450079628086276</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2800164319687242</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.249983560111918</v>
+      </c>
+      <c r="C85">
+        <v>-431.3270767378477</v>
+      </c>
+      <c r="D85">
+        <v>156.6469232621523</v>
+      </c>
+      <c r="E85">
+        <v>579.5740000000001</v>
+      </c>
+      <c r="F85">
+        <v>753.474</v>
+      </c>
+      <c r="G85">
+        <v>165.5</v>
+      </c>
+      <c r="H85">
+        <v>733.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>200.2</v>
+      </c>
+      <c r="K85">
+        <v>146.1</v>
+      </c>
+      <c r="L85">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M85">
+        <v>195.5590809887801</v>
+      </c>
+      <c r="N85">
+        <v>-141.4590809887801</v>
+      </c>
+      <c r="O85">
+        <v>-28.29181619775602</v>
+      </c>
+      <c r="P85">
+        <v>-113.1672647910241</v>
+      </c>
+      <c r="Q85">
+        <v>32.93273520897591</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2734211661082325</v>
+      </c>
+      <c r="T85">
+        <v>3.177144900039444</v>
+      </c>
+      <c r="U85">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V85">
+        <v>0.05532854800345876</v>
+      </c>
+      <c r="W85">
+        <v>0.2451830865946006</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2766427400172938</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2521909924823618</v>
+      </c>
+      <c r="C86">
+        <v>-442.0255176248634</v>
+      </c>
+      <c r="D86">
+        <v>155.0264823751365</v>
+      </c>
+      <c r="E86">
+        <v>588.6519999999999</v>
+      </c>
+      <c r="F86">
+        <v>762.5519999999999</v>
+      </c>
+      <c r="G86">
+        <v>165.5</v>
+      </c>
+      <c r="H86">
+        <v>733.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>200.2</v>
+      </c>
+      <c r="K86">
+        <v>146.1</v>
+      </c>
+      <c r="L86">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M86">
+        <v>197.915214494669</v>
+      </c>
+      <c r="N86">
+        <v>-143.815214494669</v>
+      </c>
+      <c r="O86">
+        <v>-28.7630428989338</v>
+      </c>
+      <c r="P86">
+        <v>-115.0521715957352</v>
+      </c>
+      <c r="Q86">
+        <v>31.04782840426481</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2880849889899969</v>
+      </c>
+      <c r="T86">
+        <v>3.375716456291908</v>
+      </c>
+      <c r="U86">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V86">
+        <v>0.0546698748129414</v>
+      </c>
+      <c r="W86">
+        <v>0.2453540407666218</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2733493740647071</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2543984248528057</v>
+      </c>
+      <c r="C87">
+        <v>-452.6907763244785</v>
+      </c>
+      <c r="D87">
+        <v>153.4392236755214</v>
+      </c>
+      <c r="E87">
+        <v>597.73</v>
+      </c>
+      <c r="F87">
+        <v>771.63</v>
+      </c>
+      <c r="G87">
+        <v>165.5</v>
+      </c>
+      <c r="H87">
+        <v>733.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>200.2</v>
+      </c>
+      <c r="K87">
+        <v>146.1</v>
+      </c>
+      <c r="L87">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M87">
+        <v>200.2713480005579</v>
+      </c>
+      <c r="N87">
+        <v>-146.1713480005579</v>
+      </c>
+      <c r="O87">
+        <v>-29.23426960011159</v>
+      </c>
+      <c r="P87">
+        <v>-116.9370784004464</v>
+      </c>
+      <c r="Q87">
+        <v>29.16292159955364</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3047039882559967</v>
+      </c>
+      <c r="T87">
+        <v>3.600764220044702</v>
+      </c>
+      <c r="U87">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V87">
+        <v>0.05402669981514208</v>
+      </c>
+      <c r="W87">
+        <v>0.2455209724875367</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2701334990757104</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2566058572232495</v>
+      </c>
+      <c r="C88">
+        <v>-463.3238617273929</v>
+      </c>
+      <c r="D88">
+        <v>151.8841382726071</v>
+      </c>
+      <c r="E88">
+        <v>606.808</v>
+      </c>
+      <c r="F88">
+        <v>780.708</v>
+      </c>
+      <c r="G88">
+        <v>165.5</v>
+      </c>
+      <c r="H88">
+        <v>733.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>200.2</v>
+      </c>
+      <c r="K88">
+        <v>146.1</v>
+      </c>
+      <c r="L88">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M88">
+        <v>202.6274815064468</v>
+      </c>
+      <c r="N88">
+        <v>-148.5274815064468</v>
+      </c>
+      <c r="O88">
+        <v>-29.70549630128937</v>
+      </c>
+      <c r="P88">
+        <v>-118.8219852051575</v>
+      </c>
+      <c r="Q88">
+        <v>27.27801479484253</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3236971302742822</v>
+      </c>
+      <c r="T88">
+        <v>3.857961664333609</v>
+      </c>
+      <c r="U88">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V88">
+        <v>0.05339848237543113</v>
+      </c>
+      <c r="W88">
+        <v>0.245684022075407</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2669924118771557</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2588132895936934</v>
+      </c>
+      <c r="C89">
+        <v>-473.925742234789</v>
+      </c>
+      <c r="D89">
+        <v>150.3602577652109</v>
+      </c>
+      <c r="E89">
+        <v>615.886</v>
+      </c>
+      <c r="F89">
+        <v>789.7859999999999</v>
+      </c>
+      <c r="G89">
+        <v>165.5</v>
+      </c>
+      <c r="H89">
+        <v>733.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>200.2</v>
+      </c>
+      <c r="K89">
+        <v>146.1</v>
+      </c>
+      <c r="L89">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M89">
+        <v>204.9836150123357</v>
+      </c>
+      <c r="N89">
+        <v>-150.8836150123358</v>
+      </c>
+      <c r="O89">
+        <v>-30.17672300246715</v>
+      </c>
+      <c r="P89">
+        <v>-120.7068920098686</v>
+      </c>
+      <c r="Q89">
+        <v>25.3931079901314</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3456122941415347</v>
+      </c>
+      <c r="T89">
+        <v>4.154727946205425</v>
+      </c>
+      <c r="U89">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V89">
+        <v>0.05278470671594342</v>
+      </c>
+      <c r="W89">
+        <v>0.2458433233968895</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2639235335797171</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2610207219641372</v>
+      </c>
+      <c r="C90">
+        <v>-484.4973477693474</v>
+      </c>
+      <c r="D90">
+        <v>148.8666522306525</v>
+      </c>
+      <c r="E90">
+        <v>624.9639999999999</v>
+      </c>
+      <c r="F90">
+        <v>798.8639999999999</v>
+      </c>
+      <c r="G90">
+        <v>165.5</v>
+      </c>
+      <c r="H90">
+        <v>733.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>200.2</v>
+      </c>
+      <c r="K90">
+        <v>146.1</v>
+      </c>
+      <c r="L90">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M90">
+        <v>207.3397485182247</v>
+      </c>
+      <c r="N90">
+        <v>-153.2397485182247</v>
+      </c>
+      <c r="O90">
+        <v>-30.64794970364494</v>
+      </c>
+      <c r="P90">
+        <v>-122.5917988145797</v>
+      </c>
+      <c r="Q90">
+        <v>23.50820118542026</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3711799853199959</v>
+      </c>
+      <c r="T90">
+        <v>4.500955275055878</v>
+      </c>
+      <c r="U90">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V90">
+        <v>0.05218488050326225</v>
+      </c>
+      <c r="W90">
+        <v>0.2459990042337928</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2609244025163112</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.263228154334581</v>
+      </c>
+      <c r="C91">
+        <v>-495.0395716675828</v>
+      </c>
+      <c r="D91">
+        <v>147.4024283324172</v>
+      </c>
+      <c r="E91">
+        <v>634.042</v>
+      </c>
+      <c r="F91">
+        <v>807.942</v>
+      </c>
+      <c r="G91">
+        <v>165.5</v>
+      </c>
+      <c r="H91">
+        <v>733.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>200.2</v>
+      </c>
+      <c r="K91">
+        <v>146.1</v>
+      </c>
+      <c r="L91">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M91">
+        <v>209.6958820241136</v>
+      </c>
+      <c r="N91">
+        <v>-155.5958820241136</v>
+      </c>
+      <c r="O91">
+        <v>-31.11917640482272</v>
+      </c>
+      <c r="P91">
+        <v>-124.4767056192909</v>
+      </c>
+      <c r="Q91">
+        <v>21.62329438070913</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4013963476218137</v>
+      </c>
+      <c r="T91">
+        <v>4.910133027333685</v>
+      </c>
+      <c r="U91">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V91">
+        <v>0.05159853353131547</v>
+      </c>
+      <c r="W91">
+        <v>0.2461511866249231</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2579926676565774</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2654355867050249</v>
+      </c>
+      <c r="C92">
+        <v>-505.5532724615914</v>
+      </c>
+      <c r="D92">
+        <v>145.9667275384086</v>
+      </c>
+      <c r="E92">
+        <v>643.12</v>
+      </c>
+      <c r="F92">
+        <v>817.02</v>
+      </c>
+      <c r="G92">
+        <v>165.5</v>
+      </c>
+      <c r="H92">
+        <v>733.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>200.2</v>
+      </c>
+      <c r="K92">
+        <v>146.1</v>
+      </c>
+      <c r="L92">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M92">
+        <v>212.0520155300025</v>
+      </c>
+      <c r="N92">
+        <v>-157.9520155300025</v>
+      </c>
+      <c r="O92">
+        <v>-31.5904031060005</v>
+      </c>
+      <c r="P92">
+        <v>-126.361612424002</v>
+      </c>
+      <c r="Q92">
+        <v>19.73838757599799</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4376559823839952</v>
+      </c>
+      <c r="T92">
+        <v>5.401146330067054</v>
+      </c>
+      <c r="U92">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V92">
+        <v>0.05102521649207864</v>
+      </c>
+      <c r="W92">
+        <v>0.2462999871851393</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2551260824603931</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2676430190754687</v>
+      </c>
+      <c r="C93">
+        <v>-516.0392755576778</v>
+      </c>
+      <c r="D93">
+        <v>144.5587244423221</v>
+      </c>
+      <c r="E93">
+        <v>652.198</v>
+      </c>
+      <c r="F93">
+        <v>826.098</v>
+      </c>
+      <c r="G93">
+        <v>165.5</v>
+      </c>
+      <c r="H93">
+        <v>733.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>200.2</v>
+      </c>
+      <c r="K93">
+        <v>146.1</v>
+      </c>
+      <c r="L93">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M93">
+        <v>214.4081490358914</v>
+      </c>
+      <c r="N93">
+        <v>-160.3081490358914</v>
+      </c>
+      <c r="O93">
+        <v>-32.06162980717829</v>
+      </c>
+      <c r="P93">
+        <v>-128.2465192287131</v>
+      </c>
+      <c r="Q93">
+        <v>17.85348077128685</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4819733137599946</v>
+      </c>
+      <c r="T93">
+        <v>6.001273700074505</v>
+      </c>
+      <c r="U93">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V93">
+        <v>0.05046449982733053</v>
+      </c>
+      <c r="W93">
+        <v>0.2464455174033728</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2523224991366526</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2698504514459125</v>
+      </c>
+      <c r="C94">
+        <v>-526.4983748187575</v>
+      </c>
+      <c r="D94">
+        <v>143.1776251812426</v>
+      </c>
+      <c r="E94">
+        <v>661.2760000000001</v>
+      </c>
+      <c r="F94">
+        <v>835.176</v>
+      </c>
+      <c r="G94">
+        <v>165.5</v>
+      </c>
+      <c r="H94">
+        <v>733.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>200.2</v>
+      </c>
+      <c r="K94">
+        <v>146.1</v>
+      </c>
+      <c r="L94">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M94">
+        <v>216.7642825417803</v>
+      </c>
+      <c r="N94">
+        <v>-162.6642825417804</v>
+      </c>
+      <c r="O94">
+        <v>-32.53285650835607</v>
+      </c>
+      <c r="P94">
+        <v>-130.1314260334243</v>
+      </c>
+      <c r="Q94">
+        <v>15.96857396657572</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5373699779799941</v>
+      </c>
+      <c r="T94">
+        <v>6.75143291258382</v>
+      </c>
+      <c r="U94">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V94">
+        <v>0.04991597265529432</v>
+      </c>
+      <c r="W94">
+        <v>0.2465878839212098</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2495798632764715</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2720578838163564</v>
+      </c>
+      <c r="C95">
+        <v>-536.9313340569076</v>
+      </c>
+      <c r="D95">
+        <v>141.8226659430923</v>
+      </c>
+      <c r="E95">
+        <v>670.354</v>
+      </c>
+      <c r="F95">
+        <v>844.254</v>
+      </c>
+      <c r="G95">
+        <v>165.5</v>
+      </c>
+      <c r="H95">
+        <v>733.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>200.2</v>
+      </c>
+      <c r="K95">
+        <v>146.1</v>
+      </c>
+      <c r="L95">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M95">
+        <v>219.1204160476693</v>
+      </c>
+      <c r="N95">
+        <v>-165.0204160476693</v>
+      </c>
+      <c r="O95">
+        <v>-33.00408320953385</v>
+      </c>
+      <c r="P95">
+        <v>-132.0163328381354</v>
+      </c>
+      <c r="Q95">
+        <v>14.08366716186458</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6085942605485648</v>
+      </c>
+      <c r="T95">
+        <v>7.715923328667224</v>
+      </c>
+      <c r="U95">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V95">
+        <v>0.04937924176652771</v>
+      </c>
+      <c r="W95">
+        <v>0.246727188793502</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2468962088326385</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2742653161868002</v>
+      </c>
+      <c r="C96">
+        <v>-547.3388884419666</v>
+      </c>
+      <c r="D96">
+        <v>140.4931115580335</v>
+      </c>
+      <c r="E96">
+        <v>679.432</v>
+      </c>
+      <c r="F96">
+        <v>853.332</v>
+      </c>
+      <c r="G96">
+        <v>165.5</v>
+      </c>
+      <c r="H96">
+        <v>733.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>200.2</v>
+      </c>
+      <c r="K96">
+        <v>146.1</v>
+      </c>
+      <c r="L96">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M96">
+        <v>221.4765495535582</v>
+      </c>
+      <c r="N96">
+        <v>-167.3765495535582</v>
+      </c>
+      <c r="O96">
+        <v>-33.47530991071164</v>
+      </c>
+      <c r="P96">
+        <v>-133.9012396428465</v>
+      </c>
+      <c r="Q96">
+        <v>12.19876035715345</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7035599706399924</v>
+      </c>
+      <c r="T96">
+        <v>9.001910550111763</v>
+      </c>
+      <c r="U96">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V96">
+        <v>0.04885393068390508</v>
+      </c>
+      <c r="W96">
+        <v>0.2468635297323412</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2442696534195253</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2764727485572441</v>
+      </c>
+      <c r="C97">
+        <v>-557.7217458316344</v>
+      </c>
+      <c r="D97">
+        <v>139.1882541683656</v>
+      </c>
+      <c r="E97">
+        <v>688.51</v>
+      </c>
+      <c r="F97">
+        <v>862.41</v>
+      </c>
+      <c r="G97">
+        <v>165.5</v>
+      </c>
+      <c r="H97">
+        <v>733.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>200.2</v>
+      </c>
+      <c r="K97">
+        <v>146.1</v>
+      </c>
+      <c r="L97">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M97">
+        <v>223.8326830594471</v>
+      </c>
+      <c r="N97">
+        <v>-169.7326830594471</v>
+      </c>
+      <c r="O97">
+        <v>-33.94653661188942</v>
+      </c>
+      <c r="P97">
+        <v>-135.7861464475577</v>
+      </c>
+      <c r="Q97">
+        <v>10.31385355244234</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8365119647679913</v>
+      </c>
+      <c r="T97">
+        <v>10.80229266013412</v>
+      </c>
+      <c r="U97">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V97">
+        <v>0.04833967878196924</v>
+      </c>
+      <c r="W97">
+        <v>0.2469970003356259</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2416983939098462</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2786801809276879</v>
+      </c>
+      <c r="C98">
+        <v>-568.0805880281367</v>
+      </c>
+      <c r="D98">
+        <v>137.9074119718632</v>
+      </c>
+      <c r="E98">
+        <v>697.588</v>
+      </c>
+      <c r="F98">
+        <v>871.4879999999999</v>
+      </c>
+      <c r="G98">
+        <v>165.5</v>
+      </c>
+      <c r="H98">
+        <v>733.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>200.2</v>
+      </c>
+      <c r="K98">
+        <v>146.1</v>
+      </c>
+      <c r="L98">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M98">
+        <v>226.188816565336</v>
+      </c>
+      <c r="N98">
+        <v>-172.088816565336</v>
+      </c>
+      <c r="O98">
+        <v>-34.4177633130672</v>
+      </c>
+      <c r="P98">
+        <v>-137.6710532522688</v>
+      </c>
+      <c r="Q98">
+        <v>8.428946747731203</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.035939955959987</v>
+      </c>
+      <c r="T98">
+        <v>13.50286582516762</v>
+      </c>
+      <c r="U98">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V98">
+        <v>0.04783614046132373</v>
+      </c>
+      <c r="W98">
+        <v>0.2471276903013421</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2391807023066186</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2808876132981317</v>
+      </c>
+      <c r="C99">
+        <v>-578.4160719661353</v>
+      </c>
+      <c r="D99">
+        <v>136.6499280338646</v>
+      </c>
+      <c r="E99">
+        <v>706.6659999999999</v>
+      </c>
+      <c r="F99">
+        <v>880.5659999999999</v>
+      </c>
+      <c r="G99">
+        <v>165.5</v>
+      </c>
+      <c r="H99">
+        <v>733.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>200.2</v>
+      </c>
+      <c r="K99">
+        <v>146.1</v>
+      </c>
+      <c r="L99">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M99">
+        <v>228.5449500712249</v>
+      </c>
+      <c r="N99">
+        <v>-174.4449500712249</v>
+      </c>
+      <c r="O99">
+        <v>-34.88899001424498</v>
+      </c>
+      <c r="P99">
+        <v>-139.5559600569799</v>
+      </c>
+      <c r="Q99">
+        <v>6.544039943020067</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.368319941279982</v>
+      </c>
+      <c r="T99">
+        <v>18.0038211002235</v>
+      </c>
+      <c r="U99">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V99">
+        <v>0.04734298437409359</v>
+      </c>
+      <c r="W99">
+        <v>0.2472556856285899</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2367149218704679</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2830950456685756</v>
+      </c>
+      <c r="C100">
+        <v>-588.7288308362354</v>
+      </c>
+      <c r="D100">
+        <v>135.4151691637645</v>
+      </c>
+      <c r="E100">
+        <v>715.7439999999999</v>
+      </c>
+      <c r="F100">
+        <v>889.6439999999999</v>
+      </c>
+      <c r="G100">
+        <v>165.5</v>
+      </c>
+      <c r="H100">
+        <v>733.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>200.2</v>
+      </c>
+      <c r="K100">
+        <v>146.1</v>
+      </c>
+      <c r="L100">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M100">
+        <v>230.9010835771138</v>
+      </c>
+      <c r="N100">
+        <v>-176.8010835771138</v>
+      </c>
+      <c r="O100">
+        <v>-35.36021671542277</v>
+      </c>
+      <c r="P100">
+        <v>-141.4408668616911</v>
+      </c>
+      <c r="Q100">
+        <v>4.659133138308931</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.033079911919974</v>
+      </c>
+      <c r="T100">
+        <v>27.00573165033524</v>
+      </c>
+      <c r="U100">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V100">
+        <v>0.04685989269680692</v>
+      </c>
+      <c r="W100">
+        <v>0.2473810688063021</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2342994634840346</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2853024780390194</v>
+      </c>
+      <c r="C101">
+        <v>-599.0194751481272</v>
+      </c>
+      <c r="D101">
+        <v>134.2025248518728</v>
+      </c>
+      <c r="E101">
+        <v>724.822</v>
+      </c>
+      <c r="F101">
+        <v>898.722</v>
+      </c>
+      <c r="G101">
+        <v>165.5</v>
+      </c>
+      <c r="H101">
+        <v>733.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>200.2</v>
+      </c>
+      <c r="K101">
+        <v>146.1</v>
+      </c>
+      <c r="L101">
+        <v>54.09999999999999</v>
+      </c>
+      <c r="M101">
+        <v>233.2572170830028</v>
+      </c>
+      <c r="N101">
+        <v>-179.1572170830028</v>
+      </c>
+      <c r="O101">
+        <v>-35.83144341660056</v>
+      </c>
+      <c r="P101">
+        <v>-143.3257736664022</v>
+      </c>
+      <c r="Q101">
+        <v>2.774226333597795</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.027359823839947</v>
+      </c>
+      <c r="T101">
+        <v>54.01146330067048</v>
+      </c>
+      <c r="U101">
+        <v>0.2595432370443839</v>
+      </c>
+      <c r="V101">
+        <v>0.04638656044734422</v>
+      </c>
+      <c r="W101">
+        <v>0.2475039189905252</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2319328022367211</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_oil_gas_distribution.xlsx
@@ -647,10 +647,10 @@
         <v>0.0321177982014033</v>
       </c>
       <c r="X2">
-        <v>0.09272312987667519</v>
+        <v>0.09271043429036005</v>
       </c>
       <c r="Y2">
-        <v>-0.06060533167527189</v>
+        <v>-0.06059263608895675</v>
       </c>
       <c r="Z2">
         <v>0.3184725912803859</v>
@@ -659,10 +659,10 @@
         <v>0.02266624395577262</v>
       </c>
       <c r="AB2">
-        <v>0.08464134117562906</v>
+        <v>0.084631953407227</v>
       </c>
       <c r="AC2">
-        <v>-0.06197509721985644</v>
+        <v>-0.06196570945145437</v>
       </c>
       <c r="AD2">
         <v>211.8</v>
@@ -781,10 +781,10 @@
         <v>0.0321177982014033</v>
       </c>
       <c r="X3">
-        <v>0.09272312987667519</v>
+        <v>0.09271043429036005</v>
       </c>
       <c r="Y3">
-        <v>-0.06060533167527189</v>
+        <v>-0.06059263608895675</v>
       </c>
       <c r="Z3">
         <v>0.3184725912803859</v>
@@ -793,10 +793,10 @@
         <v>0.02266624395577262</v>
       </c>
       <c r="AB3">
-        <v>0.08464134117562906</v>
+        <v>0.084631953407227</v>
       </c>
       <c r="AC3">
-        <v>-0.06197509721985644</v>
+        <v>-0.06196570945145437</v>
       </c>
       <c r="AD3">
         <v>211.8</v>
@@ -1133,49 +1133,49 @@
         <v>3.54777070063694</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>13.1143584380361</v>
       </c>
       <c r="G2">
         <v>1.05794205794206</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.609065934065934</v>
       </c>
       <c r="I2">
         <v>0.260548652970845</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K2">
         <v>601.1</v>
       </c>
       <c r="L2">
-        <v>851.624236580582</v>
+        <v>730.2996745282881</v>
       </c>
       <c r="M2">
         <v>633.8</v>
       </c>
       <c r="N2">
-        <v>672.5242365805821</v>
+        <v>673.134674528288</v>
       </c>
       <c r="O2">
         <v>211.8</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>121.935</v>
       </c>
       <c r="Q2">
-        <v>0.0846413411756291</v>
+        <v>0.084631953407227</v>
       </c>
       <c r="R2">
-        <v>0.0824048399419491</v>
+        <v>0.0823628053357192</v>
       </c>
       <c r="S2">
         <v>0.0617047822134061</v>
       </c>
       <c r="T2">
-        <v>0.0540247822134061</v>
+        <v>0.0529047822134061</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.09272312987667521</v>
+        <v>0.09271043429035999</v>
       </c>
       <c r="X2">
-        <v>0.0824048399419491</v>
+        <v>0.0875612800043627</v>
       </c>
       <c r="Y2">
         <v>0.725689499165987</v>
       </c>
       <c r="Z2">
-        <v>0.566112022670692</v>
+        <v>0.646033719988907</v>
       </c>
       <c r="AA2">
         <v>211.8</v>
@@ -1230,7 +1230,7 @@
         <v>601.1</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823122</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0824048399419491</v>
+        <v>0.08239493608629718</v>
       </c>
       <c r="C2">
-        <v>851.6242365805819</v>
+        <v>851.6436549871778</v>
       </c>
       <c r="D2">
-        <v>672.5242365805818</v>
+        <v>672.5436549871778</v>
       </c>
       <c r="E2">
         <v>-211.8</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0824048399419491</v>
+        <v>0.08239493608629718</v>
       </c>
       <c r="T2">
         <v>0.5661120226706918</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08241387808419927</v>
+        <v>0.08239279403625864</v>
       </c>
       <c r="C3">
-        <v>843.3292238543983</v>
+        <v>843.5540239995756</v>
       </c>
       <c r="D3">
-        <v>672.3582238543983</v>
+        <v>672.5830239995756</v>
       </c>
       <c r="E3">
         <v>-203.671</v>
@@ -1533,37 +1533,37 @@
         <v>105.75</v>
       </c>
       <c r="M3">
-        <v>0.5489593182659724</v>
+        <v>0.5375787182659725</v>
       </c>
       <c r="N3">
-        <v>105.201040681734</v>
+        <v>105.212421281734</v>
       </c>
       <c r="O3">
-        <v>21.0402081363468</v>
+        <v>21.0424842563468</v>
       </c>
       <c r="P3">
-        <v>84.16083254538719</v>
+        <v>84.1699370253872</v>
       </c>
       <c r="Q3">
-        <v>228.6608325453872</v>
+        <v>228.6699370253872</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08270063662834869</v>
+        <v>0.08269065274153999</v>
       </c>
       <c r="T3">
         <v>0.5706866652781318</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>192.6372255307337</v>
+        <v>196.7153765705418</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08242291622644943</v>
+        <v>0.08239065198622011</v>
       </c>
       <c r="C4">
-        <v>835.0342930685296</v>
+        <v>835.4643976213687</v>
       </c>
       <c r="D4">
-        <v>672.1922930685296</v>
+        <v>672.6223976213687</v>
       </c>
       <c r="E4">
         <v>-195.542</v>
@@ -1615,37 +1615,37 @@
         <v>105.75</v>
       </c>
       <c r="M4">
-        <v>1.097918636531945</v>
+        <v>1.075157436531945</v>
       </c>
       <c r="N4">
-        <v>104.652081363468</v>
+        <v>104.674842563468</v>
       </c>
       <c r="O4">
-        <v>20.93041627269361</v>
+        <v>20.93496851269361</v>
       </c>
       <c r="P4">
-        <v>83.72166509077442</v>
+        <v>83.73987405077443</v>
       </c>
       <c r="Q4">
-        <v>228.2216650907744</v>
+        <v>228.2398740507744</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08300246998181765</v>
+        <v>0.08299240443056326</v>
       </c>
       <c r="T4">
         <v>0.5753546679387848</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>96.31861276536686</v>
+        <v>98.35768828527091</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08243195436869959</v>
+        <v>0.08238850993618156</v>
       </c>
       <c r="C5">
-        <v>826.7394441623242</v>
+        <v>827.3747758533677</v>
       </c>
       <c r="D5">
-        <v>672.0264441623242</v>
+        <v>672.6617758533677</v>
       </c>
       <c r="E5">
         <v>-187.413</v>
@@ -1697,37 +1697,37 @@
         <v>105.75</v>
       </c>
       <c r="M5">
-        <v>1.646877954797917</v>
+        <v>1.612736154797917</v>
       </c>
       <c r="N5">
-        <v>104.1031220452021</v>
+        <v>104.1372638452021</v>
       </c>
       <c r="O5">
-        <v>20.82062440904041</v>
+        <v>20.82745276904041</v>
       </c>
       <c r="P5">
-        <v>83.28249763616165</v>
+        <v>83.30981107616165</v>
       </c>
       <c r="Q5">
-        <v>227.7824976361617</v>
+        <v>227.8098110761617</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08331052670339938</v>
+        <v>0.08330037780389628</v>
       </c>
       <c r="T5">
         <v>0.5801189180769769</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.21240851024459</v>
+        <v>65.57179219018062</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08244099251094975</v>
+        <v>0.08238636788614304</v>
       </c>
       <c r="C6">
-        <v>818.4446770751912</v>
+        <v>819.2851586963808</v>
       </c>
       <c r="D6">
-        <v>671.8606770751911</v>
+        <v>672.7011586963807</v>
       </c>
       <c r="E6">
         <v>-179.284</v>
@@ -1779,37 +1779,37 @@
         <v>105.75</v>
       </c>
       <c r="M6">
-        <v>2.19583727306389</v>
+        <v>2.15031487306389</v>
       </c>
       <c r="N6">
-        <v>103.5541627269361</v>
+        <v>103.5996851269361</v>
       </c>
       <c r="O6">
-        <v>20.71083254538722</v>
+        <v>20.71993702538722</v>
       </c>
       <c r="P6">
-        <v>82.84333018154886</v>
+        <v>82.87974810154887</v>
       </c>
       <c r="Q6">
-        <v>227.3433301815489</v>
+        <v>227.3797481015489</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.0836250012733474</v>
+        <v>0.08361476728917375</v>
       </c>
       <c r="T6">
         <v>0.5849824234263816</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.15930638268343</v>
+        <v>49.17884414263545</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08245003065319989</v>
+        <v>0.0823842258361045</v>
       </c>
       <c r="C7">
-        <v>810.1499917465991</v>
+        <v>811.195546151219</v>
       </c>
       <c r="D7">
-        <v>671.694991746599</v>
+        <v>672.740546151219</v>
       </c>
       <c r="E7">
         <v>-171.155</v>
@@ -1861,37 +1861,37 @@
         <v>105.75</v>
       </c>
       <c r="M7">
-        <v>2.744796591329862</v>
+        <v>2.687893591329863</v>
       </c>
       <c r="N7">
-        <v>103.0052034086701</v>
+        <v>103.0621064086701</v>
       </c>
       <c r="O7">
-        <v>20.60104068173402</v>
+        <v>20.61242128173402</v>
       </c>
       <c r="P7">
-        <v>82.40416272693609</v>
+        <v>82.44968512693609</v>
       </c>
       <c r="Q7">
-        <v>226.9041627269361</v>
+        <v>226.9496851269361</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08394609636055747</v>
+        <v>0.08393577550045705</v>
       </c>
       <c r="T7">
         <v>0.5899483183620893</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.52744510614674</v>
+        <v>39.34307531410835</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08245906879545008</v>
+        <v>0.08238208378606597</v>
       </c>
       <c r="C8">
-        <v>801.8553881160753</v>
+        <v>803.1059382186919</v>
       </c>
       <c r="D8">
-        <v>671.5293881160753</v>
+        <v>672.7799382186919</v>
       </c>
       <c r="E8">
         <v>-163.026</v>
@@ -1943,37 +1943,37 @@
         <v>105.75</v>
       </c>
       <c r="M8">
-        <v>3.293755909595834</v>
+        <v>3.225472309595834</v>
       </c>
       <c r="N8">
-        <v>102.4562440904041</v>
+        <v>102.5245276904041</v>
       </c>
       <c r="O8">
-        <v>20.49124881808083</v>
+        <v>20.50490553808083</v>
       </c>
       <c r="P8">
-        <v>81.96499527232331</v>
+        <v>82.01962215232331</v>
       </c>
       <c r="Q8">
-        <v>226.4649952723233</v>
+        <v>226.5196221523233</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08427402325813374</v>
+        <v>0.08426361367368257</v>
       </c>
       <c r="T8">
         <v>0.5950198706368549</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.10620425512229</v>
+        <v>32.78589609509031</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08246810693770022</v>
+        <v>0.08237994173602745</v>
       </c>
       <c r="C9">
-        <v>793.5608661232095</v>
+        <v>795.01633489961</v>
       </c>
       <c r="D9">
-        <v>671.3638661232095</v>
+        <v>672.81933489961</v>
       </c>
       <c r="E9">
         <v>-154.897</v>
@@ -2025,37 +2025,37 @@
         <v>105.75</v>
       </c>
       <c r="M9">
-        <v>3.842715227861807</v>
+        <v>3.763051027861807</v>
       </c>
       <c r="N9">
-        <v>101.9072847721382</v>
+        <v>101.9869489721382</v>
       </c>
       <c r="O9">
-        <v>20.38145695442763</v>
+        <v>20.39738979442764</v>
       </c>
       <c r="P9">
-        <v>81.52582781771054</v>
+        <v>81.58955917771053</v>
       </c>
       <c r="Q9">
-        <v>226.0258278177105</v>
+        <v>226.0895591777105</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08460900234705571</v>
+        <v>0.08459850213020326</v>
       </c>
       <c r="T9">
         <v>0.6002004885519379</v>
       </c>
       <c r="U9">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.51960364724768</v>
+        <v>28.10219665293454</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08247714507995041</v>
+        <v>0.08237779968598891</v>
       </c>
       <c r="C10">
-        <v>785.2664257076475</v>
+        <v>786.9267361947843</v>
       </c>
       <c r="D10">
-        <v>671.1984257076475</v>
+        <v>672.8587361947843</v>
       </c>
       <c r="E10">
         <v>-146.768</v>
@@ -2107,37 +2107,37 @@
         <v>105.75</v>
       </c>
       <c r="M10">
-        <v>4.39167454612778</v>
+        <v>4.30062974612778</v>
       </c>
       <c r="N10">
-        <v>101.3583254538722</v>
+        <v>101.4493702538722</v>
       </c>
       <c r="O10">
-        <v>20.27166509077444</v>
+        <v>20.28987405077444</v>
       </c>
       <c r="P10">
-        <v>81.08666036309776</v>
+        <v>81.15949620309775</v>
       </c>
       <c r="Q10">
-        <v>225.5866603630978</v>
+        <v>225.6594962030977</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08495126359008469</v>
+        <v>0.08494067077056133</v>
       </c>
       <c r="T10">
         <v>0.6054937285956096</v>
       </c>
       <c r="U10">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.07965319134172</v>
+        <v>24.58942207131772</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08248618322220057</v>
+        <v>0.08237565763595037</v>
       </c>
       <c r="C11">
-        <v>776.9720668090974</v>
+        <v>778.8371421050251</v>
       </c>
       <c r="D11">
-        <v>671.0330668090974</v>
+        <v>672.898142105025</v>
       </c>
       <c r="E11">
         <v>-138.639</v>
@@ -2189,37 +2189,37 @@
         <v>105.75</v>
       </c>
       <c r="M11">
-        <v>4.940633864393751</v>
+        <v>4.838208464393752</v>
       </c>
       <c r="N11">
-        <v>100.8093661356062</v>
+        <v>100.9117915356062</v>
       </c>
       <c r="O11">
-        <v>20.16187322712125</v>
+        <v>20.18235830712125</v>
       </c>
       <c r="P11">
-        <v>80.64749290848498</v>
+        <v>80.72943322848498</v>
       </c>
       <c r="Q11">
-        <v>225.147492908485</v>
+        <v>225.229433228485</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08530104705823519</v>
+        <v>0.08529035960081739</v>
       </c>
       <c r="T11">
         <v>0.610903303585296</v>
       </c>
       <c r="U11">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.40413617008153</v>
+        <v>21.85726406339354</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08249522136445073</v>
+        <v>0.08237351558591186</v>
       </c>
       <c r="C12">
-        <v>768.6777893673252</v>
+        <v>770.7475526311428</v>
       </c>
       <c r="D12">
-        <v>670.8677893673253</v>
+        <v>672.9375526311427</v>
       </c>
       <c r="E12">
         <v>-130.51</v>
@@ -2271,37 +2271,37 @@
         <v>105.75</v>
       </c>
       <c r="M12">
-        <v>5.489593182659725</v>
+        <v>5.375787182659725</v>
       </c>
       <c r="N12">
-        <v>100.2604068173403</v>
+        <v>100.3742128173403</v>
       </c>
       <c r="O12">
-        <v>20.05208136346805</v>
+        <v>20.07484256346805</v>
       </c>
       <c r="P12">
-        <v>80.20832545387221</v>
+        <v>80.2993702538722</v>
       </c>
       <c r="Q12">
-        <v>224.7083254538722</v>
+        <v>224.7993702538722</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08565860349234458</v>
+        <v>0.08564781929396804</v>
       </c>
       <c r="T12">
         <v>0.6164330913525312</v>
       </c>
       <c r="U12">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.26372255307337</v>
+        <v>19.67153765705418</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08250425950670087</v>
+        <v>0.08237137353587332</v>
       </c>
       <c r="C13">
-        <v>760.3835933221568</v>
+        <v>762.6579677739493</v>
       </c>
       <c r="D13">
-        <v>670.7025933221568</v>
+        <v>672.9769677739492</v>
       </c>
       <c r="E13">
         <v>-122.381</v>
@@ -2353,37 +2353,37 @@
         <v>105.75</v>
       </c>
       <c r="M13">
-        <v>6.038552500925697</v>
+        <v>5.913365900925697</v>
       </c>
       <c r="N13">
-        <v>99.71144749907427</v>
+        <v>99.83663409907427</v>
       </c>
       <c r="O13">
-        <v>19.94228949981485</v>
+        <v>19.96732681981486</v>
       </c>
       <c r="P13">
-        <v>79.76915799925942</v>
+        <v>79.86930727925942</v>
       </c>
       <c r="Q13">
-        <v>224.2691579992594</v>
+        <v>224.3693072792594</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08602419490250136</v>
+        <v>0.08601331178921195</v>
       </c>
       <c r="T13">
         <v>0.6220871440134119</v>
       </c>
       <c r="U13">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.51247504824852</v>
+        <v>17.88321605186744</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08251329764895105</v>
+        <v>0.08236923148583479</v>
       </c>
       <c r="C14">
-        <v>752.0894786134763</v>
+        <v>754.5683875342552</v>
       </c>
       <c r="D14">
-        <v>670.5374786134763</v>
+        <v>673.0163875342552</v>
       </c>
       <c r="E14">
         <v>-114.252</v>
@@ -2435,37 +2435,37 @@
         <v>105.75</v>
       </c>
       <c r="M14">
-        <v>6.587511819191668</v>
+        <v>6.450944619191668</v>
       </c>
       <c r="N14">
-        <v>99.16248818080831</v>
+        <v>99.2990553808083</v>
       </c>
       <c r="O14">
-        <v>19.83249763616166</v>
+        <v>19.85981107616166</v>
       </c>
       <c r="P14">
-        <v>79.32999054464665</v>
+        <v>79.43924430464664</v>
       </c>
       <c r="Q14">
-        <v>223.8299905446466</v>
+        <v>223.9392443046466</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08639809520834354</v>
+        <v>0.08638711093207506</v>
       </c>
       <c r="T14">
         <v>0.627869697871131</v>
       </c>
       <c r="U14">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.05310212756115</v>
+        <v>16.39294804754515</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.0825223357912012</v>
+        <v>0.08236708943579624</v>
       </c>
       <c r="C15">
-        <v>743.7954451812287</v>
+        <v>746.4788119128729</v>
       </c>
       <c r="D15">
-        <v>670.3724451812287</v>
+        <v>673.0558119128729</v>
       </c>
       <c r="E15">
         <v>-106.123</v>
@@ -2517,37 +2517,37 @@
         <v>105.75</v>
       </c>
       <c r="M15">
-        <v>7.136471137457642</v>
+        <v>6.988523337457642</v>
       </c>
       <c r="N15">
-        <v>98.61352886254232</v>
+        <v>98.76147666254234</v>
       </c>
       <c r="O15">
-        <v>19.72270577250847</v>
+        <v>19.75229533250847</v>
       </c>
       <c r="P15">
-        <v>78.89082309003386</v>
+        <v>79.00918133003387</v>
       </c>
       <c r="Q15">
-        <v>223.3908230900338</v>
+        <v>223.5091813300339</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08678059092351542</v>
+        <v>0.08676950315868212</v>
       </c>
       <c r="T15">
         <v>0.6337851840014411</v>
       </c>
       <c r="U15">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.81824811774875</v>
+        <v>15.13195204388783</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08253137393345138</v>
+        <v>0.0823649473857577</v>
       </c>
       <c r="C16">
-        <v>735.5014929654166</v>
+        <v>738.3892409106132</v>
       </c>
       <c r="D16">
-        <v>670.2074929654166</v>
+        <v>673.0952409106133</v>
       </c>
       <c r="E16">
         <v>-97.99399999999999</v>
@@ -2599,37 +2599,37 @@
         <v>105.75</v>
       </c>
       <c r="M16">
-        <v>7.685430455723615</v>
+        <v>7.526102055723615</v>
       </c>
       <c r="N16">
-        <v>98.06456954427635</v>
+        <v>98.22389794427636</v>
       </c>
       <c r="O16">
-        <v>19.61291390885527</v>
+        <v>19.64477958885527</v>
       </c>
       <c r="P16">
-        <v>78.45165563542108</v>
+        <v>78.57911835542109</v>
       </c>
       <c r="Q16">
-        <v>222.9516556354211</v>
+        <v>223.0791183554211</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08717198188787735</v>
+        <v>0.08716078822776843</v>
       </c>
       <c r="T16">
         <v>0.6398382395766424</v>
       </c>
       <c r="U16">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.75980182362384</v>
+        <v>14.05109832646727</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08254041207570154</v>
+        <v>0.08236280533571919</v>
       </c>
       <c r="C17">
-        <v>727.207621906103</v>
+        <v>730.2996745282878</v>
       </c>
       <c r="D17">
-        <v>670.0426219061029</v>
+        <v>673.1346745282877</v>
       </c>
       <c r="E17">
         <v>-89.86500000000001</v>
@@ -2681,37 +2681,37 @@
         <v>105.75</v>
       </c>
       <c r="M17">
-        <v>8.234389773989585</v>
+        <v>8.063680773989585</v>
       </c>
       <c r="N17">
-        <v>97.51561022601038</v>
+        <v>97.68631922601038</v>
       </c>
       <c r="O17">
-        <v>19.50312204520208</v>
+        <v>19.53726384520208</v>
       </c>
       <c r="P17">
-        <v>78.0124881808083</v>
+        <v>78.14905538080831</v>
       </c>
       <c r="Q17">
-        <v>222.5124881808083</v>
+        <v>222.6490553808083</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08757258205140073</v>
+        <v>0.08756128000436267</v>
       </c>
       <c r="T17">
         <v>0.6460337199889071</v>
       </c>
       <c r="U17">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.84248170204892</v>
+        <v>13.11435843803612</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08269025021795171</v>
+        <v>0.08255266328568063</v>
       </c>
       <c r="C18">
-        <v>716.3570913905417</v>
+        <v>718.6933763428335</v>
       </c>
       <c r="D18">
-        <v>667.3210913905417</v>
+        <v>669.6573763428335</v>
       </c>
       <c r="E18">
         <v>-81.73599999999999</v>
@@ -2763,37 +2763,37 @@
         <v>105.75</v>
       </c>
       <c r="M18">
-        <v>8.92641949225556</v>
+        <v>8.796355492255559</v>
       </c>
       <c r="N18">
-        <v>96.82358050774441</v>
+        <v>96.95364450774441</v>
       </c>
       <c r="O18">
-        <v>19.36471610154888</v>
+        <v>19.39072890154888</v>
       </c>
       <c r="P18">
-        <v>77.45886440619553</v>
+        <v>77.56291560619553</v>
       </c>
       <c r="Q18">
-        <v>221.9588644061955</v>
+        <v>222.0629156061955</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08798272031405563</v>
+        <v>0.08797130729944722</v>
       </c>
       <c r="T18">
         <v>0.6523767118395591</v>
       </c>
       <c r="U18">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.84685529195074</v>
+        <v>12.02202435919101</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08270808836020185</v>
+        <v>0.0825625212356421</v>
       </c>
       <c r="C19">
-        <v>707.9055667331124</v>
+        <v>710.384806262071</v>
       </c>
       <c r="D19">
-        <v>666.9985667331124</v>
+        <v>669.477806262071</v>
       </c>
       <c r="E19">
         <v>-73.607</v>
@@ -2845,37 +2845,37 @@
         <v>105.75</v>
       </c>
       <c r="M19">
-        <v>9.484320710521532</v>
+        <v>9.346127710521532</v>
       </c>
       <c r="N19">
-        <v>96.26567928947844</v>
+        <v>96.40387228947844</v>
       </c>
       <c r="O19">
-        <v>19.25313585789569</v>
+        <v>19.28077445789569</v>
       </c>
       <c r="P19">
-        <v>77.01254343158276</v>
+        <v>77.12309783158275</v>
       </c>
       <c r="Q19">
-        <v>221.5125434315827</v>
+        <v>221.6230978315828</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08840274142641305</v>
+        <v>0.08839121477031696</v>
       </c>
       <c r="T19">
         <v>0.6588725468673353</v>
       </c>
       <c r="U19">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.14998145124775</v>
+        <v>11.31484645570919</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08272592650245203</v>
+        <v>0.08257237918560358</v>
       </c>
       <c r="C20">
-        <v>699.4543536855058</v>
+        <v>702.0763324597059</v>
       </c>
       <c r="D20">
-        <v>666.6763536855058</v>
+        <v>669.2983324597059</v>
       </c>
       <c r="E20">
         <v>-65.47800000000001</v>
@@ -2927,37 +2927,37 @@
         <v>105.75</v>
       </c>
       <c r="M20">
-        <v>10.0422219287875</v>
+        <v>9.895899928787504</v>
       </c>
       <c r="N20">
-        <v>95.70777807121247</v>
+        <v>95.85410007121247</v>
       </c>
       <c r="O20">
-        <v>19.1415556142425</v>
+        <v>19.17082001424249</v>
       </c>
       <c r="P20">
-        <v>76.56622245696998</v>
+        <v>76.68328005696998</v>
       </c>
       <c r="Q20">
-        <v>221.06622245697</v>
+        <v>221.18328005697</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08883300695614503</v>
+        <v>0.08882136388681766</v>
       </c>
       <c r="T20">
         <v>0.6655268168957889</v>
       </c>
       <c r="U20">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.53053803728954</v>
+        <v>10.68624387483645</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08274376464470219</v>
+        <v>0.08258223713556503</v>
       </c>
       <c r="C21">
-        <v>691.0034517963445</v>
+        <v>693.7679548583284</v>
       </c>
       <c r="D21">
-        <v>666.3544517963445</v>
+        <v>669.1189548583284</v>
       </c>
       <c r="E21">
         <v>-57.34899999999999</v>
@@ -3009,37 +3009,37 @@
         <v>105.75</v>
       </c>
       <c r="M21">
-        <v>10.60012314705348</v>
+        <v>10.44567214705348</v>
       </c>
       <c r="N21">
-        <v>95.14987685294649</v>
+        <v>95.3043278529465</v>
       </c>
       <c r="O21">
-        <v>19.0299753705893</v>
+        <v>19.0608655705893</v>
       </c>
       <c r="P21">
-        <v>76.11990148235719</v>
+        <v>76.2434622823572</v>
       </c>
       <c r="Q21">
-        <v>220.6199014823572</v>
+        <v>220.7434622823572</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08927389632611732</v>
+        <v>0.08926213396915789</v>
       </c>
       <c r="T21">
         <v>0.6723453898879082</v>
       </c>
       <c r="U21">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.976299193221671</v>
+        <v>10.12380998668717</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08311360278695235</v>
+        <v>0.0828640950855265</v>
       </c>
       <c r="C22">
-        <v>676.2698016386101</v>
+        <v>680.5505668520508</v>
       </c>
       <c r="D22">
-        <v>659.7498016386102</v>
+        <v>664.0305668520508</v>
       </c>
       <c r="E22">
         <v>-49.21999999999997</v>
@@ -3091,37 +3091,37 @@
         <v>105.75</v>
       </c>
       <c r="M22">
-        <v>11.51570036531945</v>
+        <v>11.27183036531945</v>
       </c>
       <c r="N22">
-        <v>94.23429963468053</v>
+        <v>94.47816963468053</v>
       </c>
       <c r="O22">
-        <v>18.84685992693611</v>
+        <v>18.89563392693611</v>
       </c>
       <c r="P22">
-        <v>75.38743970774442</v>
+        <v>75.58253570774443</v>
       </c>
       <c r="Q22">
-        <v>219.8874397077444</v>
+        <v>220.0825357077444</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08972580793033891</v>
+        <v>0.08971392330355661</v>
       </c>
       <c r="T22">
         <v>0.6793344272048302</v>
       </c>
       <c r="U22">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.183114933979653</v>
+        <v>9.381794843663172</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08314904092920251</v>
+        <v>0.08288755303548798</v>
       </c>
       <c r="C23">
-        <v>667.5148067873822</v>
+        <v>672.001566217466</v>
       </c>
       <c r="D23">
-        <v>659.1238067873821</v>
+        <v>663.6105662174659</v>
       </c>
       <c r="E23">
         <v>-41.09100000000001</v>
@@ -3173,37 +3173,37 @@
         <v>105.75</v>
       </c>
       <c r="M23">
-        <v>12.09148538358542</v>
+        <v>11.83542188358542</v>
       </c>
       <c r="N23">
-        <v>93.65851461641455</v>
+        <v>93.91457811641455</v>
       </c>
       <c r="O23">
-        <v>18.73170292328291</v>
+        <v>18.78291562328291</v>
       </c>
       <c r="P23">
-        <v>74.92681169313164</v>
+        <v>75.13166249313164</v>
       </c>
       <c r="Q23">
-        <v>219.4268116931316</v>
+        <v>219.6316624931316</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09018916033466738</v>
+        <v>0.09017715034262366</v>
       </c>
       <c r="T23">
         <v>0.6865004021753452</v>
       </c>
       <c r="U23">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.745823746647289</v>
+        <v>8.935042708250641</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08318447907145267</v>
+        <v>0.08291101098544944</v>
       </c>
       <c r="C24">
-        <v>658.7609987438955</v>
+        <v>663.4530965494926</v>
       </c>
       <c r="D24">
-        <v>658.4989987438955</v>
+        <v>663.1910965494925</v>
       </c>
       <c r="E24">
         <v>-32.96199999999999</v>
@@ -3255,37 +3255,37 @@
         <v>105.75</v>
       </c>
       <c r="M24">
-        <v>12.66727040185139</v>
+        <v>12.39901340185139</v>
       </c>
       <c r="N24">
-        <v>93.08272959814857</v>
+        <v>93.35098659814858</v>
       </c>
       <c r="O24">
-        <v>18.61654591962971</v>
+        <v>18.67019731962972</v>
       </c>
       <c r="P24">
-        <v>74.46618367851886</v>
+        <v>74.68078927851886</v>
       </c>
       <c r="Q24">
-        <v>218.9661836785189</v>
+        <v>219.1807892785189</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09066439356987607</v>
+        <v>0.09065225499807705</v>
       </c>
       <c r="T24">
         <v>0.6938501200938223</v>
       </c>
       <c r="U24">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.348286303617865</v>
+        <v>8.528904403330156</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08321991721370284</v>
+        <v>0.0829344689354109</v>
       </c>
       <c r="C25">
-        <v>650.0083741362887</v>
+        <v>654.9051568418909</v>
       </c>
       <c r="D25">
-        <v>657.8753741362887</v>
+        <v>662.7721568418908</v>
       </c>
       <c r="E25">
         <v>-24.83299999999997</v>
@@ -3337,37 +3337,37 @@
         <v>105.75</v>
       </c>
       <c r="M25">
-        <v>13.24305542011737</v>
+        <v>12.96260492011737</v>
       </c>
       <c r="N25">
-        <v>92.5069445798826</v>
+        <v>92.7873950798826</v>
       </c>
       <c r="O25">
-        <v>18.50138891597652</v>
+        <v>18.55747901597652</v>
       </c>
       <c r="P25">
-        <v>74.00555566390608</v>
+        <v>74.22991606390607</v>
       </c>
       <c r="Q25">
-        <v>218.5055556639061</v>
+        <v>218.7299160639061</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.0911519705254798</v>
+        <v>0.09113970003419157</v>
       </c>
       <c r="T25">
         <v>0.7013907397764156</v>
       </c>
       <c r="U25">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.985317333895349</v>
+        <v>8.158082472750584</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.083543355355953</v>
+        <v>0.08295792688537236</v>
       </c>
       <c r="C26">
-        <v>636.2417728463118</v>
+        <v>646.3577460909625</v>
       </c>
       <c r="D26">
-        <v>652.2377728463118</v>
+        <v>662.3537460909624</v>
       </c>
       <c r="E26">
         <v>-16.70400000000001</v>
@@ -3419,45 +3419,45 @@
         <v>105.75</v>
       </c>
       <c r="M26">
-        <v>14.11148443838334</v>
+        <v>13.52619643838334</v>
       </c>
       <c r="N26">
-        <v>91.63851556161663</v>
+        <v>92.22380356161663</v>
       </c>
       <c r="O26">
-        <v>18.32770311232333</v>
+        <v>18.44476071232333</v>
       </c>
       <c r="P26">
-        <v>73.31081244929331</v>
+        <v>73.7790428492933</v>
       </c>
       <c r="Q26">
-        <v>217.8108124492933</v>
+        <v>218.2790428492933</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09165237845359939</v>
+        <v>0.09163997257125646</v>
       </c>
       <c r="T26">
         <v>0.7091297968190771</v>
       </c>
       <c r="U26">
-        <v>0.07233097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05786478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.493896227696585</v>
+        <v>7.818162369719311</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08359079349820317</v>
+        <v>0.08314138483533384</v>
       </c>
       <c r="C27">
-        <v>627.2940298302201</v>
+        <v>634.9746069918637</v>
       </c>
       <c r="D27">
-        <v>651.4190298302201</v>
+        <v>659.0996069918637</v>
       </c>
       <c r="E27">
         <v>-8.574999999999989</v>
@@ -3501,37 +3501,37 @@
         <v>105.75</v>
       </c>
       <c r="M27">
-        <v>14.69946295664931</v>
+        <v>14.25236795664931</v>
       </c>
       <c r="N27">
-        <v>91.05053704335066</v>
+        <v>91.49763204335066</v>
       </c>
       <c r="O27">
-        <v>18.21010740867013</v>
+        <v>18.29952640867013</v>
       </c>
       <c r="P27">
-        <v>72.84042963468053</v>
+        <v>73.19810563468053</v>
       </c>
       <c r="Q27">
-        <v>217.3404296346805</v>
+        <v>217.6981056346805</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09216613059313553</v>
+        <v>0.09215358570930976</v>
       </c>
       <c r="T27">
         <v>0.7170752287162097</v>
       </c>
       <c r="U27">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.194140378588722</v>
+        <v>7.419819662364476</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08363823164045331</v>
+        <v>0.08317124278529529</v>
       </c>
       <c r="C28">
-        <v>618.348339745568</v>
+        <v>626.3190159122403</v>
       </c>
       <c r="D28">
-        <v>650.602339745568</v>
+        <v>658.5730159122403</v>
       </c>
       <c r="E28">
         <v>-0.4459999999999695</v>
@@ -3583,37 +3583,37 @@
         <v>105.75</v>
       </c>
       <c r="M28">
-        <v>15.28744147491529</v>
+        <v>14.82246267491529</v>
       </c>
       <c r="N28">
-        <v>90.46255852508469</v>
+        <v>90.92753732508469</v>
       </c>
       <c r="O28">
-        <v>18.09251170501694</v>
+        <v>18.18550746501694</v>
       </c>
       <c r="P28">
-        <v>72.37004682006776</v>
+        <v>72.74202986006775</v>
       </c>
       <c r="Q28">
-        <v>216.8700468200678</v>
+        <v>217.2420298600678</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09269376792563208</v>
+        <v>0.09268108028352665</v>
       </c>
       <c r="T28">
         <v>0.7252354020159674</v>
       </c>
       <c r="U28">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.917442671719924</v>
+        <v>7.134441983042764</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08368566978270348</v>
+        <v>0.08320110073525677</v>
       </c>
       <c r="C29">
-        <v>609.4046948806847</v>
+        <v>617.6642656062727</v>
       </c>
       <c r="D29">
-        <v>649.7876948806847</v>
+        <v>658.0472656062727</v>
       </c>
       <c r="E29">
         <v>7.683000000000021</v>
@@ -3665,37 +3665,37 @@
         <v>105.75</v>
       </c>
       <c r="M29">
-        <v>15.87541999318126</v>
+        <v>15.39255739318126</v>
       </c>
       <c r="N29">
-        <v>89.87458000681872</v>
+        <v>90.35744260681872</v>
       </c>
       <c r="O29">
-        <v>17.97491600136375</v>
+        <v>18.07148852136374</v>
       </c>
       <c r="P29">
-        <v>71.89966400545498</v>
+        <v>72.28595408545497</v>
       </c>
       <c r="Q29">
-        <v>216.399664005455</v>
+        <v>216.785954085455</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09323586107545732</v>
+        <v>0.09322302676388648</v>
       </c>
       <c r="T29">
         <v>0.7336191417074993</v>
       </c>
       <c r="U29">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.661241091285854</v>
+        <v>6.870203391078219</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08373310792495364</v>
+        <v>0.08323095868521824</v>
       </c>
       <c r="C30">
-        <v>600.4630875624775</v>
+        <v>609.0103540619549</v>
       </c>
       <c r="D30">
-        <v>648.9750875624776</v>
+        <v>657.522354061955</v>
       </c>
       <c r="E30">
         <v>15.81200000000004</v>
@@ -3747,37 +3747,37 @@
         <v>105.75</v>
       </c>
       <c r="M30">
-        <v>16.46339851144723</v>
+        <v>15.96265211144723</v>
       </c>
       <c r="N30">
-        <v>89.28660148855275</v>
+        <v>89.78734788855274</v>
       </c>
       <c r="O30">
-        <v>17.85732029771055</v>
+        <v>17.95746957771055</v>
       </c>
       <c r="P30">
-        <v>71.4292811908422</v>
+        <v>71.82987831084219</v>
       </c>
       <c r="Q30">
-        <v>215.9292811908422</v>
+        <v>216.3298783108422</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09379301236833326</v>
+        <v>0.09378002731314519</v>
       </c>
       <c r="T30">
         <v>0.7422357630571292</v>
       </c>
       <c r="U30">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.42333962373993</v>
+        <v>6.624838984253996</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0837805460672038</v>
+        <v>0.0832608166351797</v>
       </c>
       <c r="C31">
-        <v>591.5235101561886</v>
+        <v>600.3572792736951</v>
       </c>
       <c r="D31">
-        <v>648.1645101561886</v>
+        <v>656.9982792736951</v>
       </c>
       <c r="E31">
         <v>23.941</v>
@@ -3829,37 +3829,37 @@
         <v>105.75</v>
       </c>
       <c r="M31">
-        <v>17.0513770297132</v>
+        <v>16.5327468297132</v>
       </c>
       <c r="N31">
-        <v>88.69862297028678</v>
+        <v>89.21725317028677</v>
       </c>
       <c r="O31">
-        <v>17.73972459405736</v>
+        <v>17.84345063405735</v>
       </c>
       <c r="P31">
-        <v>70.95889837622943</v>
+        <v>71.37380253622942</v>
       </c>
       <c r="Q31">
-        <v>215.4588983762294</v>
+        <v>215.8738025362294</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09436585806382541</v>
+        <v>0.09435271801872105</v>
       </c>
       <c r="T31">
         <v>0.7510951061349179</v>
       </c>
       <c r="U31">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.201845153955796</v>
+        <v>6.396396260659031</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08416398420945398</v>
+        <v>0.08329067458514117</v>
       </c>
       <c r="C32">
-        <v>576.9162727997686</v>
+        <v>591.70503924229</v>
       </c>
       <c r="D32">
-        <v>641.6862727997686</v>
+        <v>656.47503924229</v>
       </c>
       <c r="E32">
         <v>32.06999999999999</v>
@@ -3911,45 +3911,45 @@
         <v>105.75</v>
       </c>
       <c r="M32">
-        <v>17.98077354797917</v>
+        <v>17.10284154797917</v>
       </c>
       <c r="N32">
-        <v>87.7692264520208</v>
+        <v>88.6471584520208</v>
       </c>
       <c r="O32">
-        <v>17.55384529040416</v>
+        <v>17.72943169040416</v>
       </c>
       <c r="P32">
-        <v>70.21538116161665</v>
+        <v>70.91772676161665</v>
       </c>
       <c r="Q32">
-        <v>214.7153811616166</v>
+        <v>215.4177267616166</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.0949550707791888</v>
+        <v>0.09494177131588478</v>
       </c>
       <c r="T32">
         <v>0.7602075733006434</v>
       </c>
       <c r="U32">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05898478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>5.881282010355168</v>
+        <v>6.183183051970398</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08422262235170412</v>
+        <v>0.08356853253510263</v>
       </c>
       <c r="C33">
-        <v>567.8079723605646</v>
+        <v>578.7464417874459</v>
       </c>
       <c r="D33">
-        <v>640.7069723605646</v>
+        <v>651.6454417874459</v>
       </c>
       <c r="E33">
         <v>40.19900000000001</v>
@@ -3993,37 +3993,37 @@
         <v>105.75</v>
       </c>
       <c r="M33">
-        <v>18.58013266624515</v>
+        <v>17.92493526624515</v>
       </c>
       <c r="N33">
-        <v>87.16986733375482</v>
+        <v>87.82506473375483</v>
       </c>
       <c r="O33">
-        <v>17.43397346675097</v>
+        <v>17.56501294675097</v>
       </c>
       <c r="P33">
-        <v>69.73589386700385</v>
+        <v>70.26005178700386</v>
       </c>
       <c r="Q33">
-        <v>214.2358938670039</v>
+        <v>214.7600517870039</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09556136212398297</v>
+        <v>0.09554789862166196</v>
       </c>
       <c r="T33">
         <v>0.7695841699494332</v>
       </c>
       <c r="U33">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.691563235827582</v>
+        <v>5.899602895589822</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08428126049395428</v>
+        <v>0.0836063904850641</v>
       </c>
       <c r="C34">
-        <v>558.7026564576111</v>
+        <v>569.9649076467545</v>
       </c>
       <c r="D34">
-        <v>639.7306564576111</v>
+        <v>650.9929076467545</v>
       </c>
       <c r="E34">
         <v>48.32800000000003</v>
@@ -4075,37 +4075,37 @@
         <v>105.75</v>
       </c>
       <c r="M34">
-        <v>19.17949178451112</v>
+        <v>18.50315898451112</v>
       </c>
       <c r="N34">
-        <v>86.57050821548886</v>
+        <v>87.24684101548885</v>
       </c>
       <c r="O34">
-        <v>17.31410164309777</v>
+        <v>17.44936820309777</v>
       </c>
       <c r="P34">
-        <v>69.25640657239109</v>
+        <v>69.79747281239108</v>
       </c>
       <c r="Q34">
-        <v>213.7564065723911</v>
+        <v>214.2974728123911</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09618548556715345</v>
+        <v>0.09617185320113847</v>
       </c>
       <c r="T34">
         <v>0.7792365488525993</v>
       </c>
       <c r="U34">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.51370188470797</v>
+        <v>5.715240305102639</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08433989863620446</v>
+        <v>0.08364424843502558</v>
       </c>
       <c r="C35">
-        <v>549.6003114680649</v>
+        <v>561.1846790468451</v>
       </c>
       <c r="D35">
-        <v>638.7573114680649</v>
+        <v>650.3416790468451</v>
       </c>
       <c r="E35">
         <v>56.45700000000005</v>
@@ -4157,37 +4157,37 @@
         <v>105.75</v>
       </c>
       <c r="M35">
-        <v>19.77885090277709</v>
+        <v>19.08138270277709</v>
       </c>
       <c r="N35">
-        <v>85.97114909722288</v>
+        <v>86.66861729722288</v>
       </c>
       <c r="O35">
-        <v>17.19422981944458</v>
+        <v>17.33372345944458</v>
       </c>
       <c r="P35">
-        <v>68.7769192777783</v>
+        <v>69.33489383777831</v>
       </c>
       <c r="Q35">
-        <v>213.2769192777783</v>
+        <v>213.8348938377783</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09682823956086636</v>
+        <v>0.0968144332904501</v>
       </c>
       <c r="T35">
         <v>0.7891770584692929</v>
       </c>
       <c r="U35">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.346620009413789</v>
+        <v>5.542051204948013</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.0843985367784546</v>
+        <v>0.08368210638498702</v>
       </c>
       <c r="C36">
-        <v>540.5009238518667</v>
+        <v>552.4057520735932</v>
       </c>
       <c r="D36">
-        <v>637.7869238518666</v>
+        <v>649.6917520735933</v>
       </c>
       <c r="E36">
         <v>64.58600000000001</v>
@@ -4239,37 +4239,37 @@
         <v>105.75</v>
       </c>
       <c r="M36">
-        <v>20.37821002104306</v>
+        <v>19.65960642104307</v>
       </c>
       <c r="N36">
-        <v>85.37178997895691</v>
+        <v>86.09039357895691</v>
       </c>
       <c r="O36">
-        <v>17.07435799579138</v>
+        <v>17.21807871579138</v>
       </c>
       <c r="P36">
-        <v>68.29743198316552</v>
+        <v>68.87231486316553</v>
       </c>
       <c r="Q36">
-        <v>212.7974319831655</v>
+        <v>213.3723148631655</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09749047094832811</v>
+        <v>0.09747648550368025</v>
       </c>
       <c r="T36">
         <v>0.7994187956501284</v>
       </c>
       <c r="U36">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.189366479725149</v>
+        <v>5.379049698920131</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08445717492070479</v>
+        <v>0.08371996433494849</v>
       </c>
       <c r="C37">
-        <v>531.4044801511088</v>
+        <v>543.6281228285043</v>
       </c>
       <c r="D37">
-        <v>636.8194801511088</v>
+        <v>649.0431228285042</v>
       </c>
       <c r="E37">
         <v>72.71500000000003</v>
@@ -4321,37 +4321,37 @@
         <v>105.75</v>
       </c>
       <c r="M37">
-        <v>20.97756913930904</v>
+        <v>20.23783013930904</v>
       </c>
       <c r="N37">
-        <v>84.77243086069093</v>
+        <v>85.51216986069093</v>
       </c>
       <c r="O37">
-        <v>16.95448617213819</v>
+        <v>17.10243397213819</v>
       </c>
       <c r="P37">
-        <v>67.81794468855274</v>
+        <v>68.40973588855275</v>
       </c>
       <c r="Q37">
-        <v>212.3179446885528</v>
+        <v>212.9097358885527</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09817307868617332</v>
+        <v>0.09815890855424059</v>
       </c>
       <c r="T37">
         <v>0.8099756632057591</v>
       </c>
       <c r="U37">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.041098866018714</v>
+        <v>5.225362564665271</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08451581306295494</v>
+        <v>0.08375782228490997</v>
       </c>
       <c r="C38">
-        <v>522.3109669894183</v>
+        <v>534.8517874286373</v>
       </c>
       <c r="D38">
-        <v>635.8549669894182</v>
+        <v>648.3957874286373</v>
       </c>
       <c r="E38">
         <v>80.84399999999999</v>
@@ -4403,37 +4403,37 @@
         <v>105.75</v>
       </c>
       <c r="M38">
-        <v>21.57692825757501</v>
+        <v>20.81605385757501</v>
       </c>
       <c r="N38">
-        <v>84.17307174242497</v>
+        <v>84.93394614242496</v>
       </c>
       <c r="O38">
-        <v>16.83461434848499</v>
+        <v>16.98678922848499</v>
       </c>
       <c r="P38">
-        <v>67.33845739393998</v>
+        <v>67.94715691393996</v>
       </c>
       <c r="Q38">
-        <v>211.83845739394</v>
+        <v>212.44715691394</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09887701791582619</v>
+        <v>0.09886265732513091</v>
       </c>
       <c r="T38">
         <v>0.8208624328725032</v>
       </c>
       <c r="U38">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.90106834196264</v>
+        <v>5.08021360453568</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.0845744512052051</v>
+        <v>0.08379568023487143</v>
       </c>
       <c r="C39">
-        <v>513.2203710713362</v>
+        <v>526.0767420065274</v>
       </c>
       <c r="D39">
-        <v>634.8933710713362</v>
+        <v>647.7497420065274</v>
       </c>
       <c r="E39">
         <v>88.97300000000001</v>
@@ -4485,37 +4485,37 @@
         <v>105.75</v>
       </c>
       <c r="M39">
-        <v>22.17628737584098</v>
+        <v>21.39427757584098</v>
       </c>
       <c r="N39">
-        <v>83.57371262415899</v>
+        <v>84.35572242415898</v>
       </c>
       <c r="O39">
-        <v>16.7147425248318</v>
+        <v>16.8711444848318</v>
       </c>
       <c r="P39">
-        <v>66.85897009932719</v>
+        <v>67.48457793932718</v>
       </c>
       <c r="Q39">
-        <v>211.3589700993272</v>
+        <v>211.9845779393272</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09960330442261089</v>
+        <v>0.09958874732684316</v>
       </c>
       <c r="T39">
         <v>0.8320948142746994</v>
       </c>
       <c r="U39">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.768607035423109</v>
+        <v>4.942910534142824</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08463308934745527</v>
+        <v>0.0838335381848329</v>
       </c>
       <c r="C40">
-        <v>504.1326791817091</v>
+        <v>517.3029827101066</v>
       </c>
       <c r="D40">
-        <v>633.9346791817092</v>
+        <v>647.1049827101066</v>
       </c>
       <c r="E40">
         <v>97.10200000000003</v>
@@ -4567,37 +4567,37 @@
         <v>105.75</v>
       </c>
       <c r="M40">
-        <v>22.77564649410695</v>
+        <v>21.97250129410696</v>
       </c>
       <c r="N40">
-        <v>82.97435350589302</v>
+        <v>83.77749870589301</v>
       </c>
       <c r="O40">
-        <v>16.5948707011786</v>
+        <v>16.7554997411786</v>
       </c>
       <c r="P40">
-        <v>66.37948280471441</v>
+        <v>67.02199896471441</v>
       </c>
       <c r="Q40">
-        <v>210.8794828047144</v>
+        <v>211.5219989647144</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1003530195263887</v>
+        <v>0.1003382595866752</v>
       </c>
       <c r="T40">
         <v>0.8436895305608375</v>
       </c>
       <c r="U40">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.643117376596186</v>
+        <v>4.812833941139065</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08469172748970544</v>
+        <v>0.08387139613479437</v>
       </c>
       <c r="C41">
-        <v>495.0478781850829</v>
+        <v>508.5305057026304</v>
       </c>
       <c r="D41">
-        <v>632.978878185083</v>
+        <v>646.4615057026305</v>
       </c>
       <c r="E41">
         <v>105.2310000000001</v>
@@ -4649,37 +4649,37 @@
         <v>105.75</v>
       </c>
       <c r="M41">
-        <v>23.37500561237293</v>
+        <v>22.55072501237293</v>
       </c>
       <c r="N41">
-        <v>82.37499438762704</v>
+        <v>83.19927498762704</v>
       </c>
       <c r="O41">
-        <v>16.47499887752541</v>
+        <v>16.63985499752541</v>
       </c>
       <c r="P41">
-        <v>65.89999551010163</v>
+        <v>66.55941999010163</v>
       </c>
       <c r="Q41">
-        <v>210.3999955101016</v>
+        <v>211.0594199901016</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1011273154532411</v>
+        <v>0.1011123460189607</v>
       </c>
       <c r="T41">
         <v>0.855664401479308</v>
       </c>
       <c r="U41">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.52406308488859</v>
+        <v>4.689427942648319</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08558236563195559</v>
+        <v>0.08390925408475583</v>
       </c>
       <c r="C42">
-        <v>472.7478975710617</v>
+        <v>499.7593071625995</v>
       </c>
       <c r="D42">
-        <v>618.8078975710617</v>
+        <v>645.8193071625996</v>
       </c>
       <c r="E42">
         <v>113.3600000000001</v>
@@ -4731,45 +4731,45 @@
         <v>105.75</v>
       </c>
       <c r="M42">
-        <v>24.8197807306389</v>
+        <v>23.1289487306389</v>
       </c>
       <c r="N42">
-        <v>80.93021926936107</v>
+        <v>82.62105126936106</v>
       </c>
       <c r="O42">
-        <v>16.18604385387222</v>
+        <v>16.52421025387221</v>
       </c>
       <c r="P42">
-        <v>64.74417541548885</v>
+        <v>66.09684101548885</v>
       </c>
       <c r="Q42">
-        <v>209.2441754154889</v>
+        <v>210.5968410154888</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1019274212443219</v>
+        <v>0.1019122353323223</v>
       </c>
       <c r="T42">
         <v>0.8680384347617275</v>
       </c>
       <c r="U42">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.26071451426871</v>
+        <v>4.57219224408211</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08566180377420576</v>
+        <v>0.0847671120347173</v>
       </c>
       <c r="C43">
-        <v>463.3857132909116</v>
+        <v>477.4126451917958</v>
       </c>
       <c r="D43">
-        <v>617.5747132909116</v>
+        <v>631.6016451917958</v>
       </c>
       <c r="E43">
         <v>121.489</v>
@@ -4813,37 +4813,37 @@
         <v>105.75</v>
       </c>
       <c r="M43">
-        <v>25.44027524890487</v>
+        <v>24.54039494890487</v>
       </c>
       <c r="N43">
-        <v>80.3097247510951</v>
+        <v>81.20960505109511</v>
       </c>
       <c r="O43">
-        <v>16.06194495021902</v>
+        <v>16.24192101021902</v>
       </c>
       <c r="P43">
-        <v>64.24777980087609</v>
+        <v>64.96768404087609</v>
       </c>
       <c r="Q43">
-        <v>208.7477798008761</v>
+        <v>209.4676840408761</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1027546492656089</v>
+        <v>0.1027392395376624</v>
       </c>
       <c r="T43">
         <v>0.8808319267994833</v>
       </c>
       <c r="U43">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.156794648067033</v>
+        <v>4.309221600556153</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08574124191645592</v>
+        <v>0.08482496998467877</v>
       </c>
       <c r="C44">
-        <v>454.0284343098244</v>
+        <v>468.3472402080781</v>
       </c>
       <c r="D44">
-        <v>616.3464343098244</v>
+        <v>630.6652402080781</v>
       </c>
       <c r="E44">
         <v>129.618</v>
@@ -4895,37 +4895,37 @@
         <v>105.75</v>
       </c>
       <c r="M44">
-        <v>26.06076976717084</v>
+        <v>25.13894116717084</v>
       </c>
       <c r="N44">
-        <v>79.68923023282913</v>
+        <v>80.61105883282913</v>
       </c>
       <c r="O44">
-        <v>15.93784604656583</v>
+        <v>16.12221176656583</v>
       </c>
       <c r="P44">
-        <v>63.75138418626331</v>
+        <v>64.4888470662633</v>
       </c>
       <c r="Q44">
-        <v>208.2513841862633</v>
+        <v>208.9888470662633</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1036104023910782</v>
+        <v>0.1035947611293935</v>
       </c>
       <c r="T44">
         <v>0.8940665737350925</v>
       </c>
       <c r="U44">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.05782334692258</v>
+        <v>4.206621086257197</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08674948005870609</v>
+        <v>0.08488282793464025</v>
       </c>
       <c r="C45">
-        <v>430.7240527660254</v>
+        <v>459.2846077193691</v>
       </c>
       <c r="D45">
-        <v>601.1710527660254</v>
+        <v>629.7316077193691</v>
       </c>
       <c r="E45">
         <v>137.747</v>
@@ -4977,45 +4977,45 @@
         <v>105.75</v>
       </c>
       <c r="M45">
-        <v>27.62504118543681</v>
+        <v>25.73748738543681</v>
       </c>
       <c r="N45">
-        <v>78.12495881456316</v>
+        <v>80.01251261456316</v>
       </c>
       <c r="O45">
-        <v>15.62499176291263</v>
+        <v>16.00250252291263</v>
       </c>
       <c r="P45">
-        <v>62.49996705165053</v>
+        <v>64.01001009165053</v>
       </c>
       <c r="Q45">
-        <v>206.9999670516505</v>
+        <v>208.5100100916505</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1044961819420026</v>
+        <v>0.1044803010225888</v>
       </c>
       <c r="T45">
         <v>0.9077655942473901</v>
       </c>
       <c r="U45">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.06322478221340606</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.828048591498519</v>
+        <v>4.108792688902379</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08685051820095625</v>
+        <v>0.0849406858846017</v>
       </c>
       <c r="C46">
-        <v>421.1153831051283</v>
+        <v>450.2247354307232</v>
       </c>
       <c r="D46">
-        <v>599.6913831051284</v>
+        <v>628.8007354307232</v>
       </c>
       <c r="E46">
         <v>145.876</v>
@@ -5059,45 +5059,45 @@
         <v>105.75</v>
       </c>
       <c r="M46">
-        <v>28.26748400370279</v>
+        <v>26.33603360370278</v>
       </c>
       <c r="N46">
-        <v>77.48251599629718</v>
+        <v>79.41396639629718</v>
       </c>
       <c r="O46">
-        <v>15.49650319925944</v>
+        <v>15.88279327925944</v>
       </c>
       <c r="P46">
-        <v>61.98601279703774</v>
+        <v>63.53117311703775</v>
       </c>
       <c r="Q46">
-        <v>206.4860127970377</v>
+        <v>208.0311731170378</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1054135964768885</v>
+        <v>0.1053974673405411</v>
       </c>
       <c r="T46">
         <v>0.9219538654922695</v>
       </c>
       <c r="U46">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.06322478221340606</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.74104748714628</v>
+        <v>4.01541103688187</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08695155634320642</v>
+        <v>0.08625854383456316</v>
       </c>
       <c r="C47">
-        <v>411.5139794184479</v>
+        <v>421.6137810747417</v>
       </c>
       <c r="D47">
-        <v>598.2189794184479</v>
+        <v>608.3187810747418</v>
       </c>
       <c r="E47">
         <v>154.0050000000001</v>
@@ -5141,37 +5141,37 @@
         <v>105.75</v>
       </c>
       <c r="M47">
-        <v>28.90992682196876</v>
+        <v>28.21489732196876</v>
       </c>
       <c r="N47">
-        <v>76.84007317803122</v>
+        <v>77.53510267803121</v>
       </c>
       <c r="O47">
-        <v>15.36801463560624</v>
+        <v>15.50702053560624</v>
       </c>
       <c r="P47">
-        <v>61.47205854242497</v>
+        <v>62.02808214242496</v>
       </c>
       <c r="Q47">
-        <v>205.972058542425</v>
+        <v>206.528082142425</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1063643715403158</v>
+        <v>0.1063479851609644</v>
       </c>
       <c r="T47">
         <v>0.9366580738733264</v>
       </c>
       <c r="U47">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.06322478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.657913098543029</v>
+        <v>3.748020019114534</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08705259448545657</v>
+        <v>0.08634440178452463</v>
       </c>
       <c r="C48">
-        <v>401.9197883173031</v>
+        <v>412.196588348562</v>
       </c>
       <c r="D48">
-        <v>596.7537883173031</v>
+        <v>607.0305883485621</v>
       </c>
       <c r="E48">
         <v>162.1340000000001</v>
@@ -5223,37 +5223,37 @@
         <v>105.75</v>
       </c>
       <c r="M48">
-        <v>29.55236964023473</v>
+        <v>28.84189504023474</v>
       </c>
       <c r="N48">
-        <v>76.19763035976524</v>
+        <v>76.90810495976524</v>
       </c>
       <c r="O48">
-        <v>15.23952607195305</v>
+        <v>15.38162099195305</v>
       </c>
       <c r="P48">
-        <v>60.95810428781219</v>
+        <v>61.52648396781219</v>
       </c>
       <c r="Q48">
-        <v>205.4581042878122</v>
+        <v>206.0264839678122</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1073503604949811</v>
+        <v>0.1073337073451071</v>
       </c>
       <c r="T48">
         <v>0.9519068825647929</v>
       </c>
       <c r="U48">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.06322478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.578393248574702</v>
+        <v>3.666541323046827</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08715363262770674</v>
+        <v>0.08643025973448609</v>
       </c>
       <c r="C49">
-        <v>392.3327569347849</v>
+        <v>402.7848399186948</v>
       </c>
       <c r="D49">
-        <v>595.2957569347849</v>
+        <v>605.7478399186948</v>
       </c>
       <c r="E49">
         <v>170.263</v>
@@ -5305,37 +5305,37 @@
         <v>105.75</v>
       </c>
       <c r="M49">
-        <v>30.1948124585007</v>
+        <v>29.4688927585007</v>
       </c>
       <c r="N49">
-        <v>75.55518754149927</v>
+        <v>76.28110724149927</v>
       </c>
       <c r="O49">
-        <v>15.11103750829985</v>
+        <v>15.25622144829985</v>
       </c>
       <c r="P49">
-        <v>60.44415003319941</v>
+        <v>61.02488579319942</v>
       </c>
       <c r="Q49">
-        <v>204.9441500331994</v>
+        <v>205.5248857931994</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1083735565800111</v>
+        <v>0.1083566265928023</v>
       </c>
       <c r="T49">
         <v>0.9677311179993336</v>
       </c>
       <c r="U49">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.06322478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.502257222009283</v>
+        <v>3.588529805535193</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08905947076995691</v>
+        <v>0.08651611768444756</v>
       </c>
       <c r="C50">
-        <v>357.9774222318205</v>
+        <v>393.3785013440283</v>
       </c>
       <c r="D50">
-        <v>569.0694222318205</v>
+        <v>604.4705013440283</v>
       </c>
       <c r="E50">
         <v>178.392</v>
@@ -5387,45 +5387,45 @@
         <v>105.75</v>
       </c>
       <c r="M50">
-        <v>32.67115767676668</v>
+        <v>30.09589047676667</v>
       </c>
       <c r="N50">
-        <v>73.07884232323329</v>
+        <v>75.6541095232333</v>
       </c>
       <c r="O50">
-        <v>14.61576846464666</v>
+        <v>15.13082190464666</v>
       </c>
       <c r="P50">
-        <v>58.46307385858663</v>
+        <v>60.52328761858664</v>
       </c>
       <c r="Q50">
-        <v>202.9630738585866</v>
+        <v>205.0232876185866</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1094361063606192</v>
+        <v>0.1094188888884859</v>
       </c>
       <c r="T50">
         <v>0.9841639778736643</v>
       </c>
       <c r="U50">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.06698478221340608</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.23679990302889</v>
+        <v>3.513768767919876</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08919810891220706</v>
+        <v>0.08769957563440903</v>
       </c>
       <c r="C51">
-        <v>348.0304921540563</v>
+        <v>368.1761680345303</v>
       </c>
       <c r="D51">
-        <v>567.2514921540563</v>
+        <v>587.3971680345303</v>
       </c>
       <c r="E51">
         <v>186.521</v>
@@ -5469,37 +5469,37 @@
         <v>105.75</v>
       </c>
       <c r="M51">
-        <v>33.35180679503265</v>
+        <v>31.83818699503265</v>
       </c>
       <c r="N51">
-        <v>72.39819320496733</v>
+        <v>73.91181300496731</v>
       </c>
       <c r="O51">
-        <v>14.47963864099347</v>
+        <v>14.78236260099346</v>
       </c>
       <c r="P51">
-        <v>57.91855456397386</v>
+        <v>59.12945040397385</v>
       </c>
       <c r="Q51">
-        <v>202.4185545639739</v>
+        <v>203.6294504039739</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1105403247600747</v>
+        <v>0.1105228085290981</v>
       </c>
       <c r="T51">
         <v>1.00124126362542</v>
       </c>
       <c r="U51">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.06698478221340608</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.17074276215075</v>
+        <v>3.321483098786339</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08933674705445724</v>
+        <v>0.0878078335843705</v>
       </c>
       <c r="C52">
-        <v>338.0951400863992</v>
+        <v>358.5333929169234</v>
       </c>
       <c r="D52">
-        <v>565.4451400863992</v>
+        <v>585.8833929169234</v>
       </c>
       <c r="E52">
         <v>194.65</v>
@@ -5551,37 +5551,37 @@
         <v>105.75</v>
       </c>
       <c r="M52">
-        <v>34.03245591329863</v>
+        <v>32.48794591329862</v>
       </c>
       <c r="N52">
-        <v>71.71754408670134</v>
+        <v>73.26205408670134</v>
       </c>
       <c r="O52">
-        <v>14.34350881734027</v>
+        <v>14.65241081734027</v>
       </c>
       <c r="P52">
-        <v>57.37403526936107</v>
+        <v>58.60964326936107</v>
       </c>
       <c r="Q52">
-        <v>201.8740352693611</v>
+        <v>203.1096432693611</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1116887118955084</v>
+        <v>0.1116708849553349</v>
       </c>
       <c r="T52">
         <v>1.019001640807245</v>
       </c>
       <c r="U52">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.06698478221340608</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.107327906907734</v>
+        <v>3.255053436810612</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08947538519670739</v>
+        <v>0.08791609153433197</v>
       </c>
       <c r="C53">
-        <v>328.1712557731209</v>
+        <v>348.8984000120037</v>
       </c>
       <c r="D53">
-        <v>563.650255773121</v>
+        <v>584.3774000120037</v>
       </c>
       <c r="E53">
         <v>202.7790000000001</v>
@@ -5633,37 +5633,37 @@
         <v>105.75</v>
       </c>
       <c r="M53">
-        <v>34.7131050315646</v>
+        <v>33.1377048315646</v>
       </c>
       <c r="N53">
-        <v>71.03689496843538</v>
+        <v>72.61229516843537</v>
       </c>
       <c r="O53">
-        <v>14.20737899368708</v>
+        <v>14.52245903368707</v>
       </c>
       <c r="P53">
-        <v>56.8295159747483</v>
+        <v>58.0898361347483</v>
       </c>
       <c r="Q53">
-        <v>201.3295159747483</v>
+        <v>202.5898361347483</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1128839719752455</v>
+        <v>0.1128658216438671</v>
       </c>
       <c r="T53">
         <v>1.037486931343431</v>
       </c>
       <c r="U53">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.06698478221340608</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.046399908733073</v>
+        <v>3.191228859618247</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09348282333895755</v>
+        <v>0.08802434948429341</v>
       </c>
       <c r="C54">
-        <v>272.6710353691312</v>
+        <v>339.2711294619119</v>
       </c>
       <c r="D54">
-        <v>516.2790353691313</v>
+        <v>582.8791294619119</v>
       </c>
       <c r="E54">
         <v>210.9080000000001</v>
@@ -5715,45 +5715,45 @@
         <v>105.75</v>
       </c>
       <c r="M54">
-        <v>39.32493854983057</v>
+        <v>33.78746374983057</v>
       </c>
       <c r="N54">
-        <v>66.42506145016941</v>
+        <v>71.96253625016939</v>
       </c>
       <c r="O54">
-        <v>13.28501229003388</v>
+        <v>14.39250725003388</v>
       </c>
       <c r="P54">
-        <v>53.14004916013553</v>
+        <v>57.57002900013551</v>
       </c>
       <c r="Q54">
-        <v>197.6400491601355</v>
+        <v>202.0700290001355</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.114129034558305</v>
+        <v>0.1141105473610881</v>
       </c>
       <c r="T54">
         <v>1.056742442318625</v>
       </c>
       <c r="U54">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.07442478221340607</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.689133254868254</v>
+        <v>3.129859073856358</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.0936958614812077</v>
+        <v>0.0881326074342549</v>
       </c>
       <c r="C55">
-        <v>262.2456547805726</v>
+        <v>329.6515220210902</v>
       </c>
       <c r="D55">
-        <v>513.9826547805726</v>
+        <v>581.3885220210902</v>
       </c>
       <c r="E55">
         <v>219.037</v>
@@ -5797,45 +5797,45 @@
         <v>105.75</v>
       </c>
       <c r="M55">
-        <v>40.08118736809654</v>
+        <v>34.43722266809655</v>
       </c>
       <c r="N55">
-        <v>65.66881263190344</v>
+        <v>71.31277733190342</v>
       </c>
       <c r="O55">
-        <v>13.13376252638069</v>
+        <v>14.26255546638068</v>
       </c>
       <c r="P55">
-        <v>52.53505010552275</v>
+        <v>57.05022186552274</v>
       </c>
       <c r="Q55">
-        <v>197.0350501055227</v>
+        <v>201.5502218655227</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1154270785278776</v>
+        <v>0.1154082401301057</v>
       </c>
       <c r="T55">
         <v>1.076817336739571</v>
       </c>
       <c r="U55">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.07442478221340607</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.638394891568854</v>
+        <v>3.070805129066615</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09390889962345789</v>
+        <v>0.08824086538421637</v>
       </c>
       <c r="C56">
-        <v>251.8406120778648</v>
+        <v>320.0395190484755</v>
       </c>
       <c r="D56">
-        <v>511.7066120778649</v>
+        <v>579.9055190484755</v>
       </c>
       <c r="E56">
         <v>227.1660000000001</v>
@@ -5879,45 +5879,45 @@
         <v>105.75</v>
       </c>
       <c r="M56">
-        <v>40.83743618636251</v>
+        <v>35.08698158636252</v>
       </c>
       <c r="N56">
-        <v>64.91256381363746</v>
+        <v>70.66301841363745</v>
       </c>
       <c r="O56">
-        <v>12.98251276272749</v>
+        <v>14.13260368272749</v>
       </c>
       <c r="P56">
-        <v>51.93005105090997</v>
+        <v>56.53041473090995</v>
       </c>
       <c r="Q56">
-        <v>196.43005105091</v>
+        <v>201.03041473091</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1167815591917796</v>
+        <v>0.1167623543238632</v>
       </c>
       <c r="T56">
         <v>1.097765052657081</v>
       </c>
       <c r="U56">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.07442478221340607</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.589535726910171</v>
+        <v>3.013938367417233</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09412193776570804</v>
+        <v>0.09178112333417782</v>
       </c>
       <c r="C57">
-        <v>241.455638268562</v>
+        <v>267.2614331808434</v>
       </c>
       <c r="D57">
-        <v>509.4506382685622</v>
+        <v>535.2564331808435</v>
       </c>
       <c r="E57">
         <v>235.2950000000001</v>
@@ -5961,37 +5961,37 @@
         <v>105.75</v>
       </c>
       <c r="M57">
-        <v>41.59368500462848</v>
+        <v>39.22408150462849</v>
       </c>
       <c r="N57">
-        <v>64.15631499537149</v>
+        <v>66.52591849537149</v>
       </c>
       <c r="O57">
-        <v>12.8312629990743</v>
+        <v>13.3051836990743</v>
       </c>
       <c r="P57">
-        <v>51.32505199629719</v>
+        <v>53.22073479629719</v>
       </c>
       <c r="Q57">
-        <v>195.8250519962972</v>
+        <v>197.7207347962972</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1181962389962993</v>
+        <v>0.1181766513706766</v>
       </c>
       <c r="T57">
         <v>1.119643778170924</v>
       </c>
       <c r="U57">
-        <v>0.09303097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.07442478221340607</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.542453259148168</v>
+        <v>2.696047834479472</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0964405759079582</v>
+        <v>0.09195178128413931</v>
       </c>
       <c r="C58">
-        <v>210.0008434823787</v>
+        <v>257.1531863771727</v>
       </c>
       <c r="D58">
-        <v>486.1248434823788</v>
+        <v>533.2771863771728</v>
       </c>
       <c r="E58">
         <v>243.4240000000001</v>
@@ -6043,45 +6043,45 @@
         <v>105.75</v>
       </c>
       <c r="M58">
-        <v>44.48948662289446</v>
+        <v>39.93724662289446</v>
       </c>
       <c r="N58">
-        <v>61.26051337710551</v>
+        <v>65.81275337710551</v>
       </c>
       <c r="O58">
-        <v>12.2521026754211</v>
+        <v>13.1625506754211</v>
       </c>
       <c r="P58">
-        <v>49.00841070168441</v>
+        <v>52.65020270168441</v>
       </c>
       <c r="Q58">
-        <v>193.5084107016844</v>
+        <v>197.1502027016844</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1196752224282973</v>
+        <v>0.1196552346468907</v>
       </c>
       <c r="T58">
         <v>1.142516991208124</v>
       </c>
       <c r="U58">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.376966066081343</v>
+        <v>2.647904123149482</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09669121405020836</v>
+        <v>0.09212243923410077</v>
       </c>
       <c r="C59">
-        <v>199.4776890110024</v>
+        <v>247.0595231838461</v>
       </c>
       <c r="D59">
-        <v>483.7306890110025</v>
+        <v>531.3125231838462</v>
       </c>
       <c r="E59">
         <v>251.5530000000001</v>
@@ -6125,45 +6125,45 @@
         <v>105.75</v>
       </c>
       <c r="M59">
-        <v>45.28394174116043</v>
+        <v>40.65041174116044</v>
       </c>
       <c r="N59">
-        <v>60.46605825883954</v>
+        <v>65.09958825883953</v>
       </c>
       <c r="O59">
-        <v>12.09321165176791</v>
+        <v>13.01991765176791</v>
       </c>
       <c r="P59">
-        <v>48.37284660707163</v>
+        <v>52.07967060707163</v>
       </c>
       <c r="Q59">
-        <v>192.8728466070716</v>
+        <v>196.5796706070716</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1212229957873649</v>
+        <v>0.1212025892382775</v>
       </c>
       <c r="T59">
         <v>1.166454074619147</v>
       </c>
       <c r="U59">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V59">
         <v>0.2</v>
       </c>
       <c r="W59">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.335264907027284</v>
+        <v>2.601449664848614</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.09694185219245852</v>
+        <v>0.09229309718406223</v>
       </c>
       <c r="C60">
-        <v>188.9780012856763</v>
+        <v>236.9802830086986</v>
       </c>
       <c r="D60">
-        <v>481.3600012856763</v>
+        <v>529.3622830086986</v>
       </c>
       <c r="E60">
         <v>259.682</v>
@@ -6207,45 +6207,45 @@
         <v>105.75</v>
       </c>
       <c r="M60">
-        <v>46.0783968594264</v>
+        <v>41.3635768594264</v>
       </c>
       <c r="N60">
-        <v>59.67160314057357</v>
+        <v>64.38642314057357</v>
       </c>
       <c r="O60">
-        <v>11.93432062811472</v>
+        <v>12.87728462811472</v>
       </c>
       <c r="P60">
-        <v>47.73728251245886</v>
+        <v>51.50913851245885</v>
       </c>
       <c r="Q60">
-        <v>192.2372825124589</v>
+        <v>196.0091385124589</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1228444726397214</v>
+        <v>0.122823627381635</v>
       </c>
       <c r="T60">
         <v>1.19153101914498</v>
       </c>
       <c r="U60">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V60">
         <v>0.2</v>
       </c>
       <c r="W60">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.29500171897509</v>
+        <v>2.55659708442019</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.09719249033470868</v>
+        <v>0.09246375513402369</v>
       </c>
       <c r="C61">
-        <v>178.5014369685936</v>
+        <v>226.9153076088251</v>
       </c>
       <c r="D61">
-        <v>479.0124369685936</v>
+        <v>527.4263076088251</v>
       </c>
       <c r="E61">
         <v>267.811</v>
@@ -6289,45 +6289,45 @@
         <v>105.75</v>
       </c>
       <c r="M61">
-        <v>46.87285197769237</v>
+        <v>42.07674197769238</v>
       </c>
       <c r="N61">
-        <v>58.8771480223076</v>
+        <v>63.67325802230759</v>
       </c>
       <c r="O61">
-        <v>11.77542960446152</v>
+        <v>12.73465160446152</v>
       </c>
       <c r="P61">
-        <v>47.10171841784608</v>
+        <v>50.93860641784607</v>
       </c>
       <c r="Q61">
-        <v>191.6017184178461</v>
+        <v>195.4386064178461</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1245450459239003</v>
+        <v>0.1245237405563759</v>
       </c>
       <c r="T61">
         <v>1.21783122925744</v>
       </c>
       <c r="U61">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.256103384755173</v>
+        <v>2.513264930446966</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.09744312847695885</v>
+        <v>0.09450641308398516</v>
       </c>
       <c r="C62">
-        <v>168.0476593871948</v>
+        <v>196.6670121805558</v>
       </c>
       <c r="D62">
-        <v>476.6876593871948</v>
+        <v>505.3070121805558</v>
       </c>
       <c r="E62">
         <v>275.94</v>
@@ -6371,37 +6371,37 @@
         <v>105.75</v>
       </c>
       <c r="M62">
-        <v>47.66730709595834</v>
+        <v>44.69209309595834</v>
       </c>
       <c r="N62">
-        <v>58.08269290404164</v>
+        <v>61.05790690404163</v>
       </c>
       <c r="O62">
-        <v>11.61653858080833</v>
+        <v>12.21158138080833</v>
       </c>
       <c r="P62">
-        <v>46.46615432323331</v>
+        <v>48.8463255232333</v>
       </c>
       <c r="Q62">
-        <v>190.9661543232333</v>
+        <v>193.3463255232333</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.126330647872288</v>
+        <v>0.1263088593898538</v>
       </c>
       <c r="T62">
         <v>1.245446449875522</v>
       </c>
       <c r="U62">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V62">
         <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.218501661675921</v>
+        <v>2.36619036331425</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.097693766619209</v>
+        <v>0.09470827103394663</v>
       </c>
       <c r="C63">
-        <v>157.616338373207</v>
+        <v>186.4524705037885</v>
       </c>
       <c r="D63">
-        <v>474.385338373207</v>
+        <v>503.2214705037886</v>
       </c>
       <c r="E63">
         <v>284.069</v>
@@ -6453,37 +6453,37 @@
         <v>105.75</v>
       </c>
       <c r="M63">
-        <v>48.46176221422431</v>
+        <v>45.43696131422431</v>
       </c>
       <c r="N63">
-        <v>57.28823778577566</v>
+        <v>60.31303868577566</v>
       </c>
       <c r="O63">
-        <v>11.45764755715513</v>
+        <v>12.06260773715513</v>
       </c>
       <c r="P63">
-        <v>45.83059022862052</v>
+        <v>48.25043094862053</v>
       </c>
       <c r="Q63">
-        <v>190.3305902286205</v>
+        <v>192.7504309486205</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1282078191513623</v>
+        <v>0.1281855227788947</v>
       </c>
       <c r="T63">
         <v>1.274477835653506</v>
       </c>
       <c r="U63">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.182132781976315</v>
+        <v>2.327400357358279</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.09794440476145916</v>
+        <v>0.09491012898390809</v>
       </c>
       <c r="C64">
-        <v>147.207150106326</v>
+        <v>176.2550732807682</v>
       </c>
       <c r="D64">
-        <v>472.1051501063261</v>
+        <v>501.1530732807683</v>
       </c>
       <c r="E64">
         <v>292.198</v>
@@ -6535,37 +6535,37 @@
         <v>105.75</v>
       </c>
       <c r="M64">
-        <v>49.25621733249029</v>
+        <v>46.18182953249029</v>
       </c>
       <c r="N64">
-        <v>56.49378266750968</v>
+        <v>59.56817046750968</v>
       </c>
       <c r="O64">
-        <v>11.29875653350194</v>
+        <v>11.91363409350194</v>
       </c>
       <c r="P64">
-        <v>45.19502613400775</v>
+        <v>47.65453637400775</v>
       </c>
       <c r="Q64">
-        <v>189.6950261340077</v>
+        <v>192.1545363740078</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.130183788918809</v>
+        <v>0.1301609579252535</v>
       </c>
       <c r="T64">
         <v>1.305037189104016</v>
       </c>
       <c r="U64">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.146937091944439</v>
+        <v>2.289861641917017</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.09819504290370934</v>
+        <v>0.09511198693386956</v>
       </c>
       <c r="C65">
-        <v>136.8197769623847</v>
+        <v>166.0746099697276</v>
       </c>
       <c r="D65">
-        <v>469.8467769623848</v>
+        <v>499.1016099697277</v>
       </c>
       <c r="E65">
         <v>300.3270000000001</v>
@@ -6617,37 +6617,37 @@
         <v>105.75</v>
       </c>
       <c r="M65">
-        <v>50.05067245075626</v>
+        <v>46.92669775075626</v>
       </c>
       <c r="N65">
-        <v>55.69932754924371</v>
+        <v>58.82330224924371</v>
       </c>
       <c r="O65">
-        <v>11.13986550984874</v>
+        <v>11.76466044984874</v>
       </c>
       <c r="P65">
-        <v>44.55946203939497</v>
+        <v>47.05864179939497</v>
       </c>
       <c r="Q65">
-        <v>189.059462039395</v>
+        <v>191.558641799395</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1322665678628744</v>
+        <v>0.1322431733497939</v>
       </c>
       <c r="T65">
         <v>1.337248399497797</v>
       </c>
       <c r="U65">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.112858725405638</v>
+        <v>2.253514631727858</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09844568104595949</v>
+        <v>0.09531384488383102</v>
       </c>
       <c r="C66">
-        <v>126.4539073658593</v>
+        <v>155.9108734622451</v>
       </c>
       <c r="D66">
-        <v>467.6099073658594</v>
+        <v>497.0668734622453</v>
       </c>
       <c r="E66">
         <v>308.4560000000001</v>
@@ -6699,37 +6699,37 @@
         <v>105.75</v>
       </c>
       <c r="M66">
-        <v>50.84512756902223</v>
+        <v>47.67156596902224</v>
       </c>
       <c r="N66">
-        <v>54.90487243097774</v>
+        <v>58.07843403097773</v>
       </c>
       <c r="O66">
-        <v>10.98097448619555</v>
+        <v>11.61568680619555</v>
       </c>
       <c r="P66">
-        <v>43.92389794478219</v>
+        <v>46.46274722478218</v>
       </c>
       <c r="Q66">
-        <v>188.4238979447822</v>
+        <v>190.9627472247822</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1344650567482767</v>
+        <v>0.1344410674090309</v>
       </c>
       <c r="T66">
         <v>1.37124912158012</v>
       </c>
       <c r="U66">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.079845307821175</v>
+        <v>2.218303465607109</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.09869631918820966</v>
+        <v>0.09551570283379249</v>
       </c>
       <c r="C67">
-        <v>116.1092356465675</v>
+        <v>145.7636600135429</v>
       </c>
       <c r="D67">
-        <v>465.3942356465676</v>
+        <v>495.048660013543</v>
       </c>
       <c r="E67">
         <v>316.5850000000001</v>
@@ -6781,37 +6781,37 @@
         <v>105.75</v>
       </c>
       <c r="M67">
-        <v>51.63958268728821</v>
+        <v>48.41643418728821</v>
       </c>
       <c r="N67">
-        <v>54.11041731271176</v>
+        <v>57.33356581271176</v>
       </c>
       <c r="O67">
-        <v>10.82208346254235</v>
+        <v>11.46671316254235</v>
       </c>
       <c r="P67">
-        <v>43.28833385016941</v>
+        <v>45.86685265016941</v>
       </c>
       <c r="Q67">
-        <v>187.7883338501694</v>
+        <v>190.3668526501694</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1367891735699878</v>
+        <v>0.1367645554145101</v>
       </c>
       <c r="T67">
         <v>1.407192742067148</v>
       </c>
       <c r="U67">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.047847687700849</v>
+        <v>2.184175719982385</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09894695733045983</v>
+        <v>0.09571756078375396</v>
       </c>
       <c r="C68">
-        <v>105.7854619004223</v>
+        <v>135.6327691744771</v>
       </c>
       <c r="D68">
-        <v>463.1994619004224</v>
+        <v>493.0467691744772</v>
       </c>
       <c r="E68">
         <v>324.7140000000001</v>
@@ -6863,37 +6863,37 @@
         <v>105.75</v>
       </c>
       <c r="M68">
-        <v>52.43403780555418</v>
+        <v>49.16130240555419</v>
       </c>
       <c r="N68">
-        <v>53.31596219444579</v>
+        <v>56.58869759444578</v>
       </c>
       <c r="O68">
-        <v>10.66319243888916</v>
+        <v>11.31773951888916</v>
       </c>
       <c r="P68">
-        <v>42.65276975555663</v>
+        <v>45.27095807555663</v>
       </c>
       <c r="Q68">
-        <v>187.1527697555566</v>
+        <v>189.7709580755566</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1392500031459171</v>
+        <v>0.1392247191850175</v>
       </c>
       <c r="T68">
         <v>1.44525069317106</v>
       </c>
       <c r="U68">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V68">
         <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.016819692432655</v>
+        <v>2.1510821484675</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.10793439547271</v>
+        <v>0.09591941873371543</v>
       </c>
       <c r="C69">
-        <v>30.6569123002007</v>
+        <v>125.5180037251715</v>
       </c>
       <c r="D69">
-        <v>396.1999123002009</v>
+        <v>491.0610037251717</v>
       </c>
       <c r="E69">
         <v>332.8430000000001</v>
@@ -6945,45 +6945,45 @@
         <v>105.75</v>
       </c>
       <c r="M69">
-        <v>62.10617382382016</v>
+        <v>49.90617062382016</v>
       </c>
       <c r="N69">
-        <v>43.64382617617981</v>
+        <v>55.84382937617981</v>
       </c>
       <c r="O69">
-        <v>8.728765235235961</v>
+        <v>11.16876587523596</v>
       </c>
       <c r="P69">
-        <v>34.91506094094385</v>
+        <v>44.67506350094385</v>
       </c>
       <c r="Q69">
-        <v>179.4150609409438</v>
+        <v>189.1750635009438</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1418599739082664</v>
+        <v>0.1418339837901011</v>
       </c>
       <c r="T69">
         <v>1.485615186766119</v>
       </c>
       <c r="U69">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V69">
         <v>0.2</v>
       </c>
       <c r="W69">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.702729269717799</v>
+        <v>2.11897644475903</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1083154336149602</v>
+        <v>0.0961212766836769</v>
       </c>
       <c r="C70">
-        <v>20.11303216880208</v>
+        <v>115.4191696102487</v>
       </c>
       <c r="D70">
-        <v>393.7850321688022</v>
+        <v>489.0911696102488</v>
       </c>
       <c r="E70">
         <v>340.972</v>
@@ -7027,45 +7027,45 @@
         <v>105.75</v>
       </c>
       <c r="M70">
-        <v>63.03313164208613</v>
+        <v>50.65103884208612</v>
       </c>
       <c r="N70">
-        <v>42.71686835791385</v>
+        <v>55.09896115791385</v>
       </c>
       <c r="O70">
-        <v>8.543373671582769</v>
+        <v>11.01979223158277</v>
       </c>
       <c r="P70">
-        <v>34.17349468633108</v>
+        <v>44.07916892633108</v>
       </c>
       <c r="Q70">
-        <v>178.6734946863311</v>
+        <v>188.5791689263311</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1446330678432626</v>
+        <v>0.1446063274330024</v>
       </c>
       <c r="T70">
         <v>1.528502461210868</v>
       </c>
       <c r="U70">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V70">
         <v>0.2</v>
       </c>
       <c r="W70">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.677689133398419</v>
+        <v>2.08781502645375</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1086964717572103</v>
+        <v>0.09632313463363837</v>
       </c>
       <c r="C71">
-        <v>9.598411594046752</v>
+        <v>105.3360758756123</v>
       </c>
       <c r="D71">
-        <v>391.3994115940469</v>
+        <v>487.1370758756124</v>
       </c>
       <c r="E71">
         <v>349.1010000000001</v>
@@ -7109,45 +7109,45 @@
         <v>105.75</v>
       </c>
       <c r="M71">
-        <v>63.9600894603521</v>
+        <v>51.39590706035209</v>
       </c>
       <c r="N71">
-        <v>41.78991053964787</v>
+        <v>54.35409293964788</v>
       </c>
       <c r="O71">
-        <v>8.357982107929574</v>
+        <v>10.87081858792958</v>
       </c>
       <c r="P71">
-        <v>33.4319284317183</v>
+        <v>43.4832743517183</v>
       </c>
       <c r="Q71">
-        <v>177.9319284317183</v>
+        <v>187.9832743517183</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1475850710643875</v>
+        <v>0.1475575319560909</v>
       </c>
       <c r="T71">
         <v>1.574156656587537</v>
       </c>
       <c r="U71">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V71">
         <v>0.2</v>
       </c>
       <c r="W71">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.653374798131776</v>
+        <v>2.057556837664565</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1090775098994605</v>
+        <v>0.09652499258359983</v>
       </c>
       <c r="C72">
-        <v>-0.8874780008277412</v>
+        <v>95.26853460674158</v>
       </c>
       <c r="D72">
-        <v>389.0425219991724</v>
+        <v>485.1985346067416</v>
       </c>
       <c r="E72">
         <v>357.2300000000001</v>
@@ -7191,45 +7191,45 @@
         <v>105.75</v>
       </c>
       <c r="M72">
-        <v>64.88704727861807</v>
+        <v>52.14077527861807</v>
       </c>
       <c r="N72">
-        <v>40.8629527213819</v>
+        <v>53.6092247213819</v>
       </c>
       <c r="O72">
-        <v>8.17259054427638</v>
+        <v>10.72184494427638</v>
       </c>
       <c r="P72">
-        <v>32.69036217710552</v>
+        <v>42.88737977710552</v>
       </c>
       <c r="Q72">
-        <v>177.1903621771055</v>
+        <v>187.3873797771055</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1507338745002541</v>
+        <v>0.1507054834473853</v>
       </c>
       <c r="T72">
         <v>1.622854464989317</v>
       </c>
       <c r="U72">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V72">
         <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.629755158158465</v>
+        <v>2.028163168555071</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1094585480417107</v>
+        <v>0.1047924505335613</v>
       </c>
       <c r="C73">
-        <v>-11.34515253706991</v>
+        <v>19.1417069870522</v>
       </c>
       <c r="D73">
-        <v>386.7138474629301</v>
+        <v>417.2007069870522</v>
       </c>
       <c r="E73">
         <v>365.359</v>
@@ -7273,37 +7273,37 @@
         <v>105.75</v>
       </c>
       <c r="M73">
-        <v>65.81400509688403</v>
+        <v>61.08130129688404</v>
       </c>
       <c r="N73">
-        <v>39.93599490311594</v>
+        <v>44.66869870311594</v>
       </c>
       <c r="O73">
-        <v>7.987198980623188</v>
+        <v>8.933739740623187</v>
       </c>
       <c r="P73">
-        <v>31.94879592249275</v>
+        <v>35.73495896249275</v>
       </c>
       <c r="Q73">
-        <v>176.4487959224928</v>
+        <v>180.2349589624928</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1540998367937666</v>
+        <v>0.1540705350415275</v>
       </c>
       <c r="T73">
         <v>1.674910742936047</v>
       </c>
       <c r="U73">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V73">
         <v>0.2</v>
       </c>
       <c r="W73">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.606800860156233</v>
+        <v>1.731299067876844</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1098395861839608</v>
+        <v>0.1051079084835227</v>
       </c>
       <c r="C74">
-        <v>-21.77511565691896</v>
+        <v>8.793622161540725</v>
       </c>
       <c r="D74">
-        <v>384.4128843430811</v>
+        <v>414.9816221615407</v>
       </c>
       <c r="E74">
         <v>373.488</v>
@@ -7355,37 +7355,37 @@
         <v>105.75</v>
       </c>
       <c r="M74">
-        <v>66.74096291515001</v>
+        <v>61.94160131515001</v>
       </c>
       <c r="N74">
-        <v>39.00903708484996</v>
+        <v>43.80839868484996</v>
       </c>
       <c r="O74">
-        <v>7.801807416969993</v>
+        <v>8.761679736969993</v>
       </c>
       <c r="P74">
-        <v>31.20722966787997</v>
+        <v>35.04671894787997</v>
       </c>
       <c r="Q74">
-        <v>175.70722966788</v>
+        <v>179.54671894788</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1577062249653872</v>
+        <v>0.1576759474638228</v>
       </c>
       <c r="T74">
         <v>1.730685326450401</v>
       </c>
       <c r="U74">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V74">
         <v>0.2</v>
       </c>
       <c r="W74">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.584484181542952</v>
+        <v>1.707253247489665</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.110220624326211</v>
+        <v>0.1054233664334842</v>
       </c>
       <c r="C75">
-        <v>-32.17785908674648</v>
+        <v>-1.530980999257167</v>
       </c>
       <c r="D75">
-        <v>382.1391409132536</v>
+        <v>412.7860190007429</v>
       </c>
       <c r="E75">
         <v>381.617</v>
@@ -7437,37 +7437,37 @@
         <v>105.75</v>
       </c>
       <c r="M75">
-        <v>67.66792073341598</v>
+        <v>62.80190133341598</v>
       </c>
       <c r="N75">
-        <v>38.08207926658399</v>
+        <v>42.94809866658399</v>
       </c>
       <c r="O75">
-        <v>7.616415853316798</v>
+        <v>8.589619733316798</v>
       </c>
       <c r="P75">
-        <v>30.46566341326719</v>
+        <v>34.35847893326719</v>
       </c>
       <c r="Q75">
-        <v>174.9656634132672</v>
+        <v>178.8584789332672</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1615797530015723</v>
+        <v>0.1615484274729548</v>
       </c>
       <c r="T75">
         <v>1.790591360595447</v>
       </c>
       <c r="U75">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V75">
         <v>0.2</v>
       </c>
       <c r="W75">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.56277891878209</v>
+        <v>1.683866216702135</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1106016624684611</v>
+        <v>0.1057388243834457</v>
       </c>
       <c r="C76">
-        <v>-42.55386298738756</v>
+        <v>-11.832473247248</v>
       </c>
       <c r="D76">
-        <v>379.8921370126125</v>
+        <v>410.613526752752</v>
       </c>
       <c r="E76">
         <v>389.746</v>
@@ -7519,37 +7519,37 @@
         <v>105.75</v>
       </c>
       <c r="M76">
-        <v>68.59487855168196</v>
+        <v>63.66220135168196</v>
       </c>
       <c r="N76">
-        <v>37.15512144831801</v>
+        <v>42.08779864831801</v>
       </c>
       <c r="O76">
-        <v>7.431024289663603</v>
+        <v>8.417559729663603</v>
       </c>
       <c r="P76">
-        <v>29.72409715865441</v>
+        <v>33.67023891865441</v>
       </c>
       <c r="Q76">
-        <v>174.2240971586544</v>
+        <v>178.1702389186544</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1657512447328486</v>
+        <v>0.1657187905597123</v>
       </c>
       <c r="T76">
         <v>1.85510555121319</v>
       </c>
       <c r="U76">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V76">
         <v>0.2</v>
       </c>
       <c r="W76">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.541660284744494</v>
+        <v>1.661111267827782</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1109827006107113</v>
+        <v>0.1060542823334072</v>
       </c>
       <c r="C77">
-        <v>-52.90359629218324</v>
+        <v>-22.11121757013518</v>
       </c>
       <c r="D77">
-        <v>377.6714037078168</v>
+        <v>408.4637824298649</v>
       </c>
       <c r="E77">
         <v>397.8750000000001</v>
@@ -7601,37 +7601,37 @@
         <v>105.75</v>
       </c>
       <c r="M77">
-        <v>69.52183636994793</v>
+        <v>64.52250136994793</v>
       </c>
       <c r="N77">
-        <v>36.22816363005204</v>
+        <v>41.22749863005204</v>
       </c>
       <c r="O77">
-        <v>7.245632726010408</v>
+        <v>8.245499726010408</v>
       </c>
       <c r="P77">
-        <v>28.98253090404163</v>
+        <v>32.98199890404163</v>
       </c>
       <c r="Q77">
-        <v>173.4825309040416</v>
+        <v>177.4819989040416</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1702564558026269</v>
+        <v>0.1702227826934104</v>
       </c>
       <c r="T77">
         <v>1.924780877080353</v>
       </c>
       <c r="U77">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V77">
         <v>0.2</v>
       </c>
       <c r="W77">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.521104814281234</v>
+        <v>1.638963117590079</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1113637387529614</v>
+        <v>0.1063697402833686</v>
       </c>
       <c r="C78">
-        <v>-63.22751703323593</v>
+        <v>-32.36756939360362</v>
       </c>
       <c r="D78">
-        <v>375.4764829667642</v>
+        <v>406.3364306063964</v>
       </c>
       <c r="E78">
         <v>406.0040000000001</v>
@@ -7683,37 +7683,37 @@
         <v>105.75</v>
       </c>
       <c r="M78">
-        <v>70.44879418821391</v>
+        <v>65.38280138821391</v>
       </c>
       <c r="N78">
-        <v>35.30120581178606</v>
+        <v>40.36719861178607</v>
       </c>
       <c r="O78">
-        <v>7.060241162357213</v>
+        <v>8.073439722357213</v>
       </c>
       <c r="P78">
-        <v>28.24096464942885</v>
+        <v>32.29375888942885</v>
       </c>
       <c r="Q78">
-        <v>172.7409646494289</v>
+        <v>176.7937588894289</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1751371011282201</v>
+        <v>0.1751021075049167</v>
       </c>
       <c r="T78">
         <v>2.000262480103111</v>
       </c>
       <c r="U78">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V78">
         <v>0.2</v>
       </c>
       <c r="W78">
-        <v>0.09122478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.501090277251218</v>
+        <v>1.617397813411262</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1539749350426736</v>
+        <v>0.1066851982333301</v>
       </c>
       <c r="C79">
-        <v>-219.2604849122641</v>
+        <v>-42.60187677722286</v>
       </c>
       <c r="D79">
-        <v>227.572515087736</v>
+        <v>404.2311232227772</v>
       </c>
       <c r="E79">
         <v>414.1330000000001</v>
@@ -7765,45 +7765,45 @@
         <v>105.75</v>
       </c>
       <c r="M79">
-        <v>112.3117702064799</v>
+        <v>66.24310140647988</v>
       </c>
       <c r="N79">
-        <v>-6.561770206479935</v>
+        <v>39.50689859352009</v>
       </c>
       <c r="O79">
-        <v>-1.312354041295987</v>
+        <v>7.901379718704018</v>
       </c>
       <c r="P79">
-        <v>-5.249416165183947</v>
+        <v>31.60551887481607</v>
       </c>
       <c r="Q79">
-        <v>139.250583834816</v>
+        <v>176.1055188748161</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1818740980478345</v>
+        <v>0.180405721430467</v>
       </c>
       <c r="T79">
-        <v>2.104453482138292</v>
+        <v>2.082307700780023</v>
       </c>
       <c r="U79">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V79">
-        <v>0.1883150800767962</v>
+        <v>0.2</v>
       </c>
       <c r="W79">
-        <v>0.1456414188203528</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.9415754003839809</v>
+        <v>1.596392647003323</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1553112448203411</v>
+        <v>0.1070006561832915</v>
       </c>
       <c r="C80">
-        <v>-230.1664360604228</v>
+        <v>-52.8144806042892</v>
       </c>
       <c r="D80">
-        <v>224.7955639395773</v>
+        <v>402.147519395711</v>
       </c>
       <c r="E80">
         <v>422.2620000000001</v>
@@ -7847,45 +7847,45 @@
         <v>105.75</v>
       </c>
       <c r="M80">
-        <v>113.7703646247459</v>
+        <v>67.10340142474585</v>
       </c>
       <c r="N80">
-        <v>-8.020364624745909</v>
+        <v>38.64659857525412</v>
       </c>
       <c r="O80">
-        <v>-1.604072924949182</v>
+        <v>7.729319715050824</v>
       </c>
       <c r="P80">
-        <v>-6.416291699796727</v>
+        <v>30.91727886020329</v>
       </c>
       <c r="Q80">
-        <v>138.0837083002033</v>
+        <v>175.4172788602033</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1880592843227361</v>
+        <v>0.1861914820765219</v>
       </c>
       <c r="T80">
-        <v>2.200110458599124</v>
+        <v>2.171811577882109</v>
       </c>
       <c r="U80">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V80">
-        <v>0.1859007841783757</v>
+        <v>0.2</v>
       </c>
       <c r="W80">
-        <v>0.1460746182940247</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.9295039208918785</v>
+        <v>1.575926074605845</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1566475545980087</v>
+        <v>0.107316114133253</v>
       </c>
       <c r="C81">
-        <v>-241.0054327866308</v>
+        <v>-63.00571476582729</v>
       </c>
       <c r="D81">
-        <v>222.0855672133694</v>
+        <v>400.0852852341729</v>
       </c>
       <c r="E81">
         <v>430.3910000000001</v>
@@ -7929,45 +7929,45 @@
         <v>105.75</v>
       </c>
       <c r="M81">
-        <v>115.2289590430119</v>
+        <v>67.96370144301183</v>
       </c>
       <c r="N81">
-        <v>-9.478959043011884</v>
+        <v>37.78629855698814</v>
       </c>
       <c r="O81">
-        <v>-1.895791808602377</v>
+        <v>7.557259711397629</v>
       </c>
       <c r="P81">
-        <v>-7.583167234409506</v>
+        <v>30.22903884559052</v>
       </c>
       <c r="Q81">
-        <v>136.9168327655905</v>
+        <v>174.7290388455905</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1948335359571521</v>
+        <v>0.1925282675460107</v>
       </c>
       <c r="T81">
-        <v>2.30487762329432</v>
+        <v>2.269839633755822</v>
       </c>
       <c r="U81">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V81">
-        <v>0.1835476096951051</v>
+        <v>0.2</v>
       </c>
       <c r="W81">
-        <v>0.1464968506924137</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.9177380484755256</v>
+        <v>1.55597764328172</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1579838643756763</v>
+        <v>0.1076315720832145</v>
       </c>
       <c r="C82">
-        <v>-251.7798677303964</v>
+        <v>-73.17590633895861</v>
       </c>
       <c r="D82">
-        <v>219.4401322696037</v>
+        <v>398.0440936610416</v>
       </c>
       <c r="E82">
         <v>438.5200000000002</v>
@@ -8011,45 +8011,45 @@
         <v>105.75</v>
       </c>
       <c r="M82">
-        <v>116.6875534612778</v>
+        <v>68.8240014612778</v>
       </c>
       <c r="N82">
-        <v>-10.93755346127786</v>
+        <v>36.92599853872217</v>
       </c>
       <c r="O82">
-        <v>-2.187510692255572</v>
+        <v>7.385199707744434</v>
       </c>
       <c r="P82">
-        <v>-8.750042769022286</v>
+        <v>29.54079883097774</v>
       </c>
       <c r="Q82">
-        <v>135.7499572309777</v>
+        <v>174.0407988309777</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2022852127550097</v>
+        <v>0.1994987315624482</v>
       </c>
       <c r="T82">
-        <v>2.420121504459037</v>
+        <v>2.377670495216906</v>
       </c>
       <c r="U82">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V82">
-        <v>0.1812532645739163</v>
+        <v>0.2</v>
       </c>
       <c r="W82">
-        <v>0.146908527280843</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.9062663228695815</v>
+        <v>1.536527922740698</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1593201741533439</v>
+        <v>0.107947030033176</v>
       </c>
       <c r="C83">
-        <v>-262.4920208708102</v>
+        <v>-83.32537575983918</v>
       </c>
       <c r="D83">
-        <v>216.8569791291899</v>
+        <v>396.0236242401609</v>
       </c>
       <c r="E83">
         <v>446.6490000000001</v>
@@ -8093,45 +8093,45 @@
         <v>105.75</v>
       </c>
       <c r="M83">
-        <v>118.1461478795438</v>
+        <v>69.68430147954376</v>
       </c>
       <c r="N83">
-        <v>-12.39614787954382</v>
+        <v>36.06569852045621</v>
       </c>
       <c r="O83">
-        <v>-2.479229575908764</v>
+        <v>7.213139704091242</v>
       </c>
       <c r="P83">
-        <v>-9.916918303635054</v>
+        <v>28.85255881636497</v>
       </c>
       <c r="Q83">
-        <v>134.583081696365</v>
+        <v>173.352558816365</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2105212765842207</v>
+        <v>0.2072029286332476</v>
       </c>
       <c r="T83">
-        <v>2.547496320483196</v>
+        <v>2.496851973673894</v>
       </c>
       <c r="U83">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V83">
-        <v>0.179015569949547</v>
+        <v>0.2</v>
       </c>
       <c r="W83">
-        <v>0.147310039015237</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.895077849747735</v>
+        <v>1.517558442213036</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1606564839310115</v>
+        <v>0.1463238618592803</v>
       </c>
       <c r="C84">
-        <v>-273.1440660803419</v>
+        <v>-242.643672962769</v>
       </c>
       <c r="D84">
-        <v>214.3339339196582</v>
+        <v>244.8343270372311</v>
       </c>
       <c r="E84">
         <v>454.7780000000001</v>
@@ -8175,37 +8175,37 @@
         <v>105.75</v>
       </c>
       <c r="M84">
-        <v>119.6047422978098</v>
+        <v>108.4062318978097</v>
       </c>
       <c r="N84">
-        <v>-13.85474229780979</v>
+        <v>-2.656231897809775</v>
       </c>
       <c r="O84">
-        <v>-2.770948459561959</v>
+        <v>-0.531246379561955</v>
       </c>
       <c r="P84">
-        <v>-11.08379383824783</v>
+        <v>-2.12498551824782</v>
       </c>
       <c r="Q84">
-        <v>133.4162061617522</v>
+        <v>142.3750144817522</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2196724586166774</v>
+        <v>0.2165801137737265</v>
       </c>
       <c r="T84">
-        <v>2.689023893843374</v>
+        <v>2.641914045494859</v>
       </c>
       <c r="U84">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V84">
-        <v>0.1768324532428452</v>
+        <v>0.1950994848703649</v>
       </c>
       <c r="W84">
-        <v>0.1477017577804994</v>
+        <v>0.1309017577804994</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.884162266214226</v>
+        <v>0.9754974243518242</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1619927937086791</v>
+        <v>0.1474921716369479</v>
       </c>
       <c r="C85">
-        <v>-283.7380772263938</v>
+        <v>-253.5854985085491</v>
       </c>
       <c r="D85">
-        <v>211.8689227736063</v>
+        <v>242.021501491451</v>
       </c>
       <c r="E85">
         <v>462.9070000000001</v>
@@ -8257,37 +8257,37 @@
         <v>105.75</v>
       </c>
       <c r="M85">
-        <v>121.0633367160757</v>
+        <v>109.7282591160757</v>
       </c>
       <c r="N85">
-        <v>-15.31333671607577</v>
+        <v>-3.978259116075762</v>
       </c>
       <c r="O85">
-        <v>-3.062667343215153</v>
+        <v>-0.7956518232151524</v>
       </c>
       <c r="P85">
-        <v>-12.25066937286061</v>
+        <v>-3.18260729286061</v>
       </c>
       <c r="Q85">
-        <v>132.2493306271394</v>
+        <v>141.3173927071394</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2299002503000114</v>
+        <v>0.2266260028192399</v>
       </c>
       <c r="T85">
-        <v>2.847201769951808</v>
+        <v>2.797320754053381</v>
       </c>
       <c r="U85">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V85">
-        <v>0.1747019417579916</v>
+        <v>0.1927488886671074</v>
       </c>
       <c r="W85">
-        <v>0.14808403753937</v>
+        <v>0.13128403753937</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8735097087899582</v>
+        <v>0.963744443335537</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1633291034863466</v>
+        <v>0.1486604814146154</v>
       </c>
       <c r="C86">
-        <v>-294.2760338566053</v>
+        <v>-264.4634267918856</v>
       </c>
       <c r="D86">
-        <v>209.4599661433947</v>
+        <v>239.2725732081145</v>
       </c>
       <c r="E86">
         <v>471.036</v>
@@ -8339,37 +8339,37 @@
         <v>105.75</v>
       </c>
       <c r="M86">
-        <v>122.5219311343417</v>
+        <v>111.0502863343417</v>
       </c>
       <c r="N86">
-        <v>-16.77193113434171</v>
+        <v>-5.300286334341706</v>
       </c>
       <c r="O86">
-        <v>-3.354386226868343</v>
+        <v>-1.060057266868341</v>
       </c>
       <c r="P86">
-        <v>-13.41754490747337</v>
+        <v>-4.240229067473365</v>
       </c>
       <c r="Q86">
-        <v>131.0824550925266</v>
+        <v>140.2597709325266</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.241406515943762</v>
+        <v>0.2379276279954423</v>
       </c>
       <c r="T86">
-        <v>3.025151880573794</v>
+        <v>2.972153301181716</v>
       </c>
       <c r="U86">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V86">
-        <v>0.1726221567370632</v>
+        <v>0.1904542590401181</v>
       </c>
       <c r="W86">
-        <v>0.1484572153992199</v>
+        <v>0.1316572153992198</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.863110783685316</v>
+        <v>0.9522712952005904</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1646654132640142</v>
+        <v>0.149828791192283</v>
       </c>
       <c r="C87">
-        <v>-304.759826500666</v>
+        <v>-275.2796106340012</v>
       </c>
       <c r="D87">
-        <v>207.105173499334</v>
+        <v>236.5853893659988</v>
       </c>
       <c r="E87">
         <v>479.165</v>
@@ -8421,37 +8421,37 @@
         <v>105.75</v>
       </c>
       <c r="M87">
-        <v>123.9805255526077</v>
+        <v>112.3723135526077</v>
       </c>
       <c r="N87">
-        <v>-18.23052555260769</v>
+        <v>-6.622313552607693</v>
       </c>
       <c r="O87">
-        <v>-3.646105110521538</v>
+        <v>-1.324462710521539</v>
       </c>
       <c r="P87">
-        <v>-14.58442044208615</v>
+        <v>-5.297850842086154</v>
       </c>
       <c r="Q87">
-        <v>129.9155795579138</v>
+        <v>139.2021491579139</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2544469503400128</v>
+        <v>0.2507361365284718</v>
       </c>
       <c r="T87">
-        <v>3.226828672612047</v>
+        <v>3.17029685459383</v>
       </c>
       <c r="U87">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V87">
-        <v>0.1705913078342742</v>
+        <v>0.1882136206984696</v>
       </c>
       <c r="W87">
-        <v>0.1488216126035438</v>
+        <v>0.1320216126035438</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8529565391713712</v>
+        <v>0.941068103492348</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1660017230416818</v>
+        <v>0.1509971009699506</v>
       </c>
       <c r="C88">
-        <v>-315.1912616184782</v>
+        <v>-286.0361072199436</v>
       </c>
       <c r="D88">
-        <v>204.8027383815218</v>
+        <v>233.9578927800564</v>
       </c>
       <c r="E88">
         <v>487.294</v>
@@ -8503,37 +8503,37 @@
         <v>105.75</v>
       </c>
       <c r="M88">
-        <v>125.4391199708736</v>
+        <v>113.6943407708736</v>
       </c>
       <c r="N88">
-        <v>-19.68911997087368</v>
+        <v>-7.944340770873666</v>
       </c>
       <c r="O88">
-        <v>-3.937823994174735</v>
+        <v>-1.588868154174733</v>
       </c>
       <c r="P88">
-        <v>-15.75129597669894</v>
+        <v>-6.355472616698933</v>
       </c>
       <c r="Q88">
-        <v>128.7487040233011</v>
+        <v>138.1445273833011</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2693503039357281</v>
+        <v>0.2653744319947912</v>
       </c>
       <c r="T88">
-        <v>3.45731643494148</v>
+        <v>3.396746629921961</v>
       </c>
       <c r="U88">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V88">
-        <v>0.1686076879757361</v>
+        <v>0.1860250902252316</v>
       </c>
       <c r="W88">
-        <v>0.1491775354542789</v>
+        <v>0.1323775354542789</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8430384398786807</v>
+        <v>0.930125451126158</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1673380328193493</v>
+        <v>0.1521654107476182</v>
       </c>
       <c r="C89">
-        <v>-325.5720662218909</v>
+        <v>-296.7348833508892</v>
       </c>
       <c r="D89">
-        <v>202.5509337781093</v>
+        <v>231.3881166491109</v>
       </c>
       <c r="E89">
         <v>495.4230000000001</v>
@@ -8585,37 +8585,37 @@
         <v>105.75</v>
       </c>
       <c r="M89">
-        <v>126.8977143891396</v>
+        <v>115.0163679891396</v>
       </c>
       <c r="N89">
-        <v>-21.14771438913965</v>
+        <v>-9.266367989139638</v>
       </c>
       <c r="O89">
-        <v>-4.229542877827931</v>
+        <v>-1.853273597827928</v>
       </c>
       <c r="P89">
-        <v>-16.91817151131172</v>
+        <v>-7.413094391311711</v>
       </c>
       <c r="Q89">
-        <v>127.5818284886883</v>
+        <v>137.0869056086883</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2865464811615533</v>
+        <v>0.2822647729174674</v>
       </c>
       <c r="T89">
-        <v>3.723263853013902</v>
+        <v>3.65803483222365</v>
       </c>
       <c r="U89">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V89">
-        <v>0.1666696685737162</v>
+        <v>0.1838868707973554</v>
       </c>
       <c r="W89">
-        <v>0.1495252761705143</v>
+        <v>0.1327252761705143</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8333483428685808</v>
+        <v>0.9194343539867768</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1686743425970169</v>
+        <v>0.1533337205252858</v>
       </c>
       <c r="C90">
-        <v>-335.9038921948533</v>
+        <v>-307.3778203540609</v>
       </c>
       <c r="D90">
-        <v>200.3481078051468</v>
+        <v>228.8741796459392</v>
       </c>
       <c r="E90">
         <v>503.5520000000001</v>
@@ -8667,37 +8667,37 @@
         <v>105.75</v>
       </c>
       <c r="M90">
-        <v>128.3563088074056</v>
+        <v>116.3383952074056</v>
       </c>
       <c r="N90">
-        <v>-22.60630880740561</v>
+        <v>-10.58839520740561</v>
       </c>
       <c r="O90">
-        <v>-4.521261761481123</v>
+        <v>-2.117679041481122</v>
       </c>
       <c r="P90">
-        <v>-18.08504704592449</v>
+        <v>-8.47071616592449</v>
       </c>
       <c r="Q90">
-        <v>126.4149529540755</v>
+        <v>136.0292838340755</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3066086879250161</v>
+        <v>0.3019701706605897</v>
       </c>
       <c r="T90">
-        <v>4.03353584076506</v>
+        <v>3.962871068242289</v>
       </c>
       <c r="U90">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V90">
-        <v>0.1647756950671967</v>
+        <v>0.1817972472655672</v>
       </c>
       <c r="W90">
-        <v>0.1498651136886534</v>
+        <v>0.1330651136886534</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8238784753359834</v>
+        <v>0.9089862363278362</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1700106523746845</v>
+        <v>0.1545020303029533</v>
       </c>
       <c r="C91">
-        <v>-346.1883203347007</v>
+        <v>-317.966718676022</v>
       </c>
       <c r="D91">
-        <v>198.1926796652994</v>
+        <v>226.4142813239781</v>
       </c>
       <c r="E91">
         <v>511.6810000000001</v>
@@ -8749,37 +8749,37 @@
         <v>105.75</v>
       </c>
       <c r="M91">
-        <v>129.8149032256716</v>
+        <v>117.6604224256716</v>
       </c>
       <c r="N91">
-        <v>-24.0649032256716</v>
+        <v>-11.91042242567158</v>
       </c>
       <c r="O91">
-        <v>-4.812980645134321</v>
+        <v>-2.382084485134317</v>
       </c>
       <c r="P91">
-        <v>-19.25192258053728</v>
+        <v>-9.528337940537266</v>
       </c>
       <c r="Q91">
-        <v>125.2480774194627</v>
+        <v>134.9716620594627</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3303185686454722</v>
+        <v>0.3252583679933707</v>
       </c>
       <c r="T91">
-        <v>4.400220917198248</v>
+        <v>4.323132074446133</v>
       </c>
       <c r="U91">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V91">
-        <v>0.1629242827630709</v>
+        <v>0.1797545815659541</v>
       </c>
       <c r="W91">
-        <v>0.1501973144086321</v>
+        <v>0.1333973144086321</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8146214138153542</v>
+        <v>0.8987729078297706</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1713469621523521</v>
+        <v>0.1556703400806209</v>
       </c>
       <c r="C92">
-        <v>-356.4268641353503</v>
+        <v>-328.5033021829109</v>
       </c>
       <c r="D92">
-        <v>196.0831358646498</v>
+        <v>224.0066978170892</v>
       </c>
       <c r="E92">
         <v>519.8100000000002</v>
@@ -8831,37 +8831,37 @@
         <v>105.75</v>
       </c>
       <c r="M92">
-        <v>131.2734976439375</v>
+        <v>118.9824496439375</v>
       </c>
       <c r="N92">
-        <v>-25.52349764393756</v>
+        <v>-13.23244964393757</v>
       </c>
       <c r="O92">
-        <v>-5.104699528787513</v>
+        <v>-2.646489928787514</v>
       </c>
       <c r="P92">
-        <v>-20.41879811515005</v>
+        <v>-10.58595971515006</v>
       </c>
       <c r="Q92">
-        <v>124.0812018848499</v>
+        <v>133.9140402848499</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3587704255100194</v>
+        <v>0.3532042047927077</v>
       </c>
       <c r="T92">
-        <v>4.840243008918073</v>
+        <v>4.755445281890746</v>
       </c>
       <c r="U92">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V92">
-        <v>0.1611140129545923</v>
+        <v>0.1777573084374435</v>
       </c>
       <c r="W92">
-        <v>0.150522132890389</v>
+        <v>0.133722132890389</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8055700647729616</v>
+        <v>0.8887865421872174</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2213814289660032</v>
+        <v>0.1568386498582885</v>
       </c>
       <c r="C93">
-        <v>-420.43258875203</v>
+        <v>-338.9892221892037</v>
       </c>
       <c r="D93">
-        <v>140.2064112479701</v>
+        <v>221.6497778107965</v>
       </c>
       <c r="E93">
         <v>527.9390000000001</v>
@@ -8913,45 +8913,45 @@
         <v>105.75</v>
       </c>
       <c r="M93">
-        <v>171.3464678622035</v>
+        <v>120.3044768622035</v>
       </c>
       <c r="N93">
-        <v>-65.59646786220355</v>
+        <v>-14.55447686220354</v>
       </c>
       <c r="O93">
-        <v>-13.11929357244071</v>
+        <v>-2.910895372440709</v>
       </c>
       <c r="P93">
-        <v>-52.47717428976284</v>
+        <v>-11.64358148976283</v>
       </c>
       <c r="Q93">
-        <v>92.02282571023716</v>
+        <v>132.8564185102372</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4068355509665047</v>
+        <v>0.3873602275474531</v>
       </c>
       <c r="T93">
-        <v>5.583594036684993</v>
+        <v>5.28382809098972</v>
       </c>
       <c r="U93">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V93">
-        <v>0.123434117223874</v>
+        <v>0.1758039314216474</v>
       </c>
       <c r="W93">
-        <v>0.2030398125044151</v>
+        <v>0.1340398125044151</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.6171705861193701</v>
+        <v>0.879019657108237</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2232397387436707</v>
+        <v>0.1580069596359561</v>
       </c>
       <c r="C94">
-        <v>-430.0299573754204</v>
+        <v>-349.4260612347883</v>
       </c>
       <c r="D94">
-        <v>138.7380426245798</v>
+        <v>219.3419387652118</v>
       </c>
       <c r="E94">
         <v>536.0680000000002</v>
@@ -8995,45 +8995,45 @@
         <v>105.75</v>
       </c>
       <c r="M94">
-        <v>173.2293960804695</v>
+        <v>121.6265040804695</v>
       </c>
       <c r="N94">
-        <v>-67.47939608046954</v>
+        <v>-15.87650408046952</v>
       </c>
       <c r="O94">
-        <v>-13.49587921609391</v>
+        <v>-3.175300816093904</v>
       </c>
       <c r="P94">
-        <v>-53.98351686437563</v>
+        <v>-12.70120326437561</v>
       </c>
       <c r="Q94">
-        <v>90.51648313562437</v>
+        <v>131.7987967356244</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4519649948373179</v>
+        <v>0.4300552559908848</v>
       </c>
       <c r="T94">
-        <v>6.281543291270619</v>
+        <v>5.944306602363436</v>
       </c>
       <c r="U94">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V94">
-        <v>0.122092442036658</v>
+        <v>0.173893019123586</v>
       </c>
       <c r="W94">
-        <v>0.2033505860398753</v>
+        <v>0.1343505860398753</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.6104622101832899</v>
+        <v>0.8694650956179302</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2250980485213383</v>
+        <v>0.1591752694136236</v>
       </c>
       <c r="C95">
-        <v>-439.5968885925748</v>
+        <v>-359.815336628508</v>
       </c>
       <c r="D95">
-        <v>137.3001114074253</v>
+        <v>217.0816633714921</v>
       </c>
       <c r="E95">
         <v>544.1970000000001</v>
@@ -9077,45 +9077,45 @@
         <v>105.75</v>
       </c>
       <c r="M95">
-        <v>175.1123242987354</v>
+        <v>122.9485312987354</v>
       </c>
       <c r="N95">
-        <v>-69.36232429873547</v>
+        <v>-17.19853129873547</v>
       </c>
       <c r="O95">
-        <v>-13.8724648597471</v>
+        <v>-3.439706259747095</v>
       </c>
       <c r="P95">
-        <v>-55.48985943898838</v>
+        <v>-13.75882503898838</v>
       </c>
       <c r="Q95">
-        <v>89.01014056101162</v>
+        <v>130.7411749610116</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5099885655283635</v>
+        <v>0.4849488639895827</v>
       </c>
       <c r="T95">
-        <v>7.178906618594995</v>
+        <v>6.793493259843927</v>
       </c>
       <c r="U95">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V95">
-        <v>0.1207796200792746</v>
+        <v>0.172023201713655</v>
       </c>
       <c r="W95">
-        <v>0.2036546762734977</v>
+        <v>0.1346546762734977</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.603898100396373</v>
+        <v>0.8601160085682751</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2269563582990059</v>
+        <v>0.1603435791912912</v>
       </c>
       <c r="C96">
-        <v>-449.1343190881918</v>
+        <v>-370.1585037748454</v>
       </c>
       <c r="D96">
-        <v>135.8916809118083</v>
+        <v>214.8674962251547</v>
       </c>
       <c r="E96">
         <v>552.326</v>
@@ -9159,45 +9159,45 @@
         <v>105.75</v>
       </c>
       <c r="M96">
-        <v>176.9952525170014</v>
+        <v>124.2705585170014</v>
       </c>
       <c r="N96">
-        <v>-71.24525251700146</v>
+        <v>-18.52055851700145</v>
       </c>
       <c r="O96">
-        <v>-14.24905050340029</v>
+        <v>-3.70411170340029</v>
       </c>
       <c r="P96">
-        <v>-56.99620201360117</v>
+        <v>-14.81644681360116</v>
       </c>
       <c r="Q96">
-        <v>87.50379798639884</v>
+        <v>129.6835531863989</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5873533264497574</v>
+        <v>0.5581403413211798</v>
       </c>
       <c r="T96">
-        <v>8.375391055027496</v>
+        <v>7.925742136484584</v>
       </c>
       <c r="U96">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V96">
-        <v>0.1194947305039632</v>
+        <v>0.1701931676528715</v>
       </c>
       <c r="W96">
-        <v>0.2039522965021494</v>
+        <v>0.1349522965021494</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.5974736525198159</v>
+        <v>0.8509658382643572</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2288146680766734</v>
+        <v>0.1615118889689588</v>
       </c>
       <c r="C97">
-        <v>-458.6431475030178</v>
+        <v>-380.4569592990755</v>
       </c>
       <c r="D97">
-        <v>134.5118524969824</v>
+        <v>212.6980407009247</v>
       </c>
       <c r="E97">
         <v>560.4550000000002</v>
@@ -9241,45 +9241,45 @@
         <v>105.75</v>
       </c>
       <c r="M97">
-        <v>178.8781807352674</v>
+        <v>125.5925857352674</v>
       </c>
       <c r="N97">
-        <v>-73.12818073526745</v>
+        <v>-19.84258573526742</v>
       </c>
       <c r="O97">
-        <v>-14.62563614705349</v>
+        <v>-3.968517147053484</v>
       </c>
       <c r="P97">
-        <v>-58.50254458821396</v>
+        <v>-15.87406858821394</v>
       </c>
       <c r="Q97">
-        <v>85.99745541178604</v>
+        <v>128.6259314117861</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6956639917397092</v>
+        <v>0.6606084095854161</v>
       </c>
       <c r="T97">
-        <v>10.050469266033</v>
+        <v>9.510890563781505</v>
       </c>
       <c r="U97">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V97">
-        <v>0.1182368912355004</v>
+        <v>0.1684016606249465</v>
       </c>
       <c r="W97">
-        <v>0.2042436510417769</v>
+        <v>0.1352436510417769</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5911844561775019</v>
+        <v>0.8420083031247324</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.230672977854341</v>
+        <v>0.1626801987466263</v>
       </c>
       <c r="C98">
-        <v>-468.1242363459002</v>
+        <v>-390.7120439849879</v>
       </c>
       <c r="D98">
-        <v>133.1597636540999</v>
+        <v>210.5719560150121</v>
       </c>
       <c r="E98">
         <v>568.5840000000001</v>
@@ -9323,45 +9323,45 @@
         <v>105.75</v>
       </c>
       <c r="M98">
-        <v>180.7611089535334</v>
+        <v>126.9146129535334</v>
       </c>
       <c r="N98">
-        <v>-75.01110895353338</v>
+        <v>-21.16461295353338</v>
       </c>
       <c r="O98">
-        <v>-15.00222179070668</v>
+        <v>-4.232922590706676</v>
       </c>
       <c r="P98">
-        <v>-60.0088871628267</v>
+        <v>-16.9316903628267</v>
       </c>
       <c r="Q98">
-        <v>84.49111283717329</v>
+        <v>127.5683096371733</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8581299896746346</v>
+        <v>0.8143105119817683</v>
       </c>
       <c r="T98">
-        <v>12.56308658254122</v>
+        <v>11.88861320472685</v>
       </c>
       <c r="U98">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V98">
-        <v>0.1170052569517973</v>
+        <v>0.1666474766601033</v>
       </c>
       <c r="W98">
-        <v>0.2045289356951621</v>
+        <v>0.1355289356951621</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5850262847589864</v>
+        <v>0.8332373833005166</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2325312876320086</v>
+        <v>0.1638485085242939</v>
       </c>
       <c r="C99">
-        <v>-477.5784137916744</v>
+        <v>-400.9250455381655</v>
       </c>
       <c r="D99">
-        <v>131.8345862083256</v>
+        <v>208.4879544618345</v>
       </c>
       <c r="E99">
         <v>576.713</v>
@@ -9405,45 +9405,45 @@
         <v>105.75</v>
       </c>
       <c r="M99">
-        <v>182.6440371717993</v>
+        <v>128.2366401717993</v>
       </c>
       <c r="N99">
-        <v>-76.89403717179937</v>
+        <v>-22.48664017179937</v>
       </c>
       <c r="O99">
-        <v>-15.37880743435987</v>
+        <v>-4.497328034359874</v>
       </c>
       <c r="P99">
-        <v>-61.5152297374395</v>
+        <v>-17.98931213743949</v>
       </c>
       <c r="Q99">
-        <v>82.9847702625605</v>
+        <v>126.5106878625605</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.128906652899513</v>
+        <v>1.070480682642358</v>
       </c>
       <c r="T99">
-        <v>16.75078211005496</v>
+        <v>15.85148427296914</v>
       </c>
       <c r="U99">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V99">
-        <v>0.1157990171894076</v>
+        <v>0.1649294614368033</v>
       </c>
       <c r="W99">
-        <v>0.2048083381907455</v>
+        <v>0.1358083381907455</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.5789950859470381</v>
+        <v>0.8246473071840164</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2343895974096761</v>
+        <v>0.1650168183019615</v>
       </c>
       <c r="C100">
-        <v>-487.0064753727514</v>
+        <v>-411.0972011867815</v>
       </c>
       <c r="D100">
-        <v>130.5355246272487</v>
+        <v>206.4447988132186</v>
       </c>
       <c r="E100">
         <v>584.8420000000001</v>
@@ -9487,45 +9487,45 @@
         <v>105.75</v>
       </c>
       <c r="M100">
-        <v>184.5269653900653</v>
+        <v>129.5586673900653</v>
       </c>
       <c r="N100">
-        <v>-78.77696539006533</v>
+        <v>-23.80866739006532</v>
       </c>
       <c r="O100">
-        <v>-15.75539307801307</v>
+        <v>-4.761733478013065</v>
       </c>
       <c r="P100">
-        <v>-63.02157231205226</v>
+        <v>-19.04693391205226</v>
       </c>
       <c r="Q100">
-        <v>81.47842768794774</v>
+        <v>125.4530660879477</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.670459979349269</v>
+        <v>1.582821023963537</v>
       </c>
       <c r="T100">
-        <v>25.12617316508244</v>
+        <v>23.77722640945371</v>
       </c>
       <c r="U100">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V100">
-        <v>0.1146173945650259</v>
+        <v>0.1632465077486726</v>
       </c>
       <c r="W100">
-        <v>0.2050820385945824</v>
+        <v>0.1360820385945824</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5730869728251295</v>
+        <v>0.8162325387433631</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2362479071873437</v>
+        <v>0.1661851280796291</v>
       </c>
       <c r="C101">
-        <v>-496.4091855716729</v>
+        <v>-421.2297001309581</v>
       </c>
       <c r="D101">
-        <v>129.2618144283272</v>
+        <v>204.4412998690419</v>
       </c>
       <c r="E101">
         <v>592.971</v>
@@ -9569,45 +9569,45 @@
         <v>105.75</v>
       </c>
       <c r="M101">
-        <v>186.4098936083313</v>
+        <v>130.8806946083313</v>
       </c>
       <c r="N101">
-        <v>-80.65989360833132</v>
+        <v>-25.13069460833131</v>
       </c>
       <c r="O101">
-        <v>-16.13197872166626</v>
+        <v>-5.026138921666263</v>
       </c>
       <c r="P101">
-        <v>-64.52791488666506</v>
+        <v>-20.10455568666505</v>
       </c>
       <c r="Q101">
-        <v>79.97208511333494</v>
+        <v>124.3954443133349</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.295119958698538</v>
+        <v>3.119842047927074</v>
       </c>
       <c r="T101">
-        <v>50.25234633016488</v>
+        <v>47.55445281890741</v>
       </c>
       <c r="U101">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V101">
-        <v>0.1134596431047731</v>
+        <v>0.1615975531249487</v>
       </c>
       <c r="W101">
-        <v>0.2053502096973316</v>
+        <v>0.1363502096973316</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.5672982155238655</v>
+        <v>0.8079877656247432</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_oil_gas_distribution.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08239493608629718</v>
+        <v>0.08239279403625864</v>
       </c>
       <c r="C2">
-        <v>851.6436549871778</v>
+        <v>843.5540239995756</v>
       </c>
       <c r="D2">
-        <v>672.5436549871778</v>
+        <v>672.5830239995756</v>
       </c>
       <c r="E2">
-        <v>-211.8</v>
+        <v>-203.671</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.129000000000001</v>
       </c>
       <c r="G2">
         <v>179.1</v>
@@ -1451,28 +1451,28 @@
         <v>105.75</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5375787182659725</v>
       </c>
       <c r="N2">
-        <v>105.75</v>
+        <v>105.212421281734</v>
       </c>
       <c r="O2">
-        <v>21.15</v>
+        <v>21.0424842563468</v>
       </c>
       <c r="P2">
-        <v>84.59999999999998</v>
+        <v>84.1699370253872</v>
       </c>
       <c r="Q2">
-        <v>229.1</v>
+        <v>228.6699370253872</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08239493608629718</v>
+        <v>0.08269065274153999</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5706866652781318</v>
       </c>
       <c r="U2">
         <v>0.06613097776675758</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>196.7153765705418</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08239279403625864</v>
+        <v>0.08239065198622011</v>
       </c>
       <c r="C3">
-        <v>843.5540239995756</v>
+        <v>835.4643976213687</v>
       </c>
       <c r="D3">
-        <v>672.5830239995756</v>
+        <v>672.6223976213687</v>
       </c>
       <c r="E3">
-        <v>-203.671</v>
+        <v>-195.542</v>
       </c>
       <c r="F3">
-        <v>8.129000000000001</v>
+        <v>16.258</v>
       </c>
       <c r="G3">
         <v>179.1</v>
@@ -1533,28 +1533,28 @@
         <v>105.75</v>
       </c>
       <c r="M3">
-        <v>0.5375787182659725</v>
+        <v>1.075157436531945</v>
       </c>
       <c r="N3">
-        <v>105.212421281734</v>
+        <v>104.674842563468</v>
       </c>
       <c r="O3">
-        <v>21.0424842563468</v>
+        <v>20.93496851269361</v>
       </c>
       <c r="P3">
-        <v>84.1699370253872</v>
+        <v>83.73987405077443</v>
       </c>
       <c r="Q3">
-        <v>228.6699370253872</v>
+        <v>228.2398740507744</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08269065274153999</v>
+        <v>0.08299240443056326</v>
       </c>
       <c r="T3">
-        <v>0.5706866652781318</v>
+        <v>0.5753546679387848</v>
       </c>
       <c r="U3">
         <v>0.06613097776675758</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>196.7153765705418</v>
+        <v>98.35768828527091</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08239065198622011</v>
+        <v>0.08238850993618156</v>
       </c>
       <c r="C4">
-        <v>835.4643976213687</v>
+        <v>827.3747758533677</v>
       </c>
       <c r="D4">
-        <v>672.6223976213687</v>
+        <v>672.6617758533677</v>
       </c>
       <c r="E4">
-        <v>-195.542</v>
+        <v>-187.413</v>
       </c>
       <c r="F4">
-        <v>16.258</v>
+        <v>24.387</v>
       </c>
       <c r="G4">
         <v>179.1</v>
@@ -1615,28 +1615,28 @@
         <v>105.75</v>
       </c>
       <c r="M4">
-        <v>1.075157436531945</v>
+        <v>1.612736154797917</v>
       </c>
       <c r="N4">
-        <v>104.674842563468</v>
+        <v>104.1372638452021</v>
       </c>
       <c r="O4">
-        <v>20.93496851269361</v>
+        <v>20.82745276904041</v>
       </c>
       <c r="P4">
-        <v>83.73987405077443</v>
+        <v>83.30981107616165</v>
       </c>
       <c r="Q4">
-        <v>228.2398740507744</v>
+        <v>227.8098110761617</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08299240443056326</v>
+        <v>0.08330037780389628</v>
       </c>
       <c r="T4">
-        <v>0.5753546679387848</v>
+        <v>0.5801189180769769</v>
       </c>
       <c r="U4">
         <v>0.06613097776675758</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>98.35768828527091</v>
+        <v>65.57179219018062</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08238850993618156</v>
+        <v>0.08238636788614304</v>
       </c>
       <c r="C5">
-        <v>827.3747758533677</v>
+        <v>819.2851586963808</v>
       </c>
       <c r="D5">
-        <v>672.6617758533677</v>
+        <v>672.7011586963807</v>
       </c>
       <c r="E5">
-        <v>-187.413</v>
+        <v>-179.284</v>
       </c>
       <c r="F5">
-        <v>24.387</v>
+        <v>32.51600000000001</v>
       </c>
       <c r="G5">
         <v>179.1</v>
@@ -1697,28 +1697,28 @@
         <v>105.75</v>
       </c>
       <c r="M5">
-        <v>1.612736154797917</v>
+        <v>2.15031487306389</v>
       </c>
       <c r="N5">
-        <v>104.1372638452021</v>
+        <v>103.5996851269361</v>
       </c>
       <c r="O5">
-        <v>20.82745276904041</v>
+        <v>20.71993702538722</v>
       </c>
       <c r="P5">
-        <v>83.30981107616165</v>
+        <v>82.87974810154887</v>
       </c>
       <c r="Q5">
-        <v>227.8098110761617</v>
+        <v>227.3797481015489</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08330037780389628</v>
+        <v>0.08361476728917375</v>
       </c>
       <c r="T5">
-        <v>0.5801189180769769</v>
+        <v>0.5849824234263816</v>
       </c>
       <c r="U5">
         <v>0.06613097776675758</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.57179219018062</v>
+        <v>49.17884414263545</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08238636788614304</v>
+        <v>0.0823842258361045</v>
       </c>
       <c r="C6">
-        <v>819.2851586963808</v>
+        <v>811.195546151219</v>
       </c>
       <c r="D6">
-        <v>672.7011586963807</v>
+        <v>672.740546151219</v>
       </c>
       <c r="E6">
-        <v>-179.284</v>
+        <v>-171.155</v>
       </c>
       <c r="F6">
-        <v>32.51600000000001</v>
+        <v>40.64500000000001</v>
       </c>
       <c r="G6">
         <v>179.1</v>
@@ -1779,28 +1779,28 @@
         <v>105.75</v>
       </c>
       <c r="M6">
-        <v>2.15031487306389</v>
+        <v>2.687893591329863</v>
       </c>
       <c r="N6">
-        <v>103.5996851269361</v>
+        <v>103.0621064086701</v>
       </c>
       <c r="O6">
-        <v>20.71993702538722</v>
+        <v>20.61242128173402</v>
       </c>
       <c r="P6">
-        <v>82.87974810154887</v>
+        <v>82.44968512693609</v>
       </c>
       <c r="Q6">
-        <v>227.3797481015489</v>
+        <v>226.9496851269361</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08361476728917375</v>
+        <v>0.08393577550045705</v>
       </c>
       <c r="T6">
-        <v>0.5849824234263816</v>
+        <v>0.5899483183620893</v>
       </c>
       <c r="U6">
         <v>0.06613097776675758</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.17884414263545</v>
+        <v>39.34307531410835</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0823842258361045</v>
+        <v>0.08238208378606597</v>
       </c>
       <c r="C7">
-        <v>811.195546151219</v>
+        <v>803.1059382186919</v>
       </c>
       <c r="D7">
-        <v>672.740546151219</v>
+        <v>672.7799382186919</v>
       </c>
       <c r="E7">
-        <v>-171.155</v>
+        <v>-163.026</v>
       </c>
       <c r="F7">
-        <v>40.64500000000001</v>
+        <v>48.77400000000001</v>
       </c>
       <c r="G7">
         <v>179.1</v>
@@ -1861,28 +1861,28 @@
         <v>105.75</v>
       </c>
       <c r="M7">
-        <v>2.687893591329863</v>
+        <v>3.225472309595835</v>
       </c>
       <c r="N7">
-        <v>103.0621064086701</v>
+        <v>102.5245276904041</v>
       </c>
       <c r="O7">
-        <v>20.61242128173402</v>
+        <v>20.50490553808083</v>
       </c>
       <c r="P7">
-        <v>82.44968512693609</v>
+        <v>82.01962215232331</v>
       </c>
       <c r="Q7">
-        <v>226.9496851269361</v>
+        <v>226.5196221523233</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08393577550045705</v>
+        <v>0.08426361367368257</v>
       </c>
       <c r="T7">
-        <v>0.5899483183620893</v>
+        <v>0.5950198706368549</v>
       </c>
       <c r="U7">
         <v>0.06613097776675758</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.34307531410835</v>
+        <v>32.78589609509031</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08238208378606597</v>
+        <v>0.08237994173602746</v>
       </c>
       <c r="C8">
-        <v>803.1059382186919</v>
+        <v>795.0163348996098</v>
       </c>
       <c r="D8">
-        <v>672.7799382186919</v>
+        <v>672.8193348996098</v>
       </c>
       <c r="E8">
-        <v>-163.026</v>
+        <v>-154.897</v>
       </c>
       <c r="F8">
-        <v>48.774</v>
+        <v>56.903</v>
       </c>
       <c r="G8">
         <v>179.1</v>
@@ -1943,28 +1943,28 @@
         <v>105.75</v>
       </c>
       <c r="M8">
-        <v>3.225472309595834</v>
+        <v>3.763051027861807</v>
       </c>
       <c r="N8">
-        <v>102.5245276904041</v>
+        <v>101.9869489721382</v>
       </c>
       <c r="O8">
-        <v>20.50490553808083</v>
+        <v>20.39738979442764</v>
       </c>
       <c r="P8">
-        <v>82.01962215232331</v>
+        <v>81.58955917771053</v>
       </c>
       <c r="Q8">
-        <v>226.5196221523233</v>
+        <v>226.0895591777105</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08426361367368257</v>
+        <v>0.08459850213020326</v>
       </c>
       <c r="T8">
-        <v>0.5950198706368549</v>
+        <v>0.6002004885519379</v>
       </c>
       <c r="U8">
         <v>0.06613097776675758</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.78589609509031</v>
+        <v>28.10219665293455</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08237994173602745</v>
+        <v>0.08237779968598891</v>
       </c>
       <c r="C9">
-        <v>795.01633489961</v>
+        <v>786.9267361947843</v>
       </c>
       <c r="D9">
-        <v>672.81933489961</v>
+        <v>672.8587361947843</v>
       </c>
       <c r="E9">
-        <v>-154.897</v>
+        <v>-146.768</v>
       </c>
       <c r="F9">
-        <v>56.90300000000001</v>
+        <v>65.03200000000001</v>
       </c>
       <c r="G9">
         <v>179.1</v>
@@ -2025,28 +2025,28 @@
         <v>105.75</v>
       </c>
       <c r="M9">
-        <v>3.763051027861807</v>
+        <v>4.30062974612778</v>
       </c>
       <c r="N9">
-        <v>101.9869489721382</v>
+        <v>101.4493702538722</v>
       </c>
       <c r="O9">
-        <v>20.39738979442764</v>
+        <v>20.28987405077444</v>
       </c>
       <c r="P9">
-        <v>81.58955917771053</v>
+        <v>81.15949620309775</v>
       </c>
       <c r="Q9">
-        <v>226.0895591777105</v>
+        <v>225.6594962030977</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08459850213020326</v>
+        <v>0.08494067077056133</v>
       </c>
       <c r="T9">
-        <v>0.6002004885519379</v>
+        <v>0.6054937285956096</v>
       </c>
       <c r="U9">
         <v>0.06613097776675758</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.10219665293454</v>
+        <v>24.58942207131772</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08237779968598891</v>
+        <v>0.08237565763595037</v>
       </c>
       <c r="C10">
-        <v>786.9267361947843</v>
+        <v>778.8371421050251</v>
       </c>
       <c r="D10">
-        <v>672.8587361947843</v>
+        <v>672.898142105025</v>
       </c>
       <c r="E10">
-        <v>-146.768</v>
+        <v>-138.639</v>
       </c>
       <c r="F10">
-        <v>65.03200000000001</v>
+        <v>73.161</v>
       </c>
       <c r="G10">
         <v>179.1</v>
@@ -2107,28 +2107,28 @@
         <v>105.75</v>
       </c>
       <c r="M10">
-        <v>4.30062974612778</v>
+        <v>4.838208464393752</v>
       </c>
       <c r="N10">
-        <v>101.4493702538722</v>
+        <v>100.9117915356062</v>
       </c>
       <c r="O10">
-        <v>20.28987405077444</v>
+        <v>20.18235830712125</v>
       </c>
       <c r="P10">
-        <v>81.15949620309775</v>
+        <v>80.72943322848498</v>
       </c>
       <c r="Q10">
-        <v>225.6594962030977</v>
+        <v>225.229433228485</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08494067077056133</v>
+        <v>0.08529035960081739</v>
       </c>
       <c r="T10">
-        <v>0.6054937285956096</v>
+        <v>0.610903303585296</v>
       </c>
       <c r="U10">
         <v>0.06613097776675758</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.58942207131772</v>
+        <v>21.85726406339354</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08237565763595037</v>
+        <v>0.08237351558591183</v>
       </c>
       <c r="C11">
-        <v>778.8371421050251</v>
+        <v>770.7475526311432</v>
       </c>
       <c r="D11">
-        <v>672.898142105025</v>
+        <v>672.9375526311431</v>
       </c>
       <c r="E11">
-        <v>-138.639</v>
+        <v>-130.51</v>
       </c>
       <c r="F11">
-        <v>73.161</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="G11">
         <v>179.1</v>
@@ -2189,28 +2189,28 @@
         <v>105.75</v>
       </c>
       <c r="M11">
-        <v>4.838208464393752</v>
+        <v>5.375787182659725</v>
       </c>
       <c r="N11">
-        <v>100.9117915356062</v>
+        <v>100.3742128173403</v>
       </c>
       <c r="O11">
-        <v>20.18235830712125</v>
+        <v>20.07484256346805</v>
       </c>
       <c r="P11">
-        <v>80.72943322848498</v>
+        <v>80.2993702538722</v>
       </c>
       <c r="Q11">
-        <v>225.229433228485</v>
+        <v>224.7993702538722</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08529035960081739</v>
+        <v>0.08564781929396803</v>
       </c>
       <c r="T11">
-        <v>0.610903303585296</v>
+        <v>0.616433091352531</v>
       </c>
       <c r="U11">
         <v>0.06613097776675758</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.85726406339354</v>
+        <v>19.67153765705418</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08237351558591186</v>
+        <v>0.08237137353587332</v>
       </c>
       <c r="C12">
-        <v>770.7475526311428</v>
+        <v>762.6579677739493</v>
       </c>
       <c r="D12">
-        <v>672.9375526311427</v>
+        <v>672.9769677739492</v>
       </c>
       <c r="E12">
-        <v>-130.51</v>
+        <v>-122.381</v>
       </c>
       <c r="F12">
-        <v>81.29000000000002</v>
+        <v>89.41900000000001</v>
       </c>
       <c r="G12">
         <v>179.1</v>
@@ -2271,28 +2271,28 @@
         <v>105.75</v>
       </c>
       <c r="M12">
-        <v>5.375787182659725</v>
+        <v>5.913365900925697</v>
       </c>
       <c r="N12">
-        <v>100.3742128173403</v>
+        <v>99.83663409907427</v>
       </c>
       <c r="O12">
-        <v>20.07484256346805</v>
+        <v>19.96732681981486</v>
       </c>
       <c r="P12">
-        <v>80.2993702538722</v>
+        <v>79.86930727925942</v>
       </c>
       <c r="Q12">
-        <v>224.7993702538722</v>
+        <v>224.3693072792594</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08564781929396804</v>
+        <v>0.08601331178921195</v>
       </c>
       <c r="T12">
-        <v>0.6164330913525312</v>
+        <v>0.6220871440134119</v>
       </c>
       <c r="U12">
         <v>0.06613097776675758</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.67153765705418</v>
+        <v>17.88321605186744</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08237137353587332</v>
+        <v>0.08236923148583479</v>
       </c>
       <c r="C13">
-        <v>762.6579677739493</v>
+        <v>754.5683875342552</v>
       </c>
       <c r="D13">
-        <v>672.9769677739492</v>
+        <v>673.0163875342552</v>
       </c>
       <c r="E13">
-        <v>-122.381</v>
+        <v>-114.252</v>
       </c>
       <c r="F13">
-        <v>89.41900000000001</v>
+        <v>97.548</v>
       </c>
       <c r="G13">
         <v>179.1</v>
@@ -2353,28 +2353,28 @@
         <v>105.75</v>
       </c>
       <c r="M13">
-        <v>5.913365900925697</v>
+        <v>6.450944619191668</v>
       </c>
       <c r="N13">
-        <v>99.83663409907427</v>
+        <v>99.2990553808083</v>
       </c>
       <c r="O13">
-        <v>19.96732681981486</v>
+        <v>19.85981107616166</v>
       </c>
       <c r="P13">
-        <v>79.86930727925942</v>
+        <v>79.43924430464664</v>
       </c>
       <c r="Q13">
-        <v>224.3693072792594</v>
+        <v>223.9392443046466</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08601331178921195</v>
+        <v>0.08638711093207506</v>
       </c>
       <c r="T13">
-        <v>0.6220871440134119</v>
+        <v>0.627869697871131</v>
       </c>
       <c r="U13">
         <v>0.06613097776675758</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.88321605186744</v>
+        <v>16.39294804754515</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08236923148583479</v>
+        <v>0.08236708943579624</v>
       </c>
       <c r="C14">
-        <v>754.5683875342552</v>
+        <v>746.4788119128729</v>
       </c>
       <c r="D14">
-        <v>673.0163875342552</v>
+        <v>673.0558119128729</v>
       </c>
       <c r="E14">
-        <v>-114.252</v>
+        <v>-106.123</v>
       </c>
       <c r="F14">
-        <v>97.548</v>
+        <v>105.677</v>
       </c>
       <c r="G14">
         <v>179.1</v>
@@ -2435,28 +2435,28 @@
         <v>105.75</v>
       </c>
       <c r="M14">
-        <v>6.450944619191668</v>
+        <v>6.988523337457642</v>
       </c>
       <c r="N14">
-        <v>99.2990553808083</v>
+        <v>98.76147666254234</v>
       </c>
       <c r="O14">
-        <v>19.85981107616166</v>
+        <v>19.75229533250847</v>
       </c>
       <c r="P14">
-        <v>79.43924430464664</v>
+        <v>79.00918133003387</v>
       </c>
       <c r="Q14">
-        <v>223.9392443046466</v>
+        <v>223.5091813300339</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08638711093207506</v>
+        <v>0.08676950315868212</v>
       </c>
       <c r="T14">
-        <v>0.627869697871131</v>
+        <v>0.6337851840014411</v>
       </c>
       <c r="U14">
         <v>0.06613097776675758</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.39294804754515</v>
+        <v>15.13195204388783</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08236708943579624</v>
+        <v>0.0823649473857577</v>
       </c>
       <c r="C15">
-        <v>746.4788119128729</v>
+        <v>738.3892409106132</v>
       </c>
       <c r="D15">
-        <v>673.0558119128729</v>
+        <v>673.0952409106133</v>
       </c>
       <c r="E15">
-        <v>-106.123</v>
+        <v>-97.99399999999999</v>
       </c>
       <c r="F15">
-        <v>105.677</v>
+        <v>113.806</v>
       </c>
       <c r="G15">
         <v>179.1</v>
@@ -2517,28 +2517,28 @@
         <v>105.75</v>
       </c>
       <c r="M15">
-        <v>6.988523337457642</v>
+        <v>7.526102055723615</v>
       </c>
       <c r="N15">
-        <v>98.76147666254234</v>
+        <v>98.22389794427636</v>
       </c>
       <c r="O15">
-        <v>19.75229533250847</v>
+        <v>19.64477958885527</v>
       </c>
       <c r="P15">
-        <v>79.00918133003387</v>
+        <v>78.57911835542109</v>
       </c>
       <c r="Q15">
-        <v>223.5091813300339</v>
+        <v>223.0791183554211</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08676950315868212</v>
+        <v>0.08716078822776843</v>
       </c>
       <c r="T15">
-        <v>0.6337851840014411</v>
+        <v>0.6398382395766424</v>
       </c>
       <c r="U15">
         <v>0.06613097776675758</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.13195204388783</v>
+        <v>14.05109832646727</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0823649473857577</v>
+        <v>0.08236280533571919</v>
       </c>
       <c r="C16">
-        <v>738.3892409106132</v>
+        <v>730.2996745282877</v>
       </c>
       <c r="D16">
-        <v>673.0952409106133</v>
+        <v>673.1346745282877</v>
       </c>
       <c r="E16">
-        <v>-97.99399999999999</v>
+        <v>-89.86499999999998</v>
       </c>
       <c r="F16">
-        <v>113.806</v>
+        <v>121.935</v>
       </c>
       <c r="G16">
         <v>179.1</v>
@@ -2599,28 +2599,28 @@
         <v>105.75</v>
       </c>
       <c r="M16">
-        <v>7.526102055723615</v>
+        <v>8.063680773989589</v>
       </c>
       <c r="N16">
-        <v>98.22389794427636</v>
+        <v>97.68631922601038</v>
       </c>
       <c r="O16">
-        <v>19.64477958885527</v>
+        <v>19.53726384520208</v>
       </c>
       <c r="P16">
-        <v>78.57911835542109</v>
+        <v>78.14905538080831</v>
       </c>
       <c r="Q16">
-        <v>223.0791183554211</v>
+        <v>222.6490553808083</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08716078822776843</v>
+        <v>0.08756128000436267</v>
       </c>
       <c r="T16">
-        <v>0.6398382395766424</v>
+        <v>0.6460337199889071</v>
       </c>
       <c r="U16">
         <v>0.06613097776675758</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.05109832646727</v>
+        <v>13.11435843803612</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08236280533571919</v>
+        <v>0.08255266328568063</v>
       </c>
       <c r="C17">
-        <v>730.2996745282878</v>
+        <v>718.6933763428335</v>
       </c>
       <c r="D17">
-        <v>673.1346745282877</v>
+        <v>669.6573763428335</v>
       </c>
       <c r="E17">
-        <v>-89.86500000000001</v>
+        <v>-81.73599999999999</v>
       </c>
       <c r="F17">
-        <v>121.935</v>
+        <v>130.064</v>
       </c>
       <c r="G17">
         <v>179.1</v>
@@ -2681,45 +2681,45 @@
         <v>105.75</v>
       </c>
       <c r="M17">
-        <v>8.063680773989585</v>
+        <v>8.796355492255559</v>
       </c>
       <c r="N17">
-        <v>97.68631922601038</v>
+        <v>96.95364450774441</v>
       </c>
       <c r="O17">
-        <v>19.53726384520208</v>
+        <v>19.39072890154888</v>
       </c>
       <c r="P17">
-        <v>78.14905538080831</v>
+        <v>77.56291560619553</v>
       </c>
       <c r="Q17">
-        <v>222.6490553808083</v>
+        <v>222.0629156061955</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08756128000436267</v>
+        <v>0.08797130729944722</v>
       </c>
       <c r="T17">
-        <v>0.6460337199889071</v>
+        <v>0.6523767118395591</v>
       </c>
       <c r="U17">
-        <v>0.06613097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.05290478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.11435843803612</v>
+        <v>12.02202435919101</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08255266328568063</v>
+        <v>0.0825625212356421</v>
       </c>
       <c r="C18">
-        <v>718.6933763428335</v>
+        <v>710.384806262071</v>
       </c>
       <c r="D18">
-        <v>669.6573763428335</v>
+        <v>669.477806262071</v>
       </c>
       <c r="E18">
-        <v>-81.73599999999999</v>
+        <v>-73.607</v>
       </c>
       <c r="F18">
-        <v>130.064</v>
+        <v>138.193</v>
       </c>
       <c r="G18">
         <v>179.1</v>
@@ -2763,28 +2763,28 @@
         <v>105.75</v>
       </c>
       <c r="M18">
-        <v>8.796355492255559</v>
+        <v>9.346127710521532</v>
       </c>
       <c r="N18">
-        <v>96.95364450774441</v>
+        <v>96.40387228947844</v>
       </c>
       <c r="O18">
-        <v>19.39072890154888</v>
+        <v>19.28077445789569</v>
       </c>
       <c r="P18">
-        <v>77.56291560619553</v>
+        <v>77.12309783158275</v>
       </c>
       <c r="Q18">
-        <v>222.0629156061955</v>
+        <v>221.6230978315828</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08797130729944722</v>
+        <v>0.08839121477031696</v>
       </c>
       <c r="T18">
-        <v>0.6523767118395591</v>
+        <v>0.6588725468673353</v>
       </c>
       <c r="U18">
         <v>0.06763097776675758</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.02202435919101</v>
+        <v>11.31484645570919</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0825625212356421</v>
+        <v>0.08257237918560356</v>
       </c>
       <c r="C19">
-        <v>710.384806262071</v>
+        <v>702.0763324597062</v>
       </c>
       <c r="D19">
-        <v>669.477806262071</v>
+        <v>669.2983324597062</v>
       </c>
       <c r="E19">
-        <v>-73.607</v>
+        <v>-65.47799999999998</v>
       </c>
       <c r="F19">
-        <v>138.193</v>
+        <v>146.322</v>
       </c>
       <c r="G19">
         <v>179.1</v>
@@ -2845,28 +2845,28 @@
         <v>105.75</v>
       </c>
       <c r="M19">
-        <v>9.346127710521532</v>
+        <v>9.895899928787506</v>
       </c>
       <c r="N19">
-        <v>96.40387228947844</v>
+        <v>95.85410007121247</v>
       </c>
       <c r="O19">
-        <v>19.28077445789569</v>
+        <v>19.17082001424249</v>
       </c>
       <c r="P19">
-        <v>77.12309783158275</v>
+        <v>76.68328005696998</v>
       </c>
       <c r="Q19">
-        <v>221.6230978315828</v>
+        <v>221.18328005697</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08839121477031696</v>
+        <v>0.08882136388681766</v>
       </c>
       <c r="T19">
-        <v>0.6588725468673353</v>
+        <v>0.665526816895789</v>
       </c>
       <c r="U19">
         <v>0.06763097776675758</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.31484645570919</v>
+        <v>10.68624387483645</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08257237918560358</v>
+        <v>0.08258223713556503</v>
       </c>
       <c r="C20">
-        <v>702.0763324597059</v>
+        <v>693.7679548583284</v>
       </c>
       <c r="D20">
-        <v>669.2983324597059</v>
+        <v>669.1189548583284</v>
       </c>
       <c r="E20">
-        <v>-65.47800000000001</v>
+        <v>-57.34899999999999</v>
       </c>
       <c r="F20">
-        <v>146.322</v>
+        <v>154.451</v>
       </c>
       <c r="G20">
         <v>179.1</v>
@@ -2927,28 +2927,28 @@
         <v>105.75</v>
       </c>
       <c r="M20">
-        <v>9.895899928787504</v>
+        <v>10.44567214705348</v>
       </c>
       <c r="N20">
-        <v>95.85410007121247</v>
+        <v>95.3043278529465</v>
       </c>
       <c r="O20">
-        <v>19.17082001424249</v>
+        <v>19.0608655705893</v>
       </c>
       <c r="P20">
-        <v>76.68328005696998</v>
+        <v>76.2434622823572</v>
       </c>
       <c r="Q20">
-        <v>221.18328005697</v>
+        <v>220.7434622823572</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08882136388681766</v>
+        <v>0.08926213396915789</v>
       </c>
       <c r="T20">
-        <v>0.6655268168957889</v>
+        <v>0.6723453898879082</v>
       </c>
       <c r="U20">
         <v>0.06763097776675758</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.68624387483645</v>
+        <v>10.12380998668717</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08258223713556503</v>
+        <v>0.0828640950855265</v>
       </c>
       <c r="C21">
-        <v>693.7679548583284</v>
+        <v>680.5505668520508</v>
       </c>
       <c r="D21">
-        <v>669.1189548583284</v>
+        <v>664.0305668520508</v>
       </c>
       <c r="E21">
-        <v>-57.34899999999999</v>
+        <v>-49.21999999999997</v>
       </c>
       <c r="F21">
-        <v>154.451</v>
+        <v>162.58</v>
       </c>
       <c r="G21">
         <v>179.1</v>
@@ -3009,45 +3009,45 @@
         <v>105.75</v>
       </c>
       <c r="M21">
-        <v>10.44567214705348</v>
+        <v>11.27183036531945</v>
       </c>
       <c r="N21">
-        <v>95.3043278529465</v>
+        <v>94.47816963468053</v>
       </c>
       <c r="O21">
-        <v>19.0608655705893</v>
+        <v>18.89563392693611</v>
       </c>
       <c r="P21">
-        <v>76.2434622823572</v>
+        <v>75.58253570774443</v>
       </c>
       <c r="Q21">
-        <v>220.7434622823572</v>
+        <v>220.0825357077444</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08926213396915789</v>
+        <v>0.08971392330355661</v>
       </c>
       <c r="T21">
-        <v>0.6723453898879082</v>
+        <v>0.6793344272048302</v>
       </c>
       <c r="U21">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05410478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.12380998668717</v>
+        <v>9.381794843663172</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0828640950855265</v>
+        <v>0.08288755303548798</v>
       </c>
       <c r="C22">
-        <v>680.5505668520508</v>
+        <v>672.0015662174659</v>
       </c>
       <c r="D22">
-        <v>664.0305668520508</v>
+        <v>663.6105662174659</v>
       </c>
       <c r="E22">
-        <v>-49.21999999999997</v>
+        <v>-41.09099999999998</v>
       </c>
       <c r="F22">
-        <v>162.58</v>
+        <v>170.709</v>
       </c>
       <c r="G22">
         <v>179.1</v>
@@ -3091,28 +3091,28 @@
         <v>105.75</v>
       </c>
       <c r="M22">
-        <v>11.27183036531945</v>
+        <v>11.83542188358542</v>
       </c>
       <c r="N22">
-        <v>94.47816963468053</v>
+        <v>93.91457811641455</v>
       </c>
       <c r="O22">
-        <v>18.89563392693611</v>
+        <v>18.78291562328291</v>
       </c>
       <c r="P22">
-        <v>75.58253570774443</v>
+        <v>75.13166249313164</v>
       </c>
       <c r="Q22">
-        <v>220.0825357077444</v>
+        <v>219.6316624931316</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08971392330355661</v>
+        <v>0.09017715034262366</v>
       </c>
       <c r="T22">
-        <v>0.6793344272048302</v>
+        <v>0.6865004021753452</v>
       </c>
       <c r="U22">
         <v>0.06933097776675758</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.381794843663172</v>
+        <v>8.935042708250638</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08288755303548798</v>
+        <v>0.08291101098544944</v>
       </c>
       <c r="C23">
-        <v>672.001566217466</v>
+        <v>663.4530965494926</v>
       </c>
       <c r="D23">
-        <v>663.6105662174659</v>
+        <v>663.1910965494925</v>
       </c>
       <c r="E23">
-        <v>-41.09100000000001</v>
+        <v>-32.96199999999999</v>
       </c>
       <c r="F23">
-        <v>170.709</v>
+        <v>178.838</v>
       </c>
       <c r="G23">
         <v>179.1</v>
@@ -3173,28 +3173,28 @@
         <v>105.75</v>
       </c>
       <c r="M23">
-        <v>11.83542188358542</v>
+        <v>12.39901340185139</v>
       </c>
       <c r="N23">
-        <v>93.91457811641455</v>
+        <v>93.35098659814858</v>
       </c>
       <c r="O23">
-        <v>18.78291562328291</v>
+        <v>18.67019731962972</v>
       </c>
       <c r="P23">
-        <v>75.13166249313164</v>
+        <v>74.68078927851886</v>
       </c>
       <c r="Q23">
-        <v>219.6316624931316</v>
+        <v>219.1807892785189</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09017715034262366</v>
+        <v>0.09065225499807705</v>
       </c>
       <c r="T23">
-        <v>0.6865004021753452</v>
+        <v>0.6938501200938223</v>
       </c>
       <c r="U23">
         <v>0.06933097776675758</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.935042708250641</v>
+        <v>8.528904403330156</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08291101098544944</v>
+        <v>0.0829344689354109</v>
       </c>
       <c r="C24">
-        <v>663.4530965494926</v>
+        <v>654.9051568418909</v>
       </c>
       <c r="D24">
-        <v>663.1910965494925</v>
+        <v>662.7721568418908</v>
       </c>
       <c r="E24">
-        <v>-32.96199999999999</v>
+        <v>-24.83299999999997</v>
       </c>
       <c r="F24">
-        <v>178.838</v>
+        <v>186.967</v>
       </c>
       <c r="G24">
         <v>179.1</v>
@@ -3255,28 +3255,28 @@
         <v>105.75</v>
       </c>
       <c r="M24">
-        <v>12.39901340185139</v>
+        <v>12.96260492011737</v>
       </c>
       <c r="N24">
-        <v>93.35098659814858</v>
+        <v>92.7873950798826</v>
       </c>
       <c r="O24">
-        <v>18.67019731962972</v>
+        <v>18.55747901597652</v>
       </c>
       <c r="P24">
-        <v>74.68078927851886</v>
+        <v>74.22991606390607</v>
       </c>
       <c r="Q24">
-        <v>219.1807892785189</v>
+        <v>218.7299160639061</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09065225499807705</v>
+        <v>0.09113970003419157</v>
       </c>
       <c r="T24">
-        <v>0.6938501200938223</v>
+        <v>0.7013907397764156</v>
       </c>
       <c r="U24">
         <v>0.06933097776675758</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.528904403330156</v>
+        <v>8.158082472750584</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0829344689354109</v>
+        <v>0.08295792688537237</v>
       </c>
       <c r="C25">
-        <v>654.9051568418909</v>
+        <v>646.3577460909623</v>
       </c>
       <c r="D25">
-        <v>662.7721568418908</v>
+        <v>662.3537460909623</v>
       </c>
       <c r="E25">
-        <v>-24.83299999999997</v>
+        <v>-16.70399999999998</v>
       </c>
       <c r="F25">
-        <v>186.967</v>
+        <v>195.096</v>
       </c>
       <c r="G25">
         <v>179.1</v>
@@ -3337,28 +3337,28 @@
         <v>105.75</v>
       </c>
       <c r="M25">
-        <v>12.96260492011737</v>
+        <v>13.52619643838334</v>
       </c>
       <c r="N25">
-        <v>92.7873950798826</v>
+        <v>92.22380356161663</v>
       </c>
       <c r="O25">
-        <v>18.55747901597652</v>
+        <v>18.44476071232333</v>
       </c>
       <c r="P25">
-        <v>74.22991606390607</v>
+        <v>73.7790428492933</v>
       </c>
       <c r="Q25">
-        <v>218.7299160639061</v>
+        <v>218.2790428492933</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09113970003419157</v>
+        <v>0.09163997257125647</v>
       </c>
       <c r="T25">
-        <v>0.7013907397764156</v>
+        <v>0.7091297968190772</v>
       </c>
       <c r="U25">
         <v>0.06933097776675758</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.158082472750584</v>
+        <v>7.818162369719309</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08295792688537236</v>
+        <v>0.08314138483533384</v>
       </c>
       <c r="C26">
-        <v>646.3577460909625</v>
+        <v>634.9746069918637</v>
       </c>
       <c r="D26">
-        <v>662.3537460909624</v>
+        <v>659.0996069918637</v>
       </c>
       <c r="E26">
-        <v>-16.70400000000001</v>
+        <v>-8.574999999999989</v>
       </c>
       <c r="F26">
-        <v>195.096</v>
+        <v>203.225</v>
       </c>
       <c r="G26">
         <v>179.1</v>
@@ -3419,45 +3419,45 @@
         <v>105.75</v>
       </c>
       <c r="M26">
-        <v>13.52619643838334</v>
+        <v>14.25236795664931</v>
       </c>
       <c r="N26">
-        <v>92.22380356161663</v>
+        <v>91.49763204335066</v>
       </c>
       <c r="O26">
-        <v>18.44476071232333</v>
+        <v>18.29952640867013</v>
       </c>
       <c r="P26">
-        <v>73.7790428492933</v>
+        <v>73.19810563468053</v>
       </c>
       <c r="Q26">
-        <v>218.2790428492933</v>
+        <v>217.6981056346805</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09163997257125646</v>
+        <v>0.09215358570930976</v>
       </c>
       <c r="T26">
-        <v>0.7091297968190771</v>
+        <v>0.7170752287162097</v>
       </c>
       <c r="U26">
-        <v>0.06933097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05546478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.818162369719311</v>
+        <v>7.419819662364476</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08314138483533384</v>
+        <v>0.08317124278529529</v>
       </c>
       <c r="C27">
-        <v>634.9746069918637</v>
+        <v>626.3190159122403</v>
       </c>
       <c r="D27">
-        <v>659.0996069918637</v>
+        <v>658.5730159122403</v>
       </c>
       <c r="E27">
-        <v>-8.574999999999989</v>
+        <v>-0.4459999999999695</v>
       </c>
       <c r="F27">
-        <v>203.225</v>
+        <v>211.354</v>
       </c>
       <c r="G27">
         <v>179.1</v>
@@ -3501,28 +3501,28 @@
         <v>105.75</v>
       </c>
       <c r="M27">
-        <v>14.25236795664931</v>
+        <v>14.82246267491529</v>
       </c>
       <c r="N27">
-        <v>91.49763204335066</v>
+        <v>90.92753732508469</v>
       </c>
       <c r="O27">
-        <v>18.29952640867013</v>
+        <v>18.18550746501694</v>
       </c>
       <c r="P27">
-        <v>73.19810563468053</v>
+        <v>72.74202986006775</v>
       </c>
       <c r="Q27">
-        <v>217.6981056346805</v>
+        <v>217.2420298600678</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09215358570930976</v>
+        <v>0.09268108028352665</v>
       </c>
       <c r="T27">
-        <v>0.7170752287162097</v>
+        <v>0.7252354020159674</v>
       </c>
       <c r="U27">
         <v>0.07013097776675759</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.419819662364476</v>
+        <v>7.134441983042764</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08317124278529529</v>
+        <v>0.08320110073525677</v>
       </c>
       <c r="C28">
-        <v>626.3190159122403</v>
+        <v>617.6642656062727</v>
       </c>
       <c r="D28">
-        <v>658.5730159122403</v>
+        <v>658.0472656062727</v>
       </c>
       <c r="E28">
-        <v>-0.4459999999999695</v>
+        <v>7.683000000000021</v>
       </c>
       <c r="F28">
-        <v>211.354</v>
+        <v>219.483</v>
       </c>
       <c r="G28">
         <v>179.1</v>
@@ -3583,28 +3583,28 @@
         <v>105.75</v>
       </c>
       <c r="M28">
-        <v>14.82246267491529</v>
+        <v>15.39255739318126</v>
       </c>
       <c r="N28">
-        <v>90.92753732508469</v>
+        <v>90.35744260681872</v>
       </c>
       <c r="O28">
-        <v>18.18550746501694</v>
+        <v>18.07148852136374</v>
       </c>
       <c r="P28">
-        <v>72.74202986006775</v>
+        <v>72.28595408545497</v>
       </c>
       <c r="Q28">
-        <v>217.2420298600678</v>
+        <v>216.785954085455</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09268108028352665</v>
+        <v>0.09322302676388648</v>
       </c>
       <c r="T28">
-        <v>0.7252354020159674</v>
+        <v>0.7336191417074993</v>
       </c>
       <c r="U28">
         <v>0.07013097776675759</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.134441983042764</v>
+        <v>6.870203391078219</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08320110073525677</v>
+        <v>0.08323095868521824</v>
       </c>
       <c r="C29">
-        <v>617.6642656062727</v>
+        <v>609.0103540619549</v>
       </c>
       <c r="D29">
-        <v>658.0472656062727</v>
+        <v>657.522354061955</v>
       </c>
       <c r="E29">
-        <v>7.683000000000021</v>
+        <v>15.81200000000004</v>
       </c>
       <c r="F29">
-        <v>219.483</v>
+        <v>227.6120000000001</v>
       </c>
       <c r="G29">
         <v>179.1</v>
@@ -3665,28 +3665,28 @@
         <v>105.75</v>
       </c>
       <c r="M29">
-        <v>15.39255739318126</v>
+        <v>15.96265211144723</v>
       </c>
       <c r="N29">
-        <v>90.35744260681872</v>
+        <v>89.78734788855274</v>
       </c>
       <c r="O29">
-        <v>18.07148852136374</v>
+        <v>17.95746957771055</v>
       </c>
       <c r="P29">
-        <v>72.28595408545497</v>
+        <v>71.82987831084219</v>
       </c>
       <c r="Q29">
-        <v>216.785954085455</v>
+        <v>216.3298783108422</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09322302676388648</v>
+        <v>0.09378002731314519</v>
       </c>
       <c r="T29">
-        <v>0.7336191417074993</v>
+        <v>0.7422357630571292</v>
       </c>
       <c r="U29">
         <v>0.07013097776675759</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.870203391078219</v>
+        <v>6.624838984253996</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08323095868521824</v>
+        <v>0.08326081663517972</v>
       </c>
       <c r="C30">
-        <v>609.0103540619549</v>
+        <v>600.3572792736948</v>
       </c>
       <c r="D30">
-        <v>657.522354061955</v>
+        <v>656.9982792736947</v>
       </c>
       <c r="E30">
-        <v>15.81200000000004</v>
+        <v>23.94100000000003</v>
       </c>
       <c r="F30">
-        <v>227.6120000000001</v>
+        <v>235.741</v>
       </c>
       <c r="G30">
         <v>179.1</v>
@@ -3747,28 +3747,28 @@
         <v>105.75</v>
       </c>
       <c r="M30">
-        <v>15.96265211144723</v>
+        <v>16.5327468297132</v>
       </c>
       <c r="N30">
-        <v>89.78734788855274</v>
+        <v>89.21725317028677</v>
       </c>
       <c r="O30">
-        <v>17.95746957771055</v>
+        <v>17.84345063405735</v>
       </c>
       <c r="P30">
-        <v>71.82987831084219</v>
+        <v>71.37380253622942</v>
       </c>
       <c r="Q30">
-        <v>216.3298783108422</v>
+        <v>215.8738025362294</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09378002731314519</v>
+        <v>0.09435271801872105</v>
       </c>
       <c r="T30">
-        <v>0.7422357630571292</v>
+        <v>0.7510951061349179</v>
       </c>
       <c r="U30">
         <v>0.07013097776675759</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.624838984253996</v>
+        <v>6.39639626065903</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0832608166351797</v>
+        <v>0.08329067458514117</v>
       </c>
       <c r="C31">
-        <v>600.3572792736951</v>
+        <v>591.70503924229</v>
       </c>
       <c r="D31">
-        <v>656.9982792736951</v>
+        <v>656.47503924229</v>
       </c>
       <c r="E31">
-        <v>23.941</v>
+        <v>32.06999999999999</v>
       </c>
       <c r="F31">
-        <v>235.741</v>
+        <v>243.87</v>
       </c>
       <c r="G31">
         <v>179.1</v>
@@ -3829,28 +3829,28 @@
         <v>105.75</v>
       </c>
       <c r="M31">
-        <v>16.5327468297132</v>
+        <v>17.10284154797917</v>
       </c>
       <c r="N31">
-        <v>89.21725317028677</v>
+        <v>88.6471584520208</v>
       </c>
       <c r="O31">
-        <v>17.84345063405735</v>
+        <v>17.72943169040416</v>
       </c>
       <c r="P31">
-        <v>71.37380253622942</v>
+        <v>70.91772676161665</v>
       </c>
       <c r="Q31">
-        <v>215.8738025362294</v>
+        <v>215.4177267616166</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09435271801872105</v>
+        <v>0.09494177131588478</v>
       </c>
       <c r="T31">
-        <v>0.7510951061349179</v>
+        <v>0.7602075733006434</v>
       </c>
       <c r="U31">
         <v>0.07013097776675759</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.396396260659031</v>
+        <v>6.183183051970398</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08329067458514117</v>
+        <v>0.08356853253510263</v>
       </c>
       <c r="C32">
-        <v>591.70503924229</v>
+        <v>578.7464417874459</v>
       </c>
       <c r="D32">
-        <v>656.47503924229</v>
+        <v>651.6454417874459</v>
       </c>
       <c r="E32">
-        <v>32.06999999999999</v>
+        <v>40.19900000000001</v>
       </c>
       <c r="F32">
-        <v>243.87</v>
+        <v>251.999</v>
       </c>
       <c r="G32">
         <v>179.1</v>
@@ -3911,45 +3911,45 @@
         <v>105.75</v>
       </c>
       <c r="M32">
-        <v>17.10284154797917</v>
+        <v>17.92493526624515</v>
       </c>
       <c r="N32">
-        <v>88.6471584520208</v>
+        <v>87.82506473375483</v>
       </c>
       <c r="O32">
-        <v>17.72943169040416</v>
+        <v>17.56501294675097</v>
       </c>
       <c r="P32">
-        <v>70.91772676161665</v>
+        <v>70.26005178700386</v>
       </c>
       <c r="Q32">
-        <v>215.4177267616166</v>
+        <v>214.7600517870039</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09494177131588478</v>
+        <v>0.09554789862166196</v>
       </c>
       <c r="T32">
-        <v>0.7602075733006434</v>
+        <v>0.7695841699494332</v>
       </c>
       <c r="U32">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05610478221340607</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.183183051970398</v>
+        <v>5.899602895589822</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08356853253510263</v>
+        <v>0.0836063904850641</v>
       </c>
       <c r="C33">
-        <v>578.7464417874459</v>
+        <v>569.9649076467545</v>
       </c>
       <c r="D33">
-        <v>651.6454417874459</v>
+        <v>650.9929076467545</v>
       </c>
       <c r="E33">
-        <v>40.19900000000001</v>
+        <v>48.32800000000003</v>
       </c>
       <c r="F33">
-        <v>251.999</v>
+        <v>260.128</v>
       </c>
       <c r="G33">
         <v>179.1</v>
@@ -3993,28 +3993,28 @@
         <v>105.75</v>
       </c>
       <c r="M33">
-        <v>17.92493526624515</v>
+        <v>18.50315898451112</v>
       </c>
       <c r="N33">
-        <v>87.82506473375483</v>
+        <v>87.24684101548885</v>
       </c>
       <c r="O33">
-        <v>17.56501294675097</v>
+        <v>17.44936820309777</v>
       </c>
       <c r="P33">
-        <v>70.26005178700386</v>
+        <v>69.79747281239108</v>
       </c>
       <c r="Q33">
-        <v>214.7600517870039</v>
+        <v>214.2974728123911</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09554789862166196</v>
+        <v>0.09617185320113847</v>
       </c>
       <c r="T33">
-        <v>0.7695841699494332</v>
+        <v>0.7792365488525993</v>
       </c>
       <c r="U33">
         <v>0.07113097776675759</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.899602895589822</v>
+        <v>5.715240305102639</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0836063904850641</v>
+        <v>0.08364424843502558</v>
       </c>
       <c r="C34">
-        <v>569.9649076467545</v>
+        <v>561.1846790468451</v>
       </c>
       <c r="D34">
-        <v>650.9929076467545</v>
+        <v>650.3416790468451</v>
       </c>
       <c r="E34">
-        <v>48.32800000000003</v>
+        <v>56.45700000000005</v>
       </c>
       <c r="F34">
-        <v>260.128</v>
+        <v>268.2570000000001</v>
       </c>
       <c r="G34">
         <v>179.1</v>
@@ -4075,28 +4075,28 @@
         <v>105.75</v>
       </c>
       <c r="M34">
-        <v>18.50315898451112</v>
+        <v>19.08138270277709</v>
       </c>
       <c r="N34">
-        <v>87.24684101548885</v>
+        <v>86.66861729722288</v>
       </c>
       <c r="O34">
-        <v>17.44936820309777</v>
+        <v>17.33372345944458</v>
       </c>
       <c r="P34">
-        <v>69.79747281239108</v>
+        <v>69.33489383777831</v>
       </c>
       <c r="Q34">
-        <v>214.2974728123911</v>
+        <v>213.8348938377783</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09617185320113847</v>
+        <v>0.0968144332904501</v>
       </c>
       <c r="T34">
-        <v>0.7792365488525993</v>
+        <v>0.7891770584692929</v>
       </c>
       <c r="U34">
         <v>0.07113097776675759</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.715240305102639</v>
+        <v>5.542051204948013</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08364424843502558</v>
+        <v>0.08368210638498702</v>
       </c>
       <c r="C35">
-        <v>561.1846790468451</v>
+        <v>552.4057520735932</v>
       </c>
       <c r="D35">
-        <v>650.3416790468451</v>
+        <v>649.6917520735933</v>
       </c>
       <c r="E35">
-        <v>56.45700000000005</v>
+        <v>64.58600000000001</v>
       </c>
       <c r="F35">
-        <v>268.2570000000001</v>
+        <v>276.386</v>
       </c>
       <c r="G35">
         <v>179.1</v>
@@ -4157,28 +4157,28 @@
         <v>105.75</v>
       </c>
       <c r="M35">
-        <v>19.08138270277709</v>
+        <v>19.65960642104307</v>
       </c>
       <c r="N35">
-        <v>86.66861729722288</v>
+        <v>86.09039357895691</v>
       </c>
       <c r="O35">
-        <v>17.33372345944458</v>
+        <v>17.21807871579138</v>
       </c>
       <c r="P35">
-        <v>69.33489383777831</v>
+        <v>68.87231486316553</v>
       </c>
       <c r="Q35">
-        <v>213.8348938377783</v>
+        <v>213.3723148631655</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0968144332904501</v>
+        <v>0.09747648550368025</v>
       </c>
       <c r="T35">
-        <v>0.7891770584692929</v>
+        <v>0.7994187956501284</v>
       </c>
       <c r="U35">
         <v>0.07113097776675759</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.542051204948013</v>
+        <v>5.379049698920131</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08368210638498702</v>
+        <v>0.08371996433494849</v>
       </c>
       <c r="C36">
-        <v>552.4057520735932</v>
+        <v>543.6281228285043</v>
       </c>
       <c r="D36">
-        <v>649.6917520735933</v>
+        <v>649.0431228285042</v>
       </c>
       <c r="E36">
-        <v>64.58600000000001</v>
+        <v>72.71500000000003</v>
       </c>
       <c r="F36">
-        <v>276.386</v>
+        <v>284.515</v>
       </c>
       <c r="G36">
         <v>179.1</v>
@@ -4239,28 +4239,28 @@
         <v>105.75</v>
       </c>
       <c r="M36">
-        <v>19.65960642104307</v>
+        <v>20.23783013930904</v>
       </c>
       <c r="N36">
-        <v>86.09039357895691</v>
+        <v>85.51216986069093</v>
       </c>
       <c r="O36">
-        <v>17.21807871579138</v>
+        <v>17.10243397213819</v>
       </c>
       <c r="P36">
-        <v>68.87231486316553</v>
+        <v>68.40973588855275</v>
       </c>
       <c r="Q36">
-        <v>213.3723148631655</v>
+        <v>212.9097358885527</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09747648550368025</v>
+        <v>0.09815890855424059</v>
       </c>
       <c r="T36">
-        <v>0.7994187956501284</v>
+        <v>0.8099756632057591</v>
       </c>
       <c r="U36">
         <v>0.07113097776675759</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.379049698920131</v>
+        <v>5.225362564665271</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08371996433494849</v>
+        <v>0.08375782228490997</v>
       </c>
       <c r="C37">
-        <v>543.6281228285043</v>
+        <v>534.8517874286372</v>
       </c>
       <c r="D37">
-        <v>649.0431228285042</v>
+        <v>648.3957874286373</v>
       </c>
       <c r="E37">
-        <v>72.71500000000003</v>
+        <v>80.84400000000005</v>
       </c>
       <c r="F37">
-        <v>284.515</v>
+        <v>292.6440000000001</v>
       </c>
       <c r="G37">
         <v>179.1</v>
@@ -4321,28 +4321,28 @@
         <v>105.75</v>
       </c>
       <c r="M37">
-        <v>20.23783013930904</v>
+        <v>20.81605385757501</v>
       </c>
       <c r="N37">
-        <v>85.51216986069093</v>
+        <v>84.93394614242496</v>
       </c>
       <c r="O37">
-        <v>17.10243397213819</v>
+        <v>16.98678922848499</v>
       </c>
       <c r="P37">
-        <v>68.40973588855275</v>
+        <v>67.94715691393996</v>
       </c>
       <c r="Q37">
-        <v>212.9097358885527</v>
+        <v>212.44715691394</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09815890855424059</v>
+        <v>0.09886265732513091</v>
       </c>
       <c r="T37">
-        <v>0.8099756632057591</v>
+        <v>0.8208624328725033</v>
       </c>
       <c r="U37">
         <v>0.07113097776675759</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.225362564665271</v>
+        <v>5.080213604535679</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08375782228490997</v>
+        <v>0.08379568023487143</v>
       </c>
       <c r="C38">
-        <v>534.8517874286373</v>
+        <v>526.0767420065274</v>
       </c>
       <c r="D38">
-        <v>648.3957874286373</v>
+        <v>647.7497420065274</v>
       </c>
       <c r="E38">
-        <v>80.84399999999999</v>
+        <v>88.97300000000001</v>
       </c>
       <c r="F38">
-        <v>292.644</v>
+        <v>300.773</v>
       </c>
       <c r="G38">
         <v>179.1</v>
@@ -4403,28 +4403,28 @@
         <v>105.75</v>
       </c>
       <c r="M38">
-        <v>20.81605385757501</v>
+        <v>21.39427757584098</v>
       </c>
       <c r="N38">
-        <v>84.93394614242496</v>
+        <v>84.35572242415898</v>
       </c>
       <c r="O38">
-        <v>16.98678922848499</v>
+        <v>16.8711444848318</v>
       </c>
       <c r="P38">
-        <v>67.94715691393996</v>
+        <v>67.48457793932718</v>
       </c>
       <c r="Q38">
-        <v>212.44715691394</v>
+        <v>211.9845779393272</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09886265732513091</v>
+        <v>0.09958874732684316</v>
       </c>
       <c r="T38">
-        <v>0.8208624328725032</v>
+        <v>0.8320948142746994</v>
       </c>
       <c r="U38">
         <v>0.07113097776675759</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.08021360453568</v>
+        <v>4.942910534142824</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08379568023487143</v>
+        <v>0.0838335381848329</v>
       </c>
       <c r="C39">
-        <v>526.0767420065274</v>
+        <v>517.3029827101066</v>
       </c>
       <c r="D39">
-        <v>647.7497420065274</v>
+        <v>647.1049827101066</v>
       </c>
       <c r="E39">
-        <v>88.97300000000001</v>
+        <v>97.10200000000003</v>
       </c>
       <c r="F39">
-        <v>300.773</v>
+        <v>308.902</v>
       </c>
       <c r="G39">
         <v>179.1</v>
@@ -4485,28 +4485,28 @@
         <v>105.75</v>
       </c>
       <c r="M39">
-        <v>21.39427757584098</v>
+        <v>21.97250129410696</v>
       </c>
       <c r="N39">
-        <v>84.35572242415898</v>
+        <v>83.77749870589301</v>
       </c>
       <c r="O39">
-        <v>16.8711444848318</v>
+        <v>16.7554997411786</v>
       </c>
       <c r="P39">
-        <v>67.48457793932718</v>
+        <v>67.02199896471441</v>
       </c>
       <c r="Q39">
-        <v>211.9845779393272</v>
+        <v>211.5219989647144</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09958874732684316</v>
+        <v>0.1003382595866752</v>
       </c>
       <c r="T39">
-        <v>0.8320948142746994</v>
+        <v>0.8436895305608375</v>
       </c>
       <c r="U39">
         <v>0.07113097776675759</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.942910534142824</v>
+        <v>4.812833941139065</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0838335381848329</v>
+        <v>0.08387139613479437</v>
       </c>
       <c r="C40">
-        <v>517.3029827101066</v>
+        <v>508.5305057026304</v>
       </c>
       <c r="D40">
-        <v>647.1049827101066</v>
+        <v>646.4615057026305</v>
       </c>
       <c r="E40">
-        <v>97.10200000000003</v>
+        <v>105.2310000000001</v>
       </c>
       <c r="F40">
-        <v>308.902</v>
+        <v>317.0310000000001</v>
       </c>
       <c r="G40">
         <v>179.1</v>
@@ -4567,28 +4567,28 @@
         <v>105.75</v>
       </c>
       <c r="M40">
-        <v>21.97250129410696</v>
+        <v>22.55072501237293</v>
       </c>
       <c r="N40">
-        <v>83.77749870589301</v>
+        <v>83.19927498762704</v>
       </c>
       <c r="O40">
-        <v>16.7554997411786</v>
+        <v>16.63985499752541</v>
       </c>
       <c r="P40">
-        <v>67.02199896471441</v>
+        <v>66.55941999010163</v>
       </c>
       <c r="Q40">
-        <v>211.5219989647144</v>
+        <v>211.0594199901016</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1003382595866752</v>
+        <v>0.1011123460189607</v>
       </c>
       <c r="T40">
-        <v>0.8436895305608375</v>
+        <v>0.855664401479308</v>
       </c>
       <c r="U40">
         <v>0.07113097776675759</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.812833941139065</v>
+        <v>4.689427942648319</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08387139613479437</v>
+        <v>0.08390925408475583</v>
       </c>
       <c r="C41">
-        <v>508.5305057026304</v>
+        <v>499.7593071625995</v>
       </c>
       <c r="D41">
-        <v>646.4615057026305</v>
+        <v>645.8193071625996</v>
       </c>
       <c r="E41">
-        <v>105.2310000000001</v>
+        <v>113.3600000000001</v>
       </c>
       <c r="F41">
-        <v>317.0310000000001</v>
+        <v>325.1600000000001</v>
       </c>
       <c r="G41">
         <v>179.1</v>
@@ -4649,28 +4649,28 @@
         <v>105.75</v>
       </c>
       <c r="M41">
-        <v>22.55072501237293</v>
+        <v>23.1289487306389</v>
       </c>
       <c r="N41">
-        <v>83.19927498762704</v>
+        <v>82.62105126936106</v>
       </c>
       <c r="O41">
-        <v>16.63985499752541</v>
+        <v>16.52421025387221</v>
       </c>
       <c r="P41">
-        <v>66.55941999010163</v>
+        <v>66.09684101548885</v>
       </c>
       <c r="Q41">
-        <v>211.0594199901016</v>
+        <v>210.5968410154888</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1011123460189607</v>
+        <v>0.1019122353323223</v>
       </c>
       <c r="T41">
-        <v>0.855664401479308</v>
+        <v>0.8680384347617275</v>
       </c>
       <c r="U41">
         <v>0.07113097776675759</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.689427942648319</v>
+        <v>4.57219224408211</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08390925408475583</v>
+        <v>0.0847671120347173</v>
       </c>
       <c r="C42">
-        <v>499.7593071625995</v>
+        <v>477.4126451917958</v>
       </c>
       <c r="D42">
-        <v>645.8193071625996</v>
+        <v>631.6016451917958</v>
       </c>
       <c r="E42">
-        <v>113.3600000000001</v>
+        <v>121.489</v>
       </c>
       <c r="F42">
-        <v>325.1600000000001</v>
+        <v>333.289</v>
       </c>
       <c r="G42">
         <v>179.1</v>
@@ -4731,45 +4731,45 @@
         <v>105.75</v>
       </c>
       <c r="M42">
-        <v>23.1289487306389</v>
+        <v>24.54039494890487</v>
       </c>
       <c r="N42">
-        <v>82.62105126936106</v>
+        <v>81.20960505109511</v>
       </c>
       <c r="O42">
-        <v>16.52421025387221</v>
+        <v>16.24192101021902</v>
       </c>
       <c r="P42">
-        <v>66.09684101548885</v>
+        <v>64.96768404087609</v>
       </c>
       <c r="Q42">
-        <v>210.5968410154888</v>
+        <v>209.4676840408761</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1019122353323223</v>
+        <v>0.1027392395376624</v>
       </c>
       <c r="T42">
-        <v>0.8680384347617275</v>
+        <v>0.8808319267994833</v>
       </c>
       <c r="U42">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.05690478221340607</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.57219224408211</v>
+        <v>4.309221600556153</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0847671120347173</v>
+        <v>0.08482496998467877</v>
       </c>
       <c r="C43">
-        <v>477.4126451917958</v>
+        <v>468.3472402080781</v>
       </c>
       <c r="D43">
-        <v>631.6016451917958</v>
+        <v>630.6652402080781</v>
       </c>
       <c r="E43">
-        <v>121.489</v>
+        <v>129.6180000000001</v>
       </c>
       <c r="F43">
-        <v>333.289</v>
+        <v>341.4180000000001</v>
       </c>
       <c r="G43">
         <v>179.1</v>
@@ -4813,28 +4813,28 @@
         <v>105.75</v>
       </c>
       <c r="M43">
-        <v>24.54039494890487</v>
+        <v>25.13894116717084</v>
       </c>
       <c r="N43">
-        <v>81.20960505109511</v>
+        <v>80.61105883282913</v>
       </c>
       <c r="O43">
-        <v>16.24192101021902</v>
+        <v>16.12221176656583</v>
       </c>
       <c r="P43">
-        <v>64.96768404087609</v>
+        <v>64.4888470662633</v>
       </c>
       <c r="Q43">
-        <v>209.4676840408761</v>
+        <v>208.9888470662633</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1027392395376624</v>
+        <v>0.1035947611293935</v>
       </c>
       <c r="T43">
-        <v>0.8808319267994833</v>
+        <v>0.8940665737350928</v>
       </c>
       <c r="U43">
         <v>0.07363097776675757</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.309221600556153</v>
+        <v>4.206621086257197</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08482496998467877</v>
+        <v>0.08488282793464025</v>
       </c>
       <c r="C44">
-        <v>468.3472402080781</v>
+        <v>459.2846077193691</v>
       </c>
       <c r="D44">
-        <v>630.6652402080781</v>
+        <v>629.7316077193691</v>
       </c>
       <c r="E44">
-        <v>129.618</v>
+        <v>137.747</v>
       </c>
       <c r="F44">
-        <v>341.418</v>
+        <v>349.547</v>
       </c>
       <c r="G44">
         <v>179.1</v>
@@ -4895,28 +4895,28 @@
         <v>105.75</v>
       </c>
       <c r="M44">
-        <v>25.13894116717084</v>
+        <v>25.73748738543681</v>
       </c>
       <c r="N44">
-        <v>80.61105883282913</v>
+        <v>80.01251261456316</v>
       </c>
       <c r="O44">
-        <v>16.12221176656583</v>
+        <v>16.00250252291263</v>
       </c>
       <c r="P44">
-        <v>64.4888470662633</v>
+        <v>64.01001009165053</v>
       </c>
       <c r="Q44">
-        <v>208.9888470662633</v>
+        <v>208.5100100916505</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1035947611293935</v>
+        <v>0.1044803010225888</v>
       </c>
       <c r="T44">
-        <v>0.8940665737350925</v>
+        <v>0.9077655942473901</v>
       </c>
       <c r="U44">
         <v>0.07363097776675757</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.206621086257197</v>
+        <v>4.108792688902379</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08488282793464025</v>
+        <v>0.0849406858846017</v>
       </c>
       <c r="C45">
-        <v>459.2846077193691</v>
+        <v>450.2247354307232</v>
       </c>
       <c r="D45">
-        <v>629.7316077193691</v>
+        <v>628.8007354307232</v>
       </c>
       <c r="E45">
-        <v>137.747</v>
+        <v>145.876</v>
       </c>
       <c r="F45">
-        <v>349.547</v>
+        <v>357.676</v>
       </c>
       <c r="G45">
         <v>179.1</v>
@@ -4977,28 +4977,28 @@
         <v>105.75</v>
       </c>
       <c r="M45">
-        <v>25.73748738543681</v>
+        <v>26.33603360370278</v>
       </c>
       <c r="N45">
-        <v>80.01251261456316</v>
+        <v>79.41396639629718</v>
       </c>
       <c r="O45">
-        <v>16.00250252291263</v>
+        <v>15.88279327925944</v>
       </c>
       <c r="P45">
-        <v>64.01001009165053</v>
+        <v>63.53117311703775</v>
       </c>
       <c r="Q45">
-        <v>208.5100100916505</v>
+        <v>208.0311731170378</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1044803010225888</v>
+        <v>0.1053974673405411</v>
       </c>
       <c r="T45">
-        <v>0.9077655942473901</v>
+        <v>0.9219538654922695</v>
       </c>
       <c r="U45">
         <v>0.07363097776675757</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.108792688902379</v>
+        <v>4.01541103688187</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0849406858846017</v>
+        <v>0.08625854383456316</v>
       </c>
       <c r="C46">
-        <v>450.2247354307232</v>
+        <v>421.6137810747417</v>
       </c>
       <c r="D46">
-        <v>628.8007354307232</v>
+        <v>608.3187810747418</v>
       </c>
       <c r="E46">
-        <v>145.876</v>
+        <v>154.0050000000001</v>
       </c>
       <c r="F46">
-        <v>357.676</v>
+        <v>365.8050000000001</v>
       </c>
       <c r="G46">
         <v>179.1</v>
@@ -5059,45 +5059,45 @@
         <v>105.75</v>
       </c>
       <c r="M46">
-        <v>26.33603360370278</v>
+        <v>28.21489732196876</v>
       </c>
       <c r="N46">
-        <v>79.41396639629718</v>
+        <v>77.53510267803121</v>
       </c>
       <c r="O46">
-        <v>15.88279327925944</v>
+        <v>15.50702053560624</v>
       </c>
       <c r="P46">
-        <v>63.53117311703775</v>
+        <v>62.02808214242496</v>
       </c>
       <c r="Q46">
-        <v>208.0311731170378</v>
+        <v>206.528082142425</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1053974673405411</v>
+        <v>0.1063479851609644</v>
       </c>
       <c r="T46">
-        <v>0.9219538654922695</v>
+        <v>0.9366580738733264</v>
       </c>
       <c r="U46">
-        <v>0.07363097776675757</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.05890478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.01541103688187</v>
+        <v>3.748020019114534</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08625854383456316</v>
+        <v>0.08634440178452463</v>
       </c>
       <c r="C47">
-        <v>421.6137810747417</v>
+        <v>412.196588348562</v>
       </c>
       <c r="D47">
-        <v>608.3187810747418</v>
+        <v>607.0305883485621</v>
       </c>
       <c r="E47">
-        <v>154.0050000000001</v>
+        <v>162.1340000000001</v>
       </c>
       <c r="F47">
-        <v>365.8050000000001</v>
+        <v>373.9340000000001</v>
       </c>
       <c r="G47">
         <v>179.1</v>
@@ -5141,28 +5141,28 @@
         <v>105.75</v>
       </c>
       <c r="M47">
-        <v>28.21489732196876</v>
+        <v>28.84189504023474</v>
       </c>
       <c r="N47">
-        <v>77.53510267803121</v>
+        <v>76.90810495976524</v>
       </c>
       <c r="O47">
-        <v>15.50702053560624</v>
+        <v>15.38162099195305</v>
       </c>
       <c r="P47">
-        <v>62.02808214242496</v>
+        <v>61.52648396781219</v>
       </c>
       <c r="Q47">
-        <v>206.528082142425</v>
+        <v>206.0264839678122</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1063479851609644</v>
+        <v>0.1073337073451071</v>
       </c>
       <c r="T47">
-        <v>0.9366580738733264</v>
+        <v>0.9519068825647929</v>
       </c>
       <c r="U47">
         <v>0.07713097776675758</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.748020019114534</v>
+        <v>3.666541323046827</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08634440178452463</v>
+        <v>0.08643025973448609</v>
       </c>
       <c r="C48">
-        <v>412.196588348562</v>
+        <v>402.7848399186948</v>
       </c>
       <c r="D48">
-        <v>607.0305883485621</v>
+        <v>605.7478399186948</v>
       </c>
       <c r="E48">
-        <v>162.1340000000001</v>
+        <v>170.263</v>
       </c>
       <c r="F48">
-        <v>373.9340000000001</v>
+        <v>382.063</v>
       </c>
       <c r="G48">
         <v>179.1</v>
@@ -5223,28 +5223,28 @@
         <v>105.75</v>
       </c>
       <c r="M48">
-        <v>28.84189504023474</v>
+        <v>29.4688927585007</v>
       </c>
       <c r="N48">
-        <v>76.90810495976524</v>
+        <v>76.28110724149927</v>
       </c>
       <c r="O48">
-        <v>15.38162099195305</v>
+        <v>15.25622144829985</v>
       </c>
       <c r="P48">
-        <v>61.52648396781219</v>
+        <v>61.02488579319942</v>
       </c>
       <c r="Q48">
-        <v>206.0264839678122</v>
+        <v>205.5248857931994</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1073337073451071</v>
+        <v>0.1083566265928023</v>
       </c>
       <c r="T48">
-        <v>0.9519068825647929</v>
+        <v>0.9677311179993336</v>
       </c>
       <c r="U48">
         <v>0.07713097776675758</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.666541323046827</v>
+        <v>3.588529805535193</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08643025973448609</v>
+        <v>0.08651611768444756</v>
       </c>
       <c r="C49">
-        <v>402.7848399186948</v>
+        <v>393.3785013440283</v>
       </c>
       <c r="D49">
-        <v>605.7478399186948</v>
+        <v>604.4705013440283</v>
       </c>
       <c r="E49">
-        <v>170.263</v>
+        <v>178.3920000000001</v>
       </c>
       <c r="F49">
-        <v>382.063</v>
+        <v>390.1920000000001</v>
       </c>
       <c r="G49">
         <v>179.1</v>
@@ -5305,28 +5305,28 @@
         <v>105.75</v>
       </c>
       <c r="M49">
-        <v>29.4688927585007</v>
+        <v>30.09589047676668</v>
       </c>
       <c r="N49">
-        <v>76.28110724149927</v>
+        <v>75.6541095232333</v>
       </c>
       <c r="O49">
-        <v>15.25622144829985</v>
+        <v>15.13082190464666</v>
       </c>
       <c r="P49">
-        <v>61.02488579319942</v>
+        <v>60.52328761858664</v>
       </c>
       <c r="Q49">
-        <v>205.5248857931994</v>
+        <v>205.0232876185866</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1083566265928023</v>
+        <v>0.1094188888884859</v>
       </c>
       <c r="T49">
-        <v>0.9677311179993336</v>
+        <v>0.9841639778736643</v>
       </c>
       <c r="U49">
         <v>0.07713097776675758</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.588529805535193</v>
+        <v>3.513768767919876</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08651611768444756</v>
+        <v>0.08769957563440903</v>
       </c>
       <c r="C50">
-        <v>393.3785013440283</v>
+        <v>368.1761680345303</v>
       </c>
       <c r="D50">
-        <v>604.4705013440283</v>
+        <v>587.3971680345303</v>
       </c>
       <c r="E50">
-        <v>178.392</v>
+        <v>186.521</v>
       </c>
       <c r="F50">
-        <v>390.192</v>
+        <v>398.321</v>
       </c>
       <c r="G50">
         <v>179.1</v>
@@ -5387,45 +5387,45 @@
         <v>105.75</v>
       </c>
       <c r="M50">
-        <v>30.09589047676667</v>
+        <v>31.83818699503265</v>
       </c>
       <c r="N50">
-        <v>75.6541095232333</v>
+        <v>73.91181300496731</v>
       </c>
       <c r="O50">
-        <v>15.13082190464666</v>
+        <v>14.78236260099346</v>
       </c>
       <c r="P50">
-        <v>60.52328761858664</v>
+        <v>59.12945040397385</v>
       </c>
       <c r="Q50">
-        <v>205.0232876185866</v>
+        <v>203.6294504039739</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1094188888884859</v>
+        <v>0.1105228085290981</v>
       </c>
       <c r="T50">
-        <v>0.9841639778736643</v>
+        <v>1.00124126362542</v>
       </c>
       <c r="U50">
-        <v>0.07713097776675758</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.06170478221340606</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.513768767919876</v>
+        <v>3.321483098786339</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08769957563440903</v>
+        <v>0.0878078335843705</v>
       </c>
       <c r="C51">
-        <v>368.1761680345303</v>
+        <v>358.5333929169234</v>
       </c>
       <c r="D51">
-        <v>587.3971680345303</v>
+        <v>585.8833929169234</v>
       </c>
       <c r="E51">
-        <v>186.521</v>
+        <v>194.65</v>
       </c>
       <c r="F51">
-        <v>398.321</v>
+        <v>406.45</v>
       </c>
       <c r="G51">
         <v>179.1</v>
@@ -5469,28 +5469,28 @@
         <v>105.75</v>
       </c>
       <c r="M51">
-        <v>31.83818699503265</v>
+        <v>32.48794591329862</v>
       </c>
       <c r="N51">
-        <v>73.91181300496731</v>
+        <v>73.26205408670134</v>
       </c>
       <c r="O51">
-        <v>14.78236260099346</v>
+        <v>14.65241081734027</v>
       </c>
       <c r="P51">
-        <v>59.12945040397385</v>
+        <v>58.60964326936107</v>
       </c>
       <c r="Q51">
-        <v>203.6294504039739</v>
+        <v>203.1096432693611</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1105228085290981</v>
+        <v>0.1116708849553349</v>
       </c>
       <c r="T51">
-        <v>1.00124126362542</v>
+        <v>1.019001640807245</v>
       </c>
       <c r="U51">
         <v>0.07993097776675759</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.321483098786339</v>
+        <v>3.255053436810612</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0878078335843705</v>
+        <v>0.08791609153433197</v>
       </c>
       <c r="C52">
-        <v>358.5333929169234</v>
+        <v>348.8984000120037</v>
       </c>
       <c r="D52">
-        <v>585.8833929169234</v>
+        <v>584.3774000120037</v>
       </c>
       <c r="E52">
-        <v>194.65</v>
+        <v>202.7790000000001</v>
       </c>
       <c r="F52">
-        <v>406.45</v>
+        <v>414.5790000000001</v>
       </c>
       <c r="G52">
         <v>179.1</v>
@@ -5551,28 +5551,28 @@
         <v>105.75</v>
       </c>
       <c r="M52">
-        <v>32.48794591329862</v>
+        <v>33.1377048315646</v>
       </c>
       <c r="N52">
-        <v>73.26205408670134</v>
+        <v>72.61229516843537</v>
       </c>
       <c r="O52">
-        <v>14.65241081734027</v>
+        <v>14.52245903368707</v>
       </c>
       <c r="P52">
-        <v>58.60964326936107</v>
+        <v>58.0898361347483</v>
       </c>
       <c r="Q52">
-        <v>203.1096432693611</v>
+        <v>202.5898361347483</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1116708849553349</v>
+        <v>0.1128658216438671</v>
       </c>
       <c r="T52">
-        <v>1.019001640807245</v>
+        <v>1.037486931343431</v>
       </c>
       <c r="U52">
         <v>0.07993097776675759</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.255053436810612</v>
+        <v>3.191228859618247</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08791609153433197</v>
+        <v>0.08802434948429341</v>
       </c>
       <c r="C53">
-        <v>348.8984000120037</v>
+        <v>339.2711294619119</v>
       </c>
       <c r="D53">
-        <v>584.3774000120037</v>
+        <v>582.8791294619119</v>
       </c>
       <c r="E53">
-        <v>202.7790000000001</v>
+        <v>210.9080000000001</v>
       </c>
       <c r="F53">
-        <v>414.5790000000001</v>
+        <v>422.7080000000001</v>
       </c>
       <c r="G53">
         <v>179.1</v>
@@ -5633,28 +5633,28 @@
         <v>105.75</v>
       </c>
       <c r="M53">
-        <v>33.1377048315646</v>
+        <v>33.78746374983057</v>
       </c>
       <c r="N53">
-        <v>72.61229516843537</v>
+        <v>71.96253625016939</v>
       </c>
       <c r="O53">
-        <v>14.52245903368707</v>
+        <v>14.39250725003388</v>
       </c>
       <c r="P53">
-        <v>58.0898361347483</v>
+        <v>57.57002900013551</v>
       </c>
       <c r="Q53">
-        <v>202.5898361347483</v>
+        <v>202.0700290001355</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1128658216438671</v>
+        <v>0.1141105473610881</v>
       </c>
       <c r="T53">
-        <v>1.037486931343431</v>
+        <v>1.056742442318625</v>
       </c>
       <c r="U53">
         <v>0.07993097776675759</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.191228859618247</v>
+        <v>3.129859073856358</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08802434948429341</v>
+        <v>0.0881326074342549</v>
       </c>
       <c r="C54">
-        <v>339.2711294619119</v>
+        <v>329.6515220210902</v>
       </c>
       <c r="D54">
-        <v>582.8791294619119</v>
+        <v>581.3885220210902</v>
       </c>
       <c r="E54">
-        <v>210.9080000000001</v>
+        <v>219.037</v>
       </c>
       <c r="F54">
-        <v>422.7080000000001</v>
+        <v>430.837</v>
       </c>
       <c r="G54">
         <v>179.1</v>
@@ -5715,28 +5715,28 @@
         <v>105.75</v>
       </c>
       <c r="M54">
-        <v>33.78746374983057</v>
+        <v>34.43722266809655</v>
       </c>
       <c r="N54">
-        <v>71.96253625016939</v>
+        <v>71.31277733190342</v>
       </c>
       <c r="O54">
-        <v>14.39250725003388</v>
+        <v>14.26255546638068</v>
       </c>
       <c r="P54">
-        <v>57.57002900013551</v>
+        <v>57.05022186552274</v>
       </c>
       <c r="Q54">
-        <v>202.0700290001355</v>
+        <v>201.5502218655227</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1141105473610881</v>
+        <v>0.1154082401301057</v>
       </c>
       <c r="T54">
-        <v>1.056742442318625</v>
+        <v>1.076817336739571</v>
       </c>
       <c r="U54">
         <v>0.07993097776675759</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.129859073856358</v>
+        <v>3.070805129066615</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0881326074342549</v>
+        <v>0.08824086538421637</v>
       </c>
       <c r="C55">
-        <v>329.6515220210902</v>
+        <v>320.0395190484755</v>
       </c>
       <c r="D55">
-        <v>581.3885220210902</v>
+        <v>579.9055190484755</v>
       </c>
       <c r="E55">
-        <v>219.037</v>
+        <v>227.1660000000001</v>
       </c>
       <c r="F55">
-        <v>430.837</v>
+        <v>438.9660000000001</v>
       </c>
       <c r="G55">
         <v>179.1</v>
@@ -5797,28 +5797,28 @@
         <v>105.75</v>
       </c>
       <c r="M55">
-        <v>34.43722266809655</v>
+        <v>35.08698158636252</v>
       </c>
       <c r="N55">
-        <v>71.31277733190342</v>
+        <v>70.66301841363745</v>
       </c>
       <c r="O55">
-        <v>14.26255546638068</v>
+        <v>14.13260368272749</v>
       </c>
       <c r="P55">
-        <v>57.05022186552274</v>
+        <v>56.53041473090995</v>
       </c>
       <c r="Q55">
-        <v>201.5502218655227</v>
+        <v>201.03041473091</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1154082401301057</v>
+        <v>0.1167623543238632</v>
       </c>
       <c r="T55">
-        <v>1.076817336739571</v>
+        <v>1.097765052657081</v>
       </c>
       <c r="U55">
         <v>0.07993097776675759</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.070805129066615</v>
+        <v>3.013938367417233</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08824086538421637</v>
+        <v>0.09178112333417782</v>
       </c>
       <c r="C56">
-        <v>320.0395190484755</v>
+        <v>267.2614331808434</v>
       </c>
       <c r="D56">
-        <v>579.9055190484755</v>
+        <v>535.2564331808435</v>
       </c>
       <c r="E56">
-        <v>227.1660000000001</v>
+        <v>235.2950000000001</v>
       </c>
       <c r="F56">
-        <v>438.9660000000001</v>
+        <v>447.0950000000001</v>
       </c>
       <c r="G56">
         <v>179.1</v>
@@ -5879,45 +5879,45 @@
         <v>105.75</v>
       </c>
       <c r="M56">
-        <v>35.08698158636252</v>
+        <v>39.22408150462849</v>
       </c>
       <c r="N56">
-        <v>70.66301841363745</v>
+        <v>66.52591849537149</v>
       </c>
       <c r="O56">
-        <v>14.13260368272749</v>
+        <v>13.3051836990743</v>
       </c>
       <c r="P56">
-        <v>56.53041473090995</v>
+        <v>53.22073479629719</v>
       </c>
       <c r="Q56">
-        <v>201.03041473091</v>
+        <v>197.7207347962972</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1167623543238632</v>
+        <v>0.1181766513706766</v>
       </c>
       <c r="T56">
-        <v>1.097765052657081</v>
+        <v>1.119643778170924</v>
       </c>
       <c r="U56">
-        <v>0.07993097776675759</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.06394478221340608</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.013938367417233</v>
+        <v>2.696047834479472</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09178112333417782</v>
+        <v>0.09195178128413931</v>
       </c>
       <c r="C57">
-        <v>267.2614331808434</v>
+        <v>257.1531863771727</v>
       </c>
       <c r="D57">
-        <v>535.2564331808435</v>
+        <v>533.2771863771728</v>
       </c>
       <c r="E57">
-        <v>235.2950000000001</v>
+        <v>243.4240000000001</v>
       </c>
       <c r="F57">
-        <v>447.0950000000001</v>
+        <v>455.2240000000001</v>
       </c>
       <c r="G57">
         <v>179.1</v>
@@ -5961,28 +5961,28 @@
         <v>105.75</v>
       </c>
       <c r="M57">
-        <v>39.22408150462849</v>
+        <v>39.93724662289446</v>
       </c>
       <c r="N57">
-        <v>66.52591849537149</v>
+        <v>65.81275337710551</v>
       </c>
       <c r="O57">
-        <v>13.3051836990743</v>
+        <v>13.1625506754211</v>
       </c>
       <c r="P57">
-        <v>53.22073479629719</v>
+        <v>52.65020270168441</v>
       </c>
       <c r="Q57">
-        <v>197.7207347962972</v>
+        <v>197.1502027016844</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1181766513706766</v>
+        <v>0.1196552346468907</v>
       </c>
       <c r="T57">
-        <v>1.119643778170924</v>
+        <v>1.142516991208124</v>
       </c>
       <c r="U57">
         <v>0.08773097776675759</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.696047834479472</v>
+        <v>2.647904123149482</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09195178128413931</v>
+        <v>0.09212243923410077</v>
       </c>
       <c r="C58">
-        <v>257.1531863771727</v>
+        <v>247.0595231838461</v>
       </c>
       <c r="D58">
-        <v>533.2771863771728</v>
+        <v>531.3125231838462</v>
       </c>
       <c r="E58">
-        <v>243.4240000000001</v>
+        <v>251.5530000000001</v>
       </c>
       <c r="F58">
-        <v>455.2240000000001</v>
+        <v>463.3530000000001</v>
       </c>
       <c r="G58">
         <v>179.1</v>
@@ -6043,28 +6043,28 @@
         <v>105.75</v>
       </c>
       <c r="M58">
-        <v>39.93724662289446</v>
+        <v>40.65041174116044</v>
       </c>
       <c r="N58">
-        <v>65.81275337710551</v>
+        <v>65.09958825883953</v>
       </c>
       <c r="O58">
-        <v>13.1625506754211</v>
+        <v>13.01991765176791</v>
       </c>
       <c r="P58">
-        <v>52.65020270168441</v>
+        <v>52.07967060707163</v>
       </c>
       <c r="Q58">
-        <v>197.1502027016844</v>
+        <v>196.5796706070716</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1196552346468907</v>
+        <v>0.1212025892382775</v>
       </c>
       <c r="T58">
-        <v>1.142516991208124</v>
+        <v>1.166454074619147</v>
       </c>
       <c r="U58">
         <v>0.08773097776675759</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.647904123149482</v>
+        <v>2.601449664848614</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09212243923410077</v>
+        <v>0.09229309718406223</v>
       </c>
       <c r="C59">
-        <v>247.0595231838461</v>
+        <v>236.9802830086985</v>
       </c>
       <c r="D59">
-        <v>531.3125231838462</v>
+        <v>529.3622830086986</v>
       </c>
       <c r="E59">
-        <v>251.5530000000001</v>
+        <v>259.6820000000001</v>
       </c>
       <c r="F59">
-        <v>463.3530000000001</v>
+        <v>471.4820000000001</v>
       </c>
       <c r="G59">
         <v>179.1</v>
@@ -6125,28 +6125,28 @@
         <v>105.75</v>
       </c>
       <c r="M59">
-        <v>40.65041174116044</v>
+        <v>41.36357685942641</v>
       </c>
       <c r="N59">
-        <v>65.09958825883953</v>
+        <v>64.38642314057356</v>
       </c>
       <c r="O59">
-        <v>13.01991765176791</v>
+        <v>12.87728462811471</v>
       </c>
       <c r="P59">
-        <v>52.07967060707163</v>
+        <v>51.50913851245885</v>
       </c>
       <c r="Q59">
-        <v>196.5796706070716</v>
+        <v>196.0091385124588</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1212025892382775</v>
+        <v>0.122823627381635</v>
       </c>
       <c r="T59">
-        <v>1.166454074619147</v>
+        <v>1.19153101914498</v>
       </c>
       <c r="U59">
         <v>0.08773097776675759</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.601449664848614</v>
+        <v>2.556597084420189</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09229309718406223</v>
+        <v>0.09246375513402369</v>
       </c>
       <c r="C60">
-        <v>236.9802830086986</v>
+        <v>226.9153076088251</v>
       </c>
       <c r="D60">
-        <v>529.3622830086986</v>
+        <v>527.4263076088251</v>
       </c>
       <c r="E60">
-        <v>259.682</v>
+        <v>267.811</v>
       </c>
       <c r="F60">
-        <v>471.482</v>
+        <v>479.611</v>
       </c>
       <c r="G60">
         <v>179.1</v>
@@ -6207,28 +6207,28 @@
         <v>105.75</v>
       </c>
       <c r="M60">
-        <v>41.3635768594264</v>
+        <v>42.07674197769238</v>
       </c>
       <c r="N60">
-        <v>64.38642314057357</v>
+        <v>63.67325802230759</v>
       </c>
       <c r="O60">
-        <v>12.87728462811472</v>
+        <v>12.73465160446152</v>
       </c>
       <c r="P60">
-        <v>51.50913851245885</v>
+        <v>50.93860641784607</v>
       </c>
       <c r="Q60">
-        <v>196.0091385124589</v>
+        <v>195.4386064178461</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.122823627381635</v>
+        <v>0.1245237405563759</v>
       </c>
       <c r="T60">
-        <v>1.19153101914498</v>
+        <v>1.21783122925744</v>
       </c>
       <c r="U60">
         <v>0.08773097776675759</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.55659708442019</v>
+        <v>2.513264930446966</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09246375513402369</v>
+        <v>0.09450641308398516</v>
       </c>
       <c r="C61">
-        <v>226.9153076088251</v>
+        <v>196.6670121805558</v>
       </c>
       <c r="D61">
-        <v>527.4263076088251</v>
+        <v>505.3070121805558</v>
       </c>
       <c r="E61">
-        <v>267.811</v>
+        <v>275.94</v>
       </c>
       <c r="F61">
-        <v>479.611</v>
+        <v>487.74</v>
       </c>
       <c r="G61">
         <v>179.1</v>
@@ -6289,45 +6289,45 @@
         <v>105.75</v>
       </c>
       <c r="M61">
-        <v>42.07674197769238</v>
+        <v>44.69209309595834</v>
       </c>
       <c r="N61">
-        <v>63.67325802230759</v>
+        <v>61.05790690404163</v>
       </c>
       <c r="O61">
-        <v>12.73465160446152</v>
+        <v>12.21158138080833</v>
       </c>
       <c r="P61">
-        <v>50.93860641784607</v>
+        <v>48.8463255232333</v>
       </c>
       <c r="Q61">
-        <v>195.4386064178461</v>
+        <v>193.3463255232333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1245237405563759</v>
+        <v>0.1263088593898538</v>
       </c>
       <c r="T61">
-        <v>1.21783122925744</v>
+        <v>1.245446449875522</v>
       </c>
       <c r="U61">
-        <v>0.08773097776675759</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.07018478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.513264930446966</v>
+        <v>2.36619036331425</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09450641308398516</v>
+        <v>0.09470827103394663</v>
       </c>
       <c r="C62">
-        <v>196.6670121805558</v>
+        <v>186.4524705037885</v>
       </c>
       <c r="D62">
-        <v>505.3070121805558</v>
+        <v>503.2214705037886</v>
       </c>
       <c r="E62">
-        <v>275.94</v>
+        <v>284.069</v>
       </c>
       <c r="F62">
-        <v>487.74</v>
+        <v>495.869</v>
       </c>
       <c r="G62">
         <v>179.1</v>
@@ -6371,28 +6371,28 @@
         <v>105.75</v>
       </c>
       <c r="M62">
-        <v>44.69209309595834</v>
+        <v>45.43696131422431</v>
       </c>
       <c r="N62">
-        <v>61.05790690404163</v>
+        <v>60.31303868577566</v>
       </c>
       <c r="O62">
-        <v>12.21158138080833</v>
+        <v>12.06260773715513</v>
       </c>
       <c r="P62">
-        <v>48.8463255232333</v>
+        <v>48.25043094862053</v>
       </c>
       <c r="Q62">
-        <v>193.3463255232333</v>
+        <v>192.7504309486205</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1263088593898538</v>
+        <v>0.1281855227788947</v>
       </c>
       <c r="T62">
-        <v>1.245446449875522</v>
+        <v>1.274477835653506</v>
       </c>
       <c r="U62">
         <v>0.09163097776675758</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.36619036331425</v>
+        <v>2.327400357358279</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09470827103394663</v>
+        <v>0.09491012898390809</v>
       </c>
       <c r="C63">
-        <v>186.4524705037885</v>
+        <v>176.2550732807682</v>
       </c>
       <c r="D63">
-        <v>503.2214705037886</v>
+        <v>501.1530732807683</v>
       </c>
       <c r="E63">
-        <v>284.069</v>
+        <v>292.198</v>
       </c>
       <c r="F63">
-        <v>495.869</v>
+        <v>503.998</v>
       </c>
       <c r="G63">
         <v>179.1</v>
@@ -6453,28 +6453,28 @@
         <v>105.75</v>
       </c>
       <c r="M63">
-        <v>45.43696131422431</v>
+        <v>46.18182953249029</v>
       </c>
       <c r="N63">
-        <v>60.31303868577566</v>
+        <v>59.56817046750968</v>
       </c>
       <c r="O63">
-        <v>12.06260773715513</v>
+        <v>11.91363409350194</v>
       </c>
       <c r="P63">
-        <v>48.25043094862053</v>
+        <v>47.65453637400775</v>
       </c>
       <c r="Q63">
-        <v>192.7504309486205</v>
+        <v>192.1545363740078</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1281855227788947</v>
+        <v>0.1301609579252535</v>
       </c>
       <c r="T63">
-        <v>1.274477835653506</v>
+        <v>1.305037189104016</v>
       </c>
       <c r="U63">
         <v>0.09163097776675758</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.327400357358279</v>
+        <v>2.289861641917017</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09491012898390809</v>
+        <v>0.09511198693386956</v>
       </c>
       <c r="C64">
-        <v>176.2550732807682</v>
+        <v>166.0746099697276</v>
       </c>
       <c r="D64">
-        <v>501.1530732807683</v>
+        <v>499.1016099697277</v>
       </c>
       <c r="E64">
-        <v>292.198</v>
+        <v>300.3270000000001</v>
       </c>
       <c r="F64">
-        <v>503.998</v>
+        <v>512.1270000000001</v>
       </c>
       <c r="G64">
         <v>179.1</v>
@@ -6535,28 +6535,28 @@
         <v>105.75</v>
       </c>
       <c r="M64">
-        <v>46.18182953249029</v>
+        <v>46.92669775075626</v>
       </c>
       <c r="N64">
-        <v>59.56817046750968</v>
+        <v>58.82330224924371</v>
       </c>
       <c r="O64">
-        <v>11.91363409350194</v>
+        <v>11.76466044984874</v>
       </c>
       <c r="P64">
-        <v>47.65453637400775</v>
+        <v>47.05864179939497</v>
       </c>
       <c r="Q64">
-        <v>192.1545363740078</v>
+        <v>191.558641799395</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1301609579252535</v>
+        <v>0.1322431733497939</v>
       </c>
       <c r="T64">
-        <v>1.305037189104016</v>
+        <v>1.337248399497797</v>
       </c>
       <c r="U64">
         <v>0.09163097776675758</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.289861641917017</v>
+        <v>2.253514631727858</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09511198693386956</v>
+        <v>0.09531384488383102</v>
       </c>
       <c r="C65">
-        <v>166.0746099697276</v>
+        <v>155.9108734622451</v>
       </c>
       <c r="D65">
-        <v>499.1016099697277</v>
+        <v>497.0668734622453</v>
       </c>
       <c r="E65">
-        <v>300.3270000000001</v>
+        <v>308.4560000000001</v>
       </c>
       <c r="F65">
-        <v>512.1270000000001</v>
+        <v>520.2560000000001</v>
       </c>
       <c r="G65">
         <v>179.1</v>
@@ -6617,28 +6617,28 @@
         <v>105.75</v>
       </c>
       <c r="M65">
-        <v>46.92669775075626</v>
+        <v>47.67156596902224</v>
       </c>
       <c r="N65">
-        <v>58.82330224924371</v>
+        <v>58.07843403097773</v>
       </c>
       <c r="O65">
-        <v>11.76466044984874</v>
+        <v>11.61568680619555</v>
       </c>
       <c r="P65">
-        <v>47.05864179939497</v>
+        <v>46.46274722478218</v>
       </c>
       <c r="Q65">
-        <v>191.558641799395</v>
+        <v>190.9627472247822</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1322431733497939</v>
+        <v>0.1344410674090309</v>
       </c>
       <c r="T65">
-        <v>1.337248399497797</v>
+        <v>1.37124912158012</v>
       </c>
       <c r="U65">
         <v>0.09163097776675758</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.253514631727858</v>
+        <v>2.218303465607109</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09531384488383102</v>
+        <v>0.09551570283379249</v>
       </c>
       <c r="C66">
-        <v>155.9108734622451</v>
+        <v>145.7636600135429</v>
       </c>
       <c r="D66">
-        <v>497.0668734622453</v>
+        <v>495.048660013543</v>
       </c>
       <c r="E66">
-        <v>308.4560000000001</v>
+        <v>316.5850000000001</v>
       </c>
       <c r="F66">
-        <v>520.2560000000001</v>
+        <v>528.3850000000001</v>
       </c>
       <c r="G66">
         <v>179.1</v>
@@ -6699,28 +6699,28 @@
         <v>105.75</v>
       </c>
       <c r="M66">
-        <v>47.67156596902224</v>
+        <v>48.41643418728821</v>
       </c>
       <c r="N66">
-        <v>58.07843403097773</v>
+        <v>57.33356581271176</v>
       </c>
       <c r="O66">
-        <v>11.61568680619555</v>
+        <v>11.46671316254235</v>
       </c>
       <c r="P66">
-        <v>46.46274722478218</v>
+        <v>45.86685265016941</v>
       </c>
       <c r="Q66">
-        <v>190.9627472247822</v>
+        <v>190.3668526501694</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1344410674090309</v>
+        <v>0.1367645554145101</v>
       </c>
       <c r="T66">
-        <v>1.37124912158012</v>
+        <v>1.407192742067148</v>
       </c>
       <c r="U66">
         <v>0.09163097776675758</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.218303465607109</v>
+        <v>2.184175719982385</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09551570283379249</v>
+        <v>0.09571756078375396</v>
       </c>
       <c r="C67">
-        <v>145.7636600135429</v>
+        <v>135.6327691744771</v>
       </c>
       <c r="D67">
-        <v>495.048660013543</v>
+        <v>493.0467691744772</v>
       </c>
       <c r="E67">
-        <v>316.5850000000001</v>
+        <v>324.7140000000001</v>
       </c>
       <c r="F67">
-        <v>528.3850000000001</v>
+        <v>536.5140000000001</v>
       </c>
       <c r="G67">
         <v>179.1</v>
@@ -6781,28 +6781,28 @@
         <v>105.75</v>
       </c>
       <c r="M67">
-        <v>48.41643418728821</v>
+        <v>49.16130240555419</v>
       </c>
       <c r="N67">
-        <v>57.33356581271176</v>
+        <v>56.58869759444578</v>
       </c>
       <c r="O67">
-        <v>11.46671316254235</v>
+        <v>11.31773951888916</v>
       </c>
       <c r="P67">
-        <v>45.86685265016941</v>
+        <v>45.27095807555663</v>
       </c>
       <c r="Q67">
-        <v>190.3668526501694</v>
+        <v>189.7709580755566</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1367645554145101</v>
+        <v>0.1392247191850175</v>
       </c>
       <c r="T67">
-        <v>1.407192742067148</v>
+        <v>1.44525069317106</v>
       </c>
       <c r="U67">
         <v>0.09163097776675758</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.184175719982385</v>
+        <v>2.1510821484675</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09571756078375396</v>
+        <v>0.09591941873371543</v>
       </c>
       <c r="C68">
-        <v>135.6327691744771</v>
+        <v>125.5180037251715</v>
       </c>
       <c r="D68">
-        <v>493.0467691744772</v>
+        <v>491.0610037251717</v>
       </c>
       <c r="E68">
-        <v>324.7140000000001</v>
+        <v>332.8430000000001</v>
       </c>
       <c r="F68">
-        <v>536.5140000000001</v>
+        <v>544.6430000000001</v>
       </c>
       <c r="G68">
         <v>179.1</v>
@@ -6863,28 +6863,28 @@
         <v>105.75</v>
       </c>
       <c r="M68">
-        <v>49.16130240555419</v>
+        <v>49.90617062382016</v>
       </c>
       <c r="N68">
-        <v>56.58869759444578</v>
+        <v>55.84382937617981</v>
       </c>
       <c r="O68">
-        <v>11.31773951888916</v>
+        <v>11.16876587523596</v>
       </c>
       <c r="P68">
-        <v>45.27095807555663</v>
+        <v>44.67506350094385</v>
       </c>
       <c r="Q68">
-        <v>189.7709580755566</v>
+        <v>189.1750635009438</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1392247191850175</v>
+        <v>0.1418339837901011</v>
       </c>
       <c r="T68">
-        <v>1.44525069317106</v>
+        <v>1.485615186766119</v>
       </c>
       <c r="U68">
         <v>0.09163097776675758</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.1510821484675</v>
+        <v>2.11897644475903</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09591941873371543</v>
+        <v>0.0961212766836769</v>
       </c>
       <c r="C69">
-        <v>125.5180037251715</v>
+        <v>115.4191696102487</v>
       </c>
       <c r="D69">
-        <v>491.0610037251717</v>
+        <v>489.0911696102488</v>
       </c>
       <c r="E69">
-        <v>332.8430000000001</v>
+        <v>340.972</v>
       </c>
       <c r="F69">
-        <v>544.6430000000001</v>
+        <v>552.772</v>
       </c>
       <c r="G69">
         <v>179.1</v>
@@ -6945,28 +6945,28 @@
         <v>105.75</v>
       </c>
       <c r="M69">
-        <v>49.90617062382016</v>
+        <v>50.65103884208612</v>
       </c>
       <c r="N69">
-        <v>55.84382937617981</v>
+        <v>55.09896115791385</v>
       </c>
       <c r="O69">
-        <v>11.16876587523596</v>
+        <v>11.01979223158277</v>
       </c>
       <c r="P69">
-        <v>44.67506350094385</v>
+        <v>44.07916892633108</v>
       </c>
       <c r="Q69">
-        <v>189.1750635009438</v>
+        <v>188.5791689263311</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1418339837901011</v>
+        <v>0.1446063274330024</v>
       </c>
       <c r="T69">
-        <v>1.485615186766119</v>
+        <v>1.528502461210868</v>
       </c>
       <c r="U69">
         <v>0.09163097776675758</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.11897644475903</v>
+        <v>2.08781502645375</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0961212766836769</v>
+        <v>0.09632313463363837</v>
       </c>
       <c r="C70">
-        <v>115.4191696102487</v>
+        <v>105.3360758756123</v>
       </c>
       <c r="D70">
-        <v>489.0911696102488</v>
+        <v>487.1370758756124</v>
       </c>
       <c r="E70">
-        <v>340.972</v>
+        <v>349.1010000000001</v>
       </c>
       <c r="F70">
-        <v>552.772</v>
+        <v>560.9010000000001</v>
       </c>
       <c r="G70">
         <v>179.1</v>
@@ -7027,28 +7027,28 @@
         <v>105.75</v>
       </c>
       <c r="M70">
-        <v>50.65103884208612</v>
+        <v>51.39590706035209</v>
       </c>
       <c r="N70">
-        <v>55.09896115791385</v>
+        <v>54.35409293964788</v>
       </c>
       <c r="O70">
-        <v>11.01979223158277</v>
+        <v>10.87081858792958</v>
       </c>
       <c r="P70">
-        <v>44.07916892633108</v>
+        <v>43.4832743517183</v>
       </c>
       <c r="Q70">
-        <v>188.5791689263311</v>
+        <v>187.9832743517183</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1446063274330024</v>
+        <v>0.1475575319560909</v>
       </c>
       <c r="T70">
-        <v>1.528502461210868</v>
+        <v>1.574156656587537</v>
       </c>
       <c r="U70">
         <v>0.09163097776675758</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.08781502645375</v>
+        <v>2.057556837664565</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09632313463363837</v>
+        <v>0.09652499258359983</v>
       </c>
       <c r="C71">
-        <v>105.3360758756123</v>
+        <v>95.26853460674158</v>
       </c>
       <c r="D71">
-        <v>487.1370758756124</v>
+        <v>485.1985346067416</v>
       </c>
       <c r="E71">
-        <v>349.1010000000001</v>
+        <v>357.2300000000001</v>
       </c>
       <c r="F71">
-        <v>560.9010000000001</v>
+        <v>569.0300000000001</v>
       </c>
       <c r="G71">
         <v>179.1</v>
@@ -7109,28 +7109,28 @@
         <v>105.75</v>
       </c>
       <c r="M71">
-        <v>51.39590706035209</v>
+        <v>52.14077527861807</v>
       </c>
       <c r="N71">
-        <v>54.35409293964788</v>
+        <v>53.6092247213819</v>
       </c>
       <c r="O71">
-        <v>10.87081858792958</v>
+        <v>10.72184494427638</v>
       </c>
       <c r="P71">
-        <v>43.4832743517183</v>
+        <v>42.88737977710552</v>
       </c>
       <c r="Q71">
-        <v>187.9832743517183</v>
+        <v>187.3873797771055</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1475575319560909</v>
+        <v>0.1507054834473853</v>
       </c>
       <c r="T71">
-        <v>1.574156656587537</v>
+        <v>1.622854464989317</v>
       </c>
       <c r="U71">
         <v>0.09163097776675758</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.057556837664565</v>
+        <v>2.028163168555071</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09652499258359983</v>
+        <v>0.1047924505335613</v>
       </c>
       <c r="C72">
-        <v>95.26853460674158</v>
+        <v>19.14170698705209</v>
       </c>
       <c r="D72">
-        <v>485.1985346067416</v>
+        <v>417.2007069870522</v>
       </c>
       <c r="E72">
-        <v>357.2300000000001</v>
+        <v>365.3590000000001</v>
       </c>
       <c r="F72">
-        <v>569.0300000000001</v>
+        <v>577.1590000000001</v>
       </c>
       <c r="G72">
         <v>179.1</v>
@@ -7191,45 +7191,45 @@
         <v>105.75</v>
       </c>
       <c r="M72">
-        <v>52.14077527861807</v>
+        <v>61.08130129688405</v>
       </c>
       <c r="N72">
-        <v>53.6092247213819</v>
+        <v>44.66869870311592</v>
       </c>
       <c r="O72">
-        <v>10.72184494427638</v>
+        <v>8.933739740623185</v>
       </c>
       <c r="P72">
-        <v>42.88737977710552</v>
+        <v>35.73495896249274</v>
       </c>
       <c r="Q72">
-        <v>187.3873797771055</v>
+        <v>180.2349589624927</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1507054834473853</v>
+        <v>0.1540705350415275</v>
       </c>
       <c r="T72">
-        <v>1.622854464989317</v>
+        <v>1.674910742936047</v>
       </c>
       <c r="U72">
-        <v>0.09163097776675758</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V72">
         <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.07330478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.028163168555071</v>
+        <v>1.731299067876843</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1047924505335613</v>
+        <v>0.1051079084835227</v>
       </c>
       <c r="C73">
-        <v>19.1417069870522</v>
+        <v>8.793622161540725</v>
       </c>
       <c r="D73">
-        <v>417.2007069870522</v>
+        <v>414.9816221615407</v>
       </c>
       <c r="E73">
-        <v>365.359</v>
+        <v>373.488</v>
       </c>
       <c r="F73">
-        <v>577.159</v>
+        <v>585.288</v>
       </c>
       <c r="G73">
         <v>179.1</v>
@@ -7273,28 +7273,28 @@
         <v>105.75</v>
       </c>
       <c r="M73">
-        <v>61.08130129688404</v>
+        <v>61.94160131515001</v>
       </c>
       <c r="N73">
-        <v>44.66869870311594</v>
+        <v>43.80839868484996</v>
       </c>
       <c r="O73">
-        <v>8.933739740623187</v>
+        <v>8.761679736969993</v>
       </c>
       <c r="P73">
-        <v>35.73495896249275</v>
+        <v>35.04671894787997</v>
       </c>
       <c r="Q73">
-        <v>180.2349589624928</v>
+        <v>179.54671894788</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1540705350415275</v>
+        <v>0.1576759474638228</v>
       </c>
       <c r="T73">
-        <v>1.674910742936047</v>
+        <v>1.730685326450401</v>
       </c>
       <c r="U73">
         <v>0.1058309777667576</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.731299067876844</v>
+        <v>1.707253247489665</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1051079084835227</v>
+        <v>0.1054233664334842</v>
       </c>
       <c r="C74">
-        <v>8.793622161540725</v>
+        <v>-1.530980999257167</v>
       </c>
       <c r="D74">
-        <v>414.9816221615407</v>
+        <v>412.7860190007429</v>
       </c>
       <c r="E74">
-        <v>373.488</v>
+        <v>381.617</v>
       </c>
       <c r="F74">
-        <v>585.288</v>
+        <v>593.417</v>
       </c>
       <c r="G74">
         <v>179.1</v>
@@ -7355,28 +7355,28 @@
         <v>105.75</v>
       </c>
       <c r="M74">
-        <v>61.94160131515001</v>
+        <v>62.80190133341598</v>
       </c>
       <c r="N74">
-        <v>43.80839868484996</v>
+        <v>42.94809866658399</v>
       </c>
       <c r="O74">
-        <v>8.761679736969993</v>
+        <v>8.589619733316798</v>
       </c>
       <c r="P74">
-        <v>35.04671894787997</v>
+        <v>34.35847893326719</v>
       </c>
       <c r="Q74">
-        <v>179.54671894788</v>
+        <v>178.8584789332672</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1576759474638228</v>
+        <v>0.1615484274729548</v>
       </c>
       <c r="T74">
-        <v>1.730685326450401</v>
+        <v>1.790591360595447</v>
       </c>
       <c r="U74">
         <v>0.1058309777667576</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.707253247489665</v>
+        <v>1.683866216702135</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1054233664334842</v>
+        <v>0.1057388243834457</v>
       </c>
       <c r="C75">
-        <v>-1.530980999257167</v>
+        <v>-11.832473247248</v>
       </c>
       <c r="D75">
-        <v>412.7860190007429</v>
+        <v>410.613526752752</v>
       </c>
       <c r="E75">
-        <v>381.617</v>
+        <v>389.746</v>
       </c>
       <c r="F75">
-        <v>593.417</v>
+        <v>601.546</v>
       </c>
       <c r="G75">
         <v>179.1</v>
@@ -7437,28 +7437,28 @@
         <v>105.75</v>
       </c>
       <c r="M75">
-        <v>62.80190133341598</v>
+        <v>63.66220135168196</v>
       </c>
       <c r="N75">
-        <v>42.94809866658399</v>
+        <v>42.08779864831801</v>
       </c>
       <c r="O75">
-        <v>8.589619733316798</v>
+        <v>8.417559729663603</v>
       </c>
       <c r="P75">
-        <v>34.35847893326719</v>
+        <v>33.67023891865441</v>
       </c>
       <c r="Q75">
-        <v>178.8584789332672</v>
+        <v>178.1702389186544</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1615484274729548</v>
+        <v>0.1657187905597123</v>
       </c>
       <c r="T75">
-        <v>1.790591360595447</v>
+        <v>1.85510555121319</v>
       </c>
       <c r="U75">
         <v>0.1058309777667576</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.683866216702135</v>
+        <v>1.661111267827782</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1057388243834457</v>
+        <v>0.1060542823334072</v>
       </c>
       <c r="C76">
-        <v>-11.832473247248</v>
+        <v>-22.11121757013518</v>
       </c>
       <c r="D76">
-        <v>410.613526752752</v>
+        <v>408.4637824298649</v>
       </c>
       <c r="E76">
-        <v>389.746</v>
+        <v>397.8750000000001</v>
       </c>
       <c r="F76">
-        <v>601.546</v>
+        <v>609.6750000000001</v>
       </c>
       <c r="G76">
         <v>179.1</v>
@@ -7519,28 +7519,28 @@
         <v>105.75</v>
       </c>
       <c r="M76">
-        <v>63.66220135168196</v>
+        <v>64.52250136994793</v>
       </c>
       <c r="N76">
-        <v>42.08779864831801</v>
+        <v>41.22749863005204</v>
       </c>
       <c r="O76">
-        <v>8.417559729663603</v>
+        <v>8.245499726010408</v>
       </c>
       <c r="P76">
-        <v>33.67023891865441</v>
+        <v>32.98199890404163</v>
       </c>
       <c r="Q76">
-        <v>178.1702389186544</v>
+        <v>177.4819989040416</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1657187905597123</v>
+        <v>0.1702227826934104</v>
       </c>
       <c r="T76">
-        <v>1.85510555121319</v>
+        <v>1.924780877080353</v>
       </c>
       <c r="U76">
         <v>0.1058309777667576</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.661111267827782</v>
+        <v>1.638963117590079</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1060542823334072</v>
+        <v>0.1063697402833686</v>
       </c>
       <c r="C77">
-        <v>-22.11121757013518</v>
+        <v>-32.36756939360362</v>
       </c>
       <c r="D77">
-        <v>408.4637824298649</v>
+        <v>406.3364306063964</v>
       </c>
       <c r="E77">
-        <v>397.8750000000001</v>
+        <v>406.0040000000001</v>
       </c>
       <c r="F77">
-        <v>609.6750000000001</v>
+        <v>617.8040000000001</v>
       </c>
       <c r="G77">
         <v>179.1</v>
@@ -7601,28 +7601,28 @@
         <v>105.75</v>
       </c>
       <c r="M77">
-        <v>64.52250136994793</v>
+        <v>65.38280138821391</v>
       </c>
       <c r="N77">
-        <v>41.22749863005204</v>
+        <v>40.36719861178607</v>
       </c>
       <c r="O77">
-        <v>8.245499726010408</v>
+        <v>8.073439722357213</v>
       </c>
       <c r="P77">
-        <v>32.98199890404163</v>
+        <v>32.29375888942885</v>
       </c>
       <c r="Q77">
-        <v>177.4819989040416</v>
+        <v>176.7937588894289</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1702227826934104</v>
+        <v>0.1751021075049167</v>
       </c>
       <c r="T77">
-        <v>1.924780877080353</v>
+        <v>2.000262480103111</v>
       </c>
       <c r="U77">
         <v>0.1058309777667576</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.638963117590079</v>
+        <v>1.617397813411262</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1063697402833686</v>
+        <v>0.1066851982333301</v>
       </c>
       <c r="C78">
-        <v>-32.36756939360362</v>
+        <v>-42.60187677722286</v>
       </c>
       <c r="D78">
-        <v>406.3364306063964</v>
+        <v>404.2311232227772</v>
       </c>
       <c r="E78">
-        <v>406.0040000000001</v>
+        <v>414.1330000000001</v>
       </c>
       <c r="F78">
-        <v>617.8040000000001</v>
+        <v>625.9330000000001</v>
       </c>
       <c r="G78">
         <v>179.1</v>
@@ -7683,28 +7683,28 @@
         <v>105.75</v>
       </c>
       <c r="M78">
-        <v>65.38280138821391</v>
+        <v>66.24310140647988</v>
       </c>
       <c r="N78">
-        <v>40.36719861178607</v>
+        <v>39.50689859352009</v>
       </c>
       <c r="O78">
-        <v>8.073439722357213</v>
+        <v>7.901379718704018</v>
       </c>
       <c r="P78">
-        <v>32.29375888942885</v>
+        <v>31.60551887481607</v>
       </c>
       <c r="Q78">
-        <v>176.7937588894289</v>
+        <v>176.1055188748161</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1751021075049167</v>
+        <v>0.180405721430467</v>
       </c>
       <c r="T78">
-        <v>2.000262480103111</v>
+        <v>2.082307700780023</v>
       </c>
       <c r="U78">
         <v>0.1058309777667576</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.617397813411262</v>
+        <v>1.596392647003323</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1066851982333301</v>
+        <v>0.1070006561832915</v>
       </c>
       <c r="C79">
-        <v>-42.60187677722286</v>
+        <v>-52.8144806042892</v>
       </c>
       <c r="D79">
-        <v>404.2311232227772</v>
+        <v>402.147519395711</v>
       </c>
       <c r="E79">
-        <v>414.1330000000001</v>
+        <v>422.2620000000001</v>
       </c>
       <c r="F79">
-        <v>625.9330000000001</v>
+        <v>634.0620000000001</v>
       </c>
       <c r="G79">
         <v>179.1</v>
@@ -7765,28 +7765,28 @@
         <v>105.75</v>
       </c>
       <c r="M79">
-        <v>66.24310140647988</v>
+        <v>67.10340142474585</v>
       </c>
       <c r="N79">
-        <v>39.50689859352009</v>
+        <v>38.64659857525412</v>
       </c>
       <c r="O79">
-        <v>7.901379718704018</v>
+        <v>7.729319715050824</v>
       </c>
       <c r="P79">
-        <v>31.60551887481607</v>
+        <v>30.91727886020329</v>
       </c>
       <c r="Q79">
-        <v>176.1055188748161</v>
+        <v>175.4172788602033</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.180405721430467</v>
+        <v>0.1861914820765219</v>
       </c>
       <c r="T79">
-        <v>2.082307700780023</v>
+        <v>2.171811577882109</v>
       </c>
       <c r="U79">
         <v>0.1058309777667576</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.596392647003323</v>
+        <v>1.575926074605845</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1070006561832915</v>
+        <v>0.107316114133253</v>
       </c>
       <c r="C80">
-        <v>-52.8144806042892</v>
+        <v>-63.00571476582729</v>
       </c>
       <c r="D80">
-        <v>402.147519395711</v>
+        <v>400.0852852341729</v>
       </c>
       <c r="E80">
-        <v>422.2620000000001</v>
+        <v>430.3910000000001</v>
       </c>
       <c r="F80">
-        <v>634.0620000000001</v>
+        <v>642.1910000000001</v>
       </c>
       <c r="G80">
         <v>179.1</v>
@@ -7847,28 +7847,28 @@
         <v>105.75</v>
       </c>
       <c r="M80">
-        <v>67.10340142474585</v>
+        <v>67.96370144301183</v>
       </c>
       <c r="N80">
-        <v>38.64659857525412</v>
+        <v>37.78629855698814</v>
       </c>
       <c r="O80">
-        <v>7.729319715050824</v>
+        <v>7.557259711397629</v>
       </c>
       <c r="P80">
-        <v>30.91727886020329</v>
+        <v>30.22903884559052</v>
       </c>
       <c r="Q80">
-        <v>175.4172788602033</v>
+        <v>174.7290388455905</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1861914820765219</v>
+        <v>0.1925282675460107</v>
       </c>
       <c r="T80">
-        <v>2.171811577882109</v>
+        <v>2.269839633755822</v>
       </c>
       <c r="U80">
         <v>0.1058309777667576</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.575926074605845</v>
+        <v>1.55597764328172</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.107316114133253</v>
+        <v>0.1076315720832145</v>
       </c>
       <c r="C81">
-        <v>-63.00571476582729</v>
+        <v>-73.17590633895861</v>
       </c>
       <c r="D81">
-        <v>400.0852852341729</v>
+        <v>398.0440936610416</v>
       </c>
       <c r="E81">
-        <v>430.3910000000001</v>
+        <v>438.5200000000002</v>
       </c>
       <c r="F81">
-        <v>642.1910000000001</v>
+        <v>650.3200000000002</v>
       </c>
       <c r="G81">
         <v>179.1</v>
@@ -7929,28 +7929,28 @@
         <v>105.75</v>
       </c>
       <c r="M81">
-        <v>67.96370144301183</v>
+        <v>68.8240014612778</v>
       </c>
       <c r="N81">
-        <v>37.78629855698814</v>
+        <v>36.92599853872217</v>
       </c>
       <c r="O81">
-        <v>7.557259711397629</v>
+        <v>7.385199707744434</v>
       </c>
       <c r="P81">
-        <v>30.22903884559052</v>
+        <v>29.54079883097774</v>
       </c>
       <c r="Q81">
-        <v>174.7290388455905</v>
+        <v>174.0407988309777</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1925282675460107</v>
+        <v>0.1994987315624482</v>
       </c>
       <c r="T81">
-        <v>2.269839633755822</v>
+        <v>2.377670495216906</v>
       </c>
       <c r="U81">
         <v>0.1058309777667576</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.55597764328172</v>
+        <v>1.536527922740698</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1076315720832145</v>
+        <v>0.107947030033176</v>
       </c>
       <c r="C82">
-        <v>-73.17590633895861</v>
+        <v>-83.32537575983918</v>
       </c>
       <c r="D82">
-        <v>398.0440936610416</v>
+        <v>396.0236242401609</v>
       </c>
       <c r="E82">
-        <v>438.5200000000002</v>
+        <v>446.6490000000001</v>
       </c>
       <c r="F82">
-        <v>650.3200000000002</v>
+        <v>658.4490000000001</v>
       </c>
       <c r="G82">
         <v>179.1</v>
@@ -8011,28 +8011,28 @@
         <v>105.75</v>
       </c>
       <c r="M82">
-        <v>68.8240014612778</v>
+        <v>69.68430147954376</v>
       </c>
       <c r="N82">
-        <v>36.92599853872217</v>
+        <v>36.06569852045621</v>
       </c>
       <c r="O82">
-        <v>7.385199707744434</v>
+        <v>7.213139704091242</v>
       </c>
       <c r="P82">
-        <v>29.54079883097774</v>
+        <v>28.85255881636497</v>
       </c>
       <c r="Q82">
-        <v>174.0407988309777</v>
+        <v>173.352558816365</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1994987315624482</v>
+        <v>0.2072029286332476</v>
       </c>
       <c r="T82">
-        <v>2.377670495216906</v>
+        <v>2.496851973673894</v>
       </c>
       <c r="U82">
         <v>0.1058309777667576</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.536527922740698</v>
+        <v>1.517558442213036</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.107947030033176</v>
+        <v>0.1463238618592803</v>
       </c>
       <c r="C83">
-        <v>-83.32537575983918</v>
+        <v>-242.643672962769</v>
       </c>
       <c r="D83">
-        <v>396.0236242401609</v>
+        <v>244.8343270372311</v>
       </c>
       <c r="E83">
-        <v>446.6490000000001</v>
+        <v>454.7780000000001</v>
       </c>
       <c r="F83">
-        <v>658.4490000000001</v>
+        <v>666.5780000000001</v>
       </c>
       <c r="G83">
         <v>179.1</v>
@@ -8093,45 +8093,45 @@
         <v>105.75</v>
       </c>
       <c r="M83">
-        <v>69.68430147954376</v>
+        <v>108.4062318978097</v>
       </c>
       <c r="N83">
-        <v>36.06569852045621</v>
+        <v>-2.656231897809775</v>
       </c>
       <c r="O83">
-        <v>7.213139704091242</v>
+        <v>-0.531246379561955</v>
       </c>
       <c r="P83">
-        <v>28.85255881636497</v>
+        <v>-2.12498551824782</v>
       </c>
       <c r="Q83">
-        <v>173.352558816365</v>
+        <v>142.3750144817522</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2072029286332476</v>
+        <v>0.2165801137737265</v>
       </c>
       <c r="T83">
-        <v>2.496851973673894</v>
+        <v>2.641914045494859</v>
       </c>
       <c r="U83">
-        <v>0.1058309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V83">
-        <v>0.2</v>
+        <v>0.1950994848703649</v>
       </c>
       <c r="W83">
-        <v>0.08466478221340606</v>
+        <v>0.1309017577804994</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.517558442213036</v>
+        <v>0.9754974243518242</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1463238618592803</v>
+        <v>0.1474921716369479</v>
       </c>
       <c r="C84">
-        <v>-242.643672962769</v>
+        <v>-253.5854985085491</v>
       </c>
       <c r="D84">
-        <v>244.8343270372311</v>
+        <v>242.021501491451</v>
       </c>
       <c r="E84">
-        <v>454.7780000000001</v>
+        <v>462.9070000000001</v>
       </c>
       <c r="F84">
-        <v>666.5780000000001</v>
+        <v>674.7070000000001</v>
       </c>
       <c r="G84">
         <v>179.1</v>
@@ -8175,37 +8175,37 @@
         <v>105.75</v>
       </c>
       <c r="M84">
-        <v>108.4062318978097</v>
+        <v>109.7282591160757</v>
       </c>
       <c r="N84">
-        <v>-2.656231897809775</v>
+        <v>-3.978259116075762</v>
       </c>
       <c r="O84">
-        <v>-0.531246379561955</v>
+        <v>-0.7956518232151524</v>
       </c>
       <c r="P84">
-        <v>-2.12498551824782</v>
+        <v>-3.18260729286061</v>
       </c>
       <c r="Q84">
-        <v>142.3750144817522</v>
+        <v>141.3173927071394</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2165801137737265</v>
+        <v>0.2266260028192399</v>
       </c>
       <c r="T84">
-        <v>2.641914045494859</v>
+        <v>2.797320754053381</v>
       </c>
       <c r="U84">
         <v>0.1626309777667576</v>
       </c>
       <c r="V84">
-        <v>0.1950994848703649</v>
+        <v>0.1927488886671074</v>
       </c>
       <c r="W84">
-        <v>0.1309017577804994</v>
+        <v>0.13128403753937</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9754974243518242</v>
+        <v>0.963744443335537</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1474921716369479</v>
+        <v>0.1486604814146154</v>
       </c>
       <c r="C85">
-        <v>-253.5854985085491</v>
+        <v>-264.4634267918857</v>
       </c>
       <c r="D85">
-        <v>242.021501491451</v>
+        <v>239.2725732081145</v>
       </c>
       <c r="E85">
-        <v>462.9070000000001</v>
+        <v>471.0360000000001</v>
       </c>
       <c r="F85">
-        <v>674.7070000000001</v>
+        <v>682.8360000000001</v>
       </c>
       <c r="G85">
         <v>179.1</v>
@@ -8257,37 +8257,37 @@
         <v>105.75</v>
       </c>
       <c r="M85">
-        <v>109.7282591160757</v>
+        <v>111.0502863343417</v>
       </c>
       <c r="N85">
-        <v>-3.978259116075762</v>
+        <v>-5.300286334341735</v>
       </c>
       <c r="O85">
-        <v>-0.7956518232151524</v>
+        <v>-1.060057266868347</v>
       </c>
       <c r="P85">
-        <v>-3.18260729286061</v>
+        <v>-4.240229067473388</v>
       </c>
       <c r="Q85">
-        <v>141.3173927071394</v>
+        <v>140.2597709325266</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2266260028192399</v>
+        <v>0.2379276279954424</v>
       </c>
       <c r="T85">
-        <v>2.797320754053381</v>
+        <v>2.972153301181717</v>
       </c>
       <c r="U85">
         <v>0.1626309777667576</v>
       </c>
       <c r="V85">
-        <v>0.1927488886671074</v>
+        <v>0.190454259040118</v>
       </c>
       <c r="W85">
-        <v>0.13128403753937</v>
+        <v>0.1316572153992198</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.963744443335537</v>
+        <v>0.9522712952005902</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1486604814146154</v>
+        <v>0.149828791192283</v>
       </c>
       <c r="C86">
-        <v>-264.4634267918856</v>
+        <v>-275.2796106340012</v>
       </c>
       <c r="D86">
-        <v>239.2725732081145</v>
+        <v>236.5853893659988</v>
       </c>
       <c r="E86">
-        <v>471.036</v>
+        <v>479.165</v>
       </c>
       <c r="F86">
-        <v>682.836</v>
+        <v>690.965</v>
       </c>
       <c r="G86">
         <v>179.1</v>
@@ -8339,37 +8339,37 @@
         <v>105.75</v>
       </c>
       <c r="M86">
-        <v>111.0502863343417</v>
+        <v>112.3723135526077</v>
       </c>
       <c r="N86">
-        <v>-5.300286334341706</v>
+        <v>-6.622313552607693</v>
       </c>
       <c r="O86">
-        <v>-1.060057266868341</v>
+        <v>-1.324462710521539</v>
       </c>
       <c r="P86">
-        <v>-4.240229067473365</v>
+        <v>-5.297850842086154</v>
       </c>
       <c r="Q86">
-        <v>140.2597709325266</v>
+        <v>139.2021491579139</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2379276279954423</v>
+        <v>0.2507361365284718</v>
       </c>
       <c r="T86">
-        <v>2.972153301181716</v>
+        <v>3.17029685459383</v>
       </c>
       <c r="U86">
         <v>0.1626309777667576</v>
       </c>
       <c r="V86">
-        <v>0.1904542590401181</v>
+        <v>0.1882136206984696</v>
       </c>
       <c r="W86">
-        <v>0.1316572153992198</v>
+        <v>0.1320216126035438</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9522712952005904</v>
+        <v>0.941068103492348</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.149828791192283</v>
+        <v>0.1509971009699506</v>
       </c>
       <c r="C87">
-        <v>-275.2796106340012</v>
+        <v>-286.0361072199436</v>
       </c>
       <c r="D87">
-        <v>236.5853893659988</v>
+        <v>233.9578927800564</v>
       </c>
       <c r="E87">
-        <v>479.165</v>
+        <v>487.294</v>
       </c>
       <c r="F87">
-        <v>690.965</v>
+        <v>699.0940000000001</v>
       </c>
       <c r="G87">
         <v>179.1</v>
@@ -8421,37 +8421,37 @@
         <v>105.75</v>
       </c>
       <c r="M87">
-        <v>112.3723135526077</v>
+        <v>113.6943407708736</v>
       </c>
       <c r="N87">
-        <v>-6.622313552607693</v>
+        <v>-7.944340770873666</v>
       </c>
       <c r="O87">
-        <v>-1.324462710521539</v>
+        <v>-1.588868154174733</v>
       </c>
       <c r="P87">
-        <v>-5.297850842086154</v>
+        <v>-6.355472616698933</v>
       </c>
       <c r="Q87">
-        <v>139.2021491579139</v>
+        <v>138.1445273833011</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2507361365284718</v>
+        <v>0.2653744319947912</v>
       </c>
       <c r="T87">
-        <v>3.17029685459383</v>
+        <v>3.396746629921961</v>
       </c>
       <c r="U87">
         <v>0.1626309777667576</v>
       </c>
       <c r="V87">
-        <v>0.1882136206984696</v>
+        <v>0.1860250902252316</v>
       </c>
       <c r="W87">
-        <v>0.1320216126035438</v>
+        <v>0.1323775354542789</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.941068103492348</v>
+        <v>0.930125451126158</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1509971009699506</v>
+        <v>0.1521654107476182</v>
       </c>
       <c r="C88">
-        <v>-286.0361072199436</v>
+        <v>-296.7348833508892</v>
       </c>
       <c r="D88">
-        <v>233.9578927800564</v>
+        <v>231.3881166491109</v>
       </c>
       <c r="E88">
-        <v>487.294</v>
+        <v>495.4230000000001</v>
       </c>
       <c r="F88">
-        <v>699.0940000000001</v>
+        <v>707.2230000000001</v>
       </c>
       <c r="G88">
         <v>179.1</v>
@@ -8503,37 +8503,37 @@
         <v>105.75</v>
       </c>
       <c r="M88">
-        <v>113.6943407708736</v>
+        <v>115.0163679891396</v>
       </c>
       <c r="N88">
-        <v>-7.944340770873666</v>
+        <v>-9.266367989139638</v>
       </c>
       <c r="O88">
-        <v>-1.588868154174733</v>
+        <v>-1.853273597827928</v>
       </c>
       <c r="P88">
-        <v>-6.355472616698933</v>
+        <v>-7.413094391311711</v>
       </c>
       <c r="Q88">
-        <v>138.1445273833011</v>
+        <v>137.0869056086883</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2653744319947912</v>
+        <v>0.2822647729174674</v>
       </c>
       <c r="T88">
-        <v>3.396746629921961</v>
+        <v>3.65803483222365</v>
       </c>
       <c r="U88">
         <v>0.1626309777667576</v>
       </c>
       <c r="V88">
-        <v>0.1860250902252316</v>
+        <v>0.1838868707973554</v>
       </c>
       <c r="W88">
-        <v>0.1323775354542789</v>
+        <v>0.1327252761705143</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.930125451126158</v>
+        <v>0.9194343539867768</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1521654107476182</v>
+        <v>0.1533337205252858</v>
       </c>
       <c r="C89">
-        <v>-296.7348833508892</v>
+        <v>-307.3778203540609</v>
       </c>
       <c r="D89">
-        <v>231.3881166491109</v>
+        <v>228.8741796459392</v>
       </c>
       <c r="E89">
-        <v>495.4230000000001</v>
+        <v>503.5520000000001</v>
       </c>
       <c r="F89">
-        <v>707.2230000000001</v>
+        <v>715.3520000000001</v>
       </c>
       <c r="G89">
         <v>179.1</v>
@@ -8585,37 +8585,37 @@
         <v>105.75</v>
       </c>
       <c r="M89">
-        <v>115.0163679891396</v>
+        <v>116.3383952074056</v>
       </c>
       <c r="N89">
-        <v>-9.266367989139638</v>
+        <v>-10.58839520740561</v>
       </c>
       <c r="O89">
-        <v>-1.853273597827928</v>
+        <v>-2.117679041481122</v>
       </c>
       <c r="P89">
-        <v>-7.413094391311711</v>
+        <v>-8.47071616592449</v>
       </c>
       <c r="Q89">
-        <v>137.0869056086883</v>
+        <v>136.0292838340755</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2822647729174674</v>
+        <v>0.3019701706605897</v>
       </c>
       <c r="T89">
-        <v>3.65803483222365</v>
+        <v>3.962871068242289</v>
       </c>
       <c r="U89">
         <v>0.1626309777667576</v>
       </c>
       <c r="V89">
-        <v>0.1838868707973554</v>
+        <v>0.1817972472655672</v>
       </c>
       <c r="W89">
-        <v>0.1327252761705143</v>
+        <v>0.1330651136886534</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9194343539867768</v>
+        <v>0.9089862363278362</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1533337205252858</v>
+        <v>0.1545020303029533</v>
       </c>
       <c r="C90">
-        <v>-307.3778203540609</v>
+        <v>-317.966718676022</v>
       </c>
       <c r="D90">
-        <v>228.8741796459392</v>
+        <v>226.4142813239781</v>
       </c>
       <c r="E90">
-        <v>503.5520000000001</v>
+        <v>511.6810000000001</v>
       </c>
       <c r="F90">
-        <v>715.3520000000001</v>
+        <v>723.4810000000001</v>
       </c>
       <c r="G90">
         <v>179.1</v>
@@ -8667,37 +8667,37 @@
         <v>105.75</v>
       </c>
       <c r="M90">
-        <v>116.3383952074056</v>
+        <v>117.6604224256716</v>
       </c>
       <c r="N90">
-        <v>-10.58839520740561</v>
+        <v>-11.91042242567158</v>
       </c>
       <c r="O90">
-        <v>-2.117679041481122</v>
+        <v>-2.382084485134317</v>
       </c>
       <c r="P90">
-        <v>-8.47071616592449</v>
+        <v>-9.528337940537266</v>
       </c>
       <c r="Q90">
-        <v>136.0292838340755</v>
+        <v>134.9716620594627</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3019701706605897</v>
+        <v>0.3252583679933707</v>
       </c>
       <c r="T90">
-        <v>3.962871068242289</v>
+        <v>4.323132074446133</v>
       </c>
       <c r="U90">
         <v>0.1626309777667576</v>
       </c>
       <c r="V90">
-        <v>0.1817972472655672</v>
+        <v>0.1797545815659541</v>
       </c>
       <c r="W90">
-        <v>0.1330651136886534</v>
+        <v>0.1333973144086321</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9089862363278362</v>
+        <v>0.8987729078297706</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1545020303029533</v>
+        <v>0.1556703400806209</v>
       </c>
       <c r="C91">
-        <v>-317.966718676022</v>
+        <v>-328.5033021829109</v>
       </c>
       <c r="D91">
-        <v>226.4142813239781</v>
+        <v>224.0066978170892</v>
       </c>
       <c r="E91">
-        <v>511.6810000000001</v>
+        <v>519.8100000000002</v>
       </c>
       <c r="F91">
-        <v>723.4810000000001</v>
+        <v>731.6100000000001</v>
       </c>
       <c r="G91">
         <v>179.1</v>
@@ -8749,37 +8749,37 @@
         <v>105.75</v>
       </c>
       <c r="M91">
-        <v>117.6604224256716</v>
+        <v>118.9824496439375</v>
       </c>
       <c r="N91">
-        <v>-11.91042242567158</v>
+        <v>-13.23244964393757</v>
       </c>
       <c r="O91">
-        <v>-2.382084485134317</v>
+        <v>-2.646489928787514</v>
       </c>
       <c r="P91">
-        <v>-9.528337940537266</v>
+        <v>-10.58595971515006</v>
       </c>
       <c r="Q91">
-        <v>134.9716620594627</v>
+        <v>133.9140402848499</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3252583679933707</v>
+        <v>0.3532042047927077</v>
       </c>
       <c r="T91">
-        <v>4.323132074446133</v>
+        <v>4.755445281890746</v>
       </c>
       <c r="U91">
         <v>0.1626309777667576</v>
       </c>
       <c r="V91">
-        <v>0.1797545815659541</v>
+        <v>0.1777573084374435</v>
       </c>
       <c r="W91">
-        <v>0.1333973144086321</v>
+        <v>0.133722132890389</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8987729078297706</v>
+        <v>0.8887865421872174</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1556703400806209</v>
+        <v>0.1568386498582885</v>
       </c>
       <c r="C92">
-        <v>-328.5033021829109</v>
+        <v>-338.9892221892037</v>
       </c>
       <c r="D92">
-        <v>224.0066978170892</v>
+        <v>221.6497778107965</v>
       </c>
       <c r="E92">
-        <v>519.8100000000002</v>
+        <v>527.9390000000001</v>
       </c>
       <c r="F92">
-        <v>731.6100000000001</v>
+        <v>739.7390000000001</v>
       </c>
       <c r="G92">
         <v>179.1</v>
@@ -8831,37 +8831,37 @@
         <v>105.75</v>
       </c>
       <c r="M92">
-        <v>118.9824496439375</v>
+        <v>120.3044768622035</v>
       </c>
       <c r="N92">
-        <v>-13.23244964393757</v>
+        <v>-14.55447686220354</v>
       </c>
       <c r="O92">
-        <v>-2.646489928787514</v>
+        <v>-2.910895372440709</v>
       </c>
       <c r="P92">
-        <v>-10.58595971515006</v>
+        <v>-11.64358148976283</v>
       </c>
       <c r="Q92">
-        <v>133.9140402848499</v>
+        <v>132.8564185102372</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3532042047927077</v>
+        <v>0.3873602275474531</v>
       </c>
       <c r="T92">
-        <v>4.755445281890746</v>
+        <v>5.28382809098972</v>
       </c>
       <c r="U92">
         <v>0.1626309777667576</v>
       </c>
       <c r="V92">
-        <v>0.1777573084374435</v>
+        <v>0.1758039314216474</v>
       </c>
       <c r="W92">
-        <v>0.133722132890389</v>
+        <v>0.1340398125044151</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8887865421872174</v>
+        <v>0.879019657108237</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1568386498582885</v>
+        <v>0.1580069596359561</v>
       </c>
       <c r="C93">
-        <v>-338.9892221892037</v>
+        <v>-349.4260612347883</v>
       </c>
       <c r="D93">
-        <v>221.6497778107965</v>
+        <v>219.3419387652118</v>
       </c>
       <c r="E93">
-        <v>527.9390000000001</v>
+        <v>536.0680000000002</v>
       </c>
       <c r="F93">
-        <v>739.7390000000001</v>
+        <v>747.8680000000002</v>
       </c>
       <c r="G93">
         <v>179.1</v>
@@ -8913,37 +8913,37 @@
         <v>105.75</v>
       </c>
       <c r="M93">
-        <v>120.3044768622035</v>
+        <v>121.6265040804695</v>
       </c>
       <c r="N93">
-        <v>-14.55447686220354</v>
+        <v>-15.87650408046952</v>
       </c>
       <c r="O93">
-        <v>-2.910895372440709</v>
+        <v>-3.175300816093904</v>
       </c>
       <c r="P93">
-        <v>-11.64358148976283</v>
+        <v>-12.70120326437561</v>
       </c>
       <c r="Q93">
-        <v>132.8564185102372</v>
+        <v>131.7987967356244</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3873602275474531</v>
+        <v>0.4300552559908848</v>
       </c>
       <c r="T93">
-        <v>5.28382809098972</v>
+        <v>5.944306602363436</v>
       </c>
       <c r="U93">
         <v>0.1626309777667576</v>
       </c>
       <c r="V93">
-        <v>0.1758039314216474</v>
+        <v>0.173893019123586</v>
       </c>
       <c r="W93">
-        <v>0.1340398125044151</v>
+        <v>0.1343505860398753</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.879019657108237</v>
+        <v>0.8694650956179302</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1580069596359561</v>
+        <v>0.1591752694136236</v>
       </c>
       <c r="C94">
-        <v>-349.4260612347883</v>
+        <v>-359.815336628508</v>
       </c>
       <c r="D94">
-        <v>219.3419387652118</v>
+        <v>217.0816633714921</v>
       </c>
       <c r="E94">
-        <v>536.0680000000002</v>
+        <v>544.1970000000001</v>
       </c>
       <c r="F94">
-        <v>747.8680000000002</v>
+        <v>755.9970000000001</v>
       </c>
       <c r="G94">
         <v>179.1</v>
@@ -8995,37 +8995,37 @@
         <v>105.75</v>
       </c>
       <c r="M94">
-        <v>121.6265040804695</v>
+        <v>122.9485312987354</v>
       </c>
       <c r="N94">
-        <v>-15.87650408046952</v>
+        <v>-17.19853129873547</v>
       </c>
       <c r="O94">
-        <v>-3.175300816093904</v>
+        <v>-3.439706259747095</v>
       </c>
       <c r="P94">
-        <v>-12.70120326437561</v>
+        <v>-13.75882503898838</v>
       </c>
       <c r="Q94">
-        <v>131.7987967356244</v>
+        <v>130.7411749610116</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4300552559908848</v>
+        <v>0.4849488639895827</v>
       </c>
       <c r="T94">
-        <v>5.944306602363436</v>
+        <v>6.793493259843927</v>
       </c>
       <c r="U94">
         <v>0.1626309777667576</v>
       </c>
       <c r="V94">
-        <v>0.173893019123586</v>
+        <v>0.172023201713655</v>
       </c>
       <c r="W94">
-        <v>0.1343505860398753</v>
+        <v>0.1346546762734977</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8694650956179302</v>
+        <v>0.8601160085682751</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1591752694136236</v>
+        <v>0.1603435791912912</v>
       </c>
       <c r="C95">
-        <v>-359.815336628508</v>
+        <v>-370.1585037748454</v>
       </c>
       <c r="D95">
-        <v>217.0816633714921</v>
+        <v>214.8674962251547</v>
       </c>
       <c r="E95">
-        <v>544.1970000000001</v>
+        <v>552.326</v>
       </c>
       <c r="F95">
-        <v>755.9970000000001</v>
+        <v>764.1260000000001</v>
       </c>
       <c r="G95">
         <v>179.1</v>
@@ -9077,37 +9077,37 @@
         <v>105.75</v>
       </c>
       <c r="M95">
-        <v>122.9485312987354</v>
+        <v>124.2705585170014</v>
       </c>
       <c r="N95">
-        <v>-17.19853129873547</v>
+        <v>-18.52055851700145</v>
       </c>
       <c r="O95">
-        <v>-3.439706259747095</v>
+        <v>-3.70411170340029</v>
       </c>
       <c r="P95">
-        <v>-13.75882503898838</v>
+        <v>-14.81644681360116</v>
       </c>
       <c r="Q95">
-        <v>130.7411749610116</v>
+        <v>129.6835531863989</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4849488639895827</v>
+        <v>0.5581403413211798</v>
       </c>
       <c r="T95">
-        <v>6.793493259843927</v>
+        <v>7.925742136484584</v>
       </c>
       <c r="U95">
         <v>0.1626309777667576</v>
       </c>
       <c r="V95">
-        <v>0.172023201713655</v>
+        <v>0.1701931676528715</v>
       </c>
       <c r="W95">
-        <v>0.1346546762734977</v>
+        <v>0.1349522965021494</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8601160085682751</v>
+        <v>0.8509658382643572</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1603435791912912</v>
+        <v>0.1615118889689588</v>
       </c>
       <c r="C96">
-        <v>-370.1585037748454</v>
+        <v>-380.4569592990755</v>
       </c>
       <c r="D96">
-        <v>214.8674962251547</v>
+        <v>212.6980407009247</v>
       </c>
       <c r="E96">
-        <v>552.326</v>
+        <v>560.4550000000002</v>
       </c>
       <c r="F96">
-        <v>764.1260000000001</v>
+        <v>772.2550000000001</v>
       </c>
       <c r="G96">
         <v>179.1</v>
@@ -9159,37 +9159,37 @@
         <v>105.75</v>
       </c>
       <c r="M96">
-        <v>124.2705585170014</v>
+        <v>125.5925857352674</v>
       </c>
       <c r="N96">
-        <v>-18.52055851700145</v>
+        <v>-19.84258573526742</v>
       </c>
       <c r="O96">
-        <v>-3.70411170340029</v>
+        <v>-3.968517147053484</v>
       </c>
       <c r="P96">
-        <v>-14.81644681360116</v>
+        <v>-15.87406858821394</v>
       </c>
       <c r="Q96">
-        <v>129.6835531863989</v>
+        <v>128.6259314117861</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5581403413211798</v>
+        <v>0.6606084095854161</v>
       </c>
       <c r="T96">
-        <v>7.925742136484584</v>
+        <v>9.510890563781505</v>
       </c>
       <c r="U96">
         <v>0.1626309777667576</v>
       </c>
       <c r="V96">
-        <v>0.1701931676528715</v>
+        <v>0.1684016606249465</v>
       </c>
       <c r="W96">
-        <v>0.1349522965021494</v>
+        <v>0.1352436510417769</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8509658382643572</v>
+        <v>0.8420083031247324</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1615118889689588</v>
+        <v>0.1626801987466264</v>
       </c>
       <c r="C97">
-        <v>-380.4569592990755</v>
+        <v>-390.7120439849881</v>
       </c>
       <c r="D97">
-        <v>212.6980407009247</v>
+        <v>210.5719560150121</v>
       </c>
       <c r="E97">
-        <v>560.4550000000002</v>
+        <v>568.5840000000001</v>
       </c>
       <c r="F97">
-        <v>772.2550000000001</v>
+        <v>780.3840000000001</v>
       </c>
       <c r="G97">
         <v>179.1</v>
@@ -9241,37 +9241,37 @@
         <v>105.75</v>
       </c>
       <c r="M97">
-        <v>125.5925857352674</v>
+        <v>126.9146129535334</v>
       </c>
       <c r="N97">
-        <v>-19.84258573526742</v>
+        <v>-21.16461295353339</v>
       </c>
       <c r="O97">
-        <v>-3.968517147053484</v>
+        <v>-4.232922590706679</v>
       </c>
       <c r="P97">
-        <v>-15.87406858821394</v>
+        <v>-16.93169036282671</v>
       </c>
       <c r="Q97">
-        <v>128.6259314117861</v>
+        <v>127.5683096371733</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6606084095854161</v>
+        <v>0.8143105119817704</v>
       </c>
       <c r="T97">
-        <v>9.510890563781505</v>
+        <v>11.88861320472689</v>
       </c>
       <c r="U97">
         <v>0.1626309777667576</v>
       </c>
       <c r="V97">
-        <v>0.1684016606249465</v>
+        <v>0.1666474766601033</v>
       </c>
       <c r="W97">
-        <v>0.1352436510417769</v>
+        <v>0.1355289356951621</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8420083031247324</v>
+        <v>0.8332373833005164</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1626801987466263</v>
+        <v>0.1638485085242939</v>
       </c>
       <c r="C98">
-        <v>-390.7120439849879</v>
+        <v>-400.9250455381655</v>
       </c>
       <c r="D98">
-        <v>210.5719560150121</v>
+        <v>208.4879544618345</v>
       </c>
       <c r="E98">
-        <v>568.5840000000001</v>
+        <v>576.713</v>
       </c>
       <c r="F98">
-        <v>780.384</v>
+        <v>788.513</v>
       </c>
       <c r="G98">
         <v>179.1</v>
@@ -9323,37 +9323,37 @@
         <v>105.75</v>
       </c>
       <c r="M98">
-        <v>126.9146129535334</v>
+        <v>128.2366401717993</v>
       </c>
       <c r="N98">
-        <v>-21.16461295353338</v>
+        <v>-22.48664017179937</v>
       </c>
       <c r="O98">
-        <v>-4.232922590706676</v>
+        <v>-4.497328034359874</v>
       </c>
       <c r="P98">
-        <v>-16.9316903628267</v>
+        <v>-17.98931213743949</v>
       </c>
       <c r="Q98">
-        <v>127.5683096371733</v>
+        <v>126.5106878625605</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8143105119817683</v>
+        <v>1.070480682642358</v>
       </c>
       <c r="T98">
-        <v>11.88861320472685</v>
+        <v>15.85148427296914</v>
       </c>
       <c r="U98">
         <v>0.1626309777667576</v>
       </c>
       <c r="V98">
-        <v>0.1666474766601033</v>
+        <v>0.1649294614368033</v>
       </c>
       <c r="W98">
-        <v>0.1355289356951621</v>
+        <v>0.1358083381907455</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8332373833005166</v>
+        <v>0.8246473071840164</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1638485085242939</v>
+        <v>0.1650168183019615</v>
       </c>
       <c r="C99">
-        <v>-400.9250455381655</v>
+        <v>-411.0972011867815</v>
       </c>
       <c r="D99">
-        <v>208.4879544618345</v>
+        <v>206.4447988132186</v>
       </c>
       <c r="E99">
-        <v>576.713</v>
+        <v>584.8420000000001</v>
       </c>
       <c r="F99">
-        <v>788.513</v>
+        <v>796.6420000000001</v>
       </c>
       <c r="G99">
         <v>179.1</v>
@@ -9405,37 +9405,37 @@
         <v>105.75</v>
       </c>
       <c r="M99">
-        <v>128.2366401717993</v>
+        <v>129.5586673900653</v>
       </c>
       <c r="N99">
-        <v>-22.48664017179937</v>
+        <v>-23.80866739006532</v>
       </c>
       <c r="O99">
-        <v>-4.497328034359874</v>
+        <v>-4.761733478013065</v>
       </c>
       <c r="P99">
-        <v>-17.98931213743949</v>
+        <v>-19.04693391205226</v>
       </c>
       <c r="Q99">
-        <v>126.5106878625605</v>
+        <v>125.4530660879477</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.070480682642358</v>
+        <v>1.582821023963537</v>
       </c>
       <c r="T99">
-        <v>15.85148427296914</v>
+        <v>23.77722640945371</v>
       </c>
       <c r="U99">
         <v>0.1626309777667576</v>
       </c>
       <c r="V99">
-        <v>0.1649294614368033</v>
+        <v>0.1632465077486726</v>
       </c>
       <c r="W99">
-        <v>0.1358083381907455</v>
+        <v>0.1360820385945824</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8246473071840164</v>
+        <v>0.8162325387433631</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1650168183019615</v>
+        <v>0.1661851280796291</v>
       </c>
       <c r="C100">
-        <v>-411.0972011867815</v>
+        <v>-421.2297001309581</v>
       </c>
       <c r="D100">
-        <v>206.4447988132186</v>
+        <v>204.4412998690419</v>
       </c>
       <c r="E100">
-        <v>584.8420000000001</v>
+        <v>592.971</v>
       </c>
       <c r="F100">
-        <v>796.6420000000001</v>
+        <v>804.7710000000001</v>
       </c>
       <c r="G100">
         <v>179.1</v>
@@ -9487,37 +9487,37 @@
         <v>105.75</v>
       </c>
       <c r="M100">
-        <v>129.5586673900653</v>
+        <v>130.8806946083313</v>
       </c>
       <c r="N100">
-        <v>-23.80866739006532</v>
+        <v>-25.13069460833131</v>
       </c>
       <c r="O100">
-        <v>-4.761733478013065</v>
+        <v>-5.026138921666263</v>
       </c>
       <c r="P100">
-        <v>-19.04693391205226</v>
+        <v>-20.10455568666505</v>
       </c>
       <c r="Q100">
-        <v>125.4530660879477</v>
+        <v>124.3954443133349</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.582821023963537</v>
+        <v>3.119842047927074</v>
       </c>
       <c r="T100">
-        <v>23.77722640945371</v>
+        <v>47.55445281890741</v>
       </c>
       <c r="U100">
         <v>0.1626309777667576</v>
       </c>
       <c r="V100">
-        <v>0.1632465077486726</v>
+        <v>0.1615975531249487</v>
       </c>
       <c r="W100">
-        <v>0.1360820385945824</v>
+        <v>0.1363502096973316</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8162325387433631</v>
+        <v>0.8079877656247432</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1661851280796291</v>
-      </c>
-      <c r="C101">
-        <v>-421.2297001309581</v>
-      </c>
-      <c r="D101">
-        <v>204.4412998690419</v>
-      </c>
-      <c r="E101">
-        <v>592.971</v>
-      </c>
-      <c r="F101">
-        <v>804.7710000000001</v>
-      </c>
-      <c r="G101">
-        <v>179.1</v>
-      </c>
-      <c r="H101">
-        <v>601.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>250.25</v>
-      </c>
-      <c r="K101">
-        <v>144.5</v>
-      </c>
-      <c r="L101">
-        <v>105.75</v>
-      </c>
-      <c r="M101">
-        <v>130.8806946083313</v>
-      </c>
-      <c r="N101">
-        <v>-25.13069460833131</v>
-      </c>
-      <c r="O101">
-        <v>-5.026138921666263</v>
-      </c>
-      <c r="P101">
-        <v>-20.10455568666505</v>
-      </c>
-      <c r="Q101">
-        <v>124.3954443133349</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.119842047927074</v>
-      </c>
-      <c r="T101">
-        <v>47.55445281890741</v>
-      </c>
-      <c r="U101">
-        <v>0.1626309777667576</v>
-      </c>
-      <c r="V101">
-        <v>0.1615975531249487</v>
-      </c>
-      <c r="W101">
-        <v>0.1363502096973316</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8079877656247432</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
